--- a/database/event/2013/event_2013_evp_summary.xlsx
+++ b/database/event/2013/event_2013_evp_summary.xlsx
@@ -496,25 +496,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8.876300000000001</v>
+        <v>8.836399999999999</v>
       </c>
       <c r="C2" t="n">
-        <v>2.9621</v>
+        <v>2.9488</v>
       </c>
       <c r="D2" t="n">
-        <v>3.1645</v>
+        <v>3.0765</v>
       </c>
       <c r="E2" t="n">
-        <v>8.876300000000001</v>
+        <v>8.836399999999999</v>
       </c>
       <c r="F2" t="n">
-        <v>5.0513</v>
+        <v>5.0114</v>
       </c>
       <c r="G2" t="n">
         <v>3.825</v>
       </c>
       <c r="H2" t="n">
-        <v>5.6174</v>
+        <v>5.5547</v>
       </c>
       <c r="I2" t="n">
         <v>5.6962</v>
@@ -542,25 +542,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.9203</v>
+        <v>4.8981</v>
       </c>
       <c r="C3" t="n">
-        <v>1.6419</v>
+        <v>1.6345</v>
       </c>
       <c r="D3" t="n">
-        <v>1.5663</v>
+        <v>1.5075</v>
       </c>
       <c r="E3" t="n">
-        <v>4.9203</v>
+        <v>4.8981</v>
       </c>
       <c r="F3" t="n">
-        <v>1.9838</v>
+        <v>1.9616</v>
       </c>
       <c r="G3" t="n">
         <v>2.9365</v>
       </c>
       <c r="H3" t="n">
-        <v>1.9838</v>
+        <v>1.9616</v>
       </c>
       <c r="I3" t="n">
         <v>2.0116</v>
@@ -594,7 +594,7 @@
         <v>1.441</v>
       </c>
       <c r="D4" t="n">
-        <v>1.3231</v>
+        <v>1.2765</v>
       </c>
       <c r="E4" t="n">
         <v>4.3183</v>
@@ -634,25 +634,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.2732</v>
+        <v>4.2467</v>
       </c>
       <c r="C5" t="n">
-        <v>1.426</v>
+        <v>1.4172</v>
       </c>
       <c r="D5" t="n">
-        <v>1.3049</v>
+        <v>1.248</v>
       </c>
       <c r="E5" t="n">
-        <v>4.2732</v>
+        <v>4.2467</v>
       </c>
       <c r="F5" t="n">
-        <v>2.3743</v>
+        <v>2.3478</v>
       </c>
       <c r="G5" t="n">
         <v>1.8989</v>
       </c>
       <c r="H5" t="n">
-        <v>2.3743</v>
+        <v>2.3478</v>
       </c>
       <c r="I5" t="n">
         <v>2.4076</v>
@@ -680,25 +680,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.2432</v>
+        <v>4.2329</v>
       </c>
       <c r="C6" t="n">
-        <v>1.416</v>
+        <v>1.4126</v>
       </c>
       <c r="D6" t="n">
-        <v>1.2928</v>
+        <v>1.2425</v>
       </c>
       <c r="E6" t="n">
-        <v>4.2432</v>
+        <v>4.2329</v>
       </c>
       <c r="F6" t="n">
-        <v>4.2432</v>
+        <v>4.2329</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>4.3503</v>
+        <v>4.3341</v>
       </c>
       <c r="I6" t="n">
         <v>4.3706</v>
@@ -726,25 +726,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.0672</v>
+        <v>4.0361</v>
       </c>
       <c r="C7" t="n">
-        <v>1.3573</v>
+        <v>1.3469</v>
       </c>
       <c r="D7" t="n">
-        <v>1.2217</v>
+        <v>1.1641</v>
       </c>
       <c r="E7" t="n">
-        <v>4.0672</v>
+        <v>4.0361</v>
       </c>
       <c r="F7" t="n">
-        <v>2.7924</v>
+        <v>2.7613</v>
       </c>
       <c r="G7" t="n">
         <v>1.2748</v>
       </c>
       <c r="H7" t="n">
-        <v>2.7924</v>
+        <v>2.7613</v>
       </c>
       <c r="I7" t="n">
         <v>2.8316</v>
@@ -772,25 +772,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.9105</v>
+        <v>3.8991</v>
       </c>
       <c r="C8" t="n">
-        <v>1.305</v>
+        <v>1.3012</v>
       </c>
       <c r="D8" t="n">
-        <v>1.1584</v>
+        <v>1.1095</v>
       </c>
       <c r="E8" t="n">
-        <v>3.9105</v>
+        <v>3.8991</v>
       </c>
       <c r="F8" t="n">
-        <v>4.5177</v>
+        <v>4.5063</v>
       </c>
       <c r="G8" t="n">
         <v>-0.6072</v>
       </c>
       <c r="H8" t="n">
-        <v>4.7807</v>
+        <v>4.7629</v>
       </c>
       <c r="I8" t="n">
         <v>4.803</v>
@@ -824,7 +824,7 @@
         <v>1.21</v>
       </c>
       <c r="D9" t="n">
-        <v>1.0434</v>
+        <v>1.0006</v>
       </c>
       <c r="E9" t="n">
         <v>3.6258</v>
@@ -870,7 +870,7 @@
         <v>1.1601</v>
       </c>
       <c r="D10" t="n">
-        <v>0.983</v>
+        <v>0.9411</v>
       </c>
       <c r="E10" t="n">
         <v>3.4764</v>
@@ -910,25 +910,25 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.2143</v>
+        <v>3.2023</v>
       </c>
       <c r="C11" t="n">
-        <v>1.0726</v>
+        <v>1.0686</v>
       </c>
       <c r="D11" t="n">
-        <v>0.8771</v>
+        <v>0.8319</v>
       </c>
       <c r="E11" t="n">
-        <v>3.2143</v>
+        <v>3.2023</v>
       </c>
       <c r="F11" t="n">
-        <v>3.2143</v>
+        <v>3.2023</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>3.2143</v>
+        <v>3.2023</v>
       </c>
       <c r="I11" t="n">
         <v>3.2293</v>
@@ -956,25 +956,25 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3.0204</v>
+        <v>3.0054</v>
       </c>
       <c r="C12" t="n">
-        <v>1.0079</v>
+        <v>1.0029</v>
       </c>
       <c r="D12" t="n">
-        <v>0.7988</v>
+        <v>0.7534</v>
       </c>
       <c r="E12" t="n">
-        <v>3.0204</v>
+        <v>3.0054</v>
       </c>
       <c r="F12" t="n">
-        <v>4.0204</v>
+        <v>4.0054</v>
       </c>
       <c r="G12" t="n">
         <v>-1</v>
       </c>
       <c r="H12" t="n">
-        <v>4.0204</v>
+        <v>4.0054</v>
       </c>
       <c r="I12" t="n">
         <v>4.0391</v>
@@ -1002,25 +1002,25 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.9526</v>
+        <v>2.9416</v>
       </c>
       <c r="C13" t="n">
-        <v>0.9853</v>
+        <v>0.9816</v>
       </c>
       <c r="D13" t="n">
-        <v>0.7714</v>
+        <v>0.728</v>
       </c>
       <c r="E13" t="n">
-        <v>2.9526</v>
+        <v>2.9416</v>
       </c>
       <c r="F13" t="n">
-        <v>2.9526</v>
+        <v>2.9416</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>2.9526</v>
+        <v>2.9416</v>
       </c>
       <c r="I13" t="n">
         <v>2.9664</v>
@@ -1054,7 +1054,7 @@
         <v>0.7883</v>
       </c>
       <c r="D14" t="n">
-        <v>0.533</v>
+        <v>0.4972</v>
       </c>
       <c r="E14" t="n">
         <v>2.3623</v>
@@ -1094,25 +1094,25 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.3612</v>
+        <v>2.3524</v>
       </c>
       <c r="C15" t="n">
-        <v>0.788</v>
+        <v>0.785</v>
       </c>
       <c r="D15" t="n">
-        <v>0.5325</v>
+        <v>0.4933</v>
       </c>
       <c r="E15" t="n">
-        <v>2.3612</v>
+        <v>2.3524</v>
       </c>
       <c r="F15" t="n">
-        <v>2.3612</v>
+        <v>2.3524</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>2.3612</v>
+        <v>2.3524</v>
       </c>
       <c r="I15" t="n">
         <v>2.3722</v>
@@ -1146,7 +1146,7 @@
         <v>0.7075</v>
       </c>
       <c r="D16" t="n">
-        <v>0.4351</v>
+        <v>0.4007</v>
       </c>
       <c r="E16" t="n">
         <v>2.12</v>
@@ -1186,25 +1186,25 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.0451</v>
+        <v>2.0261</v>
       </c>
       <c r="C17" t="n">
-        <v>0.6825</v>
+        <v>0.6761</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4048</v>
+        <v>0.3633</v>
       </c>
       <c r="E17" t="n">
-        <v>2.0451</v>
+        <v>2.0261</v>
       </c>
       <c r="F17" t="n">
-        <v>1.6977</v>
+        <v>1.6787</v>
       </c>
       <c r="G17" t="n">
         <v>0.3474</v>
       </c>
       <c r="H17" t="n">
-        <v>1.6977</v>
+        <v>1.6787</v>
       </c>
       <c r="I17" t="n">
         <v>1.7215</v>
@@ -1232,25 +1232,25 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.7484</v>
+        <v>1.7418</v>
       </c>
       <c r="C18" t="n">
-        <v>0.5835</v>
+        <v>0.5813</v>
       </c>
       <c r="D18" t="n">
-        <v>0.285</v>
+        <v>0.25</v>
       </c>
       <c r="E18" t="n">
-        <v>1.7484</v>
+        <v>1.7418</v>
       </c>
       <c r="F18" t="n">
-        <v>1.7484</v>
+        <v>1.7418</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>1.7484</v>
+        <v>1.7418</v>
       </c>
       <c r="I18" t="n">
         <v>1.7565</v>
@@ -1284,7 +1284,7 @@
         <v>0.4311</v>
       </c>
       <c r="D19" t="n">
-        <v>0.1005</v>
+        <v>0.0707</v>
       </c>
       <c r="E19" t="n">
         <v>1.2918</v>
@@ -1324,25 +1324,25 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.0213</v>
+        <v>1.0174</v>
       </c>
       <c r="C20" t="n">
-        <v>0.3408</v>
+        <v>0.3395</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.008800000000000001</v>
+        <v>-0.0386</v>
       </c>
       <c r="E20" t="n">
-        <v>1.0213</v>
+        <v>1.0174</v>
       </c>
       <c r="F20" t="n">
-        <v>1.0335</v>
+        <v>1.0296</v>
       </c>
       <c r="G20" t="n">
         <v>-0.0122</v>
       </c>
       <c r="H20" t="n">
-        <v>1.0335</v>
+        <v>1.0296</v>
       </c>
       <c r="I20" t="n">
         <v>1.0383</v>
@@ -1376,7 +1376,7 @@
         <v>0.2464</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.123</v>
+        <v>-0.1497</v>
       </c>
       <c r="E21" t="n">
         <v>0.7385</v>
@@ -1416,25 +1416,25 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.4893</v>
+        <v>0.4846</v>
       </c>
       <c r="C22" t="n">
-        <v>0.1633</v>
+        <v>0.1617</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.2237</v>
+        <v>-0.2508</v>
       </c>
       <c r="E22" t="n">
-        <v>0.4893</v>
+        <v>0.4846</v>
       </c>
       <c r="F22" t="n">
-        <v>1.2701</v>
+        <v>1.2654</v>
       </c>
       <c r="G22" t="n">
         <v>-0.7808</v>
       </c>
       <c r="H22" t="n">
-        <v>1.2701</v>
+        <v>1.2654</v>
       </c>
       <c r="I22" t="n">
         <v>1.276</v>
@@ -1468,7 +1468,7 @@
         <v>0.1409</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.2508</v>
+        <v>-0.2757</v>
       </c>
       <c r="E23" t="n">
         <v>0.4222</v>
@@ -1508,25 +1508,25 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.364</v>
+        <v>0.3589</v>
       </c>
       <c r="C24" t="n">
-        <v>0.1215</v>
+        <v>0.1198</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.2743</v>
+        <v>-0.3009</v>
       </c>
       <c r="E24" t="n">
-        <v>0.364</v>
+        <v>0.3589</v>
       </c>
       <c r="F24" t="n">
-        <v>1.364</v>
+        <v>1.3589</v>
       </c>
       <c r="G24" t="n">
         <v>-1</v>
       </c>
       <c r="H24" t="n">
-        <v>1.364</v>
+        <v>1.3589</v>
       </c>
       <c r="I24" t="n">
         <v>1.3703</v>
@@ -1560,7 +1560,7 @@
         <v>0.1183</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.2782</v>
+        <v>-0.3027</v>
       </c>
       <c r="E25" t="n">
         <v>0.3544</v>
@@ -1600,25 +1600,25 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-0.1077</v>
+        <v>-0.1073</v>
       </c>
       <c r="C26" t="n">
-        <v>-0.0359</v>
+        <v>-0.0358</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.4649</v>
+        <v>-0.4867</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.1077</v>
+        <v>-0.1073</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.1077</v>
+        <v>-0.1073</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.1077</v>
+        <v>-0.1073</v>
       </c>
       <c r="I26" t="n">
         <v>-0.1082</v>
@@ -1652,7 +1652,7 @@
         <v>-0.0789</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.5169</v>
+        <v>-0.5381</v>
       </c>
       <c r="E27" t="n">
         <v>-0.2365</v>
@@ -1698,7 +1698,7 @@
         <v>-0.148</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.6006</v>
+        <v>-0.6206</v>
       </c>
       <c r="E28" t="n">
         <v>-0.4436</v>
@@ -1738,25 +1738,25 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.5031</v>
+        <v>-0.5012</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.1679</v>
+        <v>-0.1673</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.6246</v>
+        <v>-0.6435999999999999</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.5031</v>
+        <v>-0.5012</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.5031</v>
+        <v>-0.5012</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.5031</v>
+        <v>-0.5012</v>
       </c>
       <c r="I29" t="n">
         <v>-0.5054</v>
@@ -1790,7 +1790,7 @@
         <v>-0.233</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.7035</v>
+        <v>-0.7221</v>
       </c>
       <c r="E30" t="n">
         <v>-0.6983</v>
@@ -1836,7 +1836,7 @@
         <v>-0.2865</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.7682</v>
+        <v>-0.786</v>
       </c>
       <c r="E31" t="n">
         <v>-0.8586</v>
@@ -1876,25 +1876,25 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.8643999999999999</v>
+        <v>-0.8612</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.2885</v>
+        <v>-0.2874</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.7706</v>
+        <v>-0.787</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.8643999999999999</v>
+        <v>-0.8612</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.8643999999999999</v>
+        <v>-0.8612</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.8643999999999999</v>
+        <v>-0.8612</v>
       </c>
       <c r="I32" t="n">
         <v>-0.8683999999999999</v>
@@ -1922,25 +1922,25 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-1.0782</v>
+        <v>-1.0742</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.3598</v>
+        <v>-0.3585</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.8569</v>
+        <v>-0.8719</v>
       </c>
       <c r="E33" t="n">
-        <v>-1.0782</v>
+        <v>-1.0742</v>
       </c>
       <c r="F33" t="n">
-        <v>-1.0782</v>
+        <v>-1.0742</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>-1.0782</v>
+        <v>-1.0742</v>
       </c>
       <c r="I33" t="n">
         <v>-1.0832</v>
@@ -1974,7 +1974,7 @@
         <v>-0.3669</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.8655</v>
+        <v>-0.882</v>
       </c>
       <c r="E34" t="n">
         <v>-1.0995</v>
@@ -2020,7 +2020,7 @@
         <v>-0.3707</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.8702</v>
+        <v>-0.8865</v>
       </c>
       <c r="E35" t="n">
         <v>-1.111</v>
@@ -2066,7 +2066,7 @@
         <v>-0.4488</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.9647</v>
+        <v>-0.9797</v>
       </c>
       <c r="E36" t="n">
         <v>-1.3449</v>
@@ -2112,7 +2112,7 @@
         <v>-0.5364</v>
       </c>
       <c r="D37" t="n">
-        <v>-1.0707</v>
+        <v>-1.0843</v>
       </c>
       <c r="E37" t="n">
         <v>-1.6074</v>
@@ -2148,93 +2148,93 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>ub1que</t>
+          <t>tarik</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-1.6885</v>
+        <v>-1.6824</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.5635</v>
+        <v>-0.5614</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.1035</v>
+        <v>-1.1142</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.6885</v>
+        <v>-1.6824</v>
       </c>
       <c r="F38" t="n">
-        <v>-1.6885</v>
+        <v>-1.6824</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>-1.6885</v>
+        <v>-1.6824</v>
       </c>
       <c r="I38" t="n">
-        <v>-1.6885</v>
+        <v>-1.6965</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>95</v>
+        <v>369</v>
       </c>
       <c r="L38" t="n">
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>-1.6885</v>
+        <v>-1.6965</v>
       </c>
       <c r="N38" t="n">
-        <v>95</v>
+        <v>369</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>tarik</t>
+          <t>ub1que</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.6887</v>
+        <v>-1.6885</v>
       </c>
       <c r="C39" t="n">
         <v>-0.5635</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.1036</v>
+        <v>-1.1166</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.6887</v>
+        <v>-1.6885</v>
       </c>
       <c r="F39" t="n">
-        <v>-1.6887</v>
+        <v>-1.6885</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>-1.6887</v>
+        <v>-1.6885</v>
       </c>
       <c r="I39" t="n">
-        <v>-1.6965</v>
+        <v>-1.6885</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>369</v>
+        <v>95</v>
       </c>
       <c r="L39" t="n">
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>-1.6965</v>
+        <v>-1.6885</v>
       </c>
       <c r="N39" t="n">
-        <v>369</v>
+        <v>95</v>
       </c>
     </row>
     <row r="40">
@@ -2250,7 +2250,7 @@
         <v>-0.6114000000000001</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.1614</v>
+        <v>-1.1738</v>
       </c>
       <c r="E40" t="n">
         <v>-1.832</v>
@@ -2296,7 +2296,7 @@
         <v>-0.7104</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.2813</v>
+        <v>-1.292</v>
       </c>
       <c r="E41" t="n">
         <v>-2.1287</v>

--- a/database/event/2013/event_2013_evp_summary.xlsx
+++ b/database/event/2013/event_2013_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8.836399999999999</v>
+        <v>8.046099999999999</v>
       </c>
       <c r="C2" t="n">
-        <v>2.9488</v>
+        <v>2.685</v>
       </c>
       <c r="D2" t="n">
-        <v>3.0765</v>
+        <v>2.9944</v>
       </c>
       <c r="E2" t="n">
-        <v>8.836399999999999</v>
+        <v>8.046099999999999</v>
       </c>
       <c r="F2" t="n">
-        <v>5.0114</v>
+        <v>4.4768</v>
       </c>
       <c r="G2" t="n">
-        <v>3.825</v>
+        <v>3.5693</v>
       </c>
       <c r="H2" t="n">
-        <v>5.5547</v>
+        <v>6.4705</v>
       </c>
       <c r="I2" t="n">
-        <v>5.6962</v>
+        <v>7.3021</v>
       </c>
       <c r="J2" t="n">
-        <v>3.825</v>
+        <v>3.5693</v>
       </c>
       <c r="K2" t="n">
         <v>331</v>
@@ -529,7 +529,7 @@
         <v>72</v>
       </c>
       <c r="M2" t="n">
-        <v>9.5212</v>
+        <v>10.8714</v>
       </c>
       <c r="N2" t="n">
         <v>403</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.8981</v>
+        <v>5.5171</v>
       </c>
       <c r="C3" t="n">
-        <v>1.6345</v>
+        <v>1.8411</v>
       </c>
       <c r="D3" t="n">
-        <v>1.5075</v>
+        <v>1.8527</v>
       </c>
       <c r="E3" t="n">
-        <v>4.8981</v>
+        <v>5.5171</v>
       </c>
       <c r="F3" t="n">
-        <v>1.9616</v>
+        <v>2.8014</v>
       </c>
       <c r="G3" t="n">
-        <v>2.9365</v>
+        <v>2.7157</v>
       </c>
       <c r="H3" t="n">
-        <v>1.9616</v>
+        <v>2.8014</v>
       </c>
       <c r="I3" t="n">
-        <v>2.0116</v>
+        <v>3.1615</v>
       </c>
       <c r="J3" t="n">
-        <v>2.9365</v>
+        <v>2.7157</v>
       </c>
       <c r="K3" t="n">
         <v>331</v>
@@ -575,7 +575,7 @@
         <v>72</v>
       </c>
       <c r="M3" t="n">
-        <v>4.9481</v>
+        <v>5.8772</v>
       </c>
       <c r="N3" t="n">
         <v>403</v>
@@ -584,81 +584,81 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>device</t>
+          <t>NBK-</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.3183</v>
+        <v>4.802</v>
       </c>
       <c r="C4" t="n">
-        <v>1.441</v>
+        <v>1.6025</v>
       </c>
       <c r="D4" t="n">
-        <v>1.2765</v>
+        <v>1.5298</v>
       </c>
       <c r="E4" t="n">
-        <v>4.3183</v>
+        <v>4.802</v>
       </c>
       <c r="F4" t="n">
-        <v>4.3183</v>
+        <v>2.9931</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>1.8089</v>
       </c>
       <c r="H4" t="n">
-        <v>4.468</v>
+        <v>3.2125</v>
       </c>
       <c r="I4" t="n">
-        <v>4.468</v>
+        <v>3.6254</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>1.8089</v>
       </c>
       <c r="K4" t="n">
-        <v>249</v>
+        <v>331</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="M4" t="n">
-        <v>4.468</v>
+        <v>5.4343</v>
       </c>
       <c r="N4" t="n">
-        <v>249</v>
+        <v>403</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>NBK-</t>
+          <t>apEX</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.2467</v>
+        <v>4.6239</v>
       </c>
       <c r="C5" t="n">
-        <v>1.4172</v>
+        <v>1.543</v>
       </c>
       <c r="D5" t="n">
-        <v>1.248</v>
+        <v>1.4494</v>
       </c>
       <c r="E5" t="n">
-        <v>4.2467</v>
+        <v>4.6239</v>
       </c>
       <c r="F5" t="n">
-        <v>2.3478</v>
+        <v>3.0902</v>
       </c>
       <c r="G5" t="n">
-        <v>1.8989</v>
+        <v>1.5337</v>
       </c>
       <c r="H5" t="n">
-        <v>2.3478</v>
+        <v>3.4257</v>
       </c>
       <c r="I5" t="n">
-        <v>2.4076</v>
+        <v>3.866</v>
       </c>
       <c r="J5" t="n">
-        <v>1.8989</v>
+        <v>1.5337</v>
       </c>
       <c r="K5" t="n">
         <v>331</v>
@@ -667,7 +667,7 @@
         <v>72</v>
       </c>
       <c r="M5" t="n">
-        <v>4.3065</v>
+        <v>5.3997</v>
       </c>
       <c r="N5" t="n">
         <v>403</v>
@@ -676,139 +676,139 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ScreaM</t>
+          <t>device</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.2329</v>
+        <v>4.1766</v>
       </c>
       <c r="C6" t="n">
-        <v>1.4126</v>
+        <v>1.3938</v>
       </c>
       <c r="D6" t="n">
-        <v>1.2425</v>
+        <v>1.2475</v>
       </c>
       <c r="E6" t="n">
-        <v>4.2329</v>
+        <v>4.1766</v>
       </c>
       <c r="F6" t="n">
-        <v>4.2329</v>
+        <v>4.1766</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>4.3341</v>
+        <v>5.8112</v>
       </c>
       <c r="I6" t="n">
-        <v>4.3706</v>
+        <v>5.8112</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>301</v>
+        <v>249</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>4.3706</v>
+        <v>5.8112</v>
       </c>
       <c r="N6" t="n">
-        <v>301</v>
+        <v>249</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>apEX</t>
+          <t>ScreaM</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.0361</v>
+        <v>3.8869</v>
       </c>
       <c r="C7" t="n">
-        <v>1.3469</v>
+        <v>1.2971</v>
       </c>
       <c r="D7" t="n">
-        <v>1.1641</v>
+        <v>1.1167</v>
       </c>
       <c r="E7" t="n">
-        <v>4.0361</v>
+        <v>3.8869</v>
       </c>
       <c r="F7" t="n">
-        <v>2.7613</v>
+        <v>3.8869</v>
       </c>
       <c r="G7" t="n">
-        <v>1.2748</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>2.7613</v>
+        <v>5.1752</v>
       </c>
       <c r="I7" t="n">
-        <v>2.8316</v>
+        <v>5.388</v>
       </c>
       <c r="J7" t="n">
-        <v>1.2748</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>331</v>
+        <v>301</v>
       </c>
       <c r="L7" t="n">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>4.1064</v>
+        <v>5.388</v>
       </c>
       <c r="N7" t="n">
-        <v>403</v>
+        <v>301</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>k0nfig</t>
+          <t>Xyp9x</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.8991</v>
+        <v>3.7762</v>
       </c>
       <c r="C8" t="n">
-        <v>1.3012</v>
+        <v>1.2601</v>
       </c>
       <c r="D8" t="n">
-        <v>1.1095</v>
+        <v>1.0668</v>
       </c>
       <c r="E8" t="n">
-        <v>3.8991</v>
+        <v>3.7762</v>
       </c>
       <c r="F8" t="n">
-        <v>4.5063</v>
+        <v>3.7762</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.6072</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>4.7629</v>
+        <v>4.932</v>
       </c>
       <c r="I8" t="n">
-        <v>4.803</v>
+        <v>4.932</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.6072</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>159</v>
+        <v>249</v>
       </c>
       <c r="L8" t="n">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>4.1958</v>
+        <v>4.932</v>
       </c>
       <c r="N8" t="n">
-        <v>231</v>
+        <v>249</v>
       </c>
     </row>
     <row r="9">
@@ -818,28 +818,28 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.6258</v>
+        <v>3.6192</v>
       </c>
       <c r="C9" t="n">
-        <v>1.21</v>
+        <v>1.2078</v>
       </c>
       <c r="D9" t="n">
-        <v>1.0006</v>
+        <v>0.9959</v>
       </c>
       <c r="E9" t="n">
-        <v>3.6258</v>
+        <v>3.6192</v>
       </c>
       <c r="F9" t="n">
-        <v>3.6258</v>
+        <v>3.6192</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>3.6258</v>
+        <v>4.5874</v>
       </c>
       <c r="I9" t="n">
-        <v>3.6258</v>
+        <v>4.5874</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -851,7 +851,7 @@
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>3.6258</v>
+        <v>4.5874</v>
       </c>
       <c r="N9" t="n">
         <v>249</v>
@@ -860,32 +860,32 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Xyp9x</t>
+          <t>dupreeh</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.4764</v>
+        <v>3.5471</v>
       </c>
       <c r="C10" t="n">
-        <v>1.1601</v>
+        <v>1.1837</v>
       </c>
       <c r="D10" t="n">
-        <v>0.9411</v>
+        <v>0.9633</v>
       </c>
       <c r="E10" t="n">
-        <v>3.4764</v>
+        <v>3.5471</v>
       </c>
       <c r="F10" t="n">
-        <v>3.4764</v>
+        <v>3.5471</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>3.4764</v>
+        <v>4.4291</v>
       </c>
       <c r="I10" t="n">
-        <v>3.4764</v>
+        <v>4.4291</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -897,7 +897,7 @@
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>3.4764</v>
+        <v>4.4291</v>
       </c>
       <c r="N10" t="n">
         <v>249</v>
@@ -906,124 +906,124 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SmithZz</t>
+          <t>k0nfig</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.2023</v>
+        <v>3.2942</v>
       </c>
       <c r="C11" t="n">
-        <v>1.0686</v>
+        <v>1.0993</v>
       </c>
       <c r="D11" t="n">
-        <v>0.8319</v>
+        <v>0.8492</v>
       </c>
       <c r="E11" t="n">
-        <v>3.2023</v>
+        <v>3.2942</v>
       </c>
       <c r="F11" t="n">
-        <v>3.2023</v>
+        <v>3.7313</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>-0.4371</v>
       </c>
       <c r="H11" t="n">
-        <v>3.2023</v>
+        <v>4.8335</v>
       </c>
       <c r="I11" t="n">
-        <v>3.2293</v>
+        <v>5.0323</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>-0.4371</v>
       </c>
       <c r="K11" t="n">
-        <v>301</v>
+        <v>159</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="M11" t="n">
-        <v>3.2293</v>
+        <v>4.5952</v>
       </c>
       <c r="N11" t="n">
-        <v>301</v>
+        <v>231</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Kjaerbye</t>
+          <t>shox</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3.0054</v>
+        <v>3.2535</v>
       </c>
       <c r="C12" t="n">
-        <v>1.0029</v>
+        <v>1.0857</v>
       </c>
       <c r="D12" t="n">
-        <v>0.7534</v>
+        <v>0.8308</v>
       </c>
       <c r="E12" t="n">
-        <v>3.0054</v>
+        <v>3.2535</v>
       </c>
       <c r="F12" t="n">
-        <v>4.0054</v>
+        <v>3.2535</v>
       </c>
       <c r="G12" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>4.0054</v>
+        <v>3.7843</v>
       </c>
       <c r="I12" t="n">
-        <v>4.0391</v>
+        <v>3.9399</v>
       </c>
       <c r="J12" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>159</v>
+        <v>301</v>
       </c>
       <c r="L12" t="n">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>3.0391</v>
+        <v>3.9399</v>
       </c>
       <c r="N12" t="n">
-        <v>231</v>
+        <v>301</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>shox</t>
+          <t>SmithZz</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.9416</v>
+        <v>3.1831</v>
       </c>
       <c r="C13" t="n">
-        <v>0.9816</v>
+        <v>1.0622</v>
       </c>
       <c r="D13" t="n">
-        <v>0.728</v>
+        <v>0.799</v>
       </c>
       <c r="E13" t="n">
-        <v>2.9416</v>
+        <v>3.1831</v>
       </c>
       <c r="F13" t="n">
-        <v>2.9416</v>
+        <v>3.1831</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>2.9416</v>
+        <v>3.6298</v>
       </c>
       <c r="I13" t="n">
-        <v>2.9664</v>
+        <v>3.7791</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1035,7 +1035,7 @@
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>2.9664</v>
+        <v>3.7791</v>
       </c>
       <c r="N13" t="n">
         <v>301</v>
@@ -1044,185 +1044,185 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>shroud</t>
+          <t>kioShiMa</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.3623</v>
+        <v>3.0172</v>
       </c>
       <c r="C14" t="n">
-        <v>0.7883</v>
+        <v>1.0069</v>
       </c>
       <c r="D14" t="n">
-        <v>0.4972</v>
+        <v>0.7241</v>
       </c>
       <c r="E14" t="n">
-        <v>2.3623</v>
+        <v>3.0172</v>
       </c>
       <c r="F14" t="n">
-        <v>2.3623</v>
+        <v>2.4277</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>0.5895</v>
       </c>
       <c r="H14" t="n">
-        <v>2.3623</v>
+        <v>2.4277</v>
       </c>
       <c r="I14" t="n">
-        <v>2.3623</v>
+        <v>2.7397</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>0.5895</v>
       </c>
       <c r="K14" t="n">
-        <v>247</v>
+        <v>331</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="M14" t="n">
-        <v>2.3623</v>
+        <v>3.3292</v>
       </c>
       <c r="N14" t="n">
-        <v>247</v>
+        <v>403</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>jdm64</t>
+          <t>shroud</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.3524</v>
+        <v>2.7585</v>
       </c>
       <c r="C15" t="n">
-        <v>0.785</v>
+        <v>0.9205</v>
       </c>
       <c r="D15" t="n">
-        <v>0.4933</v>
+        <v>0.6073</v>
       </c>
       <c r="E15" t="n">
-        <v>2.3524</v>
+        <v>2.7585</v>
       </c>
       <c r="F15" t="n">
-        <v>2.3524</v>
+        <v>2.7585</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>2.3524</v>
+        <v>2.7585</v>
       </c>
       <c r="I15" t="n">
-        <v>2.3722</v>
+        <v>2.7585</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>369</v>
+        <v>247</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>2.3722</v>
+        <v>2.7585</v>
       </c>
       <c r="N15" t="n">
-        <v>369</v>
+        <v>247</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>dupreeh</t>
+          <t>Kjaerbye</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.12</v>
+        <v>2.4742</v>
       </c>
       <c r="C16" t="n">
-        <v>0.7075</v>
+        <v>0.8257</v>
       </c>
       <c r="D16" t="n">
-        <v>0.4007</v>
+        <v>0.479</v>
       </c>
       <c r="E16" t="n">
-        <v>2.12</v>
+        <v>2.4742</v>
       </c>
       <c r="F16" t="n">
-        <v>2.12</v>
+        <v>3.2964</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>-0.8222</v>
       </c>
       <c r="H16" t="n">
-        <v>2.12</v>
+        <v>3.8786</v>
       </c>
       <c r="I16" t="n">
-        <v>2.12</v>
+        <v>4.0381</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>-0.8222</v>
       </c>
       <c r="K16" t="n">
-        <v>249</v>
+        <v>159</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="M16" t="n">
-        <v>2.12</v>
+        <v>3.2159</v>
       </c>
       <c r="N16" t="n">
-        <v>249</v>
+        <v>231</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>kioShiMa</t>
+          <t>jdm64</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.0261</v>
+        <v>2.3993</v>
       </c>
       <c r="C17" t="n">
-        <v>0.6761</v>
+        <v>0.8007</v>
       </c>
       <c r="D17" t="n">
-        <v>0.3633</v>
+        <v>0.4452</v>
       </c>
       <c r="E17" t="n">
-        <v>2.0261</v>
+        <v>2.3993</v>
       </c>
       <c r="F17" t="n">
-        <v>1.6787</v>
+        <v>2.3993</v>
       </c>
       <c r="G17" t="n">
-        <v>0.3474</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>1.6787</v>
+        <v>2.3993</v>
       </c>
       <c r="I17" t="n">
-        <v>1.7215</v>
+        <v>2.498</v>
       </c>
       <c r="J17" t="n">
-        <v>0.3474</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>331</v>
+        <v>369</v>
       </c>
       <c r="L17" t="n">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>2.0689</v>
+        <v>2.498</v>
       </c>
       <c r="N17" t="n">
-        <v>403</v>
+        <v>369</v>
       </c>
     </row>
     <row r="18">
@@ -1232,28 +1232,28 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.7418</v>
+        <v>2.3874</v>
       </c>
       <c r="C18" t="n">
-        <v>0.5813</v>
+        <v>0.7967</v>
       </c>
       <c r="D18" t="n">
-        <v>0.25</v>
+        <v>0.4398</v>
       </c>
       <c r="E18" t="n">
-        <v>1.7418</v>
+        <v>2.3874</v>
       </c>
       <c r="F18" t="n">
-        <v>1.7418</v>
+        <v>2.3874</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>1.7418</v>
+        <v>2.3874</v>
       </c>
       <c r="I18" t="n">
-        <v>1.7565</v>
+        <v>2.4856</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1265,7 +1265,7 @@
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>1.7565</v>
+        <v>2.4856</v>
       </c>
       <c r="N18" t="n">
         <v>301</v>
@@ -1278,28 +1278,28 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.2918</v>
+        <v>1.8906</v>
       </c>
       <c r="C19" t="n">
-        <v>0.4311</v>
+        <v>0.6309</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0707</v>
+        <v>0.2155</v>
       </c>
       <c r="E19" t="n">
-        <v>1.2918</v>
+        <v>1.8906</v>
       </c>
       <c r="F19" t="n">
-        <v>1.2918</v>
+        <v>1.8906</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>1.2918</v>
+        <v>1.8906</v>
       </c>
       <c r="I19" t="n">
-        <v>1.2918</v>
+        <v>1.8906</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -1311,7 +1311,7 @@
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>1.2918</v>
+        <v>1.8906</v>
       </c>
       <c r="N19" t="n">
         <v>249</v>
@@ -1320,127 +1320,127 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>RUBINO</t>
+          <t>Skadoodle</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.0174</v>
+        <v>1.3076</v>
       </c>
       <c r="C20" t="n">
-        <v>0.3395</v>
+        <v>0.4364</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.0386</v>
+        <v>-0.0477</v>
       </c>
       <c r="E20" t="n">
-        <v>1.0174</v>
+        <v>1.3076</v>
       </c>
       <c r="F20" t="n">
-        <v>1.0296</v>
+        <v>1.3076</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.0122</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>1.0296</v>
+        <v>1.3076</v>
       </c>
       <c r="I20" t="n">
-        <v>1.0383</v>
+        <v>1.3076</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.0122</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>159</v>
+        <v>247</v>
       </c>
       <c r="L20" t="n">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>1.0261</v>
+        <v>1.3076</v>
       </c>
       <c r="N20" t="n">
-        <v>231</v>
+        <v>247</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Skadoodle</t>
+          <t>RUBINO</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.7385</v>
+        <v>1.2629</v>
       </c>
       <c r="C21" t="n">
-        <v>0.2464</v>
+        <v>0.4214</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.1497</v>
+        <v>-0.0679</v>
       </c>
       <c r="E21" t="n">
-        <v>0.7385</v>
+        <v>1.2629</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7385</v>
+        <v>1.2079</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>0.055</v>
       </c>
       <c r="H21" t="n">
-        <v>0.7385</v>
+        <v>1.2079</v>
       </c>
       <c r="I21" t="n">
-        <v>0.7385</v>
+        <v>1.2576</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>0.055</v>
       </c>
       <c r="K21" t="n">
-        <v>247</v>
+        <v>159</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="M21" t="n">
-        <v>0.7385</v>
+        <v>1.3126</v>
       </c>
       <c r="N21" t="n">
-        <v>247</v>
+        <v>231</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>TENZKI</t>
+          <t>MSL</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.4846</v>
+        <v>1.0713</v>
       </c>
       <c r="C22" t="n">
-        <v>0.1617</v>
+        <v>0.3575</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.2508</v>
+        <v>-0.1544</v>
       </c>
       <c r="E22" t="n">
-        <v>0.4846</v>
+        <v>1.0713</v>
       </c>
       <c r="F22" t="n">
-        <v>1.2654</v>
+        <v>1.9318</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.7808</v>
+        <v>-0.8605</v>
       </c>
       <c r="H22" t="n">
-        <v>1.2654</v>
+        <v>1.9318</v>
       </c>
       <c r="I22" t="n">
-        <v>1.276</v>
+        <v>2.0113</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.7808</v>
+        <v>-0.8605</v>
       </c>
       <c r="K22" t="n">
         <v>159</v>
@@ -1449,7 +1449,7 @@
         <v>72</v>
       </c>
       <c r="M22" t="n">
-        <v>0.4952</v>
+        <v>1.1508</v>
       </c>
       <c r="N22" t="n">
         <v>231</v>
@@ -1458,814 +1458,814 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>waterfaLLZ</t>
+          <t>TENZKI</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.4222</v>
+        <v>0.9036999999999999</v>
       </c>
       <c r="C23" t="n">
-        <v>0.1409</v>
+        <v>0.3016</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.2757</v>
+        <v>-0.23</v>
       </c>
       <c r="E23" t="n">
-        <v>0.4222</v>
+        <v>0.9036999999999999</v>
       </c>
       <c r="F23" t="n">
-        <v>0.4222</v>
+        <v>1.4731</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>-0.5694</v>
       </c>
       <c r="H23" t="n">
-        <v>0.4222</v>
+        <v>1.4731</v>
       </c>
       <c r="I23" t="n">
-        <v>0.4222</v>
+        <v>1.5337</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>-0.5694</v>
       </c>
       <c r="K23" t="n">
-        <v>95</v>
+        <v>159</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="M23" t="n">
-        <v>0.4222</v>
+        <v>0.9643</v>
       </c>
       <c r="N23" t="n">
-        <v>95</v>
+        <v>231</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>MSL</t>
+          <t>waterfaLLZ</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.3589</v>
+        <v>0.8571</v>
       </c>
       <c r="C24" t="n">
-        <v>0.1198</v>
+        <v>0.286</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.3009</v>
+        <v>-0.2511</v>
       </c>
       <c r="E24" t="n">
-        <v>0.3589</v>
+        <v>0.8571</v>
       </c>
       <c r="F24" t="n">
-        <v>1.3589</v>
+        <v>0.8571</v>
       </c>
       <c r="G24" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>1.3589</v>
+        <v>0.8571</v>
       </c>
       <c r="I24" t="n">
-        <v>1.3703</v>
+        <v>0.8571</v>
       </c>
       <c r="J24" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>159</v>
+        <v>95</v>
       </c>
       <c r="L24" t="n">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0.3703000000000001</v>
+        <v>0.8571</v>
       </c>
       <c r="N24" t="n">
-        <v>231</v>
+        <v>95</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Shara</t>
+          <t>RpK</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.3544</v>
+        <v>0.7516</v>
       </c>
       <c r="C25" t="n">
-        <v>0.1183</v>
+        <v>0.2508</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.3027</v>
+        <v>-0.2987</v>
       </c>
       <c r="E25" t="n">
-        <v>0.3544</v>
+        <v>0.7516</v>
       </c>
       <c r="F25" t="n">
-        <v>0.3544</v>
+        <v>0.7516</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>0.3544</v>
+        <v>0.7516</v>
       </c>
       <c r="I25" t="n">
-        <v>0.3544</v>
+        <v>0.7825</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>107</v>
+        <v>301</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>0.3544</v>
+        <v>0.7825</v>
       </c>
       <c r="N25" t="n">
-        <v>107</v>
+        <v>301</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>RpK</t>
+          <t>Shara</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-0.1073</v>
+        <v>0.5039</v>
       </c>
       <c r="C26" t="n">
-        <v>-0.0358</v>
+        <v>0.1682</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.4867</v>
+        <v>-0.4105</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.1073</v>
+        <v>0.5039</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.1073</v>
+        <v>0.5039</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.1073</v>
+        <v>0.5039</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.1082</v>
+        <v>0.5039</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>301</v>
+        <v>107</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>-0.1082</v>
+        <v>0.5039</v>
       </c>
       <c r="N26" t="n">
-        <v>301</v>
+        <v>107</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>cheti</t>
+          <t>reltuC</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.2365</v>
+        <v>0.4306</v>
       </c>
       <c r="C27" t="n">
-        <v>-0.0789</v>
+        <v>0.1437</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.5381</v>
+        <v>-0.4436</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.2365</v>
+        <v>0.4306</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.2365</v>
+        <v>0.4306</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.2365</v>
+        <v>0.4306</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.2365</v>
+        <v>0.4484</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>95</v>
+        <v>369</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>-0.2365</v>
+        <v>0.4484</v>
       </c>
       <c r="N27" t="n">
-        <v>95</v>
+        <v>369</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>WorldEdit</t>
+          <t>FugLy</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.4436</v>
+        <v>0.0065</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.148</v>
+        <v>0.0022</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.6206</v>
+        <v>-0.6351</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.4436</v>
+        <v>0.0065</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.4436</v>
+        <v>0.0065</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.4436</v>
+        <v>0.0065</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.4436</v>
+        <v>0.0067</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>107</v>
+        <v>369</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.4436</v>
+        <v>0.0067</v>
       </c>
       <c r="N28" t="n">
-        <v>107</v>
+        <v>369</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>reltuC</t>
+          <t>WorldEdit</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.5012</v>
+        <v>-0.0133</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.1673</v>
+        <v>-0.0044</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.6435999999999999</v>
+        <v>-0.644</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.5012</v>
+        <v>-0.0133</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.5012</v>
+        <v>-0.0133</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.5012</v>
+        <v>-0.0133</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.5054</v>
+        <v>-0.0133</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>369</v>
+        <v>107</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.5054</v>
+        <v>-0.0133</v>
       </c>
       <c r="N29" t="n">
-        <v>369</v>
+        <v>107</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>B1ad3</t>
+          <t>cheti</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.6983</v>
+        <v>-0.1055</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.233</v>
+        <v>-0.0352</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.7221</v>
+        <v>-0.6856</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.6983</v>
+        <v>-0.1055</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.6983</v>
+        <v>-0.1055</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.6983</v>
+        <v>-0.1055</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.6983</v>
+        <v>-0.1055</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>107</v>
+        <v>95</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.6983</v>
+        <v>-0.1055</v>
       </c>
       <c r="N30" t="n">
-        <v>107</v>
+        <v>95</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>markeloff</t>
+          <t>hazed</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.8586</v>
+        <v>-0.231</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.2865</v>
+        <v>-0.0771</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.786</v>
+        <v>-0.7423</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.8586</v>
+        <v>-0.231</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.8586</v>
+        <v>-0.231</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.8586</v>
+        <v>-0.231</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.8586</v>
+        <v>-0.2404</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>107</v>
+        <v>369</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.8586</v>
+        <v>-0.2404</v>
       </c>
       <c r="N31" t="n">
-        <v>107</v>
+        <v>369</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>FugLy</t>
+          <t>Stewie2K</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.8612</v>
+        <v>-0.301</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.2874</v>
+        <v>-0.1004</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.787</v>
+        <v>-0.7739</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.8612</v>
+        <v>-0.301</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.8612</v>
+        <v>-0.301</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.8612</v>
+        <v>-0.301</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.8683999999999999</v>
+        <v>-0.301</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>369</v>
+        <v>247</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.8683999999999999</v>
+        <v>-0.301</v>
       </c>
       <c r="N32" t="n">
-        <v>369</v>
+        <v>247</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>hazed</t>
+          <t>B1ad3</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-1.0742</v>
+        <v>-0.403</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.3585</v>
+        <v>-0.1345</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.8719</v>
+        <v>-0.8199</v>
       </c>
       <c r="E33" t="n">
-        <v>-1.0742</v>
+        <v>-0.403</v>
       </c>
       <c r="F33" t="n">
-        <v>-1.0742</v>
+        <v>-0.403</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>-1.0742</v>
+        <v>-0.403</v>
       </c>
       <c r="I33" t="n">
-        <v>-1.0832</v>
+        <v>-0.403</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>369</v>
+        <v>107</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>-1.0832</v>
+        <v>-0.403</v>
       </c>
       <c r="N33" t="n">
-        <v>369</v>
+        <v>107</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Stewie2K</t>
+          <t>markeloff</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-1.0995</v>
+        <v>-0.5542</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.3669</v>
+        <v>-0.1849</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.882</v>
+        <v>-0.8882</v>
       </c>
       <c r="E34" t="n">
-        <v>-1.0995</v>
+        <v>-0.5542</v>
       </c>
       <c r="F34" t="n">
-        <v>-1.0995</v>
+        <v>-0.5542</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>-1.0995</v>
+        <v>-0.5542</v>
       </c>
       <c r="I34" t="n">
-        <v>-1.0995</v>
+        <v>-0.5542</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>247</v>
+        <v>107</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>-1.0995</v>
+        <v>-0.5542</v>
       </c>
       <c r="N34" t="n">
-        <v>247</v>
+        <v>107</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>bondik</t>
+          <t>n0thing</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-1.111</v>
+        <v>-0.6532</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.3707</v>
+        <v>-0.218</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.8865</v>
+        <v>-0.9329</v>
       </c>
       <c r="E35" t="n">
-        <v>-1.111</v>
+        <v>-0.6532</v>
       </c>
       <c r="F35" t="n">
-        <v>-1.111</v>
+        <v>-0.6532</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-1.111</v>
+        <v>-0.6532</v>
       </c>
       <c r="I35" t="n">
-        <v>-1.111</v>
+        <v>-0.6532</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>107</v>
+        <v>247</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-1.111</v>
+        <v>-0.6532</v>
       </c>
       <c r="N35" t="n">
-        <v>107</v>
+        <v>247</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>n0thing</t>
+          <t>bondik</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-1.3449</v>
+        <v>-0.6902</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.4488</v>
+        <v>-0.2303</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.9797</v>
+        <v>-0.9496</v>
       </c>
       <c r="E36" t="n">
-        <v>-1.3449</v>
+        <v>-0.6902</v>
       </c>
       <c r="F36" t="n">
-        <v>-1.3449</v>
+        <v>-0.6902</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-1.3449</v>
+        <v>-0.6902</v>
       </c>
       <c r="I36" t="n">
-        <v>-1.3449</v>
+        <v>-0.6902</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>247</v>
+        <v>107</v>
       </c>
       <c r="L36" t="n">
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-1.3449</v>
+        <v>-0.6902</v>
       </c>
       <c r="N36" t="n">
-        <v>247</v>
+        <v>107</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>fejtZ</t>
+          <t>tarik</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-1.6074</v>
+        <v>-0.8092</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.5364</v>
+        <v>-0.27</v>
       </c>
       <c r="D37" t="n">
-        <v>-1.0843</v>
+        <v>-1.0033</v>
       </c>
       <c r="E37" t="n">
-        <v>-1.6074</v>
+        <v>-0.8092</v>
       </c>
       <c r="F37" t="n">
-        <v>-1.6074</v>
+        <v>-0.8092</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-1.6074</v>
+        <v>-0.8092</v>
       </c>
       <c r="I37" t="n">
-        <v>-1.6074</v>
+        <v>-0.8425</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>95</v>
+        <v>369</v>
       </c>
       <c r="L37" t="n">
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>-1.6074</v>
+        <v>-0.8425</v>
       </c>
       <c r="N37" t="n">
-        <v>95</v>
+        <v>369</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>tarik</t>
+          <t>fejtZ</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-1.6824</v>
+        <v>-1.1899</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.5614</v>
+        <v>-0.3971</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.1142</v>
+        <v>-1.1752</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.6824</v>
+        <v>-1.1899</v>
       </c>
       <c r="F38" t="n">
-        <v>-1.6824</v>
+        <v>-1.1899</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>-1.6824</v>
+        <v>-1.1899</v>
       </c>
       <c r="I38" t="n">
-        <v>-1.6965</v>
+        <v>-1.1899</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>369</v>
+        <v>95</v>
       </c>
       <c r="L38" t="n">
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>-1.6965</v>
+        <v>-1.1899</v>
       </c>
       <c r="N38" t="n">
-        <v>369</v>
+        <v>95</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>ub1que</t>
+          <t>freakazoid</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.6885</v>
+        <v>-1.218</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.5635</v>
+        <v>-0.4065</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.1166</v>
+        <v>-1.1879</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.6885</v>
+        <v>-1.218</v>
       </c>
       <c r="F39" t="n">
-        <v>-1.6885</v>
+        <v>-1.218</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>-1.6885</v>
+        <v>-1.218</v>
       </c>
       <c r="I39" t="n">
-        <v>-1.6885</v>
+        <v>-1.218</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>95</v>
+        <v>247</v>
       </c>
       <c r="L39" t="n">
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>-1.6885</v>
+        <v>-1.218</v>
       </c>
       <c r="N39" t="n">
-        <v>95</v>
+        <v>247</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>jmqa</t>
+          <t>ub1que</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-1.832</v>
+        <v>-1.3085</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.6114000000000001</v>
+        <v>-0.4367</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.1738</v>
+        <v>-1.2287</v>
       </c>
       <c r="E40" t="n">
-        <v>-1.832</v>
+        <v>-1.3085</v>
       </c>
       <c r="F40" t="n">
-        <v>-1.832</v>
+        <v>-1.3085</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>-1.832</v>
+        <v>-1.3085</v>
       </c>
       <c r="I40" t="n">
-        <v>-1.832</v>
+        <v>-1.3085</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -2277,7 +2277,7 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>-1.832</v>
+        <v>-1.3085</v>
       </c>
       <c r="N40" t="n">
         <v>95</v>
@@ -2286,47 +2286,47 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>freakazoid</t>
+          <t>jmqa</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-2.1287</v>
+        <v>-1.3719</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.7104</v>
+        <v>-0.4578</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.292</v>
+        <v>-1.2574</v>
       </c>
       <c r="E41" t="n">
-        <v>-2.1287</v>
+        <v>-1.3719</v>
       </c>
       <c r="F41" t="n">
-        <v>-2.1287</v>
+        <v>-1.3719</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>-2.1287</v>
+        <v>-1.3719</v>
       </c>
       <c r="I41" t="n">
-        <v>-2.1287</v>
+        <v>-1.3719</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>247</v>
+        <v>95</v>
       </c>
       <c r="L41" t="n">
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>-2.1287</v>
+        <v>-1.3719</v>
       </c>
       <c r="N41" t="n">
-        <v>247</v>
+        <v>95</v>
       </c>
     </row>
   </sheetData>
@@ -2429,10 +2429,10 @@
         <v>1.93</v>
       </c>
       <c r="I2" t="n">
-        <v>1.8508</v>
+        <v>1.5726</v>
       </c>
       <c r="J2" t="n">
-        <v>37.016</v>
+        <v>31.452</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>1.84</v>
       </c>
       <c r="I3" t="n">
-        <v>1.6965</v>
+        <v>1.4729</v>
       </c>
       <c r="J3" t="n">
-        <v>33.93</v>
+        <v>29.458</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>1.62</v>
       </c>
       <c r="I4" t="n">
-        <v>1.2857</v>
+        <v>1.2254</v>
       </c>
       <c r="J4" t="n">
-        <v>25.714</v>
+        <v>24.508</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>1.33</v>
       </c>
       <c r="I5" t="n">
-        <v>0.6568000000000001</v>
+        <v>0.7912</v>
       </c>
       <c r="J5" t="n">
-        <v>13.136</v>
+        <v>15.824</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>1.1</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1244</v>
+        <v>0.2236</v>
       </c>
       <c r="J6" t="n">
-        <v>2.488</v>
+        <v>4.472</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>0.74</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.2873</v>
+        <v>-0.2413</v>
       </c>
       <c r="J7" t="n">
-        <v>-5.746</v>
+        <v>-4.826</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.3653</v>
+        <v>-0.2924</v>
       </c>
       <c r="J8" t="n">
-        <v>-7.306</v>
+        <v>-5.848</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>0.64</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.4469</v>
+        <v>-0.3404</v>
       </c>
       <c r="J9" t="n">
-        <v>-8.938000000000001</v>
+        <v>-6.808</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>0.54</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.6264</v>
+        <v>-0.4302</v>
       </c>
       <c r="J10" t="n">
-        <v>-12.528</v>
+        <v>-8.603999999999999</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>0.46</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.7393</v>
+        <v>-0.5054</v>
       </c>
       <c r="J11" t="n">
-        <v>-14.786</v>
+        <v>-10.108</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>1.62</v>
       </c>
       <c r="I12" t="n">
-        <v>1.4285</v>
+        <v>1.2781</v>
       </c>
       <c r="J12" t="n">
-        <v>32.8555</v>
+        <v>29.3963</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>1.24</v>
       </c>
       <c r="I13" t="n">
-        <v>0.5858</v>
+        <v>0.6454</v>
       </c>
       <c r="J13" t="n">
-        <v>13.4734</v>
+        <v>14.8442</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>1.21</v>
       </c>
       <c r="I14" t="n">
-        <v>0.5053</v>
+        <v>0.5749</v>
       </c>
       <c r="J14" t="n">
-        <v>11.6219</v>
+        <v>13.2227</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>1.14</v>
       </c>
       <c r="I15" t="n">
-        <v>0.3211</v>
+        <v>0.3987</v>
       </c>
       <c r="J15" t="n">
-        <v>7.3853</v>
+        <v>9.1701</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>1.07</v>
       </c>
       <c r="I16" t="n">
-        <v>0.124</v>
+        <v>0.2014</v>
       </c>
       <c r="J16" t="n">
-        <v>2.852</v>
+        <v>4.6322</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>1.1</v>
       </c>
       <c r="I17" t="n">
-        <v>0.2886</v>
+        <v>0.3013</v>
       </c>
       <c r="J17" t="n">
-        <v>6.6378</v>
+        <v>6.9299</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>1</v>
       </c>
       <c r="I18" t="n">
-        <v>0.0772</v>
+        <v>0.0398</v>
       </c>
       <c r="J18" t="n">
-        <v>1.7756</v>
+        <v>0.9154</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>0.75</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.4111</v>
+        <v>-0.2684</v>
       </c>
       <c r="J19" t="n">
-        <v>-9.455299999999999</v>
+        <v>-6.1732</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>0.75</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.4111</v>
+        <v>-0.2684</v>
       </c>
       <c r="J20" t="n">
-        <v>-9.455299999999999</v>
+        <v>-6.1732</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>0.61</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.6048</v>
+        <v>-0.4012</v>
       </c>
       <c r="J21" t="n">
-        <v>-13.9104</v>
+        <v>-9.227600000000001</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>1.43</v>
       </c>
       <c r="I22" t="n">
-        <v>1.1108</v>
+        <v>1.0658</v>
       </c>
       <c r="J22" t="n">
-        <v>32.2132</v>
+        <v>30.9082</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>1.17</v>
       </c>
       <c r="I23" t="n">
-        <v>0.4999</v>
+        <v>0.4977</v>
       </c>
       <c r="J23" t="n">
-        <v>14.4971</v>
+        <v>14.4333</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>1.05</v>
       </c>
       <c r="I24" t="n">
-        <v>0.1127</v>
+        <v>0.1676</v>
       </c>
       <c r="J24" t="n">
-        <v>3.2683</v>
+        <v>4.8604</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>1.04</v>
       </c>
       <c r="I25" t="n">
-        <v>0.0784</v>
+        <v>0.1346</v>
       </c>
       <c r="J25" t="n">
-        <v>2.2736</v>
+        <v>3.9034</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>1</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.09810000000000001</v>
+        <v>-0.0328</v>
       </c>
       <c r="J26" t="n">
-        <v>-2.8449</v>
+        <v>-0.9512</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>1.01</v>
       </c>
       <c r="I27" t="n">
-        <v>0.0645</v>
+        <v>0.0461</v>
       </c>
       <c r="J27" t="n">
-        <v>1.8705</v>
+        <v>1.3369</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>1.01</v>
       </c>
       <c r="I28" t="n">
-        <v>0.0645</v>
+        <v>0.0461</v>
       </c>
       <c r="J28" t="n">
-        <v>1.8705</v>
+        <v>1.3369</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>0.97</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.058</v>
+        <v>-0.0467</v>
       </c>
       <c r="J29" t="n">
-        <v>-1.682</v>
+        <v>-1.3543</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>0.96</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.0824</v>
+        <v>-0.0597</v>
       </c>
       <c r="J30" t="n">
-        <v>-2.3896</v>
+        <v>-1.7313</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>0.82</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.3422</v>
+        <v>-0.2134</v>
       </c>
       <c r="J31" t="n">
-        <v>-9.9238</v>
+        <v>-6.1886</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>1.87</v>
       </c>
       <c r="I32" t="n">
-        <v>1.7827</v>
+        <v>1.5224</v>
       </c>
       <c r="J32" t="n">
-        <v>33.8713</v>
+        <v>28.9256</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>1.54</v>
       </c>
       <c r="I33" t="n">
-        <v>1.1665</v>
+        <v>1.1423</v>
       </c>
       <c r="J33" t="n">
-        <v>22.1635</v>
+        <v>21.7037</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>1.46</v>
       </c>
       <c r="I34" t="n">
-        <v>0.9734</v>
+        <v>1.0486</v>
       </c>
       <c r="J34" t="n">
-        <v>18.4946</v>
+        <v>19.9234</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>1.27</v>
       </c>
       <c r="I35" t="n">
-        <v>0.5526</v>
+        <v>0.6715</v>
       </c>
       <c r="J35" t="n">
-        <v>10.4994</v>
+        <v>12.7585</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>1.25</v>
       </c>
       <c r="I36" t="n">
-        <v>0.5076000000000001</v>
+        <v>0.6246</v>
       </c>
       <c r="J36" t="n">
-        <v>9.644399999999999</v>
+        <v>11.8674</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>0.79</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.2438</v>
+        <v>-0.2056</v>
       </c>
       <c r="J37" t="n">
-        <v>-4.6322</v>
+        <v>-3.9064</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>0.78</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.2597</v>
+        <v>-0.216</v>
       </c>
       <c r="J38" t="n">
-        <v>-4.9343</v>
+        <v>-4.104</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>0.64</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.5057</v>
+        <v>-0.3486</v>
       </c>
       <c r="J39" t="n">
-        <v>-9.6083</v>
+        <v>-6.6234</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>0.62</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.537</v>
+        <v>-0.367</v>
       </c>
       <c r="J40" t="n">
-        <v>-10.203</v>
+        <v>-6.973</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.6244</v>
+        <v>-0.4229</v>
       </c>
       <c r="J41" t="n">
-        <v>-11.8636</v>
+        <v>-8.0351</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>2.14</v>
       </c>
       <c r="I42" t="n">
-        <v>2.0593</v>
+        <v>1.806</v>
       </c>
       <c r="J42" t="n">
-        <v>41.186</v>
+        <v>36.12</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>1.68</v>
       </c>
       <c r="I43" t="n">
-        <v>1.4124</v>
+        <v>1.2957</v>
       </c>
       <c r="J43" t="n">
-        <v>28.248</v>
+        <v>25.914</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>1.52</v>
       </c>
       <c r="I44" t="n">
-        <v>1.0654</v>
+        <v>1.114</v>
       </c>
       <c r="J44" t="n">
-        <v>21.308</v>
+        <v>22.28</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>1.28</v>
       </c>
       <c r="I45" t="n">
-        <v>0.5542</v>
+        <v>0.6812</v>
       </c>
       <c r="J45" t="n">
-        <v>11.084</v>
+        <v>13.624</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>1.11</v>
       </c>
       <c r="I46" t="n">
-        <v>0.1545</v>
+        <v>0.2551</v>
       </c>
       <c r="J46" t="n">
-        <v>3.09</v>
+        <v>5.102</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>0.86</v>
       </c>
       <c r="I47" t="n">
-        <v>-0.07389999999999999</v>
+        <v>-0.0886</v>
       </c>
       <c r="J47" t="n">
-        <v>-1.478</v>
+        <v>-1.772</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>0.77</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.2168</v>
+        <v>-0.1945</v>
       </c>
       <c r="J48" t="n">
-        <v>-4.336</v>
+        <v>-3.89</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>0.44</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.7518</v>
+        <v>-0.5163</v>
       </c>
       <c r="J49" t="n">
-        <v>-15.036</v>
+        <v>-10.326</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>0.4</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.8062</v>
+        <v>-0.5547</v>
       </c>
       <c r="J50" t="n">
-        <v>-16.124</v>
+        <v>-11.094</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.39</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.8195</v>
+        <v>-0.5643</v>
       </c>
       <c r="J51" t="n">
-        <v>-16.39</v>
+        <v>-11.286</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.71</v>
       </c>
       <c r="I52" t="n">
-        <v>1.5859</v>
+        <v>1.3828</v>
       </c>
       <c r="J52" t="n">
-        <v>41.2334</v>
+        <v>35.9528</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>1.42</v>
       </c>
       <c r="I53" t="n">
-        <v>1.0191</v>
+        <v>1.0196</v>
       </c>
       <c r="J53" t="n">
-        <v>26.4966</v>
+        <v>26.5096</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>1.15</v>
       </c>
       <c r="I54" t="n">
-        <v>0.3388</v>
+        <v>0.4204</v>
       </c>
       <c r="J54" t="n">
-        <v>8.8088</v>
+        <v>10.9304</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>1.14</v>
       </c>
       <c r="I55" t="n">
-        <v>0.3124</v>
+        <v>0.3941</v>
       </c>
       <c r="J55" t="n">
-        <v>8.122400000000001</v>
+        <v>10.2466</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>0.96</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.319</v>
+        <v>-0.2355</v>
       </c>
       <c r="J56" t="n">
-        <v>-8.294</v>
+        <v>-6.123</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>0.95</v>
       </c>
       <c r="I57" t="n">
-        <v>-0.0346</v>
+        <v>-0.0529</v>
       </c>
       <c r="J57" t="n">
-        <v>-0.8996</v>
+        <v>-1.3754</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>0.89</v>
       </c>
       <c r="I58" t="n">
-        <v>-0.1455</v>
+        <v>-0.125</v>
       </c>
       <c r="J58" t="n">
-        <v>-3.783</v>
+        <v>-3.25</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>0.78</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.3517</v>
+        <v>-0.2359</v>
       </c>
       <c r="J59" t="n">
-        <v>-9.1442</v>
+        <v>-6.1334</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>0.74</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.4154</v>
+        <v>-0.2743</v>
       </c>
       <c r="J60" t="n">
-        <v>-10.8004</v>
+        <v>-7.1318</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>0.71</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.4601</v>
+        <v>-0.303</v>
       </c>
       <c r="J61" t="n">
-        <v>-11.9626</v>
+        <v>-7.878</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>1.33</v>
       </c>
       <c r="I62" t="n">
-        <v>0.9326</v>
+        <v>0.9109</v>
       </c>
       <c r="J62" t="n">
-        <v>27.978</v>
+        <v>27.327</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>1.16</v>
       </c>
       <c r="I63" t="n">
-        <v>0.5201</v>
+        <v>0.49</v>
       </c>
       <c r="J63" t="n">
-        <v>15.603</v>
+        <v>14.7</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>1.1</v>
       </c>
       <c r="I64" t="n">
-        <v>0.3453</v>
+        <v>0.3284</v>
       </c>
       <c r="J64" t="n">
-        <v>10.359</v>
+        <v>9.852</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>1.06</v>
       </c>
       <c r="I65" t="n">
-        <v>0.1955</v>
+        <v>0.214</v>
       </c>
       <c r="J65" t="n">
-        <v>5.865</v>
+        <v>6.42</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>0.7</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.9255</v>
+        <v>-0.8932</v>
       </c>
       <c r="J66" t="n">
-        <v>-27.765</v>
+        <v>-26.796</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>1.21</v>
       </c>
       <c r="I67" t="n">
-        <v>0.3689</v>
+        <v>0.4332</v>
       </c>
       <c r="J67" t="n">
-        <v>11.067</v>
+        <v>12.996</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>1.15</v>
       </c>
       <c r="I68" t="n">
-        <v>0.2777</v>
+        <v>0.3247</v>
       </c>
       <c r="J68" t="n">
-        <v>8.331</v>
+        <v>9.741</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>1.07</v>
       </c>
       <c r="I69" t="n">
-        <v>0.1251</v>
+        <v>0.1705</v>
       </c>
       <c r="J69" t="n">
-        <v>3.753</v>
+        <v>5.115</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>1</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.0409</v>
+        <v>-0.0072</v>
       </c>
       <c r="J70" t="n">
-        <v>-1.227</v>
+        <v>-0.216</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>0.99</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.07539999999999999</v>
+        <v>-0.0283</v>
       </c>
       <c r="J71" t="n">
-        <v>-2.262</v>
+        <v>-0.849</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>1.23</v>
       </c>
       <c r="I72" t="n">
-        <v>0.4471</v>
+        <v>0.5158</v>
       </c>
       <c r="J72" t="n">
-        <v>12.9659</v>
+        <v>14.9582</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>1.04</v>
       </c>
       <c r="I73" t="n">
-        <v>0.1404</v>
+        <v>0.1299</v>
       </c>
       <c r="J73" t="n">
-        <v>4.0716</v>
+        <v>3.7671</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>1.03</v>
       </c>
       <c r="I74" t="n">
-        <v>0.1192</v>
+        <v>0.105</v>
       </c>
       <c r="J74" t="n">
-        <v>3.4568</v>
+        <v>3.045</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>0.71</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.495</v>
+        <v>-0.3197</v>
       </c>
       <c r="J75" t="n">
-        <v>-14.355</v>
+        <v>-9.2713</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.5217000000000001</v>
+        <v>-0.3387</v>
       </c>
       <c r="J76" t="n">
-        <v>-15.1293</v>
+        <v>-9.8223</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>1.63</v>
       </c>
       <c r="I77" t="n">
-        <v>1.4808</v>
+        <v>1.3099</v>
       </c>
       <c r="J77" t="n">
-        <v>42.9432</v>
+        <v>37.9871</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>1.25</v>
       </c>
       <c r="I78" t="n">
-        <v>0.679</v>
+        <v>0.6808</v>
       </c>
       <c r="J78" t="n">
-        <v>19.691</v>
+        <v>19.7432</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>1.11</v>
       </c>
       <c r="I79" t="n">
-        <v>0.2725</v>
+        <v>0.3336</v>
       </c>
       <c r="J79" t="n">
-        <v>7.9025</v>
+        <v>9.6744</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>1.01</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.0594</v>
+        <v>0.0098</v>
       </c>
       <c r="J80" t="n">
-        <v>-1.7226</v>
+        <v>0.2842</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>0.93</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.3858</v>
+        <v>-0.3104</v>
       </c>
       <c r="J81" t="n">
-        <v>-11.1882</v>
+        <v>-9.0016</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>1.29</v>
       </c>
       <c r="I82" t="n">
-        <v>0.4516</v>
+        <v>0.3918</v>
       </c>
       <c r="J82" t="n">
-        <v>13.0964</v>
+        <v>11.3622</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>1.26</v>
       </c>
       <c r="I83" t="n">
-        <v>0.4103</v>
+        <v>0.3563</v>
       </c>
       <c r="J83" t="n">
-        <v>11.8987</v>
+        <v>10.3327</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>1.22</v>
       </c>
       <c r="I84" t="n">
-        <v>0.3522</v>
+        <v>0.3084</v>
       </c>
       <c r="J84" t="n">
-        <v>10.2138</v>
+        <v>8.9436</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>1.08</v>
       </c>
       <c r="I85" t="n">
-        <v>0.1103</v>
+        <v>0.1267</v>
       </c>
       <c r="J85" t="n">
-        <v>3.1987</v>
+        <v>3.6743</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>1</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.06419999999999999</v>
+        <v>-0.0158</v>
       </c>
       <c r="J86" t="n">
-        <v>-1.8618</v>
+        <v>-0.4582</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>1.5</v>
       </c>
       <c r="I87" t="n">
-        <v>0.7959000000000001</v>
+        <v>0.7685</v>
       </c>
       <c r="J87" t="n">
-        <v>23.0811</v>
+        <v>22.2865</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>0.9</v>
       </c>
       <c r="I88" t="n">
-        <v>-0.1888</v>
+        <v>-0.125</v>
       </c>
       <c r="J88" t="n">
-        <v>-5.4752</v>
+        <v>-3.625</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>0.79</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.3741</v>
+        <v>-0.2381</v>
       </c>
       <c r="J89" t="n">
-        <v>-10.8489</v>
+        <v>-6.9049</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>0.72</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.4744</v>
+        <v>-0.3063</v>
       </c>
       <c r="J90" t="n">
-        <v>-13.7576</v>
+        <v>-8.8827</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>0.64</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.5806</v>
+        <v>-0.382</v>
       </c>
       <c r="J91" t="n">
-        <v>-16.8374</v>
+        <v>-11.078</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>1.08</v>
       </c>
       <c r="I92" t="n">
-        <v>0.2627</v>
+        <v>0.2665</v>
       </c>
       <c r="J92" t="n">
-        <v>6.3048</v>
+        <v>6.396</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>0.87</v>
       </c>
       <c r="I93" t="n">
-        <v>-0.1849</v>
+        <v>-0.148</v>
       </c>
       <c r="J93" t="n">
-        <v>-4.4376</v>
+        <v>-3.552</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>0.76</v>
       </c>
       <c r="I94" t="n">
-        <v>-0.3879</v>
+        <v>-0.2561</v>
       </c>
       <c r="J94" t="n">
-        <v>-9.3096</v>
+        <v>-6.1464</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>0.75</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.4034</v>
+        <v>-0.2658</v>
       </c>
       <c r="J95" t="n">
-        <v>-9.6816</v>
+        <v>-6.3792</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>0.65</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.5468</v>
+        <v>-0.361</v>
       </c>
       <c r="J96" t="n">
-        <v>-13.1232</v>
+        <v>-8.664</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1.58</v>
       </c>
       <c r="I97" t="n">
-        <v>1.3703</v>
+        <v>1.2382</v>
       </c>
       <c r="J97" t="n">
-        <v>32.8872</v>
+        <v>29.7168</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>1.2</v>
       </c>
       <c r="I98" t="n">
-        <v>0.5053</v>
+        <v>0.5578</v>
       </c>
       <c r="J98" t="n">
-        <v>12.1272</v>
+        <v>13.3872</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>1.14</v>
       </c>
       <c r="I99" t="n">
-        <v>0.3398</v>
+        <v>0.4072</v>
       </c>
       <c r="J99" t="n">
-        <v>8.155200000000001</v>
+        <v>9.7728</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>1.14</v>
       </c>
       <c r="I100" t="n">
-        <v>0.3398</v>
+        <v>0.4072</v>
       </c>
       <c r="J100" t="n">
-        <v>8.155200000000001</v>
+        <v>9.7728</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>1.03</v>
       </c>
       <c r="I101" t="n">
-        <v>0.007900000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="J101" t="n">
-        <v>0.1896</v>
+        <v>1.92</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.33</v>
       </c>
       <c r="I102" t="n">
-        <v>0.9748</v>
+        <v>0.9468</v>
       </c>
       <c r="J102" t="n">
-        <v>29.244</v>
+        <v>28.404</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>1.19</v>
       </c>
       <c r="I103" t="n">
-        <v>0.6447000000000001</v>
+        <v>0.5968</v>
       </c>
       <c r="J103" t="n">
-        <v>19.341</v>
+        <v>17.904</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>0.89</v>
       </c>
       <c r="I104" t="n">
-        <v>-0.4238</v>
+        <v>-0.3763</v>
       </c>
       <c r="J104" t="n">
-        <v>-12.714</v>
+        <v>-11.289</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>0.85</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.5358000000000001</v>
+        <v>-0.4872</v>
       </c>
       <c r="J105" t="n">
-        <v>-16.074</v>
+        <v>-14.616</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.72</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.8582</v>
+        <v>-0.8231000000000001</v>
       </c>
       <c r="J106" t="n">
-        <v>-25.746</v>
+        <v>-24.693</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.46</v>
       </c>
       <c r="I107" t="n">
-        <v>0.6768999999999999</v>
+        <v>0.8361</v>
       </c>
       <c r="J107" t="n">
-        <v>20.307</v>
+        <v>25.083</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>1.35</v>
       </c>
       <c r="I108" t="n">
-        <v>0.5432</v>
+        <v>0.6592</v>
       </c>
       <c r="J108" t="n">
-        <v>16.296</v>
+        <v>19.776</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>1.21</v>
       </c>
       <c r="I109" t="n">
-        <v>0.3533</v>
+        <v>0.4235</v>
       </c>
       <c r="J109" t="n">
-        <v>10.599</v>
+        <v>12.705</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>0.89</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.2762</v>
+        <v>-0.1592</v>
       </c>
       <c r="J110" t="n">
-        <v>-8.286</v>
+        <v>-4.776</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>0.73</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.5019</v>
+        <v>-0.321</v>
       </c>
       <c r="J111" t="n">
-        <v>-15.057</v>
+        <v>-9.630000000000001</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>1.18</v>
       </c>
       <c r="I112" t="n">
-        <v>0.4639</v>
+        <v>0.4153</v>
       </c>
       <c r="J112" t="n">
-        <v>10.2058</v>
+        <v>9.1366</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>0.84</v>
       </c>
       <c r="I113" t="n">
-        <v>-0.1867</v>
+        <v>-0.1627</v>
       </c>
       <c r="J113" t="n">
-        <v>-4.1074</v>
+        <v>-3.5794</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>0.63</v>
       </c>
       <c r="I114" t="n">
-        <v>-0.5425</v>
+        <v>-0.3651</v>
       </c>
       <c r="J114" t="n">
-        <v>-11.935</v>
+        <v>-8.0322</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>0.54</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.6663</v>
+        <v>-0.4492</v>
       </c>
       <c r="J115" t="n">
-        <v>-14.6586</v>
+        <v>-9.882400000000001</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>0.43</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.8057</v>
+        <v>-0.5517</v>
       </c>
       <c r="J116" t="n">
-        <v>-17.7254</v>
+        <v>-12.1374</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>1.91</v>
       </c>
       <c r="I117" t="n">
-        <v>1.0811</v>
+        <v>0.9913999999999999</v>
       </c>
       <c r="J117" t="n">
-        <v>23.7842</v>
+        <v>21.8108</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>1.58</v>
       </c>
       <c r="I118" t="n">
-        <v>0.7378</v>
+        <v>0.6733</v>
       </c>
       <c r="J118" t="n">
-        <v>16.2316</v>
+        <v>14.8126</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>1.34</v>
       </c>
       <c r="I119" t="n">
-        <v>0.4253</v>
+        <v>0.4244</v>
       </c>
       <c r="J119" t="n">
-        <v>9.3566</v>
+        <v>9.3368</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>1.32</v>
       </c>
       <c r="I120" t="n">
-        <v>0.3989</v>
+        <v>0.4023</v>
       </c>
       <c r="J120" t="n">
-        <v>8.7758</v>
+        <v>8.8506</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>0.87</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.3466</v>
+        <v>-0.2052</v>
       </c>
       <c r="J121" t="n">
-        <v>-7.6252</v>
+        <v>-4.5144</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.67</v>
       </c>
       <c r="I122" t="n">
-        <v>1.5573</v>
+        <v>1.3611</v>
       </c>
       <c r="J122" t="n">
-        <v>40.4898</v>
+        <v>35.3886</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>1.15</v>
       </c>
       <c r="I123" t="n">
-        <v>0.39</v>
+        <v>0.4407</v>
       </c>
       <c r="J123" t="n">
-        <v>10.14</v>
+        <v>11.4582</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>1.14</v>
       </c>
       <c r="I124" t="n">
-        <v>0.3612</v>
+        <v>0.4149</v>
       </c>
       <c r="J124" t="n">
-        <v>9.3912</v>
+        <v>10.7874</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>1.07</v>
       </c>
       <c r="I125" t="n">
-        <v>0.1551</v>
+        <v>0.2193</v>
       </c>
       <c r="J125" t="n">
-        <v>4.0326</v>
+        <v>5.7018</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.88</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.525</v>
+        <v>-0.456</v>
       </c>
       <c r="J126" t="n">
-        <v>-13.65</v>
+        <v>-11.856</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.33</v>
       </c>
       <c r="I127" t="n">
-        <v>0.5810999999999999</v>
+        <v>0.6973</v>
       </c>
       <c r="J127" t="n">
-        <v>15.1086</v>
+        <v>18.1298</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>0.96</v>
       </c>
       <c r="I128" t="n">
-        <v>-0.0707</v>
+        <v>-0.0582</v>
       </c>
       <c r="J128" t="n">
-        <v>-1.8382</v>
+        <v>-1.5132</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>0.83</v>
       </c>
       <c r="I129" t="n">
-        <v>-0.3213</v>
+        <v>-0.201</v>
       </c>
       <c r="J129" t="n">
-        <v>-8.3538</v>
+        <v>-5.226</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>0.83</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.3213</v>
+        <v>-0.201</v>
       </c>
       <c r="J130" t="n">
-        <v>-8.3538</v>
+        <v>-5.226</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>0.73</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.4669</v>
+        <v>-0.3</v>
       </c>
       <c r="J131" t="n">
-        <v>-12.1394</v>
+        <v>-7.8</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>1.1</v>
       </c>
       <c r="I132" t="n">
-        <v>0.3535</v>
+        <v>0.3308</v>
       </c>
       <c r="J132" t="n">
-        <v>10.2515</v>
+        <v>9.5932</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>1.08</v>
       </c>
       <c r="I133" t="n">
-        <v>0.2883</v>
+        <v>0.2739</v>
       </c>
       <c r="J133" t="n">
-        <v>8.3607</v>
+        <v>7.9431</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>1.08</v>
       </c>
       <c r="I134" t="n">
-        <v>0.2883</v>
+        <v>0.2739</v>
       </c>
       <c r="J134" t="n">
-        <v>8.3607</v>
+        <v>7.9431</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>1.03</v>
       </c>
       <c r="I135" t="n">
-        <v>0.0902</v>
+        <v>0.1188</v>
       </c>
       <c r="J135" t="n">
-        <v>2.6158</v>
+        <v>3.4452</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>1.01</v>
       </c>
       <c r="I136" t="n">
-        <v>0.0043</v>
+        <v>0.0418</v>
       </c>
       <c r="J136" t="n">
-        <v>0.1247</v>
+        <v>1.2122</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>1.25</v>
       </c>
       <c r="I137" t="n">
-        <v>0.4564</v>
+        <v>0.532</v>
       </c>
       <c r="J137" t="n">
-        <v>13.2356</v>
+        <v>15.428</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>0.95</v>
       </c>
       <c r="I138" t="n">
-        <v>-0.132</v>
+        <v>-0.0751</v>
       </c>
       <c r="J138" t="n">
-        <v>-3.828</v>
+        <v>-2.1779</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I139" t="n">
-        <v>-0.1521</v>
+        <v>-0.0873</v>
       </c>
       <c r="J139" t="n">
-        <v>-4.4109</v>
+        <v>-2.5317</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>0.93</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.1714</v>
+        <v>-0.0992</v>
       </c>
       <c r="J140" t="n">
-        <v>-4.9706</v>
+        <v>-2.8768</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>0.89</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.2423</v>
+        <v>-0.1444</v>
       </c>
       <c r="J141" t="n">
-        <v>-7.0267</v>
+        <v>-4.1876</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.35</v>
       </c>
       <c r="I142" t="n">
-        <v>0.9419</v>
+        <v>0.9297</v>
       </c>
       <c r="J142" t="n">
-        <v>26.3732</v>
+        <v>26.0316</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>1.29</v>
       </c>
       <c r="I143" t="n">
-        <v>0.8062</v>
+        <v>0.7907</v>
       </c>
       <c r="J143" t="n">
-        <v>22.5736</v>
+        <v>22.1396</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>1.17</v>
       </c>
       <c r="I144" t="n">
-        <v>0.5031</v>
+        <v>0.4986</v>
       </c>
       <c r="J144" t="n">
-        <v>14.0868</v>
+        <v>13.9608</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>0.96</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.2713</v>
+        <v>-0.1999</v>
       </c>
       <c r="J145" t="n">
-        <v>-7.5964</v>
+        <v>-5.5972</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>0.9</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.4549</v>
+        <v>-0.3864</v>
       </c>
       <c r="J146" t="n">
-        <v>-12.7372</v>
+        <v>-10.8192</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>1.74</v>
       </c>
       <c r="I147" t="n">
-        <v>1.0053</v>
+        <v>1.1774</v>
       </c>
       <c r="J147" t="n">
-        <v>28.1484</v>
+        <v>32.9672</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>1.15</v>
       </c>
       <c r="I148" t="n">
-        <v>0.287</v>
+        <v>0.3297</v>
       </c>
       <c r="J148" t="n">
-        <v>8.036</v>
+        <v>9.2316</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>0.89</v>
       </c>
       <c r="I149" t="n">
-        <v>-0.2612</v>
+        <v>-0.1519</v>
       </c>
       <c r="J149" t="n">
-        <v>-7.3136</v>
+        <v>-4.2532</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>0.8</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.3964</v>
+        <v>-0.2458</v>
       </c>
       <c r="J150" t="n">
-        <v>-11.0992</v>
+        <v>-6.8824</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>0.72</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.5044999999999999</v>
+        <v>-0.3237</v>
       </c>
       <c r="J151" t="n">
-        <v>-14.126</v>
+        <v>-9.063599999999999</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>1.05</v>
       </c>
       <c r="I152" t="n">
-        <v>0.3182</v>
+        <v>0.3602</v>
       </c>
       <c r="J152" t="n">
-        <v>6.0458</v>
+        <v>6.8438</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>0.61</v>
       </c>
       <c r="I153" t="n">
-        <v>-0.4839</v>
+        <v>-0.3644</v>
       </c>
       <c r="J153" t="n">
-        <v>-9.194100000000001</v>
+        <v>-6.9236</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>0.47</v>
       </c>
       <c r="I154" t="n">
-        <v>-0.7184</v>
+        <v>-0.4921</v>
       </c>
       <c r="J154" t="n">
-        <v>-13.6496</v>
+        <v>-9.3499</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>0.46</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.7323</v>
+        <v>-0.5016</v>
       </c>
       <c r="J155" t="n">
-        <v>-13.9137</v>
+        <v>-9.5304</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>0.38</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.8389</v>
+        <v>-0.578</v>
       </c>
       <c r="J156" t="n">
-        <v>-15.9391</v>
+        <v>-10.982</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>1.61</v>
       </c>
       <c r="I157" t="n">
-        <v>1.3222</v>
+        <v>1.2284</v>
       </c>
       <c r="J157" t="n">
-        <v>25.1218</v>
+        <v>23.3396</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>1.58</v>
       </c>
       <c r="I158" t="n">
-        <v>1.2632</v>
+        <v>1.1931</v>
       </c>
       <c r="J158" t="n">
-        <v>24.0008</v>
+        <v>22.6689</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>1.48</v>
       </c>
       <c r="I159" t="n">
-        <v>1.0537</v>
+        <v>1.0746</v>
       </c>
       <c r="J159" t="n">
-        <v>20.0203</v>
+        <v>20.4174</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>1.45</v>
       </c>
       <c r="I160" t="n">
-        <v>0.9797</v>
+        <v>1.0379</v>
       </c>
       <c r="J160" t="n">
-        <v>18.6143</v>
+        <v>19.7201</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>1.12</v>
       </c>
       <c r="I161" t="n">
-        <v>0.2036</v>
+        <v>0.3023</v>
       </c>
       <c r="J161" t="n">
-        <v>3.8684</v>
+        <v>5.7437</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>1.11</v>
       </c>
       <c r="I162" t="n">
-        <v>0.2569</v>
+        <v>0.2754</v>
       </c>
       <c r="J162" t="n">
-        <v>6.9363</v>
+        <v>7.4358</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>1.07</v>
       </c>
       <c r="I163" t="n">
-        <v>0.1873</v>
+        <v>0.1913</v>
       </c>
       <c r="J163" t="n">
-        <v>5.0571</v>
+        <v>5.1651</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>0.93</v>
       </c>
       <c r="I164" t="n">
-        <v>-0.1614</v>
+        <v>-0.0968</v>
       </c>
       <c r="J164" t="n">
-        <v>-4.3578</v>
+        <v>-2.6136</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>0.9</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.2169</v>
+        <v>-0.1307</v>
       </c>
       <c r="J165" t="n">
-        <v>-5.8563</v>
+        <v>-3.5289</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>0.83</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.331</v>
+        <v>-0.2049</v>
       </c>
       <c r="J166" t="n">
-        <v>-8.936999999999999</v>
+        <v>-5.5323</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>1.44</v>
       </c>
       <c r="I167" t="n">
-        <v>1.1548</v>
+        <v>1.0916</v>
       </c>
       <c r="J167" t="n">
-        <v>31.1796</v>
+        <v>29.4732</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>1.33</v>
       </c>
       <c r="I168" t="n">
-        <v>0.9193</v>
+        <v>0.9005</v>
       </c>
       <c r="J168" t="n">
-        <v>24.8211</v>
+        <v>24.3135</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>1.16</v>
       </c>
       <c r="I169" t="n">
-        <v>0.504</v>
+        <v>0.483</v>
       </c>
       <c r="J169" t="n">
-        <v>13.608</v>
+        <v>13.041</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>0.82</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.6516</v>
+        <v>-0.5958</v>
       </c>
       <c r="J170" t="n">
-        <v>-17.5932</v>
+        <v>-16.0866</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>0.72</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.8871</v>
+        <v>-0.8502999999999999</v>
       </c>
       <c r="J171" t="n">
-        <v>-23.9517</v>
+        <v>-22.9581</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>1.03</v>
       </c>
       <c r="I172" t="n">
-        <v>0.164</v>
+        <v>0.142</v>
       </c>
       <c r="J172" t="n">
-        <v>4.428</v>
+        <v>3.834</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>0.88</v>
       </c>
       <c r="I173" t="n">
-        <v>-0.1713</v>
+        <v>-0.1384</v>
       </c>
       <c r="J173" t="n">
-        <v>-4.6251</v>
+        <v>-3.7368</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>0.8</v>
       </c>
       <c r="I174" t="n">
-        <v>-0.3264</v>
+        <v>-0.2184</v>
       </c>
       <c r="J174" t="n">
-        <v>-8.812799999999999</v>
+        <v>-5.8968</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>0.78</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.3596</v>
+        <v>-0.2378</v>
       </c>
       <c r="J175" t="n">
-        <v>-9.709199999999999</v>
+        <v>-6.4206</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>0.66</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.5354</v>
+        <v>-0.3527</v>
       </c>
       <c r="J176" t="n">
-        <v>-14.4558</v>
+        <v>-9.5229</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>1.35</v>
       </c>
       <c r="I177" t="n">
-        <v>0.8944</v>
+        <v>0.9006999999999999</v>
       </c>
       <c r="J177" t="n">
-        <v>24.1488</v>
+        <v>24.3189</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>1.33</v>
       </c>
       <c r="I178" t="n">
-        <v>0.849</v>
+        <v>0.8558</v>
       </c>
       <c r="J178" t="n">
-        <v>22.923</v>
+        <v>23.1066</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>1.16</v>
       </c>
       <c r="I179" t="n">
-        <v>0.3923</v>
+        <v>0.4581</v>
       </c>
       <c r="J179" t="n">
-        <v>10.5921</v>
+        <v>12.3687</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>1.15</v>
       </c>
       <c r="I180" t="n">
-        <v>0.365</v>
+        <v>0.4324</v>
       </c>
       <c r="J180" t="n">
-        <v>9.855</v>
+        <v>11.6748</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>1.12</v>
       </c>
       <c r="I181" t="n">
-        <v>0.2824</v>
+        <v>0.3528</v>
       </c>
       <c r="J181" t="n">
-        <v>7.6248</v>
+        <v>9.525600000000001</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>1.72</v>
       </c>
       <c r="I182" t="n">
-        <v>0.9706</v>
+        <v>0.8885</v>
       </c>
       <c r="J182" t="n">
-        <v>28.1474</v>
+        <v>25.7665</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>1.05</v>
       </c>
       <c r="I183" t="n">
-        <v>0.0762</v>
+        <v>0.08840000000000001</v>
       </c>
       <c r="J183" t="n">
-        <v>2.2098</v>
+        <v>2.5636</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I184" t="n">
-        <v>-0.1865</v>
+        <v>-0.09909999999999999</v>
       </c>
       <c r="J184" t="n">
-        <v>-5.4085</v>
+        <v>-2.8739</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>0.92</v>
       </c>
       <c r="I185" t="n">
-        <v>-0.2218</v>
+        <v>-0.1228</v>
       </c>
       <c r="J185" t="n">
-        <v>-6.4322</v>
+        <v>-3.5612</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>0.89</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.2712</v>
+        <v>-0.1567</v>
       </c>
       <c r="J186" t="n">
-        <v>-7.8648</v>
+        <v>-4.5443</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>1.39</v>
       </c>
       <c r="I187" t="n">
-        <v>0.6192</v>
+        <v>0.5762</v>
       </c>
       <c r="J187" t="n">
-        <v>17.9568</v>
+        <v>16.7098</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>1.19</v>
       </c>
       <c r="I188" t="n">
-        <v>0.3537</v>
+        <v>0.3118</v>
       </c>
       <c r="J188" t="n">
-        <v>10.2573</v>
+        <v>9.042199999999999</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>1.1</v>
       </c>
       <c r="I189" t="n">
-        <v>0.2102</v>
+        <v>0.181</v>
       </c>
       <c r="J189" t="n">
-        <v>6.0958</v>
+        <v>5.249</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>0.79</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.4073</v>
+        <v>-0.254</v>
       </c>
       <c r="J190" t="n">
-        <v>-11.8117</v>
+        <v>-7.366</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>0.75</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.4621</v>
+        <v>-0.2932</v>
       </c>
       <c r="J191" t="n">
-        <v>-13.4009</v>
+        <v>-8.502800000000001</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>1.32</v>
       </c>
       <c r="I192" t="n">
-        <v>0.569</v>
+        <v>0.6806</v>
       </c>
       <c r="J192" t="n">
-        <v>19.346</v>
+        <v>23.1404</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I193" t="n">
-        <v>-0.1145</v>
+        <v>-0.0825</v>
       </c>
       <c r="J193" t="n">
-        <v>-3.893</v>
+        <v>-2.805</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>0.83</v>
       </c>
       <c r="I194" t="n">
-        <v>-0.3206</v>
+        <v>-0.2008</v>
       </c>
       <c r="J194" t="n">
-        <v>-10.9004</v>
+        <v>-6.8272</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>0.79</v>
       </c>
       <c r="I195" t="n">
-        <v>-0.3813</v>
+        <v>-0.2411</v>
       </c>
       <c r="J195" t="n">
-        <v>-12.9642</v>
+        <v>-8.1974</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>0.79</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.3813</v>
+        <v>-0.2411</v>
       </c>
       <c r="J196" t="n">
-        <v>-12.9642</v>
+        <v>-8.1974</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>1.41</v>
       </c>
       <c r="I197" t="n">
-        <v>1.0533</v>
+        <v>1.0296</v>
       </c>
       <c r="J197" t="n">
-        <v>35.8122</v>
+        <v>35.0064</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>1.39</v>
       </c>
       <c r="I198" t="n">
-        <v>1.0108</v>
+        <v>0.9971</v>
       </c>
       <c r="J198" t="n">
-        <v>34.3672</v>
+        <v>33.9014</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>1.08</v>
       </c>
       <c r="I199" t="n">
-        <v>0.1929</v>
+        <v>0.2525</v>
       </c>
       <c r="J199" t="n">
-        <v>6.5586</v>
+        <v>8.585000000000001</v>
       </c>
     </row>
     <row r="200">
@@ -10349,10 +10349,10 @@
         <v>1.06</v>
       </c>
       <c r="I200" t="n">
-        <v>0.1303</v>
+        <v>0.192</v>
       </c>
       <c r="J200" t="n">
-        <v>4.4302</v>
+        <v>6.528</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>0.9</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.4663</v>
+        <v>-0.3954</v>
       </c>
       <c r="J201" t="n">
-        <v>-15.8542</v>
+        <v>-13.4436</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>1.39</v>
       </c>
       <c r="I202" t="n">
-        <v>1.0233</v>
+        <v>1.0043</v>
       </c>
       <c r="J202" t="n">
-        <v>30.699</v>
+        <v>30.129</v>
       </c>
     </row>
     <row r="203">
@@ -10469,10 +10469,10 @@
         <v>1.25</v>
       </c>
       <c r="I203" t="n">
-        <v>0.7050999999999999</v>
+        <v>0.6922</v>
       </c>
       <c r="J203" t="n">
-        <v>21.153</v>
+        <v>20.766</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>1.07</v>
       </c>
       <c r="I204" t="n">
-        <v>0.1748</v>
+        <v>0.2284</v>
       </c>
       <c r="J204" t="n">
-        <v>5.244</v>
+        <v>6.852</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>1.01</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.0416</v>
+        <v>0.0205</v>
       </c>
       <c r="J205" t="n">
-        <v>-1.248</v>
+        <v>0.615</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>1</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.1008</v>
+        <v>-0.0343</v>
       </c>
       <c r="J206" t="n">
-        <v>-3.024</v>
+        <v>-1.029</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>1.35</v>
       </c>
       <c r="I207" t="n">
-        <v>0.5909</v>
+        <v>0.7118</v>
       </c>
       <c r="J207" t="n">
-        <v>17.727</v>
+        <v>21.354</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>1.22</v>
       </c>
       <c r="I208" t="n">
-        <v>0.419</v>
+        <v>0.4821</v>
       </c>
       <c r="J208" t="n">
-        <v>12.57</v>
+        <v>14.463</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>0.87</v>
       </c>
       <c r="I209" t="n">
-        <v>-0.2716</v>
+        <v>-0.1646</v>
       </c>
       <c r="J209" t="n">
-        <v>-8.148</v>
+        <v>-4.938</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>0.73</v>
       </c>
       <c r="I210" t="n">
-        <v>-0.4766</v>
+        <v>-0.3053</v>
       </c>
       <c r="J210" t="n">
-        <v>-14.298</v>
+        <v>-9.159000000000001</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>0.73</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.4766</v>
+        <v>-0.3053</v>
       </c>
       <c r="J211" t="n">
-        <v>-14.298</v>
+        <v>-9.159000000000001</v>
       </c>
     </row>
     <row r="212">
@@ -10829,10 +10829,10 @@
         <v>1.28</v>
       </c>
       <c r="I212" t="n">
-        <v>0.7862</v>
+        <v>0.7691</v>
       </c>
       <c r="J212" t="n">
-        <v>21.2274</v>
+        <v>20.7657</v>
       </c>
     </row>
     <row r="213">
@@ -10869,10 +10869,10 @@
         <v>1.14</v>
       </c>
       <c r="I213" t="n">
-        <v>0.4188</v>
+        <v>0.4236</v>
       </c>
       <c r="J213" t="n">
-        <v>11.3076</v>
+        <v>11.4372</v>
       </c>
     </row>
     <row r="214">
@@ -10909,10 +10909,10 @@
         <v>1.11</v>
       </c>
       <c r="I214" t="n">
-        <v>0.3117</v>
+        <v>0.3458</v>
       </c>
       <c r="J214" t="n">
-        <v>8.415900000000001</v>
+        <v>9.336600000000001</v>
       </c>
     </row>
     <row r="215">
@@ -10949,10 +10949,10 @@
         <v>1.09</v>
       </c>
       <c r="I215" t="n">
-        <v>0.2481</v>
+        <v>0.2905</v>
       </c>
       <c r="J215" t="n">
-        <v>6.6987</v>
+        <v>7.8435</v>
       </c>
     </row>
     <row r="216">
@@ -10989,10 +10989,10 @@
         <v>1.02</v>
       </c>
       <c r="I216" t="n">
-        <v>0.008800000000000001</v>
+        <v>0.06560000000000001</v>
       </c>
       <c r="J216" t="n">
-        <v>0.2376</v>
+        <v>1.7712</v>
       </c>
     </row>
     <row r="217">
@@ -11029,10 +11029,10 @@
         <v>1.72</v>
       </c>
       <c r="I217" t="n">
-        <v>1.0032</v>
+        <v>1.1784</v>
       </c>
       <c r="J217" t="n">
-        <v>27.0864</v>
+        <v>31.8168</v>
       </c>
     </row>
     <row r="218">
@@ -11069,10 +11069,10 @@
         <v>1.07</v>
       </c>
       <c r="I218" t="n">
-        <v>0.1726</v>
+        <v>0.1827</v>
       </c>
       <c r="J218" t="n">
-        <v>4.6602</v>
+        <v>4.9329</v>
       </c>
     </row>
     <row r="219">
@@ -11109,10 +11109,10 @@
         <v>0.91</v>
       </c>
       <c r="I219" t="n">
-        <v>-0.2119</v>
+        <v>-0.1235</v>
       </c>
       <c r="J219" t="n">
-        <v>-5.7213</v>
+        <v>-3.3345</v>
       </c>
     </row>
     <row r="220">
@@ -11149,10 +11149,10 @@
         <v>0.82</v>
       </c>
       <c r="I220" t="n">
-        <v>-0.3554</v>
+        <v>-0.2193</v>
       </c>
       <c r="J220" t="n">
-        <v>-9.595800000000001</v>
+        <v>-5.9211</v>
       </c>
     </row>
     <row r="221">
@@ -11189,10 +11189,10 @@
         <v>0.5</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.7642</v>
+        <v>-0.5197000000000001</v>
       </c>
       <c r="J221" t="n">
-        <v>-20.6334</v>
+        <v>-14.0319</v>
       </c>
     </row>
     <row r="222">
@@ -11229,10 +11229,10 @@
         <v>2.05</v>
       </c>
       <c r="I222" t="n">
-        <v>2.004</v>
+        <v>1.7128</v>
       </c>
       <c r="J222" t="n">
-        <v>36.072</v>
+        <v>30.8304</v>
       </c>
     </row>
     <row r="223">
@@ -11269,10 +11269,10 @@
         <v>1.82</v>
       </c>
       <c r="I223" t="n">
-        <v>1.6772</v>
+        <v>1.4573</v>
       </c>
       <c r="J223" t="n">
-        <v>30.1896</v>
+        <v>26.2314</v>
       </c>
     </row>
     <row r="224">
@@ -11309,10 +11309,10 @@
         <v>1.4</v>
       </c>
       <c r="I224" t="n">
-        <v>0.8186</v>
+        <v>0.9485</v>
       </c>
       <c r="J224" t="n">
-        <v>14.7348</v>
+        <v>17.073</v>
       </c>
     </row>
     <row r="225">
@@ -11349,10 +11349,10 @@
         <v>1.36</v>
       </c>
       <c r="I225" t="n">
-        <v>0.7335</v>
+        <v>0.8651</v>
       </c>
       <c r="J225" t="n">
-        <v>13.203</v>
+        <v>15.5718</v>
       </c>
     </row>
     <row r="226">
@@ -11389,10 +11389,10 @@
         <v>0.99</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.2645</v>
+        <v>-0.1742</v>
       </c>
       <c r="J226" t="n">
-        <v>-4.761</v>
+        <v>-3.1356</v>
       </c>
     </row>
     <row r="227">
@@ -11429,10 +11429,10 @@
         <v>0.8</v>
       </c>
       <c r="I227" t="n">
-        <v>-0.1805</v>
+        <v>-0.1676</v>
       </c>
       <c r="J227" t="n">
-        <v>-3.249</v>
+        <v>-3.0168</v>
       </c>
     </row>
     <row r="228">
@@ -11469,10 +11469,10 @@
         <v>0.66</v>
       </c>
       <c r="I228" t="n">
-        <v>-0.3977</v>
+        <v>-0.3163</v>
       </c>
       <c r="J228" t="n">
-        <v>-7.1586</v>
+        <v>-5.6934</v>
       </c>
     </row>
     <row r="229">
@@ -11509,10 +11509,10 @@
         <v>0.59</v>
       </c>
       <c r="I229" t="n">
-        <v>-0.5225</v>
+        <v>-0.3812</v>
       </c>
       <c r="J229" t="n">
-        <v>-9.404999999999999</v>
+        <v>-6.8616</v>
       </c>
     </row>
     <row r="230">
@@ -11549,10 +11549,10 @@
         <v>0.52</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.6445</v>
+        <v>-0.4443</v>
       </c>
       <c r="J230" t="n">
-        <v>-11.601</v>
+        <v>-7.9974</v>
       </c>
     </row>
     <row r="231">
@@ -11589,10 +11589,10 @@
         <v>0.38</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.8378</v>
+        <v>-0.5773</v>
       </c>
       <c r="J231" t="n">
-        <v>-15.0804</v>
+        <v>-10.3914</v>
       </c>
     </row>
     <row r="232">
@@ -11629,10 +11629,10 @@
         <v>1.95</v>
       </c>
       <c r="I232" t="n">
-        <v>1.8767</v>
+        <v>1.5925</v>
       </c>
       <c r="J232" t="n">
-        <v>37.534</v>
+        <v>31.85</v>
       </c>
     </row>
     <row r="233">
@@ -11669,10 +11669,10 @@
         <v>1.71</v>
       </c>
       <c r="I233" t="n">
-        <v>1.4559</v>
+        <v>1.3258</v>
       </c>
       <c r="J233" t="n">
-        <v>29.118</v>
+        <v>26.516</v>
       </c>
     </row>
     <row r="234">
@@ -11709,10 +11709,10 @@
         <v>1.5</v>
       </c>
       <c r="I234" t="n">
-        <v>1.0066</v>
+        <v>1.088</v>
       </c>
       <c r="J234" t="n">
-        <v>20.132</v>
+        <v>21.76</v>
       </c>
     </row>
     <row r="235">
@@ -11749,10 +11749,10 @@
         <v>1.46</v>
       </c>
       <c r="I235" t="n">
-        <v>0.9237</v>
+        <v>1.0386</v>
       </c>
       <c r="J235" t="n">
-        <v>18.474</v>
+        <v>20.772</v>
       </c>
     </row>
     <row r="236">
@@ -11789,10 +11789,10 @@
         <v>1.26</v>
       </c>
       <c r="I236" t="n">
-        <v>0.5023</v>
+        <v>0.6288</v>
       </c>
       <c r="J236" t="n">
-        <v>10.046</v>
+        <v>12.576</v>
       </c>
     </row>
     <row r="237">
@@ -11829,10 +11829,10 @@
         <v>0.74</v>
       </c>
       <c r="I237" t="n">
-        <v>-0.2097</v>
+        <v>-0.1893</v>
       </c>
       <c r="J237" t="n">
-        <v>-4.194</v>
+        <v>-3.786</v>
       </c>
     </row>
     <row r="238">
@@ -11869,10 +11869,10 @@
         <v>0.67</v>
       </c>
       <c r="I238" t="n">
-        <v>-0.3165</v>
+        <v>-0.27</v>
       </c>
       <c r="J238" t="n">
-        <v>-6.33</v>
+        <v>-5.4</v>
       </c>
     </row>
     <row r="239">
@@ -11909,10 +11909,10 @@
         <v>0.51</v>
       </c>
       <c r="I239" t="n">
-        <v>-0.5706</v>
+        <v>-0.4354</v>
       </c>
       <c r="J239" t="n">
-        <v>-11.412</v>
+        <v>-8.708</v>
       </c>
     </row>
     <row r="240">
@@ -11949,10 +11949,10 @@
         <v>0.3</v>
       </c>
       <c r="I240" t="n">
-        <v>-0.9141</v>
+        <v>-0.6358</v>
       </c>
       <c r="J240" t="n">
-        <v>-18.282</v>
+        <v>-12.716</v>
       </c>
     </row>
     <row r="241">
@@ -11989,10 +11989,10 @@
         <v>0.22</v>
       </c>
       <c r="I241" t="n">
-        <v>-1.019</v>
+        <v>-0.7174</v>
       </c>
       <c r="J241" t="n">
-        <v>-20.38</v>
+        <v>-14.348</v>
       </c>
     </row>
     <row r="242">
@@ -12029,10 +12029,10 @@
         <v>1.38</v>
       </c>
       <c r="I242" t="n">
-        <v>0.6057</v>
+        <v>0.5232</v>
       </c>
       <c r="J242" t="n">
-        <v>21.8052</v>
+        <v>18.8352</v>
       </c>
     </row>
     <row r="243">
@@ -12069,10 +12069,10 @@
         <v>1.05</v>
       </c>
       <c r="I243" t="n">
-        <v>0.1084</v>
+        <v>0.09379999999999999</v>
       </c>
       <c r="J243" t="n">
-        <v>3.9024</v>
+        <v>3.3768</v>
       </c>
     </row>
     <row r="244">
@@ -12109,10 +12109,10 @@
         <v>1</v>
       </c>
       <c r="I244" t="n">
-        <v>-0.028</v>
+        <v>-0.0038</v>
       </c>
       <c r="J244" t="n">
-        <v>-1.008</v>
+        <v>-0.1368</v>
       </c>
     </row>
     <row r="245">
@@ -12149,10 +12149,10 @@
         <v>0.98</v>
       </c>
       <c r="I245" t="n">
-        <v>-0.0886</v>
+        <v>-0.0404</v>
       </c>
       <c r="J245" t="n">
-        <v>-3.1896</v>
+        <v>-1.4544</v>
       </c>
     </row>
     <row r="246">
@@ -12189,10 +12189,10 @@
         <v>0.83</v>
       </c>
       <c r="I246" t="n">
-        <v>-0.3507</v>
+        <v>-0.2141</v>
       </c>
       <c r="J246" t="n">
-        <v>-12.6252</v>
+        <v>-7.7076</v>
       </c>
     </row>
     <row r="247">
@@ -12229,10 +12229,10 @@
         <v>1.29</v>
       </c>
       <c r="I247" t="n">
-        <v>0.4788</v>
+        <v>0.4371</v>
       </c>
       <c r="J247" t="n">
-        <v>17.2368</v>
+        <v>15.7356</v>
       </c>
     </row>
     <row r="248">
@@ -12269,10 +12269,10 @@
         <v>1.28</v>
       </c>
       <c r="I248" t="n">
-        <v>0.4655</v>
+        <v>0.4241</v>
       </c>
       <c r="J248" t="n">
-        <v>16.758</v>
+        <v>15.2676</v>
       </c>
     </row>
     <row r="249">
@@ -12309,10 +12309,10 @@
         <v>1.07</v>
       </c>
       <c r="I249" t="n">
-        <v>0.124</v>
+        <v>0.1302</v>
       </c>
       <c r="J249" t="n">
-        <v>4.464</v>
+        <v>4.6872</v>
       </c>
     </row>
     <row r="250">
@@ -12349,10 +12349,10 @@
         <v>0.97</v>
       </c>
       <c r="I250" t="n">
-        <v>-0.1231</v>
+        <v>-0.0586</v>
       </c>
       <c r="J250" t="n">
-        <v>-4.4316</v>
+        <v>-2.1096</v>
       </c>
     </row>
     <row r="251">
@@ -12389,10 +12389,10 @@
         <v>0.82</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.373</v>
+        <v>-0.2284</v>
       </c>
       <c r="J251" t="n">
-        <v>-13.428</v>
+        <v>-8.2224</v>
       </c>
     </row>
     <row r="252">
@@ -12429,10 +12429,10 @@
         <v>1.07</v>
       </c>
       <c r="I252" t="n">
-        <v>0.2038</v>
+        <v>0.2034</v>
       </c>
       <c r="J252" t="n">
-        <v>5.9102</v>
+        <v>5.8986</v>
       </c>
     </row>
     <row r="253">
@@ -12469,10 +12469,10 @@
         <v>1.01</v>
       </c>
       <c r="I253" t="n">
-        <v>0.07679999999999999</v>
+        <v>0.0528</v>
       </c>
       <c r="J253" t="n">
-        <v>2.2272</v>
+        <v>1.5312</v>
       </c>
     </row>
     <row r="254">
@@ -12509,10 +12509,10 @@
         <v>0.99</v>
       </c>
       <c r="I254" t="n">
-        <v>0.0066</v>
+        <v>-0.0137</v>
       </c>
       <c r="J254" t="n">
-        <v>0.1914</v>
+        <v>-0.3973</v>
       </c>
     </row>
     <row r="255">
@@ -12549,10 +12549,10 @@
         <v>0.87</v>
       </c>
       <c r="I255" t="n">
-        <v>-0.2524</v>
+        <v>-0.1584</v>
       </c>
       <c r="J255" t="n">
-        <v>-7.3196</v>
+        <v>-4.5936</v>
       </c>
     </row>
     <row r="256">
@@ -12589,10 +12589,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I256" t="n">
-        <v>-0.5187</v>
+        <v>-0.337</v>
       </c>
       <c r="J256" t="n">
-        <v>-15.0423</v>
+        <v>-9.773</v>
       </c>
     </row>
     <row r="257">
@@ -12629,10 +12629,10 @@
         <v>1.36</v>
       </c>
       <c r="I257" t="n">
-        <v>0.9563</v>
+        <v>0.946</v>
       </c>
       <c r="J257" t="n">
-        <v>27.7327</v>
+        <v>27.434</v>
       </c>
     </row>
     <row r="258">
@@ -12669,10 +12669,10 @@
         <v>1.28</v>
       </c>
       <c r="I258" t="n">
-        <v>0.7748</v>
+        <v>0.7624</v>
       </c>
       <c r="J258" t="n">
-        <v>22.4692</v>
+        <v>22.1096</v>
       </c>
     </row>
     <row r="259">
@@ -12709,10 +12709,10 @@
         <v>1.12</v>
       </c>
       <c r="I259" t="n">
-        <v>0.3264</v>
+        <v>0.3689</v>
       </c>
       <c r="J259" t="n">
-        <v>9.4656</v>
+        <v>10.6981</v>
       </c>
     </row>
     <row r="260">
@@ -12749,10 +12749,10 @@
         <v>1.09</v>
       </c>
       <c r="I260" t="n">
-        <v>0.2349</v>
+        <v>0.2861</v>
       </c>
       <c r="J260" t="n">
-        <v>6.8121</v>
+        <v>8.296900000000001</v>
       </c>
     </row>
     <row r="261">
@@ -12789,10 +12789,10 @@
         <v>0.89</v>
       </c>
       <c r="I261" t="n">
-        <v>-0.4874</v>
+        <v>-0.4189</v>
       </c>
       <c r="J261" t="n">
-        <v>-14.1346</v>
+        <v>-12.1481</v>
       </c>
     </row>
     <row r="262">
@@ -12829,10 +12829,10 @@
         <v>0.85</v>
       </c>
       <c r="I262" t="n">
-        <v>-0.1683</v>
+        <v>-0.1509</v>
       </c>
       <c r="J262" t="n">
-        <v>-3.7026</v>
+        <v>-3.3198</v>
       </c>
     </row>
     <row r="263">
@@ -12869,10 +12869,10 @@
         <v>0.84</v>
       </c>
       <c r="I263" t="n">
-        <v>-0.1847</v>
+        <v>-0.1619</v>
       </c>
       <c r="J263" t="n">
-        <v>-4.0634</v>
+        <v>-3.5618</v>
       </c>
     </row>
     <row r="264">
@@ -12909,10 +12909,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I264" t="n">
-        <v>-0.4486</v>
+        <v>-0.3086</v>
       </c>
       <c r="J264" t="n">
-        <v>-9.869199999999999</v>
+        <v>-6.7892</v>
       </c>
     </row>
     <row r="265">
@@ -12949,10 +12949,10 @@
         <v>0.65</v>
       </c>
       <c r="I265" t="n">
-        <v>-0.5114</v>
+        <v>-0.3458</v>
       </c>
       <c r="J265" t="n">
-        <v>-11.2508</v>
+        <v>-7.6076</v>
       </c>
     </row>
     <row r="266">
@@ -12989,10 +12989,10 @@
         <v>0.57</v>
       </c>
       <c r="I266" t="n">
-        <v>-0.625</v>
+        <v>-0.4205</v>
       </c>
       <c r="J266" t="n">
-        <v>-13.75</v>
+        <v>-9.250999999999999</v>
       </c>
     </row>
     <row r="267">
@@ -13029,10 +13029,10 @@
         <v>1.71</v>
       </c>
       <c r="I267" t="n">
-        <v>1.5227</v>
+        <v>1.3502</v>
       </c>
       <c r="J267" t="n">
-        <v>33.4994</v>
+        <v>29.7044</v>
       </c>
     </row>
     <row r="268">
@@ -13069,10 +13069,10 @@
         <v>1.56</v>
       </c>
       <c r="I268" t="n">
-        <v>1.2367</v>
+        <v>1.1733</v>
       </c>
       <c r="J268" t="n">
-        <v>27.2074</v>
+        <v>25.8126</v>
       </c>
     </row>
     <row r="269">
@@ -13109,10 +13109,10 @@
         <v>1.49</v>
       </c>
       <c r="I269" t="n">
-        <v>1.0924</v>
+        <v>1.0895</v>
       </c>
       <c r="J269" t="n">
-        <v>24.0328</v>
+        <v>23.969</v>
       </c>
     </row>
     <row r="270">
@@ -13149,10 +13149,10 @@
         <v>1.2</v>
       </c>
       <c r="I270" t="n">
-        <v>0.4099</v>
+        <v>0.5158</v>
       </c>
       <c r="J270" t="n">
-        <v>9.017799999999999</v>
+        <v>11.3476</v>
       </c>
     </row>
     <row r="271">
@@ -13189,10 +13189,10 @@
         <v>1.14</v>
       </c>
       <c r="I271" t="n">
-        <v>0.2626</v>
+        <v>0.3621</v>
       </c>
       <c r="J271" t="n">
-        <v>5.7772</v>
+        <v>7.9662</v>
       </c>
     </row>
     <row r="272">
@@ -13229,10 +13229,10 @@
         <v>1.1</v>
       </c>
       <c r="I272" t="n">
-        <v>0.2675</v>
+        <v>0.2133</v>
       </c>
       <c r="J272" t="n">
-        <v>7.2225</v>
+        <v>5.7591</v>
       </c>
     </row>
     <row r="273">
@@ -13269,10 +13269,10 @@
         <v>0.95</v>
       </c>
       <c r="I273" t="n">
-        <v>-0.07149999999999999</v>
+        <v>-0.0664</v>
       </c>
       <c r="J273" t="n">
-        <v>-1.9305</v>
+        <v>-1.7928</v>
       </c>
     </row>
     <row r="274">
@@ -13309,10 +13309,10 @@
         <v>0.95</v>
       </c>
       <c r="I274" t="n">
-        <v>-0.07149999999999999</v>
+        <v>-0.0664</v>
       </c>
       <c r="J274" t="n">
-        <v>-1.9305</v>
+        <v>-1.7928</v>
       </c>
     </row>
     <row r="275">
@@ -13349,10 +13349,10 @@
         <v>0.77</v>
       </c>
       <c r="I275" t="n">
-        <v>-0.3995</v>
+        <v>-0.256</v>
       </c>
       <c r="J275" t="n">
-        <v>-10.7865</v>
+        <v>-6.912</v>
       </c>
     </row>
     <row r="276">
@@ -13389,10 +13389,10 @@
         <v>0.71</v>
       </c>
       <c r="I276" t="n">
-        <v>-0.4846</v>
+        <v>-0.3141</v>
       </c>
       <c r="J276" t="n">
-        <v>-13.0842</v>
+        <v>-8.480700000000001</v>
       </c>
     </row>
     <row r="277">
@@ -13429,10 +13429,10 @@
         <v>1.23</v>
       </c>
       <c r="I277" t="n">
-        <v>0.3845</v>
+        <v>0.3271</v>
       </c>
       <c r="J277" t="n">
-        <v>10.3815</v>
+        <v>8.8317</v>
       </c>
     </row>
     <row r="278">
@@ -13469,10 +13469,10 @@
         <v>1.23</v>
       </c>
       <c r="I278" t="n">
-        <v>0.3845</v>
+        <v>0.3271</v>
       </c>
       <c r="J278" t="n">
-        <v>10.3815</v>
+        <v>8.8317</v>
       </c>
     </row>
     <row r="279">
@@ -13509,10 +13509,10 @@
         <v>1.2</v>
       </c>
       <c r="I279" t="n">
-        <v>0.3406</v>
+        <v>0.29</v>
       </c>
       <c r="J279" t="n">
-        <v>9.196199999999999</v>
+        <v>7.83</v>
       </c>
     </row>
     <row r="280">
@@ -13549,10 +13549,10 @@
         <v>1</v>
       </c>
       <c r="I280" t="n">
-        <v>-0.0521</v>
+        <v>-0.011</v>
       </c>
       <c r="J280" t="n">
-        <v>-1.4067</v>
+        <v>-0.297</v>
       </c>
     </row>
     <row r="281">
@@ -13589,10 +13589,10 @@
         <v>0.95</v>
       </c>
       <c r="I281" t="n">
-        <v>-0.1723</v>
+        <v>-0.0886</v>
       </c>
       <c r="J281" t="n">
-        <v>-4.6521</v>
+        <v>-2.3922</v>
       </c>
     </row>
     <row r="282">
@@ -13629,10 +13629,10 @@
         <v>1.72</v>
       </c>
       <c r="I282" t="n">
-        <v>1.4859</v>
+        <v>1.3405</v>
       </c>
       <c r="J282" t="n">
-        <v>29.718</v>
+        <v>26.81</v>
       </c>
     </row>
     <row r="283">
@@ -13669,10 +13669,10 @@
         <v>1.61</v>
       </c>
       <c r="I283" t="n">
-        <v>1.2727</v>
+        <v>1.2156</v>
       </c>
       <c r="J283" t="n">
-        <v>25.454</v>
+        <v>24.312</v>
       </c>
     </row>
     <row r="284">
@@ -13709,10 +13709,10 @@
         <v>1.53</v>
       </c>
       <c r="I284" t="n">
-        <v>1.0854</v>
+        <v>1.1252</v>
       </c>
       <c r="J284" t="n">
-        <v>21.708</v>
+        <v>22.504</v>
       </c>
     </row>
     <row r="285">
@@ -13749,10 +13749,10 @@
         <v>1.45</v>
       </c>
       <c r="I285" t="n">
-        <v>0.9135</v>
+        <v>1.0278</v>
       </c>
       <c r="J285" t="n">
-        <v>18.27</v>
+        <v>20.556</v>
       </c>
     </row>
     <row r="286">
@@ -13789,10 +13789,10 @@
         <v>1.44</v>
       </c>
       <c r="I286" t="n">
-        <v>0.8925</v>
+        <v>1.0133</v>
       </c>
       <c r="J286" t="n">
-        <v>17.85</v>
+        <v>20.266</v>
       </c>
     </row>
     <row r="287">
@@ -13829,10 +13829,10 @@
         <v>0.84</v>
       </c>
       <c r="I287" t="n">
-        <v>-0.1214</v>
+        <v>-0.1243</v>
       </c>
       <c r="J287" t="n">
-        <v>-2.428</v>
+        <v>-2.486</v>
       </c>
     </row>
     <row r="288">
@@ -13869,10 +13869,10 @@
         <v>0.65</v>
       </c>
       <c r="I288" t="n">
-        <v>-0.4189</v>
+        <v>-0.3278</v>
       </c>
       <c r="J288" t="n">
-        <v>-8.378</v>
+        <v>-6.556</v>
       </c>
     </row>
     <row r="289">
@@ -13909,10 +13909,10 @@
         <v>0.58</v>
       </c>
       <c r="I289" t="n">
-        <v>-0.5528</v>
+        <v>-0.3908</v>
       </c>
       <c r="J289" t="n">
-        <v>-11.056</v>
+        <v>-7.816</v>
       </c>
     </row>
     <row r="290">
@@ -13949,10 +13949,10 @@
         <v>0.5</v>
       </c>
       <c r="I290" t="n">
-        <v>-0.6776</v>
+        <v>-0.4645</v>
       </c>
       <c r="J290" t="n">
-        <v>-13.552</v>
+        <v>-9.289999999999999</v>
       </c>
     </row>
     <row r="291">
@@ -13989,10 +13989,10 @@
         <v>0.42</v>
       </c>
       <c r="I291" t="n">
-        <v>-0.7877</v>
+        <v>-0.5405</v>
       </c>
       <c r="J291" t="n">
-        <v>-15.754</v>
+        <v>-10.81</v>
       </c>
     </row>
     <row r="292">
@@ -14029,10 +14029,10 @@
         <v>1.77</v>
       </c>
       <c r="I292" t="n">
-        <v>1.5923</v>
+        <v>1.4026</v>
       </c>
       <c r="J292" t="n">
-        <v>31.846</v>
+        <v>28.052</v>
       </c>
     </row>
     <row r="293">
@@ -14069,10 +14069,10 @@
         <v>1.63</v>
       </c>
       <c r="I293" t="n">
-        <v>1.3306</v>
+        <v>1.2426</v>
       </c>
       <c r="J293" t="n">
-        <v>26.612</v>
+        <v>24.852</v>
       </c>
     </row>
     <row r="294">
@@ -14109,10 +14109,10 @@
         <v>1.59</v>
       </c>
       <c r="I294" t="n">
-        <v>1.2508</v>
+        <v>1.1965</v>
       </c>
       <c r="J294" t="n">
-        <v>25.016</v>
+        <v>23.93</v>
       </c>
     </row>
     <row r="295">
@@ -14149,10 +14149,10 @@
         <v>1.43</v>
       </c>
       <c r="I295" t="n">
-        <v>0.8867</v>
+        <v>1.0025</v>
       </c>
       <c r="J295" t="n">
-        <v>17.734</v>
+        <v>20.05</v>
       </c>
     </row>
     <row r="296">
@@ -14189,10 +14189,10 @@
         <v>1.15</v>
       </c>
       <c r="I296" t="n">
-        <v>0.2629</v>
+        <v>0.3692</v>
       </c>
       <c r="J296" t="n">
-        <v>5.258</v>
+        <v>7.384</v>
       </c>
     </row>
     <row r="297">
@@ -14229,10 +14229,10 @@
         <v>0.9</v>
       </c>
       <c r="I297" t="n">
-        <v>-0.0556</v>
+        <v>-0.0757</v>
       </c>
       <c r="J297" t="n">
-        <v>-1.112</v>
+        <v>-1.514</v>
       </c>
     </row>
     <row r="298">
@@ -14269,10 +14269,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I298" t="n">
-        <v>-0.3961</v>
+        <v>-0.3019</v>
       </c>
       <c r="J298" t="n">
-        <v>-7.922</v>
+        <v>-6.038</v>
       </c>
     </row>
     <row r="299">
@@ -14309,10 +14309,10 @@
         <v>0.65</v>
       </c>
       <c r="I299" t="n">
-        <v>-0.4777</v>
+        <v>-0.3374</v>
       </c>
       <c r="J299" t="n">
-        <v>-9.554</v>
+        <v>-6.748</v>
       </c>
     </row>
     <row r="300">
@@ -14349,10 +14349,10 @@
         <v>0.65</v>
       </c>
       <c r="I300" t="n">
-        <v>-0.4777</v>
+        <v>-0.3374</v>
       </c>
       <c r="J300" t="n">
-        <v>-9.554</v>
+        <v>-6.748</v>
       </c>
     </row>
     <row r="301">
@@ -14389,10 +14389,10 @@
         <v>0.42</v>
       </c>
       <c r="I301" t="n">
-        <v>-0.8048</v>
+        <v>-0.5516</v>
       </c>
       <c r="J301" t="n">
-        <v>-16.096</v>
+        <v>-11.032</v>
       </c>
     </row>
     <row r="302">
@@ -14429,10 +14429,10 @@
         <v>1.18</v>
       </c>
       <c r="I302" t="n">
-        <v>0.5568</v>
+        <v>0.5338000000000001</v>
       </c>
       <c r="J302" t="n">
-        <v>16.704</v>
+        <v>16.014</v>
       </c>
     </row>
     <row r="303">
@@ -14469,10 +14469,10 @@
         <v>1.18</v>
       </c>
       <c r="I303" t="n">
-        <v>0.5568</v>
+        <v>0.5338000000000001</v>
       </c>
       <c r="J303" t="n">
-        <v>16.704</v>
+        <v>16.014</v>
       </c>
     </row>
     <row r="304">
@@ -14509,10 +14509,10 @@
         <v>1.11</v>
       </c>
       <c r="I304" t="n">
-        <v>0.3539</v>
+        <v>0.3505</v>
       </c>
       <c r="J304" t="n">
-        <v>10.617</v>
+        <v>10.515</v>
       </c>
     </row>
     <row r="305">
@@ -14549,10 +14549,10 @@
         <v>1.04</v>
       </c>
       <c r="I305" t="n">
-        <v>0.1024</v>
+        <v>0.1449</v>
       </c>
       <c r="J305" t="n">
-        <v>3.072</v>
+        <v>4.347</v>
       </c>
     </row>
     <row r="306">
@@ -14589,10 +14589,10 @@
         <v>0.97</v>
       </c>
       <c r="I306" t="n">
-        <v>-0.219</v>
+        <v>-0.1549</v>
       </c>
       <c r="J306" t="n">
-        <v>-6.57</v>
+        <v>-4.647</v>
       </c>
     </row>
     <row r="307">
@@ -14629,10 +14629,10 @@
         <v>1.31</v>
       </c>
       <c r="I307" t="n">
-        <v>0.5346</v>
+        <v>0.6361</v>
       </c>
       <c r="J307" t="n">
-        <v>16.038</v>
+        <v>19.083</v>
       </c>
     </row>
     <row r="308">
@@ -14669,10 +14669,10 @@
         <v>1.05</v>
       </c>
       <c r="I308" t="n">
-        <v>0.1372</v>
+        <v>0.1401</v>
       </c>
       <c r="J308" t="n">
-        <v>4.116</v>
+        <v>4.203</v>
       </c>
     </row>
     <row r="309">
@@ -14709,10 +14709,10 @@
         <v>0.93</v>
       </c>
       <c r="I309" t="n">
-        <v>-0.1729</v>
+        <v>-0.09959999999999999</v>
       </c>
       <c r="J309" t="n">
-        <v>-5.187</v>
+        <v>-2.988</v>
       </c>
     </row>
     <row r="310">
@@ -14749,10 +14749,10 @@
         <v>0.87</v>
       </c>
       <c r="I310" t="n">
-        <v>-0.2764</v>
+        <v>-0.1664</v>
       </c>
       <c r="J310" t="n">
-        <v>-8.292</v>
+        <v>-4.992</v>
       </c>
     </row>
     <row r="311">
@@ -14789,10 +14789,10 @@
         <v>0.82</v>
       </c>
       <c r="I311" t="n">
-        <v>-0.3534</v>
+        <v>-0.2184</v>
       </c>
       <c r="J311" t="n">
-        <v>-10.602</v>
+        <v>-6.552</v>
       </c>
     </row>
     <row r="312">
@@ -14829,10 +14829,10 @@
         <v>1.48</v>
       </c>
       <c r="I312" t="n">
-        <v>1.1209</v>
+        <v>1.0909</v>
       </c>
       <c r="J312" t="n">
-        <v>22.418</v>
+        <v>21.818</v>
       </c>
     </row>
     <row r="313">
@@ -14869,10 +14869,10 @@
         <v>1.41</v>
       </c>
       <c r="I313" t="n">
-        <v>0.9717</v>
+        <v>0.9943</v>
       </c>
       <c r="J313" t="n">
-        <v>19.434</v>
+        <v>19.886</v>
       </c>
     </row>
     <row r="314">
@@ -14909,10 +14909,10 @@
         <v>1.4</v>
       </c>
       <c r="I314" t="n">
-        <v>0.9495</v>
+        <v>0.9771</v>
       </c>
       <c r="J314" t="n">
-        <v>18.99</v>
+        <v>19.542</v>
       </c>
     </row>
     <row r="315">
@@ -14949,10 +14949,10 @@
         <v>1.19</v>
       </c>
       <c r="I315" t="n">
-        <v>0.4206</v>
+        <v>0.5117</v>
       </c>
       <c r="J315" t="n">
-        <v>8.412000000000001</v>
+        <v>10.234</v>
       </c>
     </row>
     <row r="316">
@@ -14989,10 +14989,10 @@
         <v>1.14</v>
       </c>
       <c r="I316" t="n">
-        <v>0.2936</v>
+        <v>0.3832</v>
       </c>
       <c r="J316" t="n">
-        <v>5.872</v>
+        <v>7.664</v>
       </c>
     </row>
     <row r="317">
@@ -15029,10 +15029,10 @@
         <v>1.16</v>
       </c>
       <c r="I317" t="n">
-        <v>0.4038</v>
+        <v>0.454</v>
       </c>
       <c r="J317" t="n">
-        <v>8.076000000000001</v>
+        <v>9.08</v>
       </c>
     </row>
     <row r="318">
@@ -15069,10 +15069,10 @@
         <v>0.8</v>
       </c>
       <c r="I318" t="n">
-        <v>-0.2934</v>
+        <v>-0.215</v>
       </c>
       <c r="J318" t="n">
-        <v>-5.868</v>
+        <v>-4.3</v>
       </c>
     </row>
     <row r="319">
@@ -15109,10 +15109,10 @@
         <v>0.72</v>
       </c>
       <c r="I319" t="n">
-        <v>-0.4369</v>
+        <v>-0.2904</v>
       </c>
       <c r="J319" t="n">
-        <v>-8.738</v>
+        <v>-5.808</v>
       </c>
     </row>
     <row r="320">
@@ -15149,10 +15149,10 @@
         <v>0.65</v>
       </c>
       <c r="I320" t="n">
-        <v>-0.538</v>
+        <v>-0.3567</v>
       </c>
       <c r="J320" t="n">
-        <v>-10.76</v>
+        <v>-7.134</v>
       </c>
     </row>
     <row r="321">
@@ -15189,10 +15189,10 @@
         <v>0.63</v>
       </c>
       <c r="I321" t="n">
-        <v>-0.5654</v>
+        <v>-0.3755</v>
       </c>
       <c r="J321" t="n">
-        <v>-11.308</v>
+        <v>-7.51</v>
       </c>
     </row>
     <row r="322">
@@ -15229,10 +15229,10 @@
         <v>1.21</v>
       </c>
       <c r="I322" t="n">
-        <v>0.4382</v>
+        <v>0.5014</v>
       </c>
       <c r="J322" t="n">
-        <v>10.955</v>
+        <v>12.535</v>
       </c>
     </row>
     <row r="323">
@@ -15269,10 +15269,10 @@
         <v>1.14</v>
       </c>
       <c r="I323" t="n">
-        <v>0.3348</v>
+        <v>0.3645</v>
       </c>
       <c r="J323" t="n">
-        <v>8.369999999999999</v>
+        <v>9.112500000000001</v>
       </c>
     </row>
     <row r="324">
@@ -15309,10 +15309,10 @@
         <v>0.85</v>
       </c>
       <c r="I324" t="n">
-        <v>-0.27</v>
+        <v>-0.175</v>
       </c>
       <c r="J324" t="n">
-        <v>-6.75</v>
+        <v>-4.375</v>
       </c>
     </row>
     <row r="325">
@@ -15349,10 +15349,10 @@
         <v>0.84</v>
       </c>
       <c r="I325" t="n">
-        <v>-0.2871</v>
+        <v>-0.1852</v>
       </c>
       <c r="J325" t="n">
-        <v>-7.1775</v>
+        <v>-4.63</v>
       </c>
     </row>
     <row r="326">
@@ -15389,10 +15389,10 @@
         <v>0.4</v>
       </c>
       <c r="I326" t="n">
-        <v>-0.865</v>
+        <v>-0.598</v>
       </c>
       <c r="J326" t="n">
-        <v>-21.625</v>
+        <v>-14.95</v>
       </c>
     </row>
     <row r="327">
@@ -15429,10 +15429,10 @@
         <v>1.59</v>
       </c>
       <c r="I327" t="n">
-        <v>1.3676</v>
+        <v>1.2393</v>
       </c>
       <c r="J327" t="n">
-        <v>34.19</v>
+        <v>30.9825</v>
       </c>
     </row>
     <row r="328">
@@ -15469,10 +15469,10 @@
         <v>1.46</v>
       </c>
       <c r="I328" t="n">
-        <v>1.1093</v>
+        <v>1.0765</v>
       </c>
       <c r="J328" t="n">
-        <v>27.7325</v>
+        <v>26.9125</v>
       </c>
     </row>
     <row r="329">
@@ -15509,10 +15509,10 @@
         <v>1.27</v>
       </c>
       <c r="I329" t="n">
-        <v>0.6714</v>
+        <v>0.7115</v>
       </c>
       <c r="J329" t="n">
-        <v>16.785</v>
+        <v>17.7875</v>
       </c>
     </row>
     <row r="330">
@@ -15549,10 +15549,10 @@
         <v>1.03</v>
       </c>
       <c r="I330" t="n">
-        <v>-0.008399999999999999</v>
+        <v>0.0688</v>
       </c>
       <c r="J330" t="n">
-        <v>-0.21</v>
+        <v>1.72</v>
       </c>
     </row>
     <row r="331">
@@ -15589,10 +15589,10 @@
         <v>0.97</v>
       </c>
       <c r="I331" t="n">
-        <v>-0.2813</v>
+        <v>-0.1977</v>
       </c>
       <c r="J331" t="n">
-        <v>-7.0325</v>
+        <v>-4.9425</v>
       </c>
     </row>
     <row r="332">
@@ -15629,10 +15629,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I332" t="n">
-        <v>-0.007900000000000001</v>
+        <v>-0.0408</v>
       </c>
       <c r="J332" t="n">
-        <v>-0.1659</v>
+        <v>-0.8568</v>
       </c>
     </row>
     <row r="333">
@@ -15669,10 +15669,10 @@
         <v>0.86</v>
       </c>
       <c r="I333" t="n">
-        <v>-0.1478</v>
+        <v>-0.1378</v>
       </c>
       <c r="J333" t="n">
-        <v>-3.1038</v>
+        <v>-2.8938</v>
       </c>
     </row>
     <row r="334">
@@ -15709,10 +15709,10 @@
         <v>0.71</v>
       </c>
       <c r="I334" t="n">
-        <v>-0.4054</v>
+        <v>-0.2897</v>
       </c>
       <c r="J334" t="n">
-        <v>-8.513400000000001</v>
+        <v>-6.0837</v>
       </c>
     </row>
     <row r="335">
@@ -15749,10 +15749,10 @@
         <v>0.66</v>
       </c>
       <c r="I335" t="n">
-        <v>-0.4924</v>
+        <v>-0.3352</v>
       </c>
       <c r="J335" t="n">
-        <v>-10.3404</v>
+        <v>-7.0392</v>
       </c>
     </row>
     <row r="336">
@@ -15789,10 +15789,10 @@
         <v>0.39</v>
       </c>
       <c r="I336" t="n">
-        <v>-0.852</v>
+        <v>-0.5871</v>
       </c>
       <c r="J336" t="n">
-        <v>-17.892</v>
+        <v>-12.3291</v>
       </c>
     </row>
     <row r="337">
@@ -15829,10 +15829,10 @@
         <v>1.52</v>
       </c>
       <c r="I337" t="n">
-        <v>1.1705</v>
+        <v>1.1297</v>
       </c>
       <c r="J337" t="n">
-        <v>24.5805</v>
+        <v>23.7237</v>
       </c>
     </row>
     <row r="338">
@@ -15869,10 +15869,10 @@
         <v>1.5</v>
       </c>
       <c r="I338" t="n">
-        <v>1.1293</v>
+        <v>1.1055</v>
       </c>
       <c r="J338" t="n">
-        <v>23.7153</v>
+        <v>23.2155</v>
       </c>
     </row>
     <row r="339">
@@ -15909,10 +15909,10 @@
         <v>1.37</v>
       </c>
       <c r="I339" t="n">
-        <v>0.8197</v>
+        <v>0.9103</v>
       </c>
       <c r="J339" t="n">
-        <v>17.2137</v>
+        <v>19.1163</v>
       </c>
     </row>
     <row r="340">
@@ -15949,10 +15949,10 @@
         <v>1.33</v>
       </c>
       <c r="I340" t="n">
-        <v>0.7242</v>
+        <v>0.8246</v>
       </c>
       <c r="J340" t="n">
-        <v>15.2082</v>
+        <v>17.3166</v>
       </c>
     </row>
     <row r="341">
@@ -15989,10 +15989,10 @@
         <v>1.23</v>
       </c>
       <c r="I341" t="n">
-        <v>0.4914</v>
+        <v>0.5952</v>
       </c>
       <c r="J341" t="n">
-        <v>10.3194</v>
+        <v>12.4992</v>
       </c>
     </row>
     <row r="342">
@@ -16029,10 +16029,10 @@
         <v>1.09</v>
       </c>
       <c r="I342" t="n">
-        <v>0.2292</v>
+        <v>0.2387</v>
       </c>
       <c r="J342" t="n">
-        <v>6.6468</v>
+        <v>6.9223</v>
       </c>
     </row>
     <row r="343">
@@ -16069,10 +16069,10 @@
         <v>1.07</v>
       </c>
       <c r="I343" t="n">
-        <v>0.1936</v>
+        <v>0.1957</v>
       </c>
       <c r="J343" t="n">
-        <v>5.6144</v>
+        <v>5.6753</v>
       </c>
     </row>
     <row r="344">
@@ -16109,10 +16109,10 @@
         <v>1.01</v>
       </c>
       <c r="I344" t="n">
-        <v>0.0654</v>
+        <v>0.0465</v>
       </c>
       <c r="J344" t="n">
-        <v>1.8966</v>
+        <v>1.3485</v>
       </c>
     </row>
     <row r="345">
@@ -16149,10 +16149,10 @@
         <v>0.88</v>
       </c>
       <c r="I345" t="n">
-        <v>-0.2455</v>
+        <v>-0.1507</v>
       </c>
       <c r="J345" t="n">
-        <v>-7.1195</v>
+        <v>-4.3703</v>
       </c>
     </row>
     <row r="346">
@@ -16189,10 +16189,10 @@
         <v>0.71</v>
       </c>
       <c r="I346" t="n">
-        <v>-0.4976</v>
+        <v>-0.3211</v>
       </c>
       <c r="J346" t="n">
-        <v>-14.4304</v>
+        <v>-9.3119</v>
       </c>
     </row>
     <row r="347">
@@ -16229,10 +16229,10 @@
         <v>1.15</v>
       </c>
       <c r="I347" t="n">
-        <v>0.5123</v>
+        <v>0.4734</v>
       </c>
       <c r="J347" t="n">
-        <v>14.8567</v>
+        <v>13.7286</v>
       </c>
     </row>
     <row r="348">
@@ -16269,10 +16269,10 @@
         <v>1.12</v>
       </c>
       <c r="I348" t="n">
-        <v>0.4281</v>
+        <v>0.392</v>
       </c>
       <c r="J348" t="n">
-        <v>12.4149</v>
+        <v>11.368</v>
       </c>
     </row>
     <row r="349">
@@ -16309,10 +16309,10 @@
         <v>1.04</v>
       </c>
       <c r="I349" t="n">
-        <v>0.1551</v>
+        <v>0.1561</v>
       </c>
       <c r="J349" t="n">
-        <v>4.4979</v>
+        <v>4.5269</v>
       </c>
     </row>
     <row r="350">
@@ -16349,10 +16349,10 @@
         <v>1.01</v>
       </c>
       <c r="I350" t="n">
-        <v>0.0192</v>
+        <v>0.0464</v>
       </c>
       <c r="J350" t="n">
-        <v>0.5568</v>
+        <v>1.3456</v>
       </c>
     </row>
     <row r="351">
@@ -16389,10 +16389,10 @@
         <v>0.88</v>
       </c>
       <c r="I351" t="n">
-        <v>-0.4738</v>
+        <v>-0.4174</v>
       </c>
       <c r="J351" t="n">
-        <v>-13.7402</v>
+        <v>-12.1046</v>
       </c>
     </row>
     <row r="352">
@@ -16429,10 +16429,10 @@
         <v>0.98</v>
       </c>
       <c r="I352" t="n">
-        <v>-0.0005</v>
+        <v>-0.0236</v>
       </c>
       <c r="J352" t="n">
-        <v>-0.014</v>
+        <v>-0.6608000000000001</v>
       </c>
     </row>
     <row r="353">
@@ -16469,10 +16469,10 @@
         <v>0.93</v>
       </c>
       <c r="I353" t="n">
-        <v>-0.1057</v>
+        <v>-0.0892</v>
       </c>
       <c r="J353" t="n">
-        <v>-2.9596</v>
+        <v>-2.4976</v>
       </c>
     </row>
     <row r="354">
@@ -16509,10 +16509,10 @@
         <v>0.89</v>
       </c>
       <c r="I354" t="n">
-        <v>-0.1852</v>
+        <v>-0.1337</v>
       </c>
       <c r="J354" t="n">
-        <v>-5.1856</v>
+        <v>-3.7436</v>
       </c>
     </row>
     <row r="355">
@@ -16549,10 +16549,10 @@
         <v>0.88</v>
       </c>
       <c r="I355" t="n">
-        <v>-0.2107</v>
+        <v>-0.1439</v>
       </c>
       <c r="J355" t="n">
-        <v>-5.8996</v>
+        <v>-4.0292</v>
       </c>
     </row>
     <row r="356">
@@ -16589,10 +16589,10 @@
         <v>0.74</v>
       </c>
       <c r="I356" t="n">
-        <v>-0.4393</v>
+        <v>-0.2837</v>
       </c>
       <c r="J356" t="n">
-        <v>-12.3004</v>
+        <v>-7.9436</v>
       </c>
     </row>
     <row r="357">
@@ -16629,10 +16629,10 @@
         <v>1.56</v>
       </c>
       <c r="I357" t="n">
-        <v>1.3572</v>
+        <v>1.2273</v>
       </c>
       <c r="J357" t="n">
-        <v>38.0016</v>
+        <v>34.3644</v>
       </c>
     </row>
     <row r="358">
@@ -16669,10 +16669,10 @@
         <v>1.38</v>
       </c>
       <c r="I358" t="n">
-        <v>0.9903</v>
+        <v>0.9796</v>
       </c>
       <c r="J358" t="n">
-        <v>27.7284</v>
+        <v>27.4288</v>
       </c>
     </row>
     <row r="359">
@@ -16709,10 +16709,10 @@
         <v>1.09</v>
       </c>
       <c r="I359" t="n">
-        <v>0.2244</v>
+        <v>0.282</v>
       </c>
       <c r="J359" t="n">
-        <v>6.2832</v>
+        <v>7.896</v>
       </c>
     </row>
     <row r="360">
@@ -16749,10 +16749,10 @@
         <v>0.97</v>
       </c>
       <c r="I360" t="n">
-        <v>-0.2487</v>
+        <v>-0.1733</v>
       </c>
       <c r="J360" t="n">
-        <v>-6.9636</v>
+        <v>-4.8524</v>
       </c>
     </row>
     <row r="361">
@@ -16789,10 +16789,10 @@
         <v>0.83</v>
       </c>
       <c r="I361" t="n">
-        <v>-0.6485</v>
+        <v>-0.5883</v>
       </c>
       <c r="J361" t="n">
-        <v>-18.158</v>
+        <v>-16.4724</v>
       </c>
     </row>
     <row r="362">
@@ -16829,10 +16829,10 @@
         <v>1.38</v>
       </c>
       <c r="I362" t="n">
-        <v>0.5661</v>
+        <v>0.4947</v>
       </c>
       <c r="J362" t="n">
-        <v>15.8508</v>
+        <v>13.8516</v>
       </c>
     </row>
     <row r="363">
@@ -16869,10 +16869,10 @@
         <v>1.25</v>
       </c>
       <c r="I363" t="n">
-        <v>0.3939</v>
+        <v>0.3436</v>
       </c>
       <c r="J363" t="n">
-        <v>11.0292</v>
+        <v>9.620799999999999</v>
       </c>
     </row>
     <row r="364">
@@ -16909,10 +16909,10 @@
         <v>1.13</v>
       </c>
       <c r="I364" t="n">
-        <v>0.1933</v>
+        <v>0.1961</v>
       </c>
       <c r="J364" t="n">
-        <v>5.4124</v>
+        <v>5.4908</v>
       </c>
     </row>
     <row r="365">
@@ -16949,10 +16949,10 @@
         <v>1.07</v>
       </c>
       <c r="I365" t="n">
-        <v>0.09080000000000001</v>
+        <v>0.111</v>
       </c>
       <c r="J365" t="n">
-        <v>2.5424</v>
+        <v>3.108</v>
       </c>
     </row>
     <row r="366">
@@ -16989,10 +16989,10 @@
         <v>1.05</v>
       </c>
       <c r="I366" t="n">
-        <v>0.054</v>
+        <v>0.0796</v>
       </c>
       <c r="J366" t="n">
-        <v>1.512</v>
+        <v>2.2288</v>
       </c>
     </row>
     <row r="367">
@@ -17029,10 +17029,10 @@
         <v>1.19</v>
       </c>
       <c r="I367" t="n">
-        <v>0.4066</v>
+        <v>0.3516</v>
       </c>
       <c r="J367" t="n">
-        <v>11.3848</v>
+        <v>9.844799999999999</v>
       </c>
     </row>
     <row r="368">
@@ -17069,10 +17069,10 @@
         <v>0.99</v>
       </c>
       <c r="I368" t="n">
-        <v>0.0197</v>
+        <v>-0.0094</v>
       </c>
       <c r="J368" t="n">
-        <v>0.5516</v>
+        <v>-0.2632</v>
       </c>
     </row>
     <row r="369">
@@ -17109,10 +17109,10 @@
         <v>0.9</v>
       </c>
       <c r="I369" t="n">
-        <v>-0.1736</v>
+        <v>-0.1241</v>
       </c>
       <c r="J369" t="n">
-        <v>-4.8608</v>
+        <v>-3.4748</v>
       </c>
     </row>
     <row r="370">
@@ -17149,10 +17149,10 @@
         <v>0.73</v>
       </c>
       <c r="I370" t="n">
-        <v>-0.4569</v>
+        <v>-0.2949</v>
       </c>
       <c r="J370" t="n">
-        <v>-12.7932</v>
+        <v>-8.257199999999999</v>
       </c>
     </row>
     <row r="371">
@@ -17189,10 +17189,10 @@
         <v>0.67</v>
       </c>
       <c r="I371" t="n">
-        <v>-0.5385</v>
+        <v>-0.3521</v>
       </c>
       <c r="J371" t="n">
-        <v>-15.078</v>
+        <v>-9.8588</v>
       </c>
     </row>
     <row r="372">
@@ -17229,10 +17229,10 @@
         <v>1.25</v>
       </c>
       <c r="I372" t="n">
-        <v>0.5288</v>
+        <v>0.6278</v>
       </c>
       <c r="J372" t="n">
-        <v>11.6336</v>
+        <v>13.8116</v>
       </c>
     </row>
     <row r="373">
@@ -17269,10 +17269,10 @@
         <v>0.82</v>
       </c>
       <c r="I373" t="n">
-        <v>-0.2614</v>
+        <v>-0.1965</v>
       </c>
       <c r="J373" t="n">
-        <v>-5.7508</v>
+        <v>-4.323</v>
       </c>
     </row>
     <row r="374">
@@ -17309,10 +17309,10 @@
         <v>0.73</v>
       </c>
       <c r="I374" t="n">
-        <v>-0.425</v>
+        <v>-0.282</v>
       </c>
       <c r="J374" t="n">
-        <v>-9.35</v>
+        <v>-6.204</v>
       </c>
     </row>
     <row r="375">
@@ -17349,10 +17349,10 @@
         <v>0.64</v>
       </c>
       <c r="I375" t="n">
-        <v>-0.5541</v>
+        <v>-0.3672</v>
       </c>
       <c r="J375" t="n">
-        <v>-12.1902</v>
+        <v>-8.0784</v>
       </c>
     </row>
     <row r="376">
@@ -17389,10 +17389,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I376" t="n">
-        <v>-0.6595</v>
+        <v>-0.442</v>
       </c>
       <c r="J376" t="n">
-        <v>-14.509</v>
+        <v>-9.724</v>
       </c>
     </row>
     <row r="377">
@@ -17429,10 +17429,10 @@
         <v>1.53</v>
       </c>
       <c r="I377" t="n">
-        <v>1.2423</v>
+        <v>1.1609</v>
       </c>
       <c r="J377" t="n">
-        <v>27.3306</v>
+        <v>25.5398</v>
       </c>
     </row>
     <row r="378">
@@ -17469,10 +17469,10 @@
         <v>1.49</v>
       </c>
       <c r="I378" t="n">
-        <v>1.162</v>
+        <v>1.1109</v>
       </c>
       <c r="J378" t="n">
-        <v>25.564</v>
+        <v>24.4398</v>
       </c>
     </row>
     <row r="379">
@@ -17509,10 +17509,10 @@
         <v>1.18</v>
       </c>
       <c r="I379" t="n">
-        <v>0.4139</v>
+        <v>0.4958</v>
       </c>
       <c r="J379" t="n">
-        <v>9.1058</v>
+        <v>10.9076</v>
       </c>
     </row>
     <row r="380">
@@ -17549,10 +17549,10 @@
         <v>1.11</v>
       </c>
       <c r="I380" t="n">
-        <v>0.229</v>
+        <v>0.3113</v>
       </c>
       <c r="J380" t="n">
-        <v>5.038</v>
+        <v>6.8486</v>
       </c>
     </row>
     <row r="381">
@@ -17589,10 +17589,10 @@
         <v>1.1</v>
       </c>
       <c r="I381" t="n">
-        <v>0.2012</v>
+        <v>0.2832</v>
       </c>
       <c r="J381" t="n">
-        <v>4.4264</v>
+        <v>6.2304</v>
       </c>
     </row>
     <row r="382">
@@ -17629,10 +17629,10 @@
         <v>1.06</v>
       </c>
       <c r="I382" t="n">
-        <v>0.1853</v>
+        <v>0.1809</v>
       </c>
       <c r="J382" t="n">
-        <v>5.3737</v>
+        <v>5.2461</v>
       </c>
     </row>
     <row r="383">
@@ -17669,10 +17669,10 @@
         <v>0.97</v>
       </c>
       <c r="I383" t="n">
-        <v>-0.0429</v>
+        <v>-0.0439</v>
       </c>
       <c r="J383" t="n">
-        <v>-1.2441</v>
+        <v>-1.2731</v>
       </c>
     </row>
     <row r="384">
@@ -17709,10 +17709,10 @@
         <v>0.96</v>
       </c>
       <c r="I384" t="n">
-        <v>-0.06519999999999999</v>
+        <v>-0.0572</v>
       </c>
       <c r="J384" t="n">
-        <v>-1.8908</v>
+        <v>-1.6588</v>
       </c>
     </row>
     <row r="385">
@@ -17749,10 +17749,10 @@
         <v>0.86</v>
       </c>
       <c r="I385" t="n">
-        <v>-0.2694</v>
+        <v>-0.1689</v>
       </c>
       <c r="J385" t="n">
-        <v>-7.8126</v>
+        <v>-4.8981</v>
       </c>
     </row>
     <row r="386">
@@ -17789,10 +17789,10 @@
         <v>0.78</v>
       </c>
       <c r="I386" t="n">
-        <v>-0.3936</v>
+        <v>-0.25</v>
       </c>
       <c r="J386" t="n">
-        <v>-11.4144</v>
+        <v>-7.25</v>
       </c>
     </row>
     <row r="387">
@@ -17829,10 +17829,10 @@
         <v>1.49</v>
       </c>
       <c r="I387" t="n">
-        <v>1.2334</v>
+        <v>1.1449</v>
       </c>
       <c r="J387" t="n">
-        <v>35.7686</v>
+        <v>33.2021</v>
       </c>
     </row>
     <row r="388">
@@ -17869,10 +17869,10 @@
         <v>1.15</v>
       </c>
       <c r="I388" t="n">
-        <v>0.4403</v>
+        <v>0.4474</v>
       </c>
       <c r="J388" t="n">
-        <v>12.7687</v>
+        <v>12.9746</v>
       </c>
     </row>
     <row r="389">
@@ -17909,10 +17909,10 @@
         <v>1.12</v>
       </c>
       <c r="I389" t="n">
-        <v>0.3347</v>
+        <v>0.3708</v>
       </c>
       <c r="J389" t="n">
-        <v>9.706300000000001</v>
+        <v>10.7532</v>
       </c>
     </row>
     <row r="390">
@@ -17949,10 +17949,10 @@
         <v>1.08</v>
       </c>
       <c r="I390" t="n">
-        <v>0.21</v>
+        <v>0.2594</v>
       </c>
       <c r="J390" t="n">
-        <v>6.09</v>
+        <v>7.5226</v>
       </c>
     </row>
     <row r="391">
@@ -17989,10 +17989,10 @@
         <v>0.85</v>
       </c>
       <c r="I391" t="n">
-        <v>-0.5899</v>
+        <v>-0.5274</v>
       </c>
       <c r="J391" t="n">
-        <v>-17.1071</v>
+        <v>-15.2946</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/2013/event_2013_evp_summary.xlsx
+++ b/database/event/2013/event_2013_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8.046099999999999</v>
+        <v>7.8934</v>
       </c>
       <c r="C2" t="n">
-        <v>2.685</v>
+        <v>2.6341</v>
       </c>
       <c r="D2" t="n">
-        <v>2.9944</v>
+        <v>2.969</v>
       </c>
       <c r="E2" t="n">
-        <v>8.046099999999999</v>
+        <v>7.8934</v>
       </c>
       <c r="F2" t="n">
-        <v>4.4768</v>
+        <v>4.2493</v>
       </c>
       <c r="G2" t="n">
-        <v>3.5693</v>
+        <v>3.6441</v>
       </c>
       <c r="H2" t="n">
-        <v>6.4705</v>
+        <v>6.5756</v>
       </c>
       <c r="I2" t="n">
-        <v>7.3021</v>
+        <v>7.0971</v>
       </c>
       <c r="J2" t="n">
-        <v>3.5693</v>
+        <v>3.6441</v>
       </c>
       <c r="K2" t="n">
         <v>331</v>
@@ -529,7 +529,7 @@
         <v>72</v>
       </c>
       <c r="M2" t="n">
-        <v>10.8714</v>
+        <v>10.7412</v>
       </c>
       <c r="N2" t="n">
         <v>403</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.5171</v>
+        <v>5.3549</v>
       </c>
       <c r="C3" t="n">
-        <v>1.8411</v>
+        <v>1.787</v>
       </c>
       <c r="D3" t="n">
-        <v>1.8527</v>
+        <v>1.8135</v>
       </c>
       <c r="E3" t="n">
-        <v>5.5171</v>
+        <v>5.3549</v>
       </c>
       <c r="F3" t="n">
-        <v>2.8014</v>
+        <v>2.5292</v>
       </c>
       <c r="G3" t="n">
-        <v>2.7157</v>
+        <v>2.8257</v>
       </c>
       <c r="H3" t="n">
-        <v>2.8014</v>
+        <v>2.8107</v>
       </c>
       <c r="I3" t="n">
-        <v>3.1615</v>
+        <v>3.0336</v>
       </c>
       <c r="J3" t="n">
-        <v>2.7157</v>
+        <v>2.8257</v>
       </c>
       <c r="K3" t="n">
         <v>331</v>
@@ -575,7 +575,7 @@
         <v>72</v>
       </c>
       <c r="M3" t="n">
-        <v>5.8772</v>
+        <v>5.859299999999999</v>
       </c>
       <c r="N3" t="n">
         <v>403</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.802</v>
+        <v>4.7119</v>
       </c>
       <c r="C4" t="n">
-        <v>1.6025</v>
+        <v>1.5724</v>
       </c>
       <c r="D4" t="n">
-        <v>1.5298</v>
+        <v>1.5208</v>
       </c>
       <c r="E4" t="n">
-        <v>4.802</v>
+        <v>4.7119</v>
       </c>
       <c r="F4" t="n">
-        <v>2.9931</v>
+        <v>2.7353</v>
       </c>
       <c r="G4" t="n">
-        <v>1.8089</v>
+        <v>1.9766</v>
       </c>
       <c r="H4" t="n">
-        <v>3.2125</v>
+        <v>3.2618</v>
       </c>
       <c r="I4" t="n">
-        <v>3.6254</v>
+        <v>3.5205</v>
       </c>
       <c r="J4" t="n">
-        <v>1.8089</v>
+        <v>1.9766</v>
       </c>
       <c r="K4" t="n">
         <v>331</v>
@@ -621,7 +621,7 @@
         <v>72</v>
       </c>
       <c r="M4" t="n">
-        <v>5.4343</v>
+        <v>5.4971</v>
       </c>
       <c r="N4" t="n">
         <v>403</v>
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.6239</v>
+        <v>4.3316</v>
       </c>
       <c r="C5" t="n">
-        <v>1.543</v>
+        <v>1.4455</v>
       </c>
       <c r="D5" t="n">
-        <v>1.4494</v>
+        <v>1.3476</v>
       </c>
       <c r="E5" t="n">
-        <v>4.6239</v>
+        <v>4.3316</v>
       </c>
       <c r="F5" t="n">
-        <v>3.0902</v>
+        <v>2.8267</v>
       </c>
       <c r="G5" t="n">
-        <v>1.5337</v>
+        <v>1.5049</v>
       </c>
       <c r="H5" t="n">
-        <v>3.4257</v>
+        <v>3.4617</v>
       </c>
       <c r="I5" t="n">
-        <v>3.866</v>
+        <v>3.7363</v>
       </c>
       <c r="J5" t="n">
-        <v>1.5337</v>
+        <v>1.5049</v>
       </c>
       <c r="K5" t="n">
         <v>331</v>
@@ -667,7 +667,7 @@
         <v>72</v>
       </c>
       <c r="M5" t="n">
-        <v>5.3997</v>
+        <v>5.2412</v>
       </c>
       <c r="N5" t="n">
         <v>403</v>
@@ -680,28 +680,28 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.1766</v>
+        <v>3.8304</v>
       </c>
       <c r="C6" t="n">
-        <v>1.3938</v>
+        <v>1.2782</v>
       </c>
       <c r="D6" t="n">
-        <v>1.2475</v>
+        <v>1.1195</v>
       </c>
       <c r="E6" t="n">
-        <v>4.1766</v>
+        <v>3.8304</v>
       </c>
       <c r="F6" t="n">
-        <v>4.1766</v>
+        <v>3.8304</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>5.8112</v>
+        <v>5.6587</v>
       </c>
       <c r="I6" t="n">
-        <v>5.8112</v>
+        <v>5.6587</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -713,7 +713,7 @@
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>5.8112</v>
+        <v>5.6587</v>
       </c>
       <c r="N6" t="n">
         <v>249</v>
@@ -726,28 +726,28 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.8869</v>
+        <v>3.5837</v>
       </c>
       <c r="C7" t="n">
-        <v>1.2971</v>
+        <v>1.1959</v>
       </c>
       <c r="D7" t="n">
-        <v>1.1167</v>
+        <v>1.0072</v>
       </c>
       <c r="E7" t="n">
-        <v>3.8869</v>
+        <v>3.5837</v>
       </c>
       <c r="F7" t="n">
-        <v>3.8869</v>
+        <v>3.5837</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>5.1752</v>
+        <v>5.1186</v>
       </c>
       <c r="I7" t="n">
-        <v>5.388</v>
+        <v>5.2505</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -759,7 +759,7 @@
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>5.388</v>
+        <v>5.2505</v>
       </c>
       <c r="N7" t="n">
         <v>301</v>
@@ -772,28 +772,28 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.7762</v>
+        <v>3.4433</v>
       </c>
       <c r="C8" t="n">
-        <v>1.2601</v>
+        <v>1.1491</v>
       </c>
       <c r="D8" t="n">
-        <v>1.0668</v>
+        <v>0.9433</v>
       </c>
       <c r="E8" t="n">
-        <v>3.7762</v>
+        <v>3.4433</v>
       </c>
       <c r="F8" t="n">
-        <v>3.7762</v>
+        <v>3.4433</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>4.932</v>
+        <v>4.8113</v>
       </c>
       <c r="I8" t="n">
-        <v>4.932</v>
+        <v>4.8113</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -805,7 +805,7 @@
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>4.932</v>
+        <v>4.8113</v>
       </c>
       <c r="N8" t="n">
         <v>249</v>
@@ -814,32 +814,32 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>cajunb</t>
+          <t>dupreeh</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.6192</v>
+        <v>3.2782</v>
       </c>
       <c r="C9" t="n">
-        <v>1.2078</v>
+        <v>1.094</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9959</v>
+        <v>0.8681</v>
       </c>
       <c r="E9" t="n">
-        <v>3.6192</v>
+        <v>3.2782</v>
       </c>
       <c r="F9" t="n">
-        <v>3.6192</v>
+        <v>3.2782</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>4.5874</v>
+        <v>4.45</v>
       </c>
       <c r="I9" t="n">
-        <v>4.5874</v>
+        <v>4.45</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -851,7 +851,7 @@
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>4.5874</v>
+        <v>4.45</v>
       </c>
       <c r="N9" t="n">
         <v>249</v>
@@ -860,32 +860,32 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>dupreeh</t>
+          <t>cajunb</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.5471</v>
+        <v>3.2596</v>
       </c>
       <c r="C10" t="n">
-        <v>1.1837</v>
+        <v>1.0878</v>
       </c>
       <c r="D10" t="n">
-        <v>0.9633</v>
+        <v>0.8596</v>
       </c>
       <c r="E10" t="n">
-        <v>3.5471</v>
+        <v>3.2596</v>
       </c>
       <c r="F10" t="n">
-        <v>3.5471</v>
+        <v>3.2596</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>4.4291</v>
+        <v>4.4094</v>
       </c>
       <c r="I10" t="n">
-        <v>4.4291</v>
+        <v>4.4094</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -897,7 +897,7 @@
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>4.4291</v>
+        <v>4.4094</v>
       </c>
       <c r="N10" t="n">
         <v>249</v>
@@ -906,124 +906,124 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>k0nfig</t>
+          <t>kioShiMa</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.2942</v>
+        <v>2.9704</v>
       </c>
       <c r="C11" t="n">
-        <v>1.0993</v>
+        <v>0.9912</v>
       </c>
       <c r="D11" t="n">
-        <v>0.8492</v>
+        <v>0.728</v>
       </c>
       <c r="E11" t="n">
-        <v>3.2942</v>
+        <v>2.9704</v>
       </c>
       <c r="F11" t="n">
-        <v>3.7313</v>
+        <v>2.3365</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.4371</v>
+        <v>0.6339</v>
       </c>
       <c r="H11" t="n">
-        <v>4.8335</v>
+        <v>2.3889</v>
       </c>
       <c r="I11" t="n">
-        <v>5.0323</v>
+        <v>2.5784</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.4371</v>
+        <v>0.6339</v>
       </c>
       <c r="K11" t="n">
-        <v>159</v>
+        <v>331</v>
       </c>
       <c r="L11" t="n">
         <v>72</v>
       </c>
       <c r="M11" t="n">
-        <v>4.5952</v>
+        <v>3.2123</v>
       </c>
       <c r="N11" t="n">
-        <v>231</v>
+        <v>403</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>shox</t>
+          <t>k0nfig</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3.2535</v>
+        <v>2.9485</v>
       </c>
       <c r="C12" t="n">
-        <v>1.0857</v>
+        <v>0.9839</v>
       </c>
       <c r="D12" t="n">
-        <v>0.8308</v>
+        <v>0.718</v>
       </c>
       <c r="E12" t="n">
-        <v>3.2535</v>
+        <v>2.9485</v>
       </c>
       <c r="F12" t="n">
-        <v>3.2535</v>
+        <v>3.4224</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>-0.4739</v>
       </c>
       <c r="H12" t="n">
-        <v>3.7843</v>
+        <v>4.7656</v>
       </c>
       <c r="I12" t="n">
-        <v>3.9399</v>
+        <v>4.8884</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>-0.4739</v>
       </c>
       <c r="K12" t="n">
-        <v>301</v>
+        <v>159</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="M12" t="n">
-        <v>3.9399</v>
+        <v>4.4145</v>
       </c>
       <c r="N12" t="n">
-        <v>301</v>
+        <v>231</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SmithZz</t>
+          <t>shox</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3.1831</v>
+        <v>2.9249</v>
       </c>
       <c r="C13" t="n">
-        <v>1.0622</v>
+        <v>0.9761</v>
       </c>
       <c r="D13" t="n">
-        <v>0.799</v>
+        <v>0.7073</v>
       </c>
       <c r="E13" t="n">
-        <v>3.1831</v>
+        <v>2.9249</v>
       </c>
       <c r="F13" t="n">
-        <v>3.1831</v>
+        <v>2.9249</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>3.6298</v>
+        <v>3.6769</v>
       </c>
       <c r="I13" t="n">
-        <v>3.7791</v>
+        <v>3.7716</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1035,7 +1035,7 @@
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>3.7791</v>
+        <v>3.7716</v>
       </c>
       <c r="N13" t="n">
         <v>301</v>
@@ -1044,47 +1044,47 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>kioShiMa</t>
+          <t>SmithZz</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3.0172</v>
+        <v>2.877</v>
       </c>
       <c r="C14" t="n">
-        <v>1.0069</v>
+        <v>0.9601</v>
       </c>
       <c r="D14" t="n">
-        <v>0.7241</v>
+        <v>0.6855</v>
       </c>
       <c r="E14" t="n">
-        <v>3.0172</v>
+        <v>2.877</v>
       </c>
       <c r="F14" t="n">
-        <v>2.4277</v>
+        <v>2.877</v>
       </c>
       <c r="G14" t="n">
-        <v>0.5895</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>2.4277</v>
+        <v>3.572</v>
       </c>
       <c r="I14" t="n">
-        <v>2.7397</v>
+        <v>3.664</v>
       </c>
       <c r="J14" t="n">
-        <v>0.5895</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>331</v>
+        <v>301</v>
       </c>
       <c r="L14" t="n">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>3.3292</v>
+        <v>3.664</v>
       </c>
       <c r="N14" t="n">
-        <v>403</v>
+        <v>301</v>
       </c>
     </row>
     <row r="15">
@@ -1094,28 +1094,28 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.7585</v>
+        <v>2.4258</v>
       </c>
       <c r="C15" t="n">
-        <v>0.9205</v>
+        <v>0.8095</v>
       </c>
       <c r="D15" t="n">
-        <v>0.6073</v>
+        <v>0.4801</v>
       </c>
       <c r="E15" t="n">
-        <v>2.7585</v>
+        <v>2.4258</v>
       </c>
       <c r="F15" t="n">
-        <v>2.7585</v>
+        <v>2.4258</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>2.7585</v>
+        <v>2.5844</v>
       </c>
       <c r="I15" t="n">
-        <v>2.7585</v>
+        <v>2.5844</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1127,7 +1127,7 @@
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>2.7585</v>
+        <v>2.5844</v>
       </c>
       <c r="N15" t="n">
         <v>247</v>
@@ -1136,47 +1136,47 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Kjaerbye</t>
+          <t>Ex6TenZ</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.4742</v>
+        <v>2.315</v>
       </c>
       <c r="C16" t="n">
-        <v>0.8257</v>
+        <v>0.7725</v>
       </c>
       <c r="D16" t="n">
-        <v>0.479</v>
+        <v>0.4296</v>
       </c>
       <c r="E16" t="n">
-        <v>2.4742</v>
+        <v>2.315</v>
       </c>
       <c r="F16" t="n">
-        <v>3.2964</v>
+        <v>2.315</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.8222</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>3.8786</v>
+        <v>2.342</v>
       </c>
       <c r="I16" t="n">
-        <v>4.0381</v>
+        <v>2.4023</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.8222</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>159</v>
+        <v>301</v>
       </c>
       <c r="L16" t="n">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>3.2159</v>
+        <v>2.4023</v>
       </c>
       <c r="N16" t="n">
-        <v>231</v>
+        <v>301</v>
       </c>
     </row>
     <row r="17">
@@ -1186,28 +1186,28 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.3993</v>
+        <v>2.2987</v>
       </c>
       <c r="C17" t="n">
-        <v>0.8007</v>
+        <v>0.7671</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4452</v>
+        <v>0.4222</v>
       </c>
       <c r="E17" t="n">
-        <v>2.3993</v>
+        <v>2.2987</v>
       </c>
       <c r="F17" t="n">
-        <v>2.3993</v>
+        <v>2.2987</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>2.3993</v>
+        <v>2.3062</v>
       </c>
       <c r="I17" t="n">
-        <v>2.498</v>
+        <v>2.3656</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1219,7 +1219,7 @@
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>2.498</v>
+        <v>2.3656</v>
       </c>
       <c r="N17" t="n">
         <v>369</v>
@@ -1228,47 +1228,47 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Ex6TenZ</t>
+          <t>Kjaerbye</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2.3874</v>
+        <v>2.1169</v>
       </c>
       <c r="C18" t="n">
-        <v>0.7967</v>
+        <v>0.7064</v>
       </c>
       <c r="D18" t="n">
-        <v>0.4398</v>
+        <v>0.3395</v>
       </c>
       <c r="E18" t="n">
-        <v>2.3874</v>
+        <v>2.1169</v>
       </c>
       <c r="F18" t="n">
-        <v>2.3874</v>
+        <v>2.9918</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>-0.8749</v>
       </c>
       <c r="H18" t="n">
-        <v>2.3874</v>
+        <v>3.8231</v>
       </c>
       <c r="I18" t="n">
-        <v>2.4856</v>
+        <v>3.9216</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>-0.8749</v>
       </c>
       <c r="K18" t="n">
-        <v>301</v>
+        <v>159</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="M18" t="n">
-        <v>2.4856</v>
+        <v>3.0467</v>
       </c>
       <c r="N18" t="n">
-        <v>301</v>
+        <v>231</v>
       </c>
     </row>
     <row r="19">
@@ -1278,28 +1278,28 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.8906</v>
+        <v>1.908</v>
       </c>
       <c r="C19" t="n">
-        <v>0.6309</v>
+        <v>0.6367</v>
       </c>
       <c r="D19" t="n">
-        <v>0.2155</v>
+        <v>0.2444</v>
       </c>
       <c r="E19" t="n">
-        <v>1.8906</v>
+        <v>1.908</v>
       </c>
       <c r="F19" t="n">
-        <v>1.8906</v>
+        <v>1.908</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>1.8906</v>
+        <v>1.908</v>
       </c>
       <c r="I19" t="n">
-        <v>1.8906</v>
+        <v>1.908</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -1311,7 +1311,7 @@
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>1.8906</v>
+        <v>1.908</v>
       </c>
       <c r="N19" t="n">
         <v>249</v>
@@ -1320,93 +1320,93 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Skadoodle</t>
+          <t>RUBINO</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.3076</v>
+        <v>1.23</v>
       </c>
       <c r="C20" t="n">
-        <v>0.4364</v>
+        <v>0.4105</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.0477</v>
+        <v>-0.0643</v>
       </c>
       <c r="E20" t="n">
-        <v>1.3076</v>
+        <v>1.23</v>
       </c>
       <c r="F20" t="n">
-        <v>1.3076</v>
+        <v>1.2035</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>0.0265</v>
       </c>
       <c r="H20" t="n">
-        <v>1.3076</v>
+        <v>1.2035</v>
       </c>
       <c r="I20" t="n">
-        <v>1.3076</v>
+        <v>1.2345</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>0.0265</v>
       </c>
       <c r="K20" t="n">
-        <v>247</v>
+        <v>159</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="M20" t="n">
-        <v>1.3076</v>
+        <v>1.261</v>
       </c>
       <c r="N20" t="n">
-        <v>247</v>
+        <v>231</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>RUBINO</t>
+          <t>Skadoodle</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.2629</v>
+        <v>1.1642</v>
       </c>
       <c r="C21" t="n">
-        <v>0.4214</v>
+        <v>0.3885</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.0679</v>
+        <v>-0.09420000000000001</v>
       </c>
       <c r="E21" t="n">
-        <v>1.2629</v>
+        <v>1.1642</v>
       </c>
       <c r="F21" t="n">
-        <v>1.2079</v>
+        <v>1.1642</v>
       </c>
       <c r="G21" t="n">
-        <v>0.055</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>1.2079</v>
+        <v>1.1642</v>
       </c>
       <c r="I21" t="n">
-        <v>1.2576</v>
+        <v>1.1642</v>
       </c>
       <c r="J21" t="n">
-        <v>0.055</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>159</v>
+        <v>247</v>
       </c>
       <c r="L21" t="n">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>1.3126</v>
+        <v>1.1642</v>
       </c>
       <c r="N21" t="n">
-        <v>231</v>
+        <v>247</v>
       </c>
     </row>
     <row r="22">
@@ -1416,31 +1416,31 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.0713</v>
+        <v>1.0936</v>
       </c>
       <c r="C22" t="n">
-        <v>0.3575</v>
+        <v>0.3649</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.1544</v>
+        <v>-0.1264</v>
       </c>
       <c r="E22" t="n">
-        <v>1.0713</v>
+        <v>1.0936</v>
       </c>
       <c r="F22" t="n">
-        <v>1.9318</v>
+        <v>1.9753</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.8605</v>
+        <v>-0.8817</v>
       </c>
       <c r="H22" t="n">
-        <v>1.9318</v>
+        <v>1.9753</v>
       </c>
       <c r="I22" t="n">
-        <v>2.0113</v>
+        <v>2.0262</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.8605</v>
+        <v>-0.8817</v>
       </c>
       <c r="K22" t="n">
         <v>159</v>
@@ -1449,7 +1449,7 @@
         <v>72</v>
       </c>
       <c r="M22" t="n">
-        <v>1.1508</v>
+        <v>1.1445</v>
       </c>
       <c r="N22" t="n">
         <v>231</v>
@@ -1462,31 +1462,31 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.9036999999999999</v>
+        <v>0.8469</v>
       </c>
       <c r="C23" t="n">
-        <v>0.3016</v>
+        <v>0.2826</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.23</v>
+        <v>-0.2387</v>
       </c>
       <c r="E23" t="n">
-        <v>0.9036999999999999</v>
+        <v>0.8469</v>
       </c>
       <c r="F23" t="n">
-        <v>1.4731</v>
+        <v>1.4687</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.5694</v>
+        <v>-0.6218</v>
       </c>
       <c r="H23" t="n">
-        <v>1.4731</v>
+        <v>1.4687</v>
       </c>
       <c r="I23" t="n">
-        <v>1.5337</v>
+        <v>1.5065</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.5694</v>
+        <v>-0.6218</v>
       </c>
       <c r="K23" t="n">
         <v>159</v>
@@ -1495,7 +1495,7 @@
         <v>72</v>
       </c>
       <c r="M23" t="n">
-        <v>0.9643</v>
+        <v>0.8846999999999999</v>
       </c>
       <c r="N23" t="n">
         <v>231</v>
@@ -1508,28 +1508,28 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.8571</v>
+        <v>0.7881</v>
       </c>
       <c r="C24" t="n">
-        <v>0.286</v>
+        <v>0.263</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.2511</v>
+        <v>-0.2654</v>
       </c>
       <c r="E24" t="n">
-        <v>0.8571</v>
+        <v>0.7881</v>
       </c>
       <c r="F24" t="n">
-        <v>0.8571</v>
+        <v>0.7881</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0.8571</v>
+        <v>0.7881</v>
       </c>
       <c r="I24" t="n">
-        <v>0.8571</v>
+        <v>0.7881</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0.8571</v>
+        <v>0.7881</v>
       </c>
       <c r="N24" t="n">
         <v>95</v>
@@ -1554,28 +1554,28 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.7516</v>
+        <v>0.6773</v>
       </c>
       <c r="C25" t="n">
-        <v>0.2508</v>
+        <v>0.226</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.2987</v>
+        <v>-0.3159</v>
       </c>
       <c r="E25" t="n">
-        <v>0.7516</v>
+        <v>0.6773</v>
       </c>
       <c r="F25" t="n">
-        <v>0.7516</v>
+        <v>0.6773</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>0.7516</v>
+        <v>0.6773</v>
       </c>
       <c r="I25" t="n">
-        <v>0.7825</v>
+        <v>0.6948</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -1587,7 +1587,7 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>0.7825</v>
+        <v>0.6948</v>
       </c>
       <c r="N25" t="n">
         <v>301</v>
@@ -1600,28 +1600,28 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.5039</v>
+        <v>0.4578</v>
       </c>
       <c r="C26" t="n">
-        <v>0.1682</v>
+        <v>0.1528</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.4105</v>
+        <v>-0.4158</v>
       </c>
       <c r="E26" t="n">
-        <v>0.5039</v>
+        <v>0.4578</v>
       </c>
       <c r="F26" t="n">
-        <v>0.5039</v>
+        <v>0.4578</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0.5039</v>
+        <v>0.4578</v>
       </c>
       <c r="I26" t="n">
-        <v>0.5039</v>
+        <v>0.4578</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -1633,7 +1633,7 @@
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>0.5039</v>
+        <v>0.4578</v>
       </c>
       <c r="N26" t="n">
         <v>107</v>
@@ -1646,28 +1646,28 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.4306</v>
+        <v>0.2897</v>
       </c>
       <c r="C27" t="n">
-        <v>0.1437</v>
+        <v>0.09669999999999999</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.4436</v>
+        <v>-0.4923</v>
       </c>
       <c r="E27" t="n">
-        <v>0.4306</v>
+        <v>0.2897</v>
       </c>
       <c r="F27" t="n">
-        <v>0.4306</v>
+        <v>0.2897</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>0.4306</v>
+        <v>0.2897</v>
       </c>
       <c r="I27" t="n">
-        <v>0.4484</v>
+        <v>0.2972</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -1679,7 +1679,7 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>0.4484</v>
+        <v>0.2972</v>
       </c>
       <c r="N27" t="n">
         <v>369</v>
@@ -1688,93 +1688,93 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>FugLy</t>
+          <t>WorldEdit</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.0065</v>
+        <v>-0.0839</v>
       </c>
       <c r="C28" t="n">
-        <v>0.0022</v>
+        <v>-0.028</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.6351</v>
+        <v>-0.6624</v>
       </c>
       <c r="E28" t="n">
-        <v>0.0065</v>
+        <v>-0.0839</v>
       </c>
       <c r="F28" t="n">
-        <v>0.0065</v>
+        <v>-0.0839</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>0.0065</v>
+        <v>-0.0839</v>
       </c>
       <c r="I28" t="n">
-        <v>0.0067</v>
+        <v>-0.0839</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>369</v>
+        <v>107</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>0.0067</v>
+        <v>-0.0839</v>
       </c>
       <c r="N28" t="n">
-        <v>369</v>
+        <v>107</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>WorldEdit</t>
+          <t>FugLy</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.0133</v>
+        <v>-0.121</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.0044</v>
+        <v>-0.0404</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.644</v>
+        <v>-0.6793</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.0133</v>
+        <v>-0.121</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.0133</v>
+        <v>-0.121</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.0133</v>
+        <v>-0.121</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.0133</v>
+        <v>-0.1241</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>107</v>
+        <v>369</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.0133</v>
+        <v>-0.1241</v>
       </c>
       <c r="N29" t="n">
-        <v>107</v>
+        <v>369</v>
       </c>
     </row>
     <row r="30">
@@ -1784,28 +1784,28 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.1055</v>
+        <v>-0.1274</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.0352</v>
+        <v>-0.0425</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.6856</v>
+        <v>-0.6822</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.1055</v>
+        <v>-0.1274</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.1055</v>
+        <v>-0.1274</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.1055</v>
+        <v>-0.1274</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.1055</v>
+        <v>-0.1274</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -1817,7 +1817,7 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.1055</v>
+        <v>-0.1274</v>
       </c>
       <c r="N30" t="n">
         <v>95</v>
@@ -1826,93 +1826,93 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>hazed</t>
+          <t>Stewie2K</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.231</v>
+        <v>-0.3107</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.0771</v>
+        <v>-0.1037</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.7423</v>
+        <v>-0.7655999999999999</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.231</v>
+        <v>-0.3107</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.231</v>
+        <v>-0.3107</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.231</v>
+        <v>-0.3107</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.2404</v>
+        <v>-0.3107</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>369</v>
+        <v>247</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.2404</v>
+        <v>-0.3107</v>
       </c>
       <c r="N31" t="n">
-        <v>369</v>
+        <v>247</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Stewie2K</t>
+          <t>hazed</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.301</v>
+        <v>-0.3933</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.1004</v>
+        <v>-0.1312</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.7739</v>
+        <v>-0.8032</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.301</v>
+        <v>-0.3933</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.301</v>
+        <v>-0.3933</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.301</v>
+        <v>-0.3933</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.301</v>
+        <v>-0.4034</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>247</v>
+        <v>369</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.301</v>
+        <v>-0.4034</v>
       </c>
       <c r="N32" t="n">
-        <v>247</v>
+        <v>369</v>
       </c>
     </row>
     <row r="33">
@@ -1922,28 +1922,28 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.403</v>
+        <v>-0.4372</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.1345</v>
+        <v>-0.1459</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.8199</v>
+        <v>-0.8232</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.403</v>
+        <v>-0.4372</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.403</v>
+        <v>-0.4372</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.403</v>
+        <v>-0.4372</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.403</v>
+        <v>-0.4372</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.403</v>
+        <v>-0.4372</v>
       </c>
       <c r="N33" t="n">
         <v>107</v>
@@ -1968,28 +1968,28 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.5542</v>
+        <v>-0.5983000000000001</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.1849</v>
+        <v>-0.1997</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.8882</v>
+        <v>-0.8966</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.5542</v>
+        <v>-0.5983000000000001</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.5542</v>
+        <v>-0.5983000000000001</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.5542</v>
+        <v>-0.5983000000000001</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.5542</v>
+        <v>-0.5983000000000001</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -2001,7 +2001,7 @@
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.5542</v>
+        <v>-0.5983000000000001</v>
       </c>
       <c r="N34" t="n">
         <v>107</v>
@@ -2010,93 +2010,93 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>n0thing</t>
+          <t>bondik</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.6532</v>
+        <v>-0.7251</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.218</v>
+        <v>-0.242</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.9329</v>
+        <v>-0.9543</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.6532</v>
+        <v>-0.7251</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.6532</v>
+        <v>-0.7251</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.6532</v>
+        <v>-0.7251</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.6532</v>
+        <v>-0.7251</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>247</v>
+        <v>107</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.6532</v>
+        <v>-0.7251</v>
       </c>
       <c r="N35" t="n">
-        <v>247</v>
+        <v>107</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>bondik</t>
+          <t>n0thing</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.6902</v>
+        <v>-0.7379</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.2303</v>
+        <v>-0.2462</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.9496</v>
+        <v>-0.9601</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.6902</v>
+        <v>-0.7379</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.6902</v>
+        <v>-0.7379</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.6902</v>
+        <v>-0.7379</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.6902</v>
+        <v>-0.7379</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>107</v>
+        <v>247</v>
       </c>
       <c r="L36" t="n">
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.6902</v>
+        <v>-0.7379</v>
       </c>
       <c r="N36" t="n">
-        <v>107</v>
+        <v>247</v>
       </c>
     </row>
     <row r="37">
@@ -2106,28 +2106,28 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-0.8092</v>
+        <v>-0.8758</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.27</v>
+        <v>-0.2923</v>
       </c>
       <c r="D37" t="n">
-        <v>-1.0033</v>
+        <v>-1.0229</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.8092</v>
+        <v>-0.8758</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.8092</v>
+        <v>-0.8758</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.8092</v>
+        <v>-0.8758</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.8425</v>
+        <v>-0.8984</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -2139,7 +2139,7 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>-0.8425</v>
+        <v>-0.8984</v>
       </c>
       <c r="N37" t="n">
         <v>369</v>
@@ -2148,93 +2148,93 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>fejtZ</t>
+          <t>freakazoid</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-1.1899</v>
+        <v>-1.2623</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.3971</v>
+        <v>-0.4212</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.1752</v>
+        <v>-1.1988</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.1899</v>
+        <v>-1.2623</v>
       </c>
       <c r="F38" t="n">
-        <v>-1.1899</v>
+        <v>-1.2623</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>-1.1899</v>
+        <v>-1.2623</v>
       </c>
       <c r="I38" t="n">
-        <v>-1.1899</v>
+        <v>-1.2623</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>95</v>
+        <v>247</v>
       </c>
       <c r="L38" t="n">
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>-1.1899</v>
+        <v>-1.2623</v>
       </c>
       <c r="N38" t="n">
-        <v>95</v>
+        <v>247</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>freakazoid</t>
+          <t>fejtZ</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.218</v>
+        <v>-1.2665</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.4065</v>
+        <v>-0.4226</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.1879</v>
+        <v>-1.2007</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.218</v>
+        <v>-1.2665</v>
       </c>
       <c r="F39" t="n">
-        <v>-1.218</v>
+        <v>-1.2665</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>-1.218</v>
+        <v>-1.2665</v>
       </c>
       <c r="I39" t="n">
-        <v>-1.218</v>
+        <v>-1.2665</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>247</v>
+        <v>95</v>
       </c>
       <c r="L39" t="n">
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>-1.218</v>
+        <v>-1.2665</v>
       </c>
       <c r="N39" t="n">
-        <v>247</v>
+        <v>95</v>
       </c>
     </row>
     <row r="40">
@@ -2244,28 +2244,28 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-1.3085</v>
+        <v>-1.3707</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.4367</v>
+        <v>-0.4574</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.2287</v>
+        <v>-1.2482</v>
       </c>
       <c r="E40" t="n">
-        <v>-1.3085</v>
+        <v>-1.3707</v>
       </c>
       <c r="F40" t="n">
-        <v>-1.3085</v>
+        <v>-1.3707</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>-1.3085</v>
+        <v>-1.3707</v>
       </c>
       <c r="I40" t="n">
-        <v>-1.3085</v>
+        <v>-1.3707</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -2277,7 +2277,7 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>-1.3085</v>
+        <v>-1.3707</v>
       </c>
       <c r="N40" t="n">
         <v>95</v>
@@ -2290,28 +2290,28 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-1.3719</v>
+        <v>-1.4366</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.4578</v>
+        <v>-0.4794</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.2574</v>
+        <v>-1.2782</v>
       </c>
       <c r="E41" t="n">
-        <v>-1.3719</v>
+        <v>-1.4366</v>
       </c>
       <c r="F41" t="n">
-        <v>-1.3719</v>
+        <v>-1.4366</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>-1.3719</v>
+        <v>-1.4366</v>
       </c>
       <c r="I41" t="n">
-        <v>-1.3719</v>
+        <v>-1.4366</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -2323,7 +2323,7 @@
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>-1.3719</v>
+        <v>-1.4366</v>
       </c>
       <c r="N41" t="n">
         <v>95</v>
@@ -2429,10 +2429,10 @@
         <v>1.93</v>
       </c>
       <c r="I2" t="n">
-        <v>1.5726</v>
+        <v>1.7156</v>
       </c>
       <c r="J2" t="n">
-        <v>31.452</v>
+        <v>34.312</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>1.84</v>
       </c>
       <c r="I3" t="n">
-        <v>1.4729</v>
+        <v>1.6088</v>
       </c>
       <c r="J3" t="n">
-        <v>29.458</v>
+        <v>32.176</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>1.62</v>
       </c>
       <c r="I4" t="n">
-        <v>1.2254</v>
+        <v>1.2781</v>
       </c>
       <c r="J4" t="n">
-        <v>24.508</v>
+        <v>25.562</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>1.33</v>
       </c>
       <c r="I5" t="n">
-        <v>0.7912</v>
+        <v>0.7643</v>
       </c>
       <c r="J5" t="n">
-        <v>15.824</v>
+        <v>15.286</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>1.1</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2236</v>
+        <v>0.2551</v>
       </c>
       <c r="J6" t="n">
-        <v>4.472</v>
+        <v>5.102</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>0.74</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.2413</v>
+        <v>-0.2665</v>
       </c>
       <c r="J7" t="n">
-        <v>-4.826</v>
+        <v>-5.33</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.2924</v>
+        <v>-0.3155</v>
       </c>
       <c r="J8" t="n">
-        <v>-5.848</v>
+        <v>-6.31</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>0.64</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.3404</v>
+        <v>-0.3614</v>
       </c>
       <c r="J9" t="n">
-        <v>-6.808</v>
+        <v>-7.228</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>0.54</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.4302</v>
+        <v>-0.447</v>
       </c>
       <c r="J10" t="n">
-        <v>-8.603999999999999</v>
+        <v>-8.94</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>0.46</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.5054</v>
+        <v>-0.5174</v>
       </c>
       <c r="J11" t="n">
-        <v>-10.108</v>
+        <v>-10.348</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>1.62</v>
       </c>
       <c r="I12" t="n">
-        <v>1.2781</v>
+        <v>1.3405</v>
       </c>
       <c r="J12" t="n">
-        <v>29.3963</v>
+        <v>30.8315</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>1.24</v>
       </c>
       <c r="I13" t="n">
-        <v>0.6454</v>
+        <v>0.6238</v>
       </c>
       <c r="J13" t="n">
-        <v>14.8442</v>
+        <v>14.3474</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>1.21</v>
       </c>
       <c r="I14" t="n">
-        <v>0.5749</v>
+        <v>0.5605</v>
       </c>
       <c r="J14" t="n">
-        <v>13.2227</v>
+        <v>12.8915</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>1.14</v>
       </c>
       <c r="I15" t="n">
-        <v>0.3987</v>
+        <v>0.4013</v>
       </c>
       <c r="J15" t="n">
-        <v>9.1701</v>
+        <v>9.229900000000001</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>1.07</v>
       </c>
       <c r="I16" t="n">
-        <v>0.2014</v>
+        <v>0.2193</v>
       </c>
       <c r="J16" t="n">
-        <v>4.6322</v>
+        <v>5.0439</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>1.1</v>
       </c>
       <c r="I17" t="n">
-        <v>0.3013</v>
+        <v>0.2927</v>
       </c>
       <c r="J17" t="n">
-        <v>6.9299</v>
+        <v>6.7321</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>1</v>
       </c>
       <c r="I18" t="n">
-        <v>0.0398</v>
+        <v>0.0288</v>
       </c>
       <c r="J18" t="n">
-        <v>0.9154</v>
+        <v>0.6624</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>0.75</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.2684</v>
+        <v>-0.2854</v>
       </c>
       <c r="J19" t="n">
-        <v>-6.1732</v>
+        <v>-6.5642</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>0.75</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.2684</v>
+        <v>-0.2854</v>
       </c>
       <c r="J20" t="n">
-        <v>-6.1732</v>
+        <v>-6.5642</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>0.61</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.4012</v>
+        <v>-0.4136</v>
       </c>
       <c r="J21" t="n">
-        <v>-9.227600000000001</v>
+        <v>-9.5128</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>1.43</v>
       </c>
       <c r="I22" t="n">
-        <v>1.0658</v>
+        <v>1.0255</v>
       </c>
       <c r="J22" t="n">
-        <v>30.9082</v>
+        <v>29.7395</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>1.17</v>
       </c>
       <c r="I23" t="n">
-        <v>0.4977</v>
+        <v>0.4863</v>
       </c>
       <c r="J23" t="n">
-        <v>14.4333</v>
+        <v>14.1027</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>1.05</v>
       </c>
       <c r="I24" t="n">
-        <v>0.1676</v>
+        <v>0.1801</v>
       </c>
       <c r="J24" t="n">
-        <v>4.8604</v>
+        <v>5.2229</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>1.04</v>
       </c>
       <c r="I25" t="n">
-        <v>0.1346</v>
+        <v>0.1485</v>
       </c>
       <c r="J25" t="n">
-        <v>3.9034</v>
+        <v>4.3065</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>1</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.0328</v>
+        <v>-0.0225</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.9512</v>
+        <v>-0.6525</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>1.01</v>
       </c>
       <c r="I27" t="n">
-        <v>0.0461</v>
+        <v>0.0493</v>
       </c>
       <c r="J27" t="n">
-        <v>1.3369</v>
+        <v>1.4297</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>1.01</v>
       </c>
       <c r="I28" t="n">
-        <v>0.0461</v>
+        <v>0.0493</v>
       </c>
       <c r="J28" t="n">
-        <v>1.3369</v>
+        <v>1.4297</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>0.97</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.0467</v>
+        <v>-0.0557</v>
       </c>
       <c r="J29" t="n">
-        <v>-1.3543</v>
+        <v>-1.6153</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>0.96</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.0597</v>
+        <v>-0.0699</v>
       </c>
       <c r="J30" t="n">
-        <v>-1.7313</v>
+        <v>-2.0271</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>0.82</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.2134</v>
+        <v>-0.2281</v>
       </c>
       <c r="J31" t="n">
-        <v>-6.1886</v>
+        <v>-6.6149</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>1.87</v>
       </c>
       <c r="I32" t="n">
-        <v>1.5224</v>
+        <v>1.5199</v>
       </c>
       <c r="J32" t="n">
-        <v>28.9256</v>
+        <v>28.8781</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>1.54</v>
       </c>
       <c r="I33" t="n">
-        <v>1.1423</v>
+        <v>1.1149</v>
       </c>
       <c r="J33" t="n">
-        <v>21.7037</v>
+        <v>21.1831</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>1.46</v>
       </c>
       <c r="I34" t="n">
-        <v>1.0486</v>
+        <v>1.0086</v>
       </c>
       <c r="J34" t="n">
-        <v>19.9234</v>
+        <v>19.1634</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>1.27</v>
       </c>
       <c r="I35" t="n">
-        <v>0.6715</v>
+        <v>0.6556</v>
       </c>
       <c r="J35" t="n">
-        <v>12.7585</v>
+        <v>12.4564</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>1.25</v>
       </c>
       <c r="I36" t="n">
-        <v>0.6246</v>
+        <v>0.6141</v>
       </c>
       <c r="J36" t="n">
-        <v>11.8674</v>
+        <v>11.6679</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>0.79</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.2056</v>
+        <v>-0.2288</v>
       </c>
       <c r="J37" t="n">
-        <v>-3.9064</v>
+        <v>-4.3472</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>0.78</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.216</v>
+        <v>-0.239</v>
       </c>
       <c r="J38" t="n">
-        <v>-4.104</v>
+        <v>-4.541</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>0.64</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.3486</v>
+        <v>-0.3677</v>
       </c>
       <c r="J39" t="n">
-        <v>-6.6234</v>
+        <v>-6.9863</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>0.62</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.367</v>
+        <v>-0.3853</v>
       </c>
       <c r="J40" t="n">
-        <v>-6.973</v>
+        <v>-7.3207</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.4229</v>
+        <v>-0.4383</v>
       </c>
       <c r="J41" t="n">
-        <v>-8.0351</v>
+        <v>-8.3277</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>2.14</v>
       </c>
       <c r="I42" t="n">
-        <v>1.806</v>
+        <v>1.8189</v>
       </c>
       <c r="J42" t="n">
-        <v>36.12</v>
+        <v>36.378</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>1.68</v>
       </c>
       <c r="I43" t="n">
-        <v>1.2957</v>
+        <v>1.2816</v>
       </c>
       <c r="J43" t="n">
-        <v>25.914</v>
+        <v>25.632</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>1.52</v>
       </c>
       <c r="I44" t="n">
-        <v>1.114</v>
+        <v>1.0854</v>
       </c>
       <c r="J44" t="n">
-        <v>22.28</v>
+        <v>21.708</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>1.28</v>
       </c>
       <c r="I45" t="n">
-        <v>0.6812</v>
+        <v>0.6667</v>
       </c>
       <c r="J45" t="n">
-        <v>13.624</v>
+        <v>13.334</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>1.11</v>
       </c>
       <c r="I46" t="n">
-        <v>0.2551</v>
+        <v>0.2833</v>
       </c>
       <c r="J46" t="n">
-        <v>5.102</v>
+        <v>5.666</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>0.86</v>
       </c>
       <c r="I47" t="n">
-        <v>-0.0886</v>
+        <v>-0.1215</v>
       </c>
       <c r="J47" t="n">
-        <v>-1.772</v>
+        <v>-2.43</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>0.77</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.1945</v>
+        <v>-0.2241</v>
       </c>
       <c r="J48" t="n">
-        <v>-3.89</v>
+        <v>-4.482</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>0.44</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.5163</v>
+        <v>-0.5286</v>
       </c>
       <c r="J49" t="n">
-        <v>-10.326</v>
+        <v>-10.572</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>0.4</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.5547</v>
+        <v>-0.5641</v>
       </c>
       <c r="J50" t="n">
-        <v>-11.094</v>
+        <v>-11.282</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.39</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.5643</v>
+        <v>-0.573</v>
       </c>
       <c r="J51" t="n">
-        <v>-11.286</v>
+        <v>-11.46</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.71</v>
       </c>
       <c r="I52" t="n">
-        <v>1.3828</v>
+        <v>1.3647</v>
       </c>
       <c r="J52" t="n">
-        <v>35.9528</v>
+        <v>35.4822</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>1.42</v>
       </c>
       <c r="I53" t="n">
-        <v>1.0196</v>
+        <v>0.9686</v>
       </c>
       <c r="J53" t="n">
-        <v>26.5096</v>
+        <v>25.1836</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>1.15</v>
       </c>
       <c r="I54" t="n">
-        <v>0.4204</v>
+        <v>0.4221</v>
       </c>
       <c r="J54" t="n">
-        <v>10.9304</v>
+        <v>10.9746</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>1.14</v>
       </c>
       <c r="I55" t="n">
-        <v>0.3941</v>
+        <v>0.3982</v>
       </c>
       <c r="J55" t="n">
-        <v>10.2466</v>
+        <v>10.3532</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>0.96</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.2355</v>
+        <v>-0.2183</v>
       </c>
       <c r="J56" t="n">
-        <v>-6.123</v>
+        <v>-5.6758</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>0.95</v>
       </c>
       <c r="I57" t="n">
-        <v>-0.0529</v>
+        <v>-0.0684</v>
       </c>
       <c r="J57" t="n">
-        <v>-1.3754</v>
+        <v>-1.7784</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>0.89</v>
       </c>
       <c r="I58" t="n">
-        <v>-0.125</v>
+        <v>-0.1427</v>
       </c>
       <c r="J58" t="n">
-        <v>-3.25</v>
+        <v>-3.7102</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>0.78</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.2359</v>
+        <v>-0.2542</v>
       </c>
       <c r="J59" t="n">
-        <v>-6.1334</v>
+        <v>-6.6092</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>0.74</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.2743</v>
+        <v>-0.292</v>
       </c>
       <c r="J60" t="n">
-        <v>-7.1318</v>
+        <v>-7.592</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>0.71</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.303</v>
+        <v>-0.3199</v>
       </c>
       <c r="J61" t="n">
-        <v>-7.878</v>
+        <v>-8.317399999999999</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>1.33</v>
       </c>
       <c r="I62" t="n">
-        <v>0.9109</v>
+        <v>0.8475</v>
       </c>
       <c r="J62" t="n">
-        <v>27.327</v>
+        <v>25.425</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>1.16</v>
       </c>
       <c r="I63" t="n">
-        <v>0.49</v>
+        <v>0.4755</v>
       </c>
       <c r="J63" t="n">
-        <v>14.7</v>
+        <v>14.265</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>1.1</v>
       </c>
       <c r="I64" t="n">
-        <v>0.3284</v>
+        <v>0.3279</v>
       </c>
       <c r="J64" t="n">
-        <v>9.852</v>
+        <v>9.837</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>1.06</v>
       </c>
       <c r="I65" t="n">
-        <v>0.214</v>
+        <v>0.2202</v>
       </c>
       <c r="J65" t="n">
-        <v>6.42</v>
+        <v>6.606</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>0.7</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.8932</v>
+        <v>-0.8228</v>
       </c>
       <c r="J66" t="n">
-        <v>-26.796</v>
+        <v>-24.684</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>1.21</v>
       </c>
       <c r="I67" t="n">
-        <v>0.4332</v>
+        <v>0.4333</v>
       </c>
       <c r="J67" t="n">
-        <v>12.996</v>
+        <v>12.999</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>1.15</v>
       </c>
       <c r="I68" t="n">
-        <v>0.3247</v>
+        <v>0.3315</v>
       </c>
       <c r="J68" t="n">
-        <v>9.741</v>
+        <v>9.945</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>1.07</v>
       </c>
       <c r="I69" t="n">
-        <v>0.1705</v>
+        <v>0.1823</v>
       </c>
       <c r="J69" t="n">
-        <v>5.115</v>
+        <v>5.469</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>1</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.0072</v>
+        <v>-0.0055</v>
       </c>
       <c r="J70" t="n">
-        <v>-0.216</v>
+        <v>-0.165</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>0.99</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.0283</v>
+        <v>-0.0312</v>
       </c>
       <c r="J71" t="n">
-        <v>-0.849</v>
+        <v>-0.9360000000000001</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>1.23</v>
       </c>
       <c r="I72" t="n">
-        <v>0.5158</v>
+        <v>0.5007</v>
       </c>
       <c r="J72" t="n">
-        <v>14.9582</v>
+        <v>14.5203</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>1.04</v>
       </c>
       <c r="I73" t="n">
-        <v>0.1299</v>
+        <v>0.1346</v>
       </c>
       <c r="J73" t="n">
-        <v>3.7671</v>
+        <v>3.9034</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>1.03</v>
       </c>
       <c r="I74" t="n">
-        <v>0.105</v>
+        <v>0.1095</v>
       </c>
       <c r="J74" t="n">
-        <v>3.045</v>
+        <v>3.1755</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>0.71</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.3197</v>
+        <v>-0.3329</v>
       </c>
       <c r="J75" t="n">
-        <v>-9.2713</v>
+        <v>-9.6541</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.3387</v>
+        <v>-0.3513</v>
       </c>
       <c r="J76" t="n">
-        <v>-9.8223</v>
+        <v>-10.1877</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>1.63</v>
       </c>
       <c r="I77" t="n">
-        <v>1.3099</v>
+        <v>1.2831</v>
       </c>
       <c r="J77" t="n">
-        <v>37.9871</v>
+        <v>37.2099</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>1.25</v>
       </c>
       <c r="I78" t="n">
-        <v>0.6808</v>
+        <v>0.6526999999999999</v>
       </c>
       <c r="J78" t="n">
-        <v>19.7432</v>
+        <v>18.9283</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>1.11</v>
       </c>
       <c r="I79" t="n">
-        <v>0.3336</v>
+        <v>0.3382</v>
       </c>
       <c r="J79" t="n">
-        <v>9.6744</v>
+        <v>9.8078</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>1.01</v>
       </c>
       <c r="I80" t="n">
-        <v>0.0098</v>
+        <v>0.0287</v>
       </c>
       <c r="J80" t="n">
-        <v>0.2842</v>
+        <v>0.8323</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>0.93</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.3104</v>
+        <v>-0.2946</v>
       </c>
       <c r="J81" t="n">
-        <v>-9.0016</v>
+        <v>-8.5434</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>1.29</v>
       </c>
       <c r="I82" t="n">
-        <v>0.3918</v>
+        <v>0.4052</v>
       </c>
       <c r="J82" t="n">
-        <v>11.3622</v>
+        <v>11.7508</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>1.26</v>
       </c>
       <c r="I83" t="n">
-        <v>0.3563</v>
+        <v>0.3711</v>
       </c>
       <c r="J83" t="n">
-        <v>10.3327</v>
+        <v>10.7619</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>1.22</v>
       </c>
       <c r="I84" t="n">
-        <v>0.3084</v>
+        <v>0.3246</v>
       </c>
       <c r="J84" t="n">
-        <v>8.9436</v>
+        <v>9.413399999999999</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>1.08</v>
       </c>
       <c r="I85" t="n">
-        <v>0.1267</v>
+        <v>0.1435</v>
       </c>
       <c r="J85" t="n">
-        <v>3.6743</v>
+        <v>4.1615</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>1</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.0158</v>
+        <v>-0.0121</v>
       </c>
       <c r="J86" t="n">
-        <v>-0.4582</v>
+        <v>-0.3509</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>1.5</v>
       </c>
       <c r="I87" t="n">
-        <v>0.7685</v>
+        <v>0.7335</v>
       </c>
       <c r="J87" t="n">
-        <v>22.2865</v>
+        <v>21.2715</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>0.9</v>
       </c>
       <c r="I88" t="n">
-        <v>-0.125</v>
+        <v>-0.1398</v>
       </c>
       <c r="J88" t="n">
-        <v>-3.625</v>
+        <v>-4.0542</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>0.79</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.2381</v>
+        <v>-0.2538</v>
       </c>
       <c r="J89" t="n">
-        <v>-6.9049</v>
+        <v>-7.3602</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>0.72</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.3063</v>
+        <v>-0.3206</v>
       </c>
       <c r="J90" t="n">
-        <v>-8.8827</v>
+        <v>-9.2974</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>0.64</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.382</v>
+        <v>-0.3938</v>
       </c>
       <c r="J91" t="n">
-        <v>-11.078</v>
+        <v>-11.4202</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>1.08</v>
       </c>
       <c r="I92" t="n">
-        <v>0.2665</v>
+        <v>0.2574</v>
       </c>
       <c r="J92" t="n">
-        <v>6.396</v>
+        <v>6.1776</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>0.87</v>
       </c>
       <c r="I93" t="n">
-        <v>-0.148</v>
+        <v>-0.1658</v>
       </c>
       <c r="J93" t="n">
-        <v>-3.552</v>
+        <v>-3.9792</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>0.76</v>
       </c>
       <c r="I94" t="n">
-        <v>-0.2561</v>
+        <v>-0.2739</v>
       </c>
       <c r="J94" t="n">
-        <v>-6.1464</v>
+        <v>-6.5736</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>0.75</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.2658</v>
+        <v>-0.2834</v>
       </c>
       <c r="J95" t="n">
-        <v>-6.3792</v>
+        <v>-6.8016</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>0.65</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.361</v>
+        <v>-0.3756</v>
       </c>
       <c r="J96" t="n">
-        <v>-8.664</v>
+        <v>-9.0144</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1.58</v>
       </c>
       <c r="I97" t="n">
-        <v>1.2382</v>
+        <v>1.2086</v>
       </c>
       <c r="J97" t="n">
-        <v>29.7168</v>
+        <v>29.0064</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>1.2</v>
       </c>
       <c r="I98" t="n">
-        <v>0.5578</v>
+        <v>0.5436</v>
       </c>
       <c r="J98" t="n">
-        <v>13.3872</v>
+        <v>13.0464</v>
       </c>
     </row>
     <row r="99">
@@ -6389,10 +6389,10 @@
         <v>1.03</v>
       </c>
       <c r="I101" t="n">
-        <v>0.08</v>
+        <v>0.101</v>
       </c>
       <c r="J101" t="n">
-        <v>1.92</v>
+        <v>2.424</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.33</v>
       </c>
       <c r="I102" t="n">
-        <v>0.9468</v>
+        <v>0.8744</v>
       </c>
       <c r="J102" t="n">
-        <v>28.404</v>
+        <v>26.232</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>1.19</v>
       </c>
       <c r="I103" t="n">
-        <v>0.5968</v>
+        <v>0.5655</v>
       </c>
       <c r="J103" t="n">
-        <v>17.904</v>
+        <v>16.965</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>0.89</v>
       </c>
       <c r="I104" t="n">
-        <v>-0.3763</v>
+        <v>-0.3674</v>
       </c>
       <c r="J104" t="n">
-        <v>-11.289</v>
+        <v>-11.022</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>0.85</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.4872</v>
+        <v>-0.468</v>
       </c>
       <c r="J105" t="n">
-        <v>-14.616</v>
+        <v>-14.04</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.72</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.8231000000000001</v>
+        <v>-0.7652</v>
       </c>
       <c r="J106" t="n">
-        <v>-24.693</v>
+        <v>-22.956</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.46</v>
       </c>
       <c r="I107" t="n">
-        <v>0.8361</v>
+        <v>0.8022</v>
       </c>
       <c r="J107" t="n">
-        <v>25.083</v>
+        <v>24.066</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>1.35</v>
       </c>
       <c r="I108" t="n">
-        <v>0.6592</v>
+        <v>0.6429</v>
       </c>
       <c r="J108" t="n">
-        <v>19.776</v>
+        <v>19.287</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>1.21</v>
       </c>
       <c r="I109" t="n">
-        <v>0.4235</v>
+        <v>0.4263</v>
       </c>
       <c r="J109" t="n">
-        <v>12.705</v>
+        <v>12.789</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>0.89</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.1592</v>
+        <v>-0.1691</v>
       </c>
       <c r="J110" t="n">
-        <v>-4.776</v>
+        <v>-5.073</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>0.73</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.321</v>
+        <v>-0.3304</v>
       </c>
       <c r="J111" t="n">
-        <v>-9.630000000000001</v>
+        <v>-9.912000000000001</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>1.18</v>
       </c>
       <c r="I112" t="n">
-        <v>0.4153</v>
+        <v>0.3944</v>
       </c>
       <c r="J112" t="n">
-        <v>9.1366</v>
+        <v>8.6768</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>0.84</v>
       </c>
       <c r="I113" t="n">
-        <v>-0.1627</v>
+        <v>-0.1845</v>
       </c>
       <c r="J113" t="n">
-        <v>-3.5794</v>
+        <v>-4.059</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>0.63</v>
       </c>
       <c r="I114" t="n">
-        <v>-0.3651</v>
+        <v>-0.3821</v>
       </c>
       <c r="J114" t="n">
-        <v>-8.0322</v>
+        <v>-8.4062</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>0.54</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.4492</v>
+        <v>-0.4619</v>
       </c>
       <c r="J115" t="n">
-        <v>-9.882400000000001</v>
+        <v>-10.1618</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>0.43</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.5517</v>
+        <v>-0.5578</v>
       </c>
       <c r="J116" t="n">
-        <v>-12.1374</v>
+        <v>-12.2716</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>1.91</v>
       </c>
       <c r="I117" t="n">
-        <v>0.9913999999999999</v>
+        <v>0.9762</v>
       </c>
       <c r="J117" t="n">
-        <v>21.8108</v>
+        <v>21.4764</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>1.58</v>
       </c>
       <c r="I118" t="n">
-        <v>0.6733</v>
+        <v>0.6773</v>
       </c>
       <c r="J118" t="n">
-        <v>14.8126</v>
+        <v>14.9006</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>1.34</v>
       </c>
       <c r="I119" t="n">
-        <v>0.4244</v>
+        <v>0.4416</v>
       </c>
       <c r="J119" t="n">
-        <v>9.3368</v>
+        <v>9.715199999999999</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>1.32</v>
       </c>
       <c r="I120" t="n">
-        <v>0.4023</v>
+        <v>0.4204</v>
       </c>
       <c r="J120" t="n">
-        <v>8.8506</v>
+        <v>9.248799999999999</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>0.87</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.2052</v>
+        <v>-0.2103</v>
       </c>
       <c r="J121" t="n">
-        <v>-4.5144</v>
+        <v>-4.6266</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.67</v>
       </c>
       <c r="I122" t="n">
-        <v>1.3611</v>
+        <v>1.3371</v>
       </c>
       <c r="J122" t="n">
-        <v>35.3886</v>
+        <v>34.7646</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>1.15</v>
       </c>
       <c r="I123" t="n">
-        <v>0.4407</v>
+        <v>0.436</v>
       </c>
       <c r="J123" t="n">
-        <v>11.4582</v>
+        <v>11.336</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>1.14</v>
       </c>
       <c r="I124" t="n">
-        <v>0.4149</v>
+        <v>0.4125</v>
       </c>
       <c r="J124" t="n">
-        <v>10.7874</v>
+        <v>10.725</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>1.07</v>
       </c>
       <c r="I125" t="n">
-        <v>0.2193</v>
+        <v>0.2317</v>
       </c>
       <c r="J125" t="n">
-        <v>5.7018</v>
+        <v>6.0242</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.88</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.456</v>
+        <v>-0.4292</v>
       </c>
       <c r="J126" t="n">
-        <v>-11.856</v>
+        <v>-11.1592</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.33</v>
       </c>
       <c r="I127" t="n">
-        <v>0.6973</v>
+        <v>0.6653</v>
       </c>
       <c r="J127" t="n">
-        <v>18.1298</v>
+        <v>17.2978</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>0.96</v>
       </c>
       <c r="I128" t="n">
-        <v>-0.0582</v>
+        <v>-0.0687</v>
       </c>
       <c r="J128" t="n">
-        <v>-1.5132</v>
+        <v>-1.7862</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>0.83</v>
       </c>
       <c r="I129" t="n">
-        <v>-0.201</v>
+        <v>-0.2163</v>
       </c>
       <c r="J129" t="n">
-        <v>-5.226</v>
+        <v>-5.6238</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>0.83</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.201</v>
+        <v>-0.2163</v>
       </c>
       <c r="J130" t="n">
-        <v>-5.226</v>
+        <v>-5.6238</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>0.73</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.3</v>
+        <v>-0.3138</v>
       </c>
       <c r="J131" t="n">
-        <v>-7.8</v>
+        <v>-8.158799999999999</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>1.1</v>
       </c>
       <c r="I132" t="n">
-        <v>0.3308</v>
+        <v>0.3295</v>
       </c>
       <c r="J132" t="n">
-        <v>9.5932</v>
+        <v>9.5555</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>1.08</v>
       </c>
       <c r="I133" t="n">
-        <v>0.2739</v>
+        <v>0.2765</v>
       </c>
       <c r="J133" t="n">
-        <v>7.9431</v>
+        <v>8.0185</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>1.08</v>
       </c>
       <c r="I134" t="n">
-        <v>0.2739</v>
+        <v>0.2765</v>
       </c>
       <c r="J134" t="n">
-        <v>7.9431</v>
+        <v>8.0185</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>1.03</v>
       </c>
       <c r="I135" t="n">
-        <v>0.1188</v>
+        <v>0.1279</v>
       </c>
       <c r="J135" t="n">
-        <v>3.4452</v>
+        <v>3.7091</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>1.01</v>
       </c>
       <c r="I136" t="n">
-        <v>0.0418</v>
+        <v>0.0508</v>
       </c>
       <c r="J136" t="n">
-        <v>1.2122</v>
+        <v>1.4732</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>1.25</v>
       </c>
       <c r="I137" t="n">
-        <v>0.532</v>
+        <v>0.5192</v>
       </c>
       <c r="J137" t="n">
-        <v>15.428</v>
+        <v>15.0568</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>0.95</v>
       </c>
       <c r="I138" t="n">
-        <v>-0.0751</v>
+        <v>-0.08550000000000001</v>
       </c>
       <c r="J138" t="n">
-        <v>-2.1779</v>
+        <v>-2.4795</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I139" t="n">
-        <v>-0.0873</v>
+        <v>-0.0984</v>
       </c>
       <c r="J139" t="n">
-        <v>-2.5317</v>
+        <v>-2.8536</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>0.93</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.0992</v>
+        <v>-0.1109</v>
       </c>
       <c r="J140" t="n">
-        <v>-2.8768</v>
+        <v>-3.2161</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>0.89</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.1444</v>
+        <v>-0.1575</v>
       </c>
       <c r="J141" t="n">
-        <v>-4.1876</v>
+        <v>-4.5675</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.35</v>
       </c>
       <c r="I142" t="n">
-        <v>0.9297</v>
+        <v>0.8691</v>
       </c>
       <c r="J142" t="n">
-        <v>26.0316</v>
+        <v>24.3348</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>1.29</v>
       </c>
       <c r="I143" t="n">
-        <v>0.7907</v>
+        <v>0.7467</v>
       </c>
       <c r="J143" t="n">
-        <v>22.1396</v>
+        <v>20.9076</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>1.17</v>
       </c>
       <c r="I144" t="n">
-        <v>0.4986</v>
+        <v>0.4869</v>
       </c>
       <c r="J144" t="n">
-        <v>13.9608</v>
+        <v>13.6332</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>0.96</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.1999</v>
+        <v>-0.1934</v>
       </c>
       <c r="J145" t="n">
-        <v>-5.5972</v>
+        <v>-5.4152</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>0.9</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.3864</v>
+        <v>-0.3682</v>
       </c>
       <c r="J146" t="n">
-        <v>-10.8192</v>
+        <v>-10.3096</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>1.74</v>
       </c>
       <c r="I147" t="n">
-        <v>1.1774</v>
+        <v>1.1549</v>
       </c>
       <c r="J147" t="n">
-        <v>32.9672</v>
+        <v>32.3372</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>1.15</v>
       </c>
       <c r="I148" t="n">
-        <v>0.3297</v>
+        <v>0.3351</v>
       </c>
       <c r="J148" t="n">
-        <v>9.2316</v>
+        <v>9.3828</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>0.89</v>
       </c>
       <c r="I149" t="n">
-        <v>-0.1519</v>
+        <v>-0.1634</v>
       </c>
       <c r="J149" t="n">
-        <v>-4.2532</v>
+        <v>-4.5752</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>0.8</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.2458</v>
+        <v>-0.2577</v>
       </c>
       <c r="J150" t="n">
-        <v>-6.8824</v>
+        <v>-7.2156</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>0.72</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.3237</v>
+        <v>-0.3343</v>
       </c>
       <c r="J151" t="n">
-        <v>-9.063599999999999</v>
+        <v>-9.3604</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>1.05</v>
       </c>
       <c r="I152" t="n">
-        <v>0.3602</v>
+        <v>0.311</v>
       </c>
       <c r="J152" t="n">
-        <v>6.8438</v>
+        <v>5.909</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>0.61</v>
       </c>
       <c r="I153" t="n">
-        <v>-0.3644</v>
+        <v>-0.3851</v>
       </c>
       <c r="J153" t="n">
-        <v>-6.9236</v>
+        <v>-7.3169</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>0.47</v>
       </c>
       <c r="I154" t="n">
-        <v>-0.4921</v>
+        <v>-0.5056</v>
       </c>
       <c r="J154" t="n">
-        <v>-9.3499</v>
+        <v>-9.606400000000001</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>0.46</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.5016</v>
+        <v>-0.5144</v>
       </c>
       <c r="J155" t="n">
-        <v>-9.5304</v>
+        <v>-9.7736</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>0.38</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.578</v>
+        <v>-0.5851</v>
       </c>
       <c r="J156" t="n">
-        <v>-10.982</v>
+        <v>-11.1169</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>1.61</v>
       </c>
       <c r="I157" t="n">
-        <v>1.2284</v>
+        <v>1.2068</v>
       </c>
       <c r="J157" t="n">
-        <v>23.3396</v>
+        <v>22.9292</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>1.58</v>
       </c>
       <c r="I158" t="n">
-        <v>1.1931</v>
+        <v>1.1689</v>
       </c>
       <c r="J158" t="n">
-        <v>22.6689</v>
+        <v>22.2091</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>1.48</v>
       </c>
       <c r="I159" t="n">
-        <v>1.0746</v>
+        <v>1.039</v>
       </c>
       <c r="J159" t="n">
-        <v>20.4174</v>
+        <v>19.741</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>1.45</v>
       </c>
       <c r="I160" t="n">
-        <v>1.0379</v>
+        <v>0.9954</v>
       </c>
       <c r="J160" t="n">
-        <v>19.7201</v>
+        <v>18.9126</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>1.12</v>
       </c>
       <c r="I161" t="n">
-        <v>0.3023</v>
+        <v>0.3224</v>
       </c>
       <c r="J161" t="n">
-        <v>5.7437</v>
+        <v>6.1256</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>1.11</v>
       </c>
       <c r="I162" t="n">
-        <v>0.2754</v>
+        <v>0.2783</v>
       </c>
       <c r="J162" t="n">
-        <v>7.4358</v>
+        <v>7.5141</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>1.07</v>
       </c>
       <c r="I163" t="n">
-        <v>0.1913</v>
+        <v>0.1972</v>
       </c>
       <c r="J163" t="n">
-        <v>5.1651</v>
+        <v>5.3244</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>0.93</v>
       </c>
       <c r="I164" t="n">
-        <v>-0.0968</v>
+        <v>-0.109</v>
       </c>
       <c r="J164" t="n">
-        <v>-2.6136</v>
+        <v>-2.943</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>0.9</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.1307</v>
+        <v>-0.1442</v>
       </c>
       <c r="J165" t="n">
-        <v>-3.5289</v>
+        <v>-3.8934</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>0.83</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.2049</v>
+        <v>-0.2193</v>
       </c>
       <c r="J166" t="n">
-        <v>-5.5323</v>
+        <v>-5.9211</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>1.44</v>
       </c>
       <c r="I167" t="n">
-        <v>1.0916</v>
+        <v>1.0438</v>
       </c>
       <c r="J167" t="n">
-        <v>29.4732</v>
+        <v>28.1826</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>1.33</v>
       </c>
       <c r="I168" t="n">
-        <v>0.9005</v>
+        <v>0.84</v>
       </c>
       <c r="J168" t="n">
-        <v>24.3135</v>
+        <v>22.68</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>1.16</v>
       </c>
       <c r="I169" t="n">
-        <v>0.483</v>
+        <v>0.4706</v>
       </c>
       <c r="J169" t="n">
-        <v>13.041</v>
+        <v>12.7062</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>0.82</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.5958</v>
+        <v>-0.5598</v>
       </c>
       <c r="J170" t="n">
-        <v>-16.0866</v>
+        <v>-15.1146</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>0.72</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.8502999999999999</v>
+        <v>-0.7844</v>
       </c>
       <c r="J171" t="n">
-        <v>-22.9581</v>
+        <v>-21.1788</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>1.03</v>
       </c>
       <c r="I172" t="n">
-        <v>0.142</v>
+        <v>0.1365</v>
       </c>
       <c r="J172" t="n">
-        <v>3.834</v>
+        <v>3.6855</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>0.88</v>
       </c>
       <c r="I173" t="n">
-        <v>-0.1384</v>
+        <v>-0.1557</v>
       </c>
       <c r="J173" t="n">
-        <v>-3.7368</v>
+        <v>-4.2039</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>0.8</v>
       </c>
       <c r="I174" t="n">
-        <v>-0.2184</v>
+        <v>-0.2364</v>
       </c>
       <c r="J174" t="n">
-        <v>-5.8968</v>
+        <v>-6.3828</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>0.78</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.2378</v>
+        <v>-0.2557</v>
       </c>
       <c r="J175" t="n">
-        <v>-6.4206</v>
+        <v>-6.9039</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>0.66</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.3527</v>
+        <v>-0.3674</v>
       </c>
       <c r="J176" t="n">
-        <v>-9.5229</v>
+        <v>-9.9198</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>1.35</v>
       </c>
       <c r="I177" t="n">
-        <v>0.9006999999999999</v>
+        <v>0.8481</v>
       </c>
       <c r="J177" t="n">
-        <v>24.3189</v>
+        <v>22.8987</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>1.33</v>
       </c>
       <c r="I178" t="n">
-        <v>0.8558</v>
+        <v>0.8088</v>
       </c>
       <c r="J178" t="n">
-        <v>23.1066</v>
+        <v>21.8376</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>1.16</v>
       </c>
       <c r="I179" t="n">
-        <v>0.4581</v>
+        <v>0.4537</v>
       </c>
       <c r="J179" t="n">
-        <v>12.3687</v>
+        <v>12.2499</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>1.15</v>
       </c>
       <c r="I180" t="n">
-        <v>0.4324</v>
+        <v>0.4304</v>
       </c>
       <c r="J180" t="n">
-        <v>11.6748</v>
+        <v>11.6208</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>1.12</v>
       </c>
       <c r="I181" t="n">
-        <v>0.3528</v>
+        <v>0.3577</v>
       </c>
       <c r="J181" t="n">
-        <v>9.525600000000001</v>
+        <v>9.6579</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>1.72</v>
       </c>
       <c r="I182" t="n">
-        <v>0.8885</v>
+        <v>0.8653</v>
       </c>
       <c r="J182" t="n">
-        <v>25.7665</v>
+        <v>25.0937</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>1.05</v>
       </c>
       <c r="I183" t="n">
-        <v>0.08840000000000001</v>
+        <v>0.1019</v>
       </c>
       <c r="J183" t="n">
-        <v>2.5636</v>
+        <v>2.9551</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I184" t="n">
-        <v>-0.09909999999999999</v>
+        <v>-0.1075</v>
       </c>
       <c r="J184" t="n">
-        <v>-2.8739</v>
+        <v>-3.1175</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>0.92</v>
       </c>
       <c r="I185" t="n">
-        <v>-0.1228</v>
+        <v>-0.1323</v>
       </c>
       <c r="J185" t="n">
-        <v>-3.5612</v>
+        <v>-3.8367</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>0.89</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.1567</v>
+        <v>-0.1671</v>
       </c>
       <c r="J186" t="n">
-        <v>-4.5443</v>
+        <v>-4.8459</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>1.39</v>
       </c>
       <c r="I187" t="n">
-        <v>0.5762</v>
+        <v>0.5662</v>
       </c>
       <c r="J187" t="n">
-        <v>16.7098</v>
+        <v>16.4198</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>1.19</v>
       </c>
       <c r="I188" t="n">
-        <v>0.3118</v>
+        <v>0.319</v>
       </c>
       <c r="J188" t="n">
-        <v>9.042199999999999</v>
+        <v>9.250999999999999</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>1.1</v>
       </c>
       <c r="I189" t="n">
-        <v>0.181</v>
+        <v>0.1922</v>
       </c>
       <c r="J189" t="n">
-        <v>5.249</v>
+        <v>5.5738</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>0.79</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.254</v>
+        <v>-0.2662</v>
       </c>
       <c r="J190" t="n">
-        <v>-7.366</v>
+        <v>-7.7198</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>0.75</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.2932</v>
+        <v>-0.3048</v>
       </c>
       <c r="J191" t="n">
-        <v>-8.502800000000001</v>
+        <v>-8.8392</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>1.32</v>
       </c>
       <c r="I192" t="n">
-        <v>0.6806</v>
+        <v>0.6501</v>
       </c>
       <c r="J192" t="n">
-        <v>23.1404</v>
+        <v>22.1034</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I193" t="n">
-        <v>-0.0825</v>
+        <v>-0.0948</v>
       </c>
       <c r="J193" t="n">
-        <v>-2.805</v>
+        <v>-3.2232</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>0.83</v>
       </c>
       <c r="I194" t="n">
-        <v>-0.2008</v>
+        <v>-0.2161</v>
       </c>
       <c r="J194" t="n">
-        <v>-6.8272</v>
+        <v>-7.3474</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>0.79</v>
       </c>
       <c r="I195" t="n">
-        <v>-0.2411</v>
+        <v>-0.2561</v>
       </c>
       <c r="J195" t="n">
-        <v>-8.1974</v>
+        <v>-8.7074</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>0.79</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.2411</v>
+        <v>-0.2561</v>
       </c>
       <c r="J196" t="n">
-        <v>-8.1974</v>
+        <v>-8.7074</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>1.41</v>
       </c>
       <c r="I197" t="n">
-        <v>1.0296</v>
+        <v>0.9745</v>
       </c>
       <c r="J197" t="n">
-        <v>35.0064</v>
+        <v>33.133</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>1.39</v>
       </c>
       <c r="I198" t="n">
-        <v>0.9971</v>
+        <v>0.9382</v>
       </c>
       <c r="J198" t="n">
-        <v>33.9014</v>
+        <v>31.8988</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>1.08</v>
       </c>
       <c r="I199" t="n">
-        <v>0.2525</v>
+        <v>0.2619</v>
       </c>
       <c r="J199" t="n">
-        <v>8.585000000000001</v>
+        <v>8.9046</v>
       </c>
     </row>
     <row r="200">
@@ -10349,10 +10349,10 @@
         <v>1.06</v>
       </c>
       <c r="I200" t="n">
-        <v>0.192</v>
+        <v>0.2051</v>
       </c>
       <c r="J200" t="n">
-        <v>6.528</v>
+        <v>6.9734</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>0.9</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.3954</v>
+        <v>-0.3744</v>
       </c>
       <c r="J201" t="n">
-        <v>-13.4436</v>
+        <v>-12.7296</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>1.39</v>
       </c>
       <c r="I202" t="n">
-        <v>1.0043</v>
+        <v>0.9445</v>
       </c>
       <c r="J202" t="n">
-        <v>30.129</v>
+        <v>28.335</v>
       </c>
     </row>
     <row r="203">
@@ -10469,10 +10469,10 @@
         <v>1.25</v>
       </c>
       <c r="I203" t="n">
-        <v>0.6922</v>
+        <v>0.6606</v>
       </c>
       <c r="J203" t="n">
-        <v>20.766</v>
+        <v>19.818</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>1.07</v>
       </c>
       <c r="I204" t="n">
-        <v>0.2284</v>
+        <v>0.238</v>
       </c>
       <c r="J204" t="n">
-        <v>6.852</v>
+        <v>7.14</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>1.01</v>
       </c>
       <c r="I205" t="n">
-        <v>0.0205</v>
+        <v>0.0362</v>
       </c>
       <c r="J205" t="n">
-        <v>0.615</v>
+        <v>1.086</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>1</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.0343</v>
+        <v>-0.0236</v>
       </c>
       <c r="J206" t="n">
-        <v>-1.029</v>
+        <v>-0.708</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>1.35</v>
       </c>
       <c r="I207" t="n">
-        <v>0.7118</v>
+        <v>0.6816</v>
       </c>
       <c r="J207" t="n">
-        <v>21.354</v>
+        <v>20.448</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>1.22</v>
       </c>
       <c r="I208" t="n">
-        <v>0.4821</v>
+        <v>0.4726</v>
       </c>
       <c r="J208" t="n">
-        <v>14.463</v>
+        <v>14.178</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>0.87</v>
       </c>
       <c r="I209" t="n">
-        <v>-0.1646</v>
+        <v>-0.1784</v>
       </c>
       <c r="J209" t="n">
-        <v>-4.938</v>
+        <v>-5.352</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>0.73</v>
       </c>
       <c r="I210" t="n">
-        <v>-0.3053</v>
+        <v>-0.318</v>
       </c>
       <c r="J210" t="n">
-        <v>-9.159000000000001</v>
+        <v>-9.539999999999999</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>0.73</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.3053</v>
+        <v>-0.318</v>
       </c>
       <c r="J211" t="n">
-        <v>-9.159000000000001</v>
+        <v>-9.539999999999999</v>
       </c>
     </row>
     <row r="212">
@@ -10829,10 +10829,10 @@
         <v>1.28</v>
       </c>
       <c r="I212" t="n">
-        <v>0.7691</v>
+        <v>0.7274</v>
       </c>
       <c r="J212" t="n">
-        <v>20.7657</v>
+        <v>19.6398</v>
       </c>
     </row>
     <row r="213">
@@ -10869,10 +10869,10 @@
         <v>1.14</v>
       </c>
       <c r="I213" t="n">
-        <v>0.4236</v>
+        <v>0.4184</v>
       </c>
       <c r="J213" t="n">
-        <v>11.4372</v>
+        <v>11.2968</v>
       </c>
     </row>
     <row r="214">
@@ -10909,10 +10909,10 @@
         <v>1.11</v>
       </c>
       <c r="I214" t="n">
-        <v>0.3458</v>
+        <v>0.3465</v>
       </c>
       <c r="J214" t="n">
-        <v>9.336600000000001</v>
+        <v>9.355499999999999</v>
       </c>
     </row>
     <row r="215">
@@ -10949,10 +10949,10 @@
         <v>1.09</v>
       </c>
       <c r="I215" t="n">
-        <v>0.2905</v>
+        <v>0.2952</v>
       </c>
       <c r="J215" t="n">
-        <v>7.8435</v>
+        <v>7.9704</v>
       </c>
     </row>
     <row r="216">
@@ -10989,10 +10989,10 @@
         <v>1.02</v>
       </c>
       <c r="I216" t="n">
-        <v>0.06560000000000001</v>
+        <v>0.0803</v>
       </c>
       <c r="J216" t="n">
-        <v>1.7712</v>
+        <v>2.1681</v>
       </c>
     </row>
     <row r="217">
@@ -11029,10 +11029,10 @@
         <v>1.72</v>
       </c>
       <c r="I217" t="n">
-        <v>1.1784</v>
+        <v>1.1529</v>
       </c>
       <c r="J217" t="n">
-        <v>31.8168</v>
+        <v>31.1283</v>
       </c>
     </row>
     <row r="218">
@@ -11069,10 +11069,10 @@
         <v>1.07</v>
       </c>
       <c r="I218" t="n">
-        <v>0.1827</v>
+        <v>0.191</v>
       </c>
       <c r="J218" t="n">
-        <v>4.9329</v>
+        <v>5.157</v>
       </c>
     </row>
     <row r="219">
@@ -11109,10 +11109,10 @@
         <v>0.91</v>
       </c>
       <c r="I219" t="n">
-        <v>-0.1235</v>
+        <v>-0.1358</v>
       </c>
       <c r="J219" t="n">
-        <v>-3.3345</v>
+        <v>-3.6666</v>
       </c>
     </row>
     <row r="220">
@@ -11149,10 +11149,10 @@
         <v>0.82</v>
       </c>
       <c r="I220" t="n">
-        <v>-0.2193</v>
+        <v>-0.2327</v>
       </c>
       <c r="J220" t="n">
-        <v>-5.9211</v>
+        <v>-6.2829</v>
       </c>
     </row>
     <row r="221">
@@ -11189,10 +11189,10 @@
         <v>0.5</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.5197000000000001</v>
+        <v>-0.5232</v>
       </c>
       <c r="J221" t="n">
-        <v>-14.0319</v>
+        <v>-14.1264</v>
       </c>
     </row>
     <row r="222">
@@ -11229,10 +11229,10 @@
         <v>2.05</v>
       </c>
       <c r="I222" t="n">
-        <v>1.7128</v>
+        <v>1.7211</v>
       </c>
       <c r="J222" t="n">
-        <v>30.8304</v>
+        <v>30.9798</v>
       </c>
     </row>
     <row r="223">
@@ -11269,10 +11269,10 @@
         <v>1.82</v>
       </c>
       <c r="I223" t="n">
-        <v>1.4573</v>
+        <v>1.4528</v>
       </c>
       <c r="J223" t="n">
-        <v>26.2314</v>
+        <v>26.1504</v>
       </c>
     </row>
     <row r="224">
@@ -11309,10 +11309,10 @@
         <v>1.4</v>
       </c>
       <c r="I224" t="n">
-        <v>0.9485</v>
+        <v>0.903</v>
       </c>
       <c r="J224" t="n">
-        <v>17.073</v>
+        <v>16.254</v>
       </c>
     </row>
     <row r="225">
@@ -11349,10 +11349,10 @@
         <v>1.36</v>
       </c>
       <c r="I225" t="n">
-        <v>0.8651</v>
+        <v>0.8277</v>
       </c>
       <c r="J225" t="n">
-        <v>15.5718</v>
+        <v>14.8986</v>
       </c>
     </row>
     <row r="226">
@@ -11389,10 +11389,10 @@
         <v>0.99</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.1742</v>
+        <v>-0.143</v>
       </c>
       <c r="J226" t="n">
-        <v>-3.1356</v>
+        <v>-2.574</v>
       </c>
     </row>
     <row r="227">
@@ -11429,10 +11429,10 @@
         <v>0.8</v>
       </c>
       <c r="I227" t="n">
-        <v>-0.1676</v>
+        <v>-0.1969</v>
       </c>
       <c r="J227" t="n">
-        <v>-3.0168</v>
+        <v>-3.5442</v>
       </c>
     </row>
     <row r="228">
@@ -11469,10 +11469,10 @@
         <v>0.66</v>
       </c>
       <c r="I228" t="n">
-        <v>-0.3163</v>
+        <v>-0.3393</v>
       </c>
       <c r="J228" t="n">
-        <v>-5.6934</v>
+        <v>-6.1074</v>
       </c>
     </row>
     <row r="229">
@@ -11509,10 +11509,10 @@
         <v>0.59</v>
       </c>
       <c r="I229" t="n">
-        <v>-0.3812</v>
+        <v>-0.4013</v>
       </c>
       <c r="J229" t="n">
-        <v>-6.8616</v>
+        <v>-7.2234</v>
       </c>
     </row>
     <row r="230">
@@ -11549,10 +11549,10 @@
         <v>0.52</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.4443</v>
+        <v>-0.461</v>
       </c>
       <c r="J230" t="n">
-        <v>-7.9974</v>
+        <v>-8.298</v>
       </c>
     </row>
     <row r="231">
@@ -11589,10 +11589,10 @@
         <v>0.38</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.5773</v>
+        <v>-0.5845</v>
       </c>
       <c r="J231" t="n">
-        <v>-10.3914</v>
+        <v>-10.521</v>
       </c>
     </row>
     <row r="232">
@@ -11629,10 +11629,10 @@
         <v>1.95</v>
       </c>
       <c r="I232" t="n">
-        <v>1.5925</v>
+        <v>1.5969</v>
       </c>
       <c r="J232" t="n">
-        <v>31.85</v>
+        <v>31.938</v>
       </c>
     </row>
     <row r="233">
@@ -11669,10 +11669,10 @@
         <v>1.71</v>
       </c>
       <c r="I233" t="n">
-        <v>1.3258</v>
+        <v>1.3146</v>
       </c>
       <c r="J233" t="n">
-        <v>26.516</v>
+        <v>26.292</v>
       </c>
     </row>
     <row r="234">
@@ -11709,10 +11709,10 @@
         <v>1.5</v>
       </c>
       <c r="I234" t="n">
-        <v>1.088</v>
+        <v>1.0571</v>
       </c>
       <c r="J234" t="n">
-        <v>21.76</v>
+        <v>21.142</v>
       </c>
     </row>
     <row r="235">
@@ -11749,10 +11749,10 @@
         <v>1.46</v>
       </c>
       <c r="I235" t="n">
-        <v>1.0386</v>
+        <v>0.9994</v>
       </c>
       <c r="J235" t="n">
-        <v>20.772</v>
+        <v>19.988</v>
       </c>
     </row>
     <row r="236">
@@ -11789,10 +11789,10 @@
         <v>1.26</v>
       </c>
       <c r="I236" t="n">
-        <v>0.6288</v>
+        <v>0.6214</v>
       </c>
       <c r="J236" t="n">
-        <v>12.576</v>
+        <v>12.428</v>
       </c>
     </row>
     <row r="237">
@@ -11829,10 +11829,10 @@
         <v>0.74</v>
       </c>
       <c r="I237" t="n">
-        <v>-0.1893</v>
+        <v>-0.2256</v>
       </c>
       <c r="J237" t="n">
-        <v>-3.786</v>
+        <v>-4.512</v>
       </c>
     </row>
     <row r="238">
@@ -11869,10 +11869,10 @@
         <v>0.67</v>
       </c>
       <c r="I238" t="n">
-        <v>-0.27</v>
+        <v>-0.3014</v>
       </c>
       <c r="J238" t="n">
-        <v>-5.4</v>
+        <v>-6.028</v>
       </c>
     </row>
     <row r="239">
@@ -11909,10 +11909,10 @@
         <v>0.51</v>
       </c>
       <c r="I239" t="n">
-        <v>-0.4354</v>
+        <v>-0.4559</v>
       </c>
       <c r="J239" t="n">
-        <v>-8.708</v>
+        <v>-9.118</v>
       </c>
     </row>
     <row r="240">
@@ -11949,10 +11949,10 @@
         <v>0.3</v>
       </c>
       <c r="I240" t="n">
-        <v>-0.6358</v>
+        <v>-0.6405</v>
       </c>
       <c r="J240" t="n">
-        <v>-12.716</v>
+        <v>-12.81</v>
       </c>
     </row>
     <row r="241">
@@ -11989,10 +11989,10 @@
         <v>0.22</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.7174</v>
+        <v>-0.7143</v>
       </c>
       <c r="J241" t="n">
-        <v>-14.348</v>
+        <v>-14.286</v>
       </c>
     </row>
     <row r="242">
@@ -12029,10 +12029,10 @@
         <v>1.38</v>
       </c>
       <c r="I242" t="n">
-        <v>0.5232</v>
+        <v>0.5252</v>
       </c>
       <c r="J242" t="n">
-        <v>18.8352</v>
+        <v>18.9072</v>
       </c>
     </row>
     <row r="243">
@@ -12069,10 +12069,10 @@
         <v>1.05</v>
       </c>
       <c r="I243" t="n">
-        <v>0.09379999999999999</v>
+        <v>0.1059</v>
       </c>
       <c r="J243" t="n">
-        <v>3.3768</v>
+        <v>3.8124</v>
       </c>
     </row>
     <row r="244">
@@ -12109,10 +12109,10 @@
         <v>1</v>
       </c>
       <c r="I244" t="n">
-        <v>-0.0038</v>
+        <v>-0.0028</v>
       </c>
       <c r="J244" t="n">
-        <v>-0.1368</v>
+        <v>-0.1008</v>
       </c>
     </row>
     <row r="245">
@@ -12149,10 +12149,10 @@
         <v>0.98</v>
       </c>
       <c r="I245" t="n">
-        <v>-0.0404</v>
+        <v>-0.0461</v>
       </c>
       <c r="J245" t="n">
-        <v>-1.4544</v>
+        <v>-1.6596</v>
       </c>
     </row>
     <row r="246">
@@ -12189,10 +12189,10 @@
         <v>0.83</v>
       </c>
       <c r="I246" t="n">
-        <v>-0.2141</v>
+        <v>-0.2265</v>
       </c>
       <c r="J246" t="n">
-        <v>-7.7076</v>
+        <v>-8.154</v>
       </c>
     </row>
     <row r="247">
@@ -12229,10 +12229,10 @@
         <v>1.29</v>
       </c>
       <c r="I247" t="n">
-        <v>0.4371</v>
+        <v>0.4391</v>
       </c>
       <c r="J247" t="n">
-        <v>15.7356</v>
+        <v>15.8076</v>
       </c>
     </row>
     <row r="248">
@@ -12269,10 +12269,10 @@
         <v>1.28</v>
       </c>
       <c r="I248" t="n">
-        <v>0.4241</v>
+        <v>0.427</v>
       </c>
       <c r="J248" t="n">
-        <v>15.2676</v>
+        <v>15.372</v>
       </c>
     </row>
     <row r="249">
@@ -12309,10 +12309,10 @@
         <v>1.07</v>
       </c>
       <c r="I249" t="n">
-        <v>0.1302</v>
+        <v>0.1426</v>
       </c>
       <c r="J249" t="n">
-        <v>4.6872</v>
+        <v>5.1336</v>
       </c>
     </row>
     <row r="250">
@@ -12349,10 +12349,10 @@
         <v>0.97</v>
       </c>
       <c r="I250" t="n">
-        <v>-0.0586</v>
+        <v>-0.0648</v>
       </c>
       <c r="J250" t="n">
-        <v>-2.1096</v>
+        <v>-2.3328</v>
       </c>
     </row>
     <row r="251">
@@ -12389,10 +12389,10 @@
         <v>0.82</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.2284</v>
+        <v>-0.2399</v>
       </c>
       <c r="J251" t="n">
-        <v>-8.2224</v>
+        <v>-8.6364</v>
       </c>
     </row>
     <row r="252">
@@ -12429,10 +12429,10 @@
         <v>1.07</v>
       </c>
       <c r="I252" t="n">
-        <v>0.2034</v>
+        <v>0.206</v>
       </c>
       <c r="J252" t="n">
-        <v>5.8986</v>
+        <v>5.974</v>
       </c>
     </row>
     <row r="253">
@@ -12469,10 +12469,10 @@
         <v>1.01</v>
       </c>
       <c r="I253" t="n">
-        <v>0.0528</v>
+        <v>0.0542</v>
       </c>
       <c r="J253" t="n">
-        <v>1.5312</v>
+        <v>1.5718</v>
       </c>
     </row>
     <row r="254">
@@ -12509,10 +12509,10 @@
         <v>0.99</v>
       </c>
       <c r="I254" t="n">
-        <v>-0.0137</v>
+        <v>-0.02</v>
       </c>
       <c r="J254" t="n">
-        <v>-0.3973</v>
+        <v>-0.58</v>
       </c>
     </row>
     <row r="255">
@@ -12549,10 +12549,10 @@
         <v>0.87</v>
       </c>
       <c r="I255" t="n">
-        <v>-0.1584</v>
+        <v>-0.1737</v>
       </c>
       <c r="J255" t="n">
-        <v>-4.5936</v>
+        <v>-5.0373</v>
       </c>
     </row>
     <row r="256">
@@ -12589,10 +12589,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I256" t="n">
-        <v>-0.337</v>
+        <v>-0.35</v>
       </c>
       <c r="J256" t="n">
-        <v>-9.773</v>
+        <v>-10.15</v>
       </c>
     </row>
     <row r="257">
@@ -12629,10 +12629,10 @@
         <v>1.36</v>
       </c>
       <c r="I257" t="n">
-        <v>0.946</v>
+        <v>0.8853</v>
       </c>
       <c r="J257" t="n">
-        <v>27.434</v>
+        <v>25.6737</v>
       </c>
     </row>
     <row r="258">
@@ -12669,10 +12669,10 @@
         <v>1.28</v>
       </c>
       <c r="I258" t="n">
-        <v>0.7624</v>
+        <v>0.7227</v>
       </c>
       <c r="J258" t="n">
-        <v>22.1096</v>
+        <v>20.9583</v>
       </c>
     </row>
     <row r="259">
@@ -12709,10 +12709,10 @@
         <v>1.12</v>
       </c>
       <c r="I259" t="n">
-        <v>0.3689</v>
+        <v>0.3688</v>
       </c>
       <c r="J259" t="n">
-        <v>10.6981</v>
+        <v>10.6952</v>
       </c>
     </row>
     <row r="260">
@@ -12749,10 +12749,10 @@
         <v>1.09</v>
       </c>
       <c r="I260" t="n">
-        <v>0.2861</v>
+        <v>0.2922</v>
       </c>
       <c r="J260" t="n">
-        <v>8.296900000000001</v>
+        <v>8.473800000000001</v>
       </c>
     </row>
     <row r="261">
@@ -12789,10 +12789,10 @@
         <v>0.89</v>
       </c>
       <c r="I261" t="n">
-        <v>-0.4189</v>
+        <v>-0.3971</v>
       </c>
       <c r="J261" t="n">
-        <v>-12.1481</v>
+        <v>-11.5159</v>
       </c>
     </row>
     <row r="262">
@@ -12829,10 +12829,10 @@
         <v>0.85</v>
       </c>
       <c r="I262" t="n">
-        <v>-0.1509</v>
+        <v>-0.1729</v>
       </c>
       <c r="J262" t="n">
-        <v>-3.3198</v>
+        <v>-3.8038</v>
       </c>
     </row>
     <row r="263">
@@ -12869,10 +12869,10 @@
         <v>0.84</v>
       </c>
       <c r="I263" t="n">
-        <v>-0.1619</v>
+        <v>-0.1838</v>
       </c>
       <c r="J263" t="n">
-        <v>-3.5618</v>
+        <v>-4.0436</v>
       </c>
     </row>
     <row r="264">
@@ -12909,10 +12909,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I264" t="n">
-        <v>-0.3086</v>
+        <v>-0.3279</v>
       </c>
       <c r="J264" t="n">
-        <v>-6.7892</v>
+        <v>-7.2138</v>
       </c>
     </row>
     <row r="265">
@@ -12949,10 +12949,10 @@
         <v>0.65</v>
       </c>
       <c r="I265" t="n">
-        <v>-0.3458</v>
+        <v>-0.3637</v>
       </c>
       <c r="J265" t="n">
-        <v>-7.6076</v>
+        <v>-8.0014</v>
       </c>
     </row>
     <row r="266">
@@ -12989,10 +12989,10 @@
         <v>0.57</v>
       </c>
       <c r="I266" t="n">
-        <v>-0.4205</v>
+        <v>-0.435</v>
       </c>
       <c r="J266" t="n">
-        <v>-9.250999999999999</v>
+        <v>-9.57</v>
       </c>
     </row>
     <row r="267">
@@ -13029,10 +13029,10 @@
         <v>1.71</v>
       </c>
       <c r="I267" t="n">
-        <v>1.3502</v>
+        <v>1.3359</v>
       </c>
       <c r="J267" t="n">
-        <v>29.7044</v>
+        <v>29.3898</v>
       </c>
     </row>
     <row r="268">
@@ -13069,10 +13069,10 @@
         <v>1.56</v>
       </c>
       <c r="I268" t="n">
-        <v>1.1733</v>
+        <v>1.1468</v>
       </c>
       <c r="J268" t="n">
-        <v>25.8126</v>
+        <v>25.2296</v>
       </c>
     </row>
     <row r="269">
@@ -13109,10 +13109,10 @@
         <v>1.49</v>
       </c>
       <c r="I269" t="n">
-        <v>1.0895</v>
+        <v>1.0555</v>
       </c>
       <c r="J269" t="n">
-        <v>23.969</v>
+        <v>23.221</v>
       </c>
     </row>
     <row r="270">
@@ -13149,10 +13149,10 @@
         <v>1.2</v>
       </c>
       <c r="I270" t="n">
-        <v>0.5158</v>
+        <v>0.5145999999999999</v>
       </c>
       <c r="J270" t="n">
-        <v>11.3476</v>
+        <v>11.3212</v>
       </c>
     </row>
     <row r="271">
@@ -13189,10 +13189,10 @@
         <v>1.14</v>
       </c>
       <c r="I271" t="n">
-        <v>0.3621</v>
+        <v>0.3759</v>
       </c>
       <c r="J271" t="n">
-        <v>7.9662</v>
+        <v>8.2698</v>
       </c>
     </row>
     <row r="272">
@@ -13229,10 +13229,10 @@
         <v>1.1</v>
       </c>
       <c r="I272" t="n">
-        <v>0.2133</v>
+        <v>0.2163</v>
       </c>
       <c r="J272" t="n">
-        <v>5.7591</v>
+        <v>5.8401</v>
       </c>
     </row>
     <row r="273">
@@ -13269,10 +13269,10 @@
         <v>0.95</v>
       </c>
       <c r="I273" t="n">
-        <v>-0.0664</v>
+        <v>-0.0789</v>
       </c>
       <c r="J273" t="n">
-        <v>-1.7928</v>
+        <v>-2.1303</v>
       </c>
     </row>
     <row r="274">
@@ -13309,10 +13309,10 @@
         <v>0.95</v>
       </c>
       <c r="I274" t="n">
-        <v>-0.0664</v>
+        <v>-0.0789</v>
       </c>
       <c r="J274" t="n">
-        <v>-1.7928</v>
+        <v>-2.1303</v>
       </c>
     </row>
     <row r="275">
@@ -13349,10 +13349,10 @@
         <v>0.77</v>
       </c>
       <c r="I275" t="n">
-        <v>-0.256</v>
+        <v>-0.2718</v>
       </c>
       <c r="J275" t="n">
-        <v>-6.912</v>
+        <v>-7.3386</v>
       </c>
     </row>
     <row r="276">
@@ -13389,10 +13389,10 @@
         <v>0.71</v>
       </c>
       <c r="I276" t="n">
-        <v>-0.3141</v>
+        <v>-0.3285</v>
       </c>
       <c r="J276" t="n">
-        <v>-8.480700000000001</v>
+        <v>-8.8695</v>
       </c>
     </row>
     <row r="277">
@@ -13429,10 +13429,10 @@
         <v>1.23</v>
       </c>
       <c r="I277" t="n">
-        <v>0.3271</v>
+        <v>0.3414</v>
       </c>
       <c r="J277" t="n">
-        <v>8.8317</v>
+        <v>9.2178</v>
       </c>
     </row>
     <row r="278">
@@ -13469,10 +13469,10 @@
         <v>1.23</v>
       </c>
       <c r="I278" t="n">
-        <v>0.3271</v>
+        <v>0.3414</v>
       </c>
       <c r="J278" t="n">
-        <v>8.8317</v>
+        <v>9.2178</v>
       </c>
     </row>
     <row r="279">
@@ -13509,10 +13509,10 @@
         <v>1.2</v>
       </c>
       <c r="I279" t="n">
-        <v>0.29</v>
+        <v>0.3053</v>
       </c>
       <c r="J279" t="n">
-        <v>7.83</v>
+        <v>8.2431</v>
       </c>
     </row>
     <row r="280">
@@ -13549,10 +13549,10 @@
         <v>1</v>
       </c>
       <c r="I280" t="n">
-        <v>-0.011</v>
+        <v>-0.008399999999999999</v>
       </c>
       <c r="J280" t="n">
-        <v>-0.297</v>
+        <v>-0.2268</v>
       </c>
     </row>
     <row r="281">
@@ -13589,10 +13589,10 @@
         <v>0.95</v>
       </c>
       <c r="I281" t="n">
-        <v>-0.0886</v>
+        <v>-0.0959</v>
       </c>
       <c r="J281" t="n">
-        <v>-2.3922</v>
+        <v>-2.5893</v>
       </c>
     </row>
     <row r="282">
@@ -13629,10 +13629,10 @@
         <v>1.72</v>
       </c>
       <c r="I282" t="n">
-        <v>1.3405</v>
+        <v>1.3296</v>
       </c>
       <c r="J282" t="n">
-        <v>26.81</v>
+        <v>26.592</v>
       </c>
     </row>
     <row r="283">
@@ -13669,10 +13669,10 @@
         <v>1.61</v>
       </c>
       <c r="I283" t="n">
-        <v>1.2156</v>
+        <v>1.1957</v>
       </c>
       <c r="J283" t="n">
-        <v>24.312</v>
+        <v>23.914</v>
       </c>
     </row>
     <row r="284">
@@ -13709,10 +13709,10 @@
         <v>1.53</v>
       </c>
       <c r="I284" t="n">
-        <v>1.1252</v>
+        <v>1.0977</v>
       </c>
       <c r="J284" t="n">
-        <v>22.504</v>
+        <v>21.954</v>
       </c>
     </row>
     <row r="285">
@@ -13749,10 +13749,10 @@
         <v>1.45</v>
       </c>
       <c r="I285" t="n">
-        <v>1.0278</v>
+        <v>0.9864000000000001</v>
       </c>
       <c r="J285" t="n">
-        <v>20.556</v>
+        <v>19.728</v>
       </c>
     </row>
     <row r="286">
@@ -13789,10 +13789,10 @@
         <v>1.44</v>
       </c>
       <c r="I286" t="n">
-        <v>1.0133</v>
+        <v>0.9701</v>
       </c>
       <c r="J286" t="n">
-        <v>20.266</v>
+        <v>19.402</v>
       </c>
     </row>
     <row r="287">
@@ -13829,10 +13829,10 @@
         <v>0.84</v>
       </c>
       <c r="I287" t="n">
-        <v>-0.1243</v>
+        <v>-0.1543</v>
       </c>
       <c r="J287" t="n">
-        <v>-2.486</v>
+        <v>-3.086</v>
       </c>
     </row>
     <row r="288">
@@ -13869,10 +13869,10 @@
         <v>0.65</v>
       </c>
       <c r="I288" t="n">
-        <v>-0.3278</v>
+        <v>-0.35</v>
       </c>
       <c r="J288" t="n">
-        <v>-6.556</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="289">
@@ -13909,10 +13909,10 @@
         <v>0.58</v>
       </c>
       <c r="I289" t="n">
-        <v>-0.3908</v>
+        <v>-0.4103</v>
       </c>
       <c r="J289" t="n">
-        <v>-7.816</v>
+        <v>-8.206</v>
       </c>
     </row>
     <row r="290">
@@ -13949,10 +13949,10 @@
         <v>0.5</v>
       </c>
       <c r="I290" t="n">
-        <v>-0.4645</v>
+        <v>-0.4798</v>
       </c>
       <c r="J290" t="n">
-        <v>-9.289999999999999</v>
+        <v>-9.596</v>
       </c>
     </row>
     <row r="291">
@@ -13989,10 +13989,10 @@
         <v>0.42</v>
       </c>
       <c r="I291" t="n">
-        <v>-0.5405</v>
+        <v>-0.5503</v>
       </c>
       <c r="J291" t="n">
-        <v>-10.81</v>
+        <v>-11.006</v>
       </c>
     </row>
     <row r="292">
@@ -14029,10 +14029,10 @@
         <v>1.77</v>
       </c>
       <c r="I292" t="n">
-        <v>1.4026</v>
+        <v>1.3945</v>
       </c>
       <c r="J292" t="n">
-        <v>28.052</v>
+        <v>27.89</v>
       </c>
     </row>
     <row r="293">
@@ -14069,10 +14069,10 @@
         <v>1.63</v>
       </c>
       <c r="I293" t="n">
-        <v>1.2426</v>
+        <v>1.2239</v>
       </c>
       <c r="J293" t="n">
-        <v>24.852</v>
+        <v>24.478</v>
       </c>
     </row>
     <row r="294">
@@ -14109,10 +14109,10 @@
         <v>1.59</v>
       </c>
       <c r="I294" t="n">
-        <v>1.1965</v>
+        <v>1.1743</v>
       </c>
       <c r="J294" t="n">
-        <v>23.93</v>
+        <v>23.486</v>
       </c>
     </row>
     <row r="295">
@@ -14149,10 +14149,10 @@
         <v>1.43</v>
       </c>
       <c r="I295" t="n">
-        <v>1.0025</v>
+        <v>0.9574</v>
       </c>
       <c r="J295" t="n">
-        <v>20.05</v>
+        <v>19.148</v>
       </c>
     </row>
     <row r="296">
@@ -14189,10 +14189,10 @@
         <v>1.15</v>
       </c>
       <c r="I296" t="n">
-        <v>0.3692</v>
+        <v>0.3863</v>
       </c>
       <c r="J296" t="n">
-        <v>7.384</v>
+        <v>7.726</v>
       </c>
     </row>
     <row r="297">
@@ -14229,10 +14229,10 @@
         <v>0.9</v>
       </c>
       <c r="I297" t="n">
-        <v>-0.0757</v>
+        <v>-0.1015</v>
       </c>
       <c r="J297" t="n">
-        <v>-1.514</v>
+        <v>-2.03</v>
       </c>
     </row>
     <row r="298">
@@ -14269,10 +14269,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I298" t="n">
-        <v>-0.3019</v>
+        <v>-0.3228</v>
       </c>
       <c r="J298" t="n">
-        <v>-6.038</v>
+        <v>-6.456</v>
       </c>
     </row>
     <row r="299">
@@ -14309,10 +14309,10 @@
         <v>0.65</v>
       </c>
       <c r="I299" t="n">
-        <v>-0.3374</v>
+        <v>-0.3573</v>
       </c>
       <c r="J299" t="n">
-        <v>-6.748</v>
+        <v>-7.146</v>
       </c>
     </row>
     <row r="300">
@@ -14349,10 +14349,10 @@
         <v>0.65</v>
       </c>
       <c r="I300" t="n">
-        <v>-0.3374</v>
+        <v>-0.3573</v>
       </c>
       <c r="J300" t="n">
-        <v>-6.748</v>
+        <v>-7.146</v>
       </c>
     </row>
     <row r="301">
@@ -14389,10 +14389,10 @@
         <v>0.42</v>
       </c>
       <c r="I301" t="n">
-        <v>-0.5516</v>
+        <v>-0.5591</v>
       </c>
       <c r="J301" t="n">
-        <v>-11.032</v>
+        <v>-11.182</v>
       </c>
     </row>
     <row r="302">
@@ -14429,10 +14429,10 @@
         <v>1.18</v>
       </c>
       <c r="I302" t="n">
-        <v>0.5338000000000001</v>
+        <v>0.5165</v>
       </c>
       <c r="J302" t="n">
-        <v>16.014</v>
+        <v>15.495</v>
       </c>
     </row>
     <row r="303">
@@ -14469,10 +14469,10 @@
         <v>1.18</v>
       </c>
       <c r="I303" t="n">
-        <v>0.5338000000000001</v>
+        <v>0.5165</v>
       </c>
       <c r="J303" t="n">
-        <v>16.014</v>
+        <v>15.495</v>
       </c>
     </row>
     <row r="304">
@@ -14509,10 +14509,10 @@
         <v>1.11</v>
       </c>
       <c r="I304" t="n">
-        <v>0.3505</v>
+        <v>0.3496</v>
       </c>
       <c r="J304" t="n">
-        <v>10.515</v>
+        <v>10.488</v>
       </c>
     </row>
     <row r="305">
@@ -14549,10 +14549,10 @@
         <v>1.04</v>
       </c>
       <c r="I305" t="n">
-        <v>0.1449</v>
+        <v>0.1556</v>
       </c>
       <c r="J305" t="n">
-        <v>4.347</v>
+        <v>4.668</v>
       </c>
     </row>
     <row r="306">
@@ -14589,10 +14589,10 @@
         <v>0.97</v>
       </c>
       <c r="I306" t="n">
-        <v>-0.1549</v>
+        <v>-0.1526</v>
       </c>
       <c r="J306" t="n">
-        <v>-4.647</v>
+        <v>-4.578</v>
       </c>
     </row>
     <row r="307">
@@ -14629,10 +14629,10 @@
         <v>1.31</v>
       </c>
       <c r="I307" t="n">
-        <v>0.6361</v>
+        <v>0.6143</v>
       </c>
       <c r="J307" t="n">
-        <v>19.083</v>
+        <v>18.429</v>
       </c>
     </row>
     <row r="308">
@@ -14669,10 +14669,10 @@
         <v>1.05</v>
       </c>
       <c r="I308" t="n">
-        <v>0.1401</v>
+        <v>0.1485</v>
       </c>
       <c r="J308" t="n">
-        <v>4.203</v>
+        <v>4.455</v>
       </c>
     </row>
     <row r="309">
@@ -14709,10 +14709,10 @@
         <v>0.93</v>
       </c>
       <c r="I309" t="n">
-        <v>-0.09959999999999999</v>
+        <v>-0.1112</v>
       </c>
       <c r="J309" t="n">
-        <v>-2.988</v>
+        <v>-3.336</v>
       </c>
     </row>
     <row r="310">
@@ -14749,10 +14749,10 @@
         <v>0.87</v>
       </c>
       <c r="I310" t="n">
-        <v>-0.1664</v>
+        <v>-0.1798</v>
       </c>
       <c r="J310" t="n">
-        <v>-4.992</v>
+        <v>-5.394</v>
       </c>
     </row>
     <row r="311">
@@ -14789,10 +14789,10 @@
         <v>0.82</v>
       </c>
       <c r="I311" t="n">
-        <v>-0.2184</v>
+        <v>-0.232</v>
       </c>
       <c r="J311" t="n">
-        <v>-6.552</v>
+        <v>-6.96</v>
       </c>
     </row>
     <row r="312">
@@ -14829,10 +14829,10 @@
         <v>1.48</v>
       </c>
       <c r="I312" t="n">
-        <v>1.0909</v>
+        <v>1.0541</v>
       </c>
       <c r="J312" t="n">
-        <v>21.818</v>
+        <v>21.082</v>
       </c>
     </row>
     <row r="313">
@@ -14869,10 +14869,10 @@
         <v>1.41</v>
       </c>
       <c r="I313" t="n">
-        <v>0.9943</v>
+        <v>0.9429999999999999</v>
       </c>
       <c r="J313" t="n">
-        <v>19.886</v>
+        <v>18.86</v>
       </c>
     </row>
     <row r="314">
@@ -14909,10 +14909,10 @@
         <v>1.4</v>
       </c>
       <c r="I314" t="n">
-        <v>0.9771</v>
+        <v>0.9251</v>
       </c>
       <c r="J314" t="n">
-        <v>19.542</v>
+        <v>18.502</v>
       </c>
     </row>
     <row r="315">
@@ -14949,10 +14949,10 @@
         <v>1.19</v>
       </c>
       <c r="I315" t="n">
-        <v>0.5117</v>
+        <v>0.5067</v>
       </c>
       <c r="J315" t="n">
-        <v>10.234</v>
+        <v>10.134</v>
       </c>
     </row>
     <row r="316">
@@ -14989,10 +14989,10 @@
         <v>1.14</v>
       </c>
       <c r="I316" t="n">
-        <v>0.3832</v>
+        <v>0.3906</v>
       </c>
       <c r="J316" t="n">
-        <v>7.664</v>
+        <v>7.812</v>
       </c>
     </row>
     <row r="317">
@@ -15029,10 +15029,10 @@
         <v>1.16</v>
       </c>
       <c r="I317" t="n">
-        <v>0.454</v>
+        <v>0.4303</v>
       </c>
       <c r="J317" t="n">
-        <v>9.08</v>
+        <v>8.606</v>
       </c>
     </row>
     <row r="318">
@@ -15069,10 +15069,10 @@
         <v>0.8</v>
       </c>
       <c r="I318" t="n">
-        <v>-0.215</v>
+        <v>-0.2339</v>
       </c>
       <c r="J318" t="n">
-        <v>-4.3</v>
+        <v>-4.678</v>
       </c>
     </row>
     <row r="319">
@@ -15109,10 +15109,10 @@
         <v>0.72</v>
       </c>
       <c r="I319" t="n">
-        <v>-0.2904</v>
+        <v>-0.3082</v>
       </c>
       <c r="J319" t="n">
-        <v>-5.808</v>
+        <v>-6.164</v>
       </c>
     </row>
     <row r="320">
@@ -15149,10 +15149,10 @@
         <v>0.65</v>
       </c>
       <c r="I320" t="n">
-        <v>-0.3567</v>
+        <v>-0.3722</v>
       </c>
       <c r="J320" t="n">
-        <v>-7.134</v>
+        <v>-7.444</v>
       </c>
     </row>
     <row r="321">
@@ -15189,10 +15189,10 @@
         <v>0.63</v>
       </c>
       <c r="I321" t="n">
-        <v>-0.3755</v>
+        <v>-0.3902</v>
       </c>
       <c r="J321" t="n">
-        <v>-7.51</v>
+        <v>-7.804</v>
       </c>
     </row>
     <row r="322">
@@ -15229,10 +15229,10 @@
         <v>1.21</v>
       </c>
       <c r="I322" t="n">
-        <v>0.5014</v>
+        <v>0.4833</v>
       </c>
       <c r="J322" t="n">
-        <v>12.535</v>
+        <v>12.0825</v>
       </c>
     </row>
     <row r="323">
@@ -15269,10 +15269,10 @@
         <v>1.14</v>
       </c>
       <c r="I323" t="n">
-        <v>0.3645</v>
+        <v>0.3565</v>
       </c>
       <c r="J323" t="n">
-        <v>9.112500000000001</v>
+        <v>8.9125</v>
       </c>
     </row>
     <row r="324">
@@ -15309,10 +15309,10 @@
         <v>0.85</v>
       </c>
       <c r="I324" t="n">
-        <v>-0.175</v>
+        <v>-0.1915</v>
       </c>
       <c r="J324" t="n">
-        <v>-4.375</v>
+        <v>-4.7875</v>
       </c>
     </row>
     <row r="325">
@@ -15349,10 +15349,10 @@
         <v>0.84</v>
       </c>
       <c r="I325" t="n">
-        <v>-0.1852</v>
+        <v>-0.2017</v>
       </c>
       <c r="J325" t="n">
-        <v>-4.63</v>
+        <v>-5.0425</v>
       </c>
     </row>
     <row r="326">
@@ -15389,10 +15389,10 @@
         <v>0.4</v>
       </c>
       <c r="I326" t="n">
-        <v>-0.598</v>
+        <v>-0.5983000000000001</v>
       </c>
       <c r="J326" t="n">
-        <v>-14.95</v>
+        <v>-14.9575</v>
       </c>
     </row>
     <row r="327">
@@ -15429,10 +15429,10 @@
         <v>1.59</v>
       </c>
       <c r="I327" t="n">
-        <v>1.2393</v>
+        <v>1.2118</v>
       </c>
       <c r="J327" t="n">
-        <v>30.9825</v>
+        <v>30.295</v>
       </c>
     </row>
     <row r="328">
@@ -15469,10 +15469,10 @@
         <v>1.46</v>
       </c>
       <c r="I328" t="n">
-        <v>1.0765</v>
+        <v>1.035</v>
       </c>
       <c r="J328" t="n">
-        <v>26.9125</v>
+        <v>25.875</v>
       </c>
     </row>
     <row r="329">
@@ -15509,10 +15509,10 @@
         <v>1.27</v>
       </c>
       <c r="I329" t="n">
-        <v>0.7115</v>
+        <v>0.6832</v>
       </c>
       <c r="J329" t="n">
-        <v>17.7875</v>
+        <v>17.08</v>
       </c>
     </row>
     <row r="330">
@@ -15549,10 +15549,10 @@
         <v>1.03</v>
       </c>
       <c r="I330" t="n">
-        <v>0.0688</v>
+        <v>0.09320000000000001</v>
       </c>
       <c r="J330" t="n">
-        <v>1.72</v>
+        <v>2.33</v>
       </c>
     </row>
     <row r="331">
@@ -15589,10 +15589,10 @@
         <v>0.97</v>
       </c>
       <c r="I331" t="n">
-        <v>-0.1977</v>
+        <v>-0.1825</v>
       </c>
       <c r="J331" t="n">
-        <v>-4.9425</v>
+        <v>-4.5625</v>
       </c>
     </row>
     <row r="332">
@@ -15629,10 +15629,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I332" t="n">
-        <v>-0.0408</v>
+        <v>-0.0623</v>
       </c>
       <c r="J332" t="n">
-        <v>-0.8568</v>
+        <v>-1.3083</v>
       </c>
     </row>
     <row r="333">
@@ -15669,10 +15669,10 @@
         <v>0.86</v>
       </c>
       <c r="I333" t="n">
-        <v>-0.1378</v>
+        <v>-0.1603</v>
       </c>
       <c r="J333" t="n">
-        <v>-2.8938</v>
+        <v>-3.3663</v>
       </c>
     </row>
     <row r="334">
@@ -15709,10 +15709,10 @@
         <v>0.71</v>
       </c>
       <c r="I334" t="n">
-        <v>-0.2897</v>
+        <v>-0.3096</v>
       </c>
       <c r="J334" t="n">
-        <v>-6.0837</v>
+        <v>-6.5016</v>
       </c>
     </row>
     <row r="335">
@@ -15749,10 +15749,10 @@
         <v>0.66</v>
       </c>
       <c r="I335" t="n">
-        <v>-0.3352</v>
+        <v>-0.3539</v>
       </c>
       <c r="J335" t="n">
-        <v>-7.0392</v>
+        <v>-7.4319</v>
       </c>
     </row>
     <row r="336">
@@ -15789,10 +15789,10 @@
         <v>0.39</v>
       </c>
       <c r="I336" t="n">
-        <v>-0.5871</v>
+        <v>-0.591</v>
       </c>
       <c r="J336" t="n">
-        <v>-12.3291</v>
+        <v>-12.411</v>
       </c>
     </row>
     <row r="337">
@@ -15829,10 +15829,10 @@
         <v>1.52</v>
       </c>
       <c r="I337" t="n">
-        <v>1.1297</v>
+        <v>1.0989</v>
       </c>
       <c r="J337" t="n">
-        <v>23.7237</v>
+        <v>23.0769</v>
       </c>
     </row>
     <row r="338">
@@ -15869,10 +15869,10 @@
         <v>1.5</v>
       </c>
       <c r="I338" t="n">
-        <v>1.1055</v>
+        <v>1.0725</v>
       </c>
       <c r="J338" t="n">
-        <v>23.2155</v>
+        <v>22.5225</v>
       </c>
     </row>
     <row r="339">
@@ -15909,10 +15909,10 @@
         <v>1.37</v>
       </c>
       <c r="I339" t="n">
-        <v>0.9103</v>
+        <v>0.8631</v>
       </c>
       <c r="J339" t="n">
-        <v>19.1163</v>
+        <v>18.1251</v>
       </c>
     </row>
     <row r="340">
@@ -15949,10 +15949,10 @@
         <v>1.33</v>
       </c>
       <c r="I340" t="n">
-        <v>0.8246</v>
+        <v>0.7875</v>
       </c>
       <c r="J340" t="n">
-        <v>17.3166</v>
+        <v>16.5375</v>
       </c>
     </row>
     <row r="341">
@@ -15989,10 +15989,10 @@
         <v>1.23</v>
       </c>
       <c r="I341" t="n">
-        <v>0.5952</v>
+        <v>0.5844</v>
       </c>
       <c r="J341" t="n">
-        <v>12.4992</v>
+        <v>12.2724</v>
       </c>
     </row>
     <row r="342">
@@ -16029,10 +16029,10 @@
         <v>1.09</v>
       </c>
       <c r="I342" t="n">
-        <v>0.2387</v>
+        <v>0.242</v>
       </c>
       <c r="J342" t="n">
-        <v>6.9223</v>
+        <v>7.018</v>
       </c>
     </row>
     <row r="343">
@@ -16069,10 +16069,10 @@
         <v>1.07</v>
       </c>
       <c r="I343" t="n">
-        <v>0.1957</v>
+        <v>0.2003</v>
       </c>
       <c r="J343" t="n">
-        <v>5.6753</v>
+        <v>5.8087</v>
       </c>
     </row>
     <row r="344">
@@ -16109,10 +16109,10 @@
         <v>1.01</v>
       </c>
       <c r="I344" t="n">
-        <v>0.0465</v>
+        <v>0.0496</v>
       </c>
       <c r="J344" t="n">
-        <v>1.3485</v>
+        <v>1.4384</v>
       </c>
     </row>
     <row r="345">
@@ -16149,10 +16149,10 @@
         <v>0.88</v>
       </c>
       <c r="I345" t="n">
-        <v>-0.1507</v>
+        <v>-0.1651</v>
       </c>
       <c r="J345" t="n">
-        <v>-4.3703</v>
+        <v>-4.7879</v>
       </c>
     </row>
     <row r="346">
@@ -16189,10 +16189,10 @@
         <v>0.71</v>
       </c>
       <c r="I346" t="n">
-        <v>-0.3211</v>
+        <v>-0.334</v>
       </c>
       <c r="J346" t="n">
-        <v>-9.3119</v>
+        <v>-9.686</v>
       </c>
     </row>
     <row r="347">
@@ -16229,10 +16229,10 @@
         <v>1.15</v>
       </c>
       <c r="I347" t="n">
-        <v>0.4734</v>
+        <v>0.4584</v>
       </c>
       <c r="J347" t="n">
-        <v>13.7286</v>
+        <v>13.2936</v>
       </c>
     </row>
     <row r="348">
@@ -16269,10 +16269,10 @@
         <v>1.12</v>
       </c>
       <c r="I348" t="n">
-        <v>0.392</v>
+        <v>0.3845</v>
       </c>
       <c r="J348" t="n">
-        <v>11.368</v>
+        <v>11.1505</v>
       </c>
     </row>
     <row r="349">
@@ -16309,10 +16309,10 @@
         <v>1.04</v>
       </c>
       <c r="I349" t="n">
-        <v>0.1561</v>
+        <v>0.1632</v>
       </c>
       <c r="J349" t="n">
-        <v>4.5269</v>
+        <v>4.7328</v>
       </c>
     </row>
     <row r="350">
@@ -16349,10 +16349,10 @@
         <v>1.01</v>
       </c>
       <c r="I350" t="n">
-        <v>0.0464</v>
+        <v>0.054</v>
       </c>
       <c r="J350" t="n">
-        <v>1.3456</v>
+        <v>1.566</v>
       </c>
     </row>
     <row r="351">
@@ -16389,10 +16389,10 @@
         <v>0.88</v>
       </c>
       <c r="I351" t="n">
-        <v>-0.4174</v>
+        <v>-0.4021</v>
       </c>
       <c r="J351" t="n">
-        <v>-12.1046</v>
+        <v>-11.6609</v>
       </c>
     </row>
     <row r="352">
@@ -16429,10 +16429,10 @@
         <v>0.98</v>
       </c>
       <c r="I352" t="n">
-        <v>-0.0236</v>
+        <v>-0.0333</v>
       </c>
       <c r="J352" t="n">
-        <v>-0.6608000000000001</v>
+        <v>-0.9324</v>
       </c>
     </row>
     <row r="353">
@@ -16469,10 +16469,10 @@
         <v>0.93</v>
       </c>
       <c r="I353" t="n">
-        <v>-0.0892</v>
+        <v>-0.1033</v>
       </c>
       <c r="J353" t="n">
-        <v>-2.4976</v>
+        <v>-2.8924</v>
       </c>
     </row>
     <row r="354">
@@ -16509,10 +16509,10 @@
         <v>0.89</v>
       </c>
       <c r="I354" t="n">
-        <v>-0.1337</v>
+        <v>-0.1494</v>
       </c>
       <c r="J354" t="n">
-        <v>-3.7436</v>
+        <v>-4.1832</v>
       </c>
     </row>
     <row r="355">
@@ -16549,10 +16549,10 @@
         <v>0.88</v>
       </c>
       <c r="I355" t="n">
-        <v>-0.1439</v>
+        <v>-0.1599</v>
       </c>
       <c r="J355" t="n">
-        <v>-4.0292</v>
+        <v>-4.4772</v>
       </c>
     </row>
     <row r="356">
@@ -16589,10 +16589,10 @@
         <v>0.74</v>
       </c>
       <c r="I356" t="n">
-        <v>-0.2837</v>
+        <v>-0.2992</v>
       </c>
       <c r="J356" t="n">
-        <v>-7.9436</v>
+        <v>-8.377599999999999</v>
       </c>
     </row>
     <row r="357">
@@ -16629,10 +16629,10 @@
         <v>1.56</v>
       </c>
       <c r="I357" t="n">
-        <v>1.2273</v>
+        <v>1.1943</v>
       </c>
       <c r="J357" t="n">
-        <v>34.3644</v>
+        <v>33.4404</v>
       </c>
     </row>
     <row r="358">
@@ -16669,10 +16669,10 @@
         <v>1.38</v>
       </c>
       <c r="I358" t="n">
-        <v>0.9796</v>
+        <v>0.9197</v>
       </c>
       <c r="J358" t="n">
-        <v>27.4288</v>
+        <v>25.7516</v>
       </c>
     </row>
     <row r="359">
@@ -16709,10 +16709,10 @@
         <v>1.09</v>
       </c>
       <c r="I359" t="n">
-        <v>0.282</v>
+        <v>0.2893</v>
       </c>
       <c r="J359" t="n">
-        <v>7.896</v>
+        <v>8.1004</v>
       </c>
     </row>
     <row r="360">
@@ -16749,10 +16749,10 @@
         <v>0.97</v>
       </c>
       <c r="I360" t="n">
-        <v>-0.1733</v>
+        <v>-0.1654</v>
       </c>
       <c r="J360" t="n">
-        <v>-4.8524</v>
+        <v>-4.6312</v>
       </c>
     </row>
     <row r="361">
@@ -16789,10 +16789,10 @@
         <v>0.83</v>
       </c>
       <c r="I361" t="n">
-        <v>-0.5883</v>
+        <v>-0.5494</v>
       </c>
       <c r="J361" t="n">
-        <v>-16.4724</v>
+        <v>-15.3832</v>
       </c>
     </row>
     <row r="362">
@@ -16829,10 +16829,10 @@
         <v>1.38</v>
       </c>
       <c r="I362" t="n">
-        <v>0.4947</v>
+        <v>0.5033</v>
       </c>
       <c r="J362" t="n">
-        <v>13.8516</v>
+        <v>14.0924</v>
       </c>
     </row>
     <row r="363">
@@ -16869,10 +16869,10 @@
         <v>1.25</v>
       </c>
       <c r="I363" t="n">
-        <v>0.3436</v>
+        <v>0.359</v>
       </c>
       <c r="J363" t="n">
-        <v>9.620799999999999</v>
+        <v>10.052</v>
       </c>
     </row>
     <row r="364">
@@ -16909,10 +16909,10 @@
         <v>1.13</v>
       </c>
       <c r="I364" t="n">
-        <v>0.1961</v>
+        <v>0.2136</v>
       </c>
       <c r="J364" t="n">
-        <v>5.4908</v>
+        <v>5.9808</v>
       </c>
     </row>
     <row r="365">
@@ -16949,10 +16949,10 @@
         <v>1.07</v>
       </c>
       <c r="I365" t="n">
-        <v>0.111</v>
+        <v>0.1277</v>
       </c>
       <c r="J365" t="n">
-        <v>3.108</v>
+        <v>3.5756</v>
       </c>
     </row>
     <row r="366">
@@ -16989,10 +16989,10 @@
         <v>1.05</v>
       </c>
       <c r="I366" t="n">
-        <v>0.0796</v>
+        <v>0.09520000000000001</v>
       </c>
       <c r="J366" t="n">
-        <v>2.2288</v>
+        <v>2.6656</v>
       </c>
     </row>
     <row r="367">
@@ -17029,10 +17029,10 @@
         <v>1.19</v>
       </c>
       <c r="I367" t="n">
-        <v>0.3516</v>
+        <v>0.3489</v>
       </c>
       <c r="J367" t="n">
-        <v>9.844799999999999</v>
+        <v>9.7692</v>
       </c>
     </row>
     <row r="368">
@@ -17069,10 +17069,10 @@
         <v>0.99</v>
       </c>
       <c r="I368" t="n">
-        <v>-0.0094</v>
+        <v>-0.0167</v>
       </c>
       <c r="J368" t="n">
-        <v>-0.2632</v>
+        <v>-0.4676</v>
       </c>
     </row>
     <row r="369">
@@ -17109,10 +17109,10 @@
         <v>0.9</v>
       </c>
       <c r="I369" t="n">
-        <v>-0.1241</v>
+        <v>-0.1392</v>
       </c>
       <c r="J369" t="n">
-        <v>-3.4748</v>
+        <v>-3.8976</v>
       </c>
     </row>
     <row r="370">
@@ -17149,10 +17149,10 @@
         <v>0.73</v>
       </c>
       <c r="I370" t="n">
-        <v>-0.2949</v>
+        <v>-0.3099</v>
       </c>
       <c r="J370" t="n">
-        <v>-8.257199999999999</v>
+        <v>-8.677199999999999</v>
       </c>
     </row>
     <row r="371">
@@ -17189,10 +17189,10 @@
         <v>0.67</v>
       </c>
       <c r="I371" t="n">
-        <v>-0.3521</v>
+        <v>-0.3653</v>
       </c>
       <c r="J371" t="n">
-        <v>-9.8588</v>
+        <v>-10.2284</v>
       </c>
     </row>
     <row r="372">
@@ -17229,10 +17229,10 @@
         <v>1.25</v>
       </c>
       <c r="I372" t="n">
-        <v>0.6278</v>
+        <v>0.59</v>
       </c>
       <c r="J372" t="n">
-        <v>13.8116</v>
+        <v>12.98</v>
       </c>
     </row>
     <row r="373">
@@ -17269,10 +17269,10 @@
         <v>0.82</v>
       </c>
       <c r="I373" t="n">
-        <v>-0.1965</v>
+        <v>-0.2152</v>
       </c>
       <c r="J373" t="n">
-        <v>-4.323</v>
+        <v>-4.7344</v>
       </c>
     </row>
     <row r="374">
@@ -17309,10 +17309,10 @@
         <v>0.73</v>
       </c>
       <c r="I374" t="n">
-        <v>-0.282</v>
+        <v>-0.2998</v>
       </c>
       <c r="J374" t="n">
-        <v>-6.204</v>
+        <v>-6.5956</v>
       </c>
     </row>
     <row r="375">
@@ -17349,10 +17349,10 @@
         <v>0.64</v>
       </c>
       <c r="I375" t="n">
-        <v>-0.3672</v>
+        <v>-0.3821</v>
       </c>
       <c r="J375" t="n">
-        <v>-8.0784</v>
+        <v>-8.4062</v>
       </c>
     </row>
     <row r="376">
@@ -17389,10 +17389,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I376" t="n">
-        <v>-0.442</v>
+        <v>-0.4533</v>
       </c>
       <c r="J376" t="n">
-        <v>-9.724</v>
+        <v>-9.9726</v>
       </c>
     </row>
     <row r="377">
@@ -17429,10 +17429,10 @@
         <v>1.53</v>
       </c>
       <c r="I377" t="n">
-        <v>1.1609</v>
+        <v>1.1286</v>
       </c>
       <c r="J377" t="n">
-        <v>25.5398</v>
+        <v>24.8292</v>
       </c>
     </row>
     <row r="378">
@@ -17469,10 +17469,10 @@
         <v>1.49</v>
       </c>
       <c r="I378" t="n">
-        <v>1.1109</v>
+        <v>1.0747</v>
       </c>
       <c r="J378" t="n">
-        <v>24.4398</v>
+        <v>23.6434</v>
       </c>
     </row>
     <row r="379">
@@ -17509,10 +17509,10 @@
         <v>1.18</v>
       </c>
       <c r="I379" t="n">
-        <v>0.4958</v>
+        <v>0.4906</v>
       </c>
       <c r="J379" t="n">
-        <v>10.9076</v>
+        <v>10.7932</v>
       </c>
     </row>
     <row r="380">
@@ -17549,10 +17549,10 @@
         <v>1.11</v>
       </c>
       <c r="I380" t="n">
-        <v>0.3113</v>
+        <v>0.3227</v>
       </c>
       <c r="J380" t="n">
-        <v>6.8486</v>
+        <v>7.0994</v>
       </c>
     </row>
     <row r="381">
@@ -17589,10 +17589,10 @@
         <v>1.1</v>
       </c>
       <c r="I381" t="n">
-        <v>0.2832</v>
+        <v>0.2968</v>
       </c>
       <c r="J381" t="n">
-        <v>6.2304</v>
+        <v>6.5296</v>
       </c>
     </row>
     <row r="382">
@@ -17629,10 +17629,10 @@
         <v>1.06</v>
       </c>
       <c r="I382" t="n">
-        <v>0.1809</v>
+        <v>0.184</v>
       </c>
       <c r="J382" t="n">
-        <v>5.2461</v>
+        <v>5.336</v>
       </c>
     </row>
     <row r="383">
@@ -17669,10 +17669,10 @@
         <v>0.97</v>
       </c>
       <c r="I383" t="n">
-        <v>-0.0439</v>
+        <v>-0.0535</v>
       </c>
       <c r="J383" t="n">
-        <v>-1.2731</v>
+        <v>-1.5515</v>
       </c>
     </row>
     <row r="384">
@@ -17709,10 +17709,10 @@
         <v>0.96</v>
       </c>
       <c r="I384" t="n">
-        <v>-0.0572</v>
+        <v>-0.068</v>
       </c>
       <c r="J384" t="n">
-        <v>-1.6588</v>
+        <v>-1.972</v>
       </c>
     </row>
     <row r="385">
@@ -17749,10 +17749,10 @@
         <v>0.86</v>
       </c>
       <c r="I385" t="n">
-        <v>-0.1689</v>
+        <v>-0.1843</v>
       </c>
       <c r="J385" t="n">
-        <v>-4.8981</v>
+        <v>-5.3447</v>
       </c>
     </row>
     <row r="386">
@@ -17789,10 +17789,10 @@
         <v>0.78</v>
       </c>
       <c r="I386" t="n">
-        <v>-0.25</v>
+        <v>-0.2651</v>
       </c>
       <c r="J386" t="n">
-        <v>-7.25</v>
+        <v>-7.6879</v>
       </c>
     </row>
     <row r="387">
@@ -17829,10 +17829,10 @@
         <v>1.49</v>
       </c>
       <c r="I387" t="n">
-        <v>1.1449</v>
+        <v>1.1048</v>
       </c>
       <c r="J387" t="n">
-        <v>33.2021</v>
+        <v>32.0392</v>
       </c>
     </row>
     <row r="388">
@@ -17869,10 +17869,10 @@
         <v>1.15</v>
       </c>
       <c r="I388" t="n">
-        <v>0.4474</v>
+        <v>0.4405</v>
       </c>
       <c r="J388" t="n">
-        <v>12.9746</v>
+        <v>12.7745</v>
       </c>
     </row>
     <row r="389">
@@ -17909,10 +17909,10 @@
         <v>1.12</v>
       </c>
       <c r="I389" t="n">
-        <v>0.3708</v>
+        <v>0.37</v>
       </c>
       <c r="J389" t="n">
-        <v>10.7532</v>
+        <v>10.73</v>
       </c>
     </row>
     <row r="390">
@@ -17949,10 +17949,10 @@
         <v>1.08</v>
       </c>
       <c r="I390" t="n">
-        <v>0.2594</v>
+        <v>0.2668</v>
       </c>
       <c r="J390" t="n">
-        <v>7.5226</v>
+        <v>7.7372</v>
       </c>
     </row>
     <row r="391">
@@ -17989,10 +17989,10 @@
         <v>0.85</v>
       </c>
       <c r="I391" t="n">
-        <v>-0.5274</v>
+        <v>-0.4962</v>
       </c>
       <c r="J391" t="n">
-        <v>-15.2946</v>
+        <v>-14.3898</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/2013/event_2013_evp_summary.xlsx
+++ b/database/event/2013/event_2013_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7.8934</v>
+        <v>7.8647</v>
       </c>
       <c r="C2" t="n">
-        <v>2.6341</v>
+        <v>2.6245</v>
       </c>
       <c r="D2" t="n">
-        <v>2.969</v>
+        <v>2.977</v>
       </c>
       <c r="E2" t="n">
-        <v>7.8934</v>
+        <v>7.8647</v>
       </c>
       <c r="F2" t="n">
-        <v>4.2493</v>
+        <v>4.1599</v>
       </c>
       <c r="G2" t="n">
-        <v>3.6441</v>
+        <v>3.7048</v>
       </c>
       <c r="H2" t="n">
-        <v>6.5756</v>
+        <v>6.5831</v>
       </c>
       <c r="I2" t="n">
-        <v>7.0971</v>
+        <v>7.1251</v>
       </c>
       <c r="J2" t="n">
-        <v>3.6441</v>
+        <v>3.7048</v>
       </c>
       <c r="K2" t="n">
         <v>331</v>
@@ -529,7 +529,7 @@
         <v>72</v>
       </c>
       <c r="M2" t="n">
-        <v>10.7412</v>
+        <v>10.8299</v>
       </c>
       <c r="N2" t="n">
         <v>403</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.3549</v>
+        <v>5.2915</v>
       </c>
       <c r="C3" t="n">
-        <v>1.787</v>
+        <v>1.7658</v>
       </c>
       <c r="D3" t="n">
-        <v>1.8135</v>
+        <v>1.8047</v>
       </c>
       <c r="E3" t="n">
-        <v>5.3549</v>
+        <v>5.2915</v>
       </c>
       <c r="F3" t="n">
-        <v>2.5292</v>
+        <v>2.4996</v>
       </c>
       <c r="G3" t="n">
-        <v>2.8257</v>
+        <v>2.7919</v>
       </c>
       <c r="H3" t="n">
-        <v>2.8107</v>
+        <v>2.7781</v>
       </c>
       <c r="I3" t="n">
-        <v>3.0336</v>
+        <v>3.0068</v>
       </c>
       <c r="J3" t="n">
-        <v>2.8257</v>
+        <v>2.7919</v>
       </c>
       <c r="K3" t="n">
         <v>331</v>
@@ -575,7 +575,7 @@
         <v>72</v>
       </c>
       <c r="M3" t="n">
-        <v>5.859299999999999</v>
+        <v>5.7987</v>
       </c>
       <c r="N3" t="n">
         <v>403</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.7119</v>
+        <v>4.627</v>
       </c>
       <c r="C4" t="n">
-        <v>1.5724</v>
+        <v>1.5441</v>
       </c>
       <c r="D4" t="n">
-        <v>1.5208</v>
+        <v>1.502</v>
       </c>
       <c r="E4" t="n">
-        <v>4.7119</v>
+        <v>4.627</v>
       </c>
       <c r="F4" t="n">
-        <v>2.7353</v>
+        <v>2.6757</v>
       </c>
       <c r="G4" t="n">
-        <v>1.9766</v>
+        <v>1.9513</v>
       </c>
       <c r="H4" t="n">
-        <v>3.2618</v>
+        <v>3.1817</v>
       </c>
       <c r="I4" t="n">
-        <v>3.5205</v>
+        <v>3.4437</v>
       </c>
       <c r="J4" t="n">
-        <v>1.9766</v>
+        <v>1.9513</v>
       </c>
       <c r="K4" t="n">
         <v>331</v>
@@ -621,7 +621,7 @@
         <v>72</v>
       </c>
       <c r="M4" t="n">
-        <v>5.4971</v>
+        <v>5.395</v>
       </c>
       <c r="N4" t="n">
         <v>403</v>
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.3316</v>
+        <v>4.2321</v>
       </c>
       <c r="C5" t="n">
-        <v>1.4455</v>
+        <v>1.4123</v>
       </c>
       <c r="D5" t="n">
-        <v>1.3476</v>
+        <v>1.3221</v>
       </c>
       <c r="E5" t="n">
-        <v>4.3316</v>
+        <v>4.2321</v>
       </c>
       <c r="F5" t="n">
-        <v>2.8267</v>
+        <v>2.7985</v>
       </c>
       <c r="G5" t="n">
-        <v>1.5049</v>
+        <v>1.4336</v>
       </c>
       <c r="H5" t="n">
-        <v>3.4617</v>
+        <v>3.4631</v>
       </c>
       <c r="I5" t="n">
-        <v>3.7363</v>
+        <v>3.7482</v>
       </c>
       <c r="J5" t="n">
-        <v>1.5049</v>
+        <v>1.4336</v>
       </c>
       <c r="K5" t="n">
         <v>331</v>
@@ -667,7 +667,7 @@
         <v>72</v>
       </c>
       <c r="M5" t="n">
-        <v>5.2412</v>
+        <v>5.1818</v>
       </c>
       <c r="N5" t="n">
         <v>403</v>
@@ -680,28 +680,28 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.8304</v>
+        <v>3.7164</v>
       </c>
       <c r="C6" t="n">
-        <v>1.2782</v>
+        <v>1.2402</v>
       </c>
       <c r="D6" t="n">
-        <v>1.1195</v>
+        <v>1.0872</v>
       </c>
       <c r="E6" t="n">
-        <v>3.8304</v>
+        <v>3.7164</v>
       </c>
       <c r="F6" t="n">
-        <v>3.8304</v>
+        <v>3.7164</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>5.6587</v>
+        <v>5.5668</v>
       </c>
       <c r="I6" t="n">
-        <v>5.6587</v>
+        <v>5.5668</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -713,7 +713,7 @@
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>5.6587</v>
+        <v>5.5668</v>
       </c>
       <c r="N6" t="n">
         <v>249</v>
@@ -726,28 +726,28 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.5837</v>
+        <v>3.4756</v>
       </c>
       <c r="C7" t="n">
-        <v>1.1959</v>
+        <v>1.1598</v>
       </c>
       <c r="D7" t="n">
-        <v>1.0072</v>
+        <v>0.9775</v>
       </c>
       <c r="E7" t="n">
-        <v>3.5837</v>
+        <v>3.4756</v>
       </c>
       <c r="F7" t="n">
-        <v>3.5837</v>
+        <v>3.4756</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>5.1186</v>
+        <v>5.015</v>
       </c>
       <c r="I7" t="n">
-        <v>5.2505</v>
+        <v>5.149</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -759,7 +759,7 @@
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>5.2505</v>
+        <v>5.149</v>
       </c>
       <c r="N7" t="n">
         <v>301</v>
@@ -772,28 +772,28 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.4433</v>
+        <v>3.3772</v>
       </c>
       <c r="C8" t="n">
-        <v>1.1491</v>
+        <v>1.127</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9433</v>
+        <v>0.9327</v>
       </c>
       <c r="E8" t="n">
-        <v>3.4433</v>
+        <v>3.3772</v>
       </c>
       <c r="F8" t="n">
-        <v>3.4433</v>
+        <v>3.3772</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>4.8113</v>
+        <v>4.7895</v>
       </c>
       <c r="I8" t="n">
-        <v>4.8113</v>
+        <v>4.7895</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -805,7 +805,7 @@
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>4.8113</v>
+        <v>4.7895</v>
       </c>
       <c r="N8" t="n">
         <v>249</v>
@@ -818,28 +818,28 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.2782</v>
+        <v>3.2696</v>
       </c>
       <c r="C9" t="n">
-        <v>1.094</v>
+        <v>1.0911</v>
       </c>
       <c r="D9" t="n">
-        <v>0.8681</v>
+        <v>0.8837</v>
       </c>
       <c r="E9" t="n">
-        <v>3.2782</v>
+        <v>3.2696</v>
       </c>
       <c r="F9" t="n">
-        <v>3.2782</v>
+        <v>3.2696</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>4.45</v>
+        <v>4.5428</v>
       </c>
       <c r="I9" t="n">
-        <v>4.45</v>
+        <v>4.5428</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -851,7 +851,7 @@
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>4.45</v>
+        <v>4.5428</v>
       </c>
       <c r="N9" t="n">
         <v>249</v>
@@ -864,28 +864,28 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.2596</v>
+        <v>3.1574</v>
       </c>
       <c r="C10" t="n">
-        <v>1.0878</v>
+        <v>1.0536</v>
       </c>
       <c r="D10" t="n">
-        <v>0.8596</v>
+        <v>0.8326</v>
       </c>
       <c r="E10" t="n">
-        <v>3.2596</v>
+        <v>3.1574</v>
       </c>
       <c r="F10" t="n">
-        <v>3.2596</v>
+        <v>3.1574</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>4.4094</v>
+        <v>4.2856</v>
       </c>
       <c r="I10" t="n">
-        <v>4.4094</v>
+        <v>4.2856</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -897,7 +897,7 @@
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>4.4094</v>
+        <v>4.2856</v>
       </c>
       <c r="N10" t="n">
         <v>249</v>
@@ -910,31 +910,31 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.9704</v>
+        <v>2.8764</v>
       </c>
       <c r="C11" t="n">
-        <v>0.9912</v>
+        <v>0.9599</v>
       </c>
       <c r="D11" t="n">
-        <v>0.728</v>
+        <v>0.7045</v>
       </c>
       <c r="E11" t="n">
-        <v>2.9704</v>
+        <v>2.8764</v>
       </c>
       <c r="F11" t="n">
-        <v>2.3365</v>
+        <v>2.3052</v>
       </c>
       <c r="G11" t="n">
-        <v>0.6339</v>
+        <v>0.5712</v>
       </c>
       <c r="H11" t="n">
-        <v>2.3889</v>
+        <v>2.3328</v>
       </c>
       <c r="I11" t="n">
-        <v>2.5784</v>
+        <v>2.5248</v>
       </c>
       <c r="J11" t="n">
-        <v>0.6339</v>
+        <v>0.5712</v>
       </c>
       <c r="K11" t="n">
         <v>331</v>
@@ -943,7 +943,7 @@
         <v>72</v>
       </c>
       <c r="M11" t="n">
-        <v>3.2123</v>
+        <v>3.096</v>
       </c>
       <c r="N11" t="n">
         <v>403</v>
@@ -956,31 +956,31 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.9485</v>
+        <v>2.874</v>
       </c>
       <c r="C12" t="n">
-        <v>0.9839</v>
+        <v>0.9591</v>
       </c>
       <c r="D12" t="n">
-        <v>0.718</v>
+        <v>0.7035</v>
       </c>
       <c r="E12" t="n">
-        <v>2.9485</v>
+        <v>2.874</v>
       </c>
       <c r="F12" t="n">
-        <v>3.4224</v>
+        <v>3.3361</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.4739</v>
+        <v>-0.4621</v>
       </c>
       <c r="H12" t="n">
-        <v>4.7656</v>
+        <v>4.6952</v>
       </c>
       <c r="I12" t="n">
-        <v>4.8884</v>
+        <v>4.8207</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.4739</v>
+        <v>-0.4621</v>
       </c>
       <c r="K12" t="n">
         <v>159</v>
@@ -989,7 +989,7 @@
         <v>72</v>
       </c>
       <c r="M12" t="n">
-        <v>4.4145</v>
+        <v>4.3586</v>
       </c>
       <c r="N12" t="n">
         <v>231</v>
@@ -1002,28 +1002,28 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.9249</v>
+        <v>2.8673</v>
       </c>
       <c r="C13" t="n">
-        <v>0.9761</v>
+        <v>0.9568</v>
       </c>
       <c r="D13" t="n">
-        <v>0.7073</v>
+        <v>0.7004</v>
       </c>
       <c r="E13" t="n">
-        <v>2.9249</v>
+        <v>2.8673</v>
       </c>
       <c r="F13" t="n">
-        <v>2.9249</v>
+        <v>2.8673</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>3.6769</v>
+        <v>3.6208</v>
       </c>
       <c r="I13" t="n">
-        <v>3.7716</v>
+        <v>3.7176</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1035,7 +1035,7 @@
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>3.7716</v>
+        <v>3.7176</v>
       </c>
       <c r="N13" t="n">
         <v>301</v>
@@ -1048,28 +1048,28 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.877</v>
+        <v>2.7896</v>
       </c>
       <c r="C14" t="n">
-        <v>0.9601</v>
+        <v>0.9308999999999999</v>
       </c>
       <c r="D14" t="n">
-        <v>0.6855</v>
+        <v>0.665</v>
       </c>
       <c r="E14" t="n">
-        <v>2.877</v>
+        <v>2.7896</v>
       </c>
       <c r="F14" t="n">
-        <v>2.877</v>
+        <v>2.7896</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>3.572</v>
+        <v>3.4427</v>
       </c>
       <c r="I14" t="n">
-        <v>3.664</v>
+        <v>3.5347</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1081,7 +1081,7 @@
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>3.664</v>
+        <v>3.5347</v>
       </c>
       <c r="N14" t="n">
         <v>301</v>
@@ -1094,28 +1094,28 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.4258</v>
+        <v>2.3796</v>
       </c>
       <c r="C15" t="n">
-        <v>0.8095</v>
+        <v>0.7941</v>
       </c>
       <c r="D15" t="n">
-        <v>0.4801</v>
+        <v>0.4782</v>
       </c>
       <c r="E15" t="n">
-        <v>2.4258</v>
+        <v>2.3796</v>
       </c>
       <c r="F15" t="n">
-        <v>2.4258</v>
+        <v>2.3796</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>2.5844</v>
+        <v>2.5033</v>
       </c>
       <c r="I15" t="n">
-        <v>2.5844</v>
+        <v>2.5033</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1127,7 +1127,7 @@
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>2.5844</v>
+        <v>2.5033</v>
       </c>
       <c r="N15" t="n">
         <v>247</v>
@@ -1140,28 +1140,28 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.315</v>
+        <v>2.1362</v>
       </c>
       <c r="C16" t="n">
-        <v>0.7725</v>
+        <v>0.7129</v>
       </c>
       <c r="D16" t="n">
-        <v>0.4296</v>
+        <v>0.3674</v>
       </c>
       <c r="E16" t="n">
-        <v>2.315</v>
+        <v>2.1362</v>
       </c>
       <c r="F16" t="n">
-        <v>2.315</v>
+        <v>2.1362</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>2.342</v>
+        <v>2.1362</v>
       </c>
       <c r="I16" t="n">
-        <v>2.4023</v>
+        <v>2.1933</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1173,7 +1173,7 @@
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>2.4023</v>
+        <v>2.1933</v>
       </c>
       <c r="N16" t="n">
         <v>301</v>
@@ -1182,93 +1182,93 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>jdm64</t>
+          <t>Kjaerbye</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.2987</v>
+        <v>2.0791</v>
       </c>
       <c r="C17" t="n">
-        <v>0.7671</v>
+        <v>0.6938</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4222</v>
+        <v>0.3413</v>
       </c>
       <c r="E17" t="n">
-        <v>2.2987</v>
+        <v>2.0791</v>
       </c>
       <c r="F17" t="n">
-        <v>2.2987</v>
+        <v>2.9063</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>-0.8272</v>
       </c>
       <c r="H17" t="n">
-        <v>2.3062</v>
+        <v>3.7102</v>
       </c>
       <c r="I17" t="n">
-        <v>2.3656</v>
+        <v>3.8093</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>-0.8272</v>
       </c>
       <c r="K17" t="n">
-        <v>369</v>
+        <v>159</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="M17" t="n">
-        <v>2.3656</v>
+        <v>2.9821</v>
       </c>
       <c r="N17" t="n">
-        <v>369</v>
+        <v>231</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Kjaerbye</t>
+          <t>jdm64</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2.1169</v>
+        <v>1.9835</v>
       </c>
       <c r="C18" t="n">
-        <v>0.7064</v>
+        <v>0.6619</v>
       </c>
       <c r="D18" t="n">
-        <v>0.3395</v>
+        <v>0.2978</v>
       </c>
       <c r="E18" t="n">
-        <v>2.1169</v>
+        <v>1.9835</v>
       </c>
       <c r="F18" t="n">
-        <v>2.9918</v>
+        <v>1.9835</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.8749</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>3.8231</v>
+        <v>1.9835</v>
       </c>
       <c r="I18" t="n">
-        <v>3.9216</v>
+        <v>2.0365</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.8749</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>159</v>
+        <v>369</v>
       </c>
       <c r="L18" t="n">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>3.0467</v>
+        <v>2.0365</v>
       </c>
       <c r="N18" t="n">
-        <v>231</v>
+        <v>369</v>
       </c>
     </row>
     <row r="19">
@@ -1278,28 +1278,28 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.908</v>
+        <v>1.7971</v>
       </c>
       <c r="C19" t="n">
-        <v>0.6367</v>
+        <v>0.5997</v>
       </c>
       <c r="D19" t="n">
-        <v>0.2444</v>
+        <v>0.2129</v>
       </c>
       <c r="E19" t="n">
-        <v>1.908</v>
+        <v>1.7971</v>
       </c>
       <c r="F19" t="n">
-        <v>1.908</v>
+        <v>1.7971</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>1.908</v>
+        <v>1.7971</v>
       </c>
       <c r="I19" t="n">
-        <v>1.908</v>
+        <v>1.7971</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -1311,7 +1311,7 @@
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>1.908</v>
+        <v>1.7971</v>
       </c>
       <c r="N19" t="n">
         <v>249</v>
@@ -1324,31 +1324,31 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.23</v>
+        <v>1.2456</v>
       </c>
       <c r="C20" t="n">
-        <v>0.4105</v>
+        <v>0.4157</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.0643</v>
+        <v>-0.0384</v>
       </c>
       <c r="E20" t="n">
-        <v>1.23</v>
+        <v>1.2456</v>
       </c>
       <c r="F20" t="n">
-        <v>1.2035</v>
+        <v>1.2716</v>
       </c>
       <c r="G20" t="n">
-        <v>0.0265</v>
+        <v>-0.026</v>
       </c>
       <c r="H20" t="n">
-        <v>1.2035</v>
+        <v>1.2716</v>
       </c>
       <c r="I20" t="n">
-        <v>1.2345</v>
+        <v>1.3056</v>
       </c>
       <c r="J20" t="n">
-        <v>0.0265</v>
+        <v>-0.026</v>
       </c>
       <c r="K20" t="n">
         <v>159</v>
@@ -1357,7 +1357,7 @@
         <v>72</v>
       </c>
       <c r="M20" t="n">
-        <v>1.261</v>
+        <v>1.2796</v>
       </c>
       <c r="N20" t="n">
         <v>231</v>
@@ -1366,93 +1366,93 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Skadoodle</t>
+          <t>MSL</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.1642</v>
+        <v>1.0457</v>
       </c>
       <c r="C21" t="n">
-        <v>0.3885</v>
+        <v>0.349</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.09420000000000001</v>
+        <v>-0.1294</v>
       </c>
       <c r="E21" t="n">
-        <v>1.1642</v>
+        <v>1.0457</v>
       </c>
       <c r="F21" t="n">
-        <v>1.1642</v>
+        <v>1.9335</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>-0.8878</v>
       </c>
       <c r="H21" t="n">
-        <v>1.1642</v>
+        <v>1.9335</v>
       </c>
       <c r="I21" t="n">
-        <v>1.1642</v>
+        <v>1.9852</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>-0.8878</v>
       </c>
       <c r="K21" t="n">
-        <v>247</v>
+        <v>159</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="M21" t="n">
-        <v>1.1642</v>
+        <v>1.0974</v>
       </c>
       <c r="N21" t="n">
-        <v>247</v>
+        <v>231</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>MSL</t>
+          <t>Skadoodle</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.0936</v>
+        <v>1.0237</v>
       </c>
       <c r="C22" t="n">
-        <v>0.3649</v>
+        <v>0.3416</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.1264</v>
+        <v>-0.1394</v>
       </c>
       <c r="E22" t="n">
-        <v>1.0936</v>
+        <v>1.0237</v>
       </c>
       <c r="F22" t="n">
-        <v>1.9753</v>
+        <v>1.0237</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.8817</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>1.9753</v>
+        <v>1.0237</v>
       </c>
       <c r="I22" t="n">
-        <v>2.0262</v>
+        <v>1.0237</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.8817</v>
+        <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>159</v>
+        <v>247</v>
       </c>
       <c r="L22" t="n">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>1.1445</v>
+        <v>1.0237</v>
       </c>
       <c r="N22" t="n">
-        <v>231</v>
+        <v>247</v>
       </c>
     </row>
     <row r="23">
@@ -1462,31 +1462,31 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.8469</v>
+        <v>0.8408</v>
       </c>
       <c r="C23" t="n">
-        <v>0.2826</v>
+        <v>0.2806</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.2387</v>
+        <v>-0.2228</v>
       </c>
       <c r="E23" t="n">
-        <v>0.8469</v>
+        <v>0.8408</v>
       </c>
       <c r="F23" t="n">
-        <v>1.4687</v>
+        <v>1.4183</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.6218</v>
+        <v>-0.5775</v>
       </c>
       <c r="H23" t="n">
-        <v>1.4687</v>
+        <v>1.4183</v>
       </c>
       <c r="I23" t="n">
-        <v>1.5065</v>
+        <v>1.4562</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.6218</v>
+        <v>-0.5775</v>
       </c>
       <c r="K23" t="n">
         <v>159</v>
@@ -1495,7 +1495,7 @@
         <v>72</v>
       </c>
       <c r="M23" t="n">
-        <v>0.8846999999999999</v>
+        <v>0.8786999999999999</v>
       </c>
       <c r="N23" t="n">
         <v>231</v>
@@ -1504,93 +1504,93 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>waterfaLLZ</t>
+          <t>RpK</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.7881</v>
+        <v>0.7602</v>
       </c>
       <c r="C24" t="n">
-        <v>0.263</v>
+        <v>0.2537</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.2654</v>
+        <v>-0.2595</v>
       </c>
       <c r="E24" t="n">
-        <v>0.7881</v>
+        <v>0.7602</v>
       </c>
       <c r="F24" t="n">
-        <v>0.7881</v>
+        <v>0.7602</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0.7881</v>
+        <v>0.7602</v>
       </c>
       <c r="I24" t="n">
-        <v>0.7881</v>
+        <v>0.7805</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>95</v>
+        <v>301</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0.7881</v>
+        <v>0.7805</v>
       </c>
       <c r="N24" t="n">
-        <v>95</v>
+        <v>301</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>RpK</t>
+          <t>waterfaLLZ</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.6773</v>
+        <v>0.7147</v>
       </c>
       <c r="C25" t="n">
-        <v>0.226</v>
+        <v>0.2385</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.3159</v>
+        <v>-0.2802</v>
       </c>
       <c r="E25" t="n">
-        <v>0.6773</v>
+        <v>0.7147</v>
       </c>
       <c r="F25" t="n">
-        <v>0.6773</v>
+        <v>0.7147</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>0.6773</v>
+        <v>0.7147</v>
       </c>
       <c r="I25" t="n">
-        <v>0.6948</v>
+        <v>0.7147</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>301</v>
+        <v>95</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>0.6948</v>
+        <v>0.7147</v>
       </c>
       <c r="N25" t="n">
-        <v>301</v>
+        <v>95</v>
       </c>
     </row>
     <row r="26">
@@ -1600,28 +1600,28 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.4578</v>
+        <v>0.3942</v>
       </c>
       <c r="C26" t="n">
-        <v>0.1528</v>
+        <v>0.1315</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.4158</v>
+        <v>-0.4262</v>
       </c>
       <c r="E26" t="n">
-        <v>0.4578</v>
+        <v>0.3942</v>
       </c>
       <c r="F26" t="n">
-        <v>0.4578</v>
+        <v>0.3942</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0.4578</v>
+        <v>0.3942</v>
       </c>
       <c r="I26" t="n">
-        <v>0.4578</v>
+        <v>0.3942</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -1633,7 +1633,7 @@
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>0.4578</v>
+        <v>0.3942</v>
       </c>
       <c r="N26" t="n">
         <v>107</v>
@@ -1646,28 +1646,28 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.2897</v>
+        <v>0.1629</v>
       </c>
       <c r="C27" t="n">
-        <v>0.09669999999999999</v>
+        <v>0.0544</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.4923</v>
+        <v>-0.5316</v>
       </c>
       <c r="E27" t="n">
-        <v>0.2897</v>
+        <v>0.1629</v>
       </c>
       <c r="F27" t="n">
-        <v>0.2897</v>
+        <v>0.1629</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>0.2897</v>
+        <v>0.1629</v>
       </c>
       <c r="I27" t="n">
-        <v>0.2972</v>
+        <v>0.1672</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -1679,7 +1679,7 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>0.2972</v>
+        <v>0.1672</v>
       </c>
       <c r="N27" t="n">
         <v>369</v>
@@ -1692,28 +1692,28 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.0839</v>
+        <v>-0.0898</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.028</v>
+        <v>-0.03</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.6624</v>
+        <v>-0.6467000000000001</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.0839</v>
+        <v>-0.0898</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.0839</v>
+        <v>-0.0898</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.0839</v>
+        <v>-0.0898</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.0839</v>
+        <v>-0.0898</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -1725,7 +1725,7 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.0839</v>
+        <v>-0.0898</v>
       </c>
       <c r="N28" t="n">
         <v>107</v>
@@ -1738,28 +1738,28 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.121</v>
+        <v>-0.1976</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.0404</v>
+        <v>-0.0659</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.6793</v>
+        <v>-0.6958</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.121</v>
+        <v>-0.1976</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.121</v>
+        <v>-0.1976</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.121</v>
+        <v>-0.1976</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.1241</v>
+        <v>-0.2029</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -1771,7 +1771,7 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.1241</v>
+        <v>-0.2029</v>
       </c>
       <c r="N29" t="n">
         <v>369</v>
@@ -1784,28 +1784,28 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.1274</v>
+        <v>-0.2288</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.0425</v>
+        <v>-0.0764</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.6822</v>
+        <v>-0.71</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.1274</v>
+        <v>-0.2288</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.1274</v>
+        <v>-0.2288</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.1274</v>
+        <v>-0.2288</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.1274</v>
+        <v>-0.2288</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -1817,7 +1817,7 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.1274</v>
+        <v>-0.2288</v>
       </c>
       <c r="N30" t="n">
         <v>95</v>
@@ -1826,139 +1826,139 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Stewie2K</t>
+          <t>hazed</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.3107</v>
+        <v>-0.2736</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.1037</v>
+        <v>-0.09130000000000001</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.7655999999999999</v>
+        <v>-0.7304</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.3107</v>
+        <v>-0.2736</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.3107</v>
+        <v>-0.2736</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.3107</v>
+        <v>-0.2736</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.3107</v>
+        <v>-0.2809</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>247</v>
+        <v>369</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.3107</v>
+        <v>-0.2809</v>
       </c>
       <c r="N31" t="n">
-        <v>247</v>
+        <v>369</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>hazed</t>
+          <t>B1ad3</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.3933</v>
+        <v>-0.4382</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.1312</v>
+        <v>-0.1462</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.8032</v>
+        <v>-0.8054</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.3933</v>
+        <v>-0.4382</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.3933</v>
+        <v>-0.4382</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.3933</v>
+        <v>-0.4382</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.4034</v>
+        <v>-0.4382</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>369</v>
+        <v>107</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.4034</v>
+        <v>-0.4382</v>
       </c>
       <c r="N32" t="n">
-        <v>369</v>
+        <v>107</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>B1ad3</t>
+          <t>Stewie2K</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.4372</v>
+        <v>-0.4487</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.1459</v>
+        <v>-0.1497</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.8232</v>
+        <v>-0.8102</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.4372</v>
+        <v>-0.4487</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.4372</v>
+        <v>-0.4487</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.4372</v>
+        <v>-0.4487</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.4372</v>
+        <v>-0.4487</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>107</v>
+        <v>247</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.4372</v>
+        <v>-0.4487</v>
       </c>
       <c r="N33" t="n">
-        <v>107</v>
+        <v>247</v>
       </c>
     </row>
     <row r="34">
@@ -1968,28 +1968,28 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.5983000000000001</v>
+        <v>-0.5597</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.1997</v>
+        <v>-0.1868</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.8966</v>
+        <v>-0.8608</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.5983000000000001</v>
+        <v>-0.5597</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.5983000000000001</v>
+        <v>-0.5597</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.5983000000000001</v>
+        <v>-0.5597</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.5983000000000001</v>
+        <v>-0.5597</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -2001,7 +2001,7 @@
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.5983000000000001</v>
+        <v>-0.5597</v>
       </c>
       <c r="N34" t="n">
         <v>107</v>
@@ -2010,93 +2010,93 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>bondik</t>
+          <t>n0thing</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.7251</v>
+        <v>-0.7035</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.242</v>
+        <v>-0.2348</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.9543</v>
+        <v>-0.9263</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.7251</v>
+        <v>-0.7035</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.7251</v>
+        <v>-0.7035</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.7251</v>
+        <v>-0.7035</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.7251</v>
+        <v>-0.7035</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>107</v>
+        <v>247</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.7251</v>
+        <v>-0.7035</v>
       </c>
       <c r="N35" t="n">
-        <v>107</v>
+        <v>247</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>n0thing</t>
+          <t>bondik</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.7379</v>
+        <v>-0.7135</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.2462</v>
+        <v>-0.2381</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.9601</v>
+        <v>-0.9308</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.7379</v>
+        <v>-0.7135</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.7379</v>
+        <v>-0.7135</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.7379</v>
+        <v>-0.7135</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.7379</v>
+        <v>-0.7135</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>247</v>
+        <v>107</v>
       </c>
       <c r="L36" t="n">
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.7379</v>
+        <v>-0.7135</v>
       </c>
       <c r="N36" t="n">
-        <v>247</v>
+        <v>107</v>
       </c>
     </row>
     <row r="37">
@@ -2106,28 +2106,28 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-0.8758</v>
+        <v>-0.8662</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.2923</v>
+        <v>-0.2891</v>
       </c>
       <c r="D37" t="n">
-        <v>-1.0229</v>
+        <v>-1.0004</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.8758</v>
+        <v>-0.8662</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.8758</v>
+        <v>-0.8662</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.8758</v>
+        <v>-0.8662</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.8984</v>
+        <v>-0.8893</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -2139,7 +2139,7 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>-0.8984</v>
+        <v>-0.8893</v>
       </c>
       <c r="N37" t="n">
         <v>369</v>
@@ -2148,93 +2148,93 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>freakazoid</t>
+          <t>fejtZ</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-1.2623</v>
+        <v>-1.2198</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.4212</v>
+        <v>-0.4071</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.1988</v>
+        <v>-1.1615</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.2623</v>
+        <v>-1.2198</v>
       </c>
       <c r="F38" t="n">
-        <v>-1.2623</v>
+        <v>-1.2198</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>-1.2623</v>
+        <v>-1.2198</v>
       </c>
       <c r="I38" t="n">
-        <v>-1.2623</v>
+        <v>-1.2198</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>247</v>
+        <v>95</v>
       </c>
       <c r="L38" t="n">
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>-1.2623</v>
+        <v>-1.2198</v>
       </c>
       <c r="N38" t="n">
-        <v>247</v>
+        <v>95</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>fejtZ</t>
+          <t>freakazoid</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.2665</v>
+        <v>-1.2393</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.4226</v>
+        <v>-0.4136</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.2007</v>
+        <v>-1.1703</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.2665</v>
+        <v>-1.2393</v>
       </c>
       <c r="F39" t="n">
-        <v>-1.2665</v>
+        <v>-1.2393</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>-1.2665</v>
+        <v>-1.2393</v>
       </c>
       <c r="I39" t="n">
-        <v>-1.2665</v>
+        <v>-1.2393</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>95</v>
+        <v>247</v>
       </c>
       <c r="L39" t="n">
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>-1.2665</v>
+        <v>-1.2393</v>
       </c>
       <c r="N39" t="n">
-        <v>95</v>
+        <v>247</v>
       </c>
     </row>
     <row r="40">
@@ -2244,28 +2244,28 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-1.3707</v>
+        <v>-1.329</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.4574</v>
+        <v>-0.4435</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.2482</v>
+        <v>-1.2112</v>
       </c>
       <c r="E40" t="n">
-        <v>-1.3707</v>
+        <v>-1.329</v>
       </c>
       <c r="F40" t="n">
-        <v>-1.3707</v>
+        <v>-1.329</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>-1.3707</v>
+        <v>-1.329</v>
       </c>
       <c r="I40" t="n">
-        <v>-1.3707</v>
+        <v>-1.329</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -2277,7 +2277,7 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>-1.3707</v>
+        <v>-1.329</v>
       </c>
       <c r="N40" t="n">
         <v>95</v>
@@ -2290,28 +2290,28 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-1.4366</v>
+        <v>-1.3951</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.4794</v>
+        <v>-0.4656</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.2782</v>
+        <v>-1.2413</v>
       </c>
       <c r="E41" t="n">
-        <v>-1.4366</v>
+        <v>-1.3951</v>
       </c>
       <c r="F41" t="n">
-        <v>-1.4366</v>
+        <v>-1.3951</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>-1.4366</v>
+        <v>-1.3951</v>
       </c>
       <c r="I41" t="n">
-        <v>-1.4366</v>
+        <v>-1.3951</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -2323,7 +2323,7 @@
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>-1.4366</v>
+        <v>-1.3951</v>
       </c>
       <c r="N41" t="n">
         <v>95</v>
@@ -2429,10 +2429,10 @@
         <v>1.93</v>
       </c>
       <c r="I2" t="n">
-        <v>1.7156</v>
+        <v>1.7493</v>
       </c>
       <c r="J2" t="n">
-        <v>34.312</v>
+        <v>34.986</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>1.84</v>
       </c>
       <c r="I3" t="n">
-        <v>1.6088</v>
+        <v>1.6374</v>
       </c>
       <c r="J3" t="n">
-        <v>32.176</v>
+        <v>32.748</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>1.62</v>
       </c>
       <c r="I4" t="n">
-        <v>1.2781</v>
+        <v>1.3121</v>
       </c>
       <c r="J4" t="n">
-        <v>25.562</v>
+        <v>26.242</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>1.33</v>
       </c>
       <c r="I5" t="n">
-        <v>0.7643</v>
+        <v>0.7514</v>
       </c>
       <c r="J5" t="n">
-        <v>15.286</v>
+        <v>15.028</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>1.1</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2551</v>
+        <v>0.2199</v>
       </c>
       <c r="J6" t="n">
-        <v>5.102</v>
+        <v>4.398</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>0.74</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.2665</v>
+        <v>-0.2534</v>
       </c>
       <c r="J7" t="n">
-        <v>-5.33</v>
+        <v>-5.068</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.3155</v>
+        <v>-0.3047</v>
       </c>
       <c r="J8" t="n">
-        <v>-6.31</v>
+        <v>-6.094</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>0.64</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.3614</v>
+        <v>-0.3521</v>
       </c>
       <c r="J9" t="n">
-        <v>-7.228</v>
+        <v>-7.042</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>0.54</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.447</v>
+        <v>-0.4407</v>
       </c>
       <c r="J10" t="n">
-        <v>-8.94</v>
+        <v>-8.814</v>
       </c>
     </row>
     <row r="11">
@@ -2829,10 +2829,10 @@
         <v>1.62</v>
       </c>
       <c r="I12" t="n">
-        <v>1.3405</v>
+        <v>1.3728</v>
       </c>
       <c r="J12" t="n">
-        <v>30.8315</v>
+        <v>31.5744</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>1.24</v>
       </c>
       <c r="I13" t="n">
-        <v>0.6238</v>
+        <v>0.5942</v>
       </c>
       <c r="J13" t="n">
-        <v>14.3474</v>
+        <v>13.6666</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>1.21</v>
       </c>
       <c r="I14" t="n">
-        <v>0.5605</v>
+        <v>0.5295</v>
       </c>
       <c r="J14" t="n">
-        <v>12.8915</v>
+        <v>12.1785</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>1.14</v>
       </c>
       <c r="I15" t="n">
-        <v>0.4013</v>
+        <v>0.3685</v>
       </c>
       <c r="J15" t="n">
-        <v>9.229900000000001</v>
+        <v>8.4755</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>1.07</v>
       </c>
       <c r="I16" t="n">
-        <v>0.2193</v>
+        <v>0.1901</v>
       </c>
       <c r="J16" t="n">
-        <v>5.0439</v>
+        <v>4.3723</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>1.1</v>
       </c>
       <c r="I17" t="n">
-        <v>0.2927</v>
+        <v>0.2457</v>
       </c>
       <c r="J17" t="n">
-        <v>6.7321</v>
+        <v>5.6511</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>1</v>
       </c>
       <c r="I18" t="n">
-        <v>0.0288</v>
+        <v>0.023</v>
       </c>
       <c r="J18" t="n">
-        <v>0.6624</v>
+        <v>0.529</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>0.75</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.2854</v>
+        <v>-0.2673</v>
       </c>
       <c r="J19" t="n">
-        <v>-6.5642</v>
+        <v>-6.1479</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>0.75</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.2854</v>
+        <v>-0.2673</v>
       </c>
       <c r="J20" t="n">
-        <v>-6.5642</v>
+        <v>-6.1479</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>0.61</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.4136</v>
+        <v>-0.4034</v>
       </c>
       <c r="J21" t="n">
-        <v>-9.5128</v>
+        <v>-9.2782</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>1.43</v>
       </c>
       <c r="I22" t="n">
-        <v>1.0255</v>
+        <v>1.0199</v>
       </c>
       <c r="J22" t="n">
-        <v>29.7395</v>
+        <v>29.5771</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>1.17</v>
       </c>
       <c r="I23" t="n">
-        <v>0.4863</v>
+        <v>0.4484</v>
       </c>
       <c r="J23" t="n">
-        <v>14.1027</v>
+        <v>13.0036</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>1.05</v>
       </c>
       <c r="I24" t="n">
-        <v>0.1801</v>
+        <v>0.1527</v>
       </c>
       <c r="J24" t="n">
-        <v>5.2229</v>
+        <v>4.4283</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>1.04</v>
       </c>
       <c r="I25" t="n">
-        <v>0.1485</v>
+        <v>0.1238</v>
       </c>
       <c r="J25" t="n">
-        <v>4.3065</v>
+        <v>3.5902</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>1</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.0225</v>
+        <v>-0.0172</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.6525</v>
+        <v>-0.4988</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>1.01</v>
       </c>
       <c r="I27" t="n">
-        <v>0.0493</v>
+        <v>0.033</v>
       </c>
       <c r="J27" t="n">
-        <v>1.4297</v>
+        <v>0.957</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>1.01</v>
       </c>
       <c r="I28" t="n">
-        <v>0.0493</v>
+        <v>0.033</v>
       </c>
       <c r="J28" t="n">
-        <v>1.4297</v>
+        <v>0.957</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>0.97</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.0557</v>
+        <v>-0.0444</v>
       </c>
       <c r="J29" t="n">
-        <v>-1.6153</v>
+        <v>-1.2876</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>0.96</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.0699</v>
+        <v>-0.0568</v>
       </c>
       <c r="J30" t="n">
-        <v>-2.0271</v>
+        <v>-1.6472</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>0.82</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.2281</v>
+        <v>-0.2078</v>
       </c>
       <c r="J31" t="n">
-        <v>-6.6149</v>
+        <v>-6.0262</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>1.87</v>
       </c>
       <c r="I32" t="n">
-        <v>1.5199</v>
+        <v>1.5528</v>
       </c>
       <c r="J32" t="n">
-        <v>28.8781</v>
+        <v>29.5032</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>1.54</v>
       </c>
       <c r="I33" t="n">
-        <v>1.1149</v>
+        <v>1.1321</v>
       </c>
       <c r="J33" t="n">
-        <v>21.1831</v>
+        <v>21.5099</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>1.46</v>
       </c>
       <c r="I34" t="n">
-        <v>1.0086</v>
+        <v>1.0168</v>
       </c>
       <c r="J34" t="n">
-        <v>19.1634</v>
+        <v>19.3192</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>1.27</v>
       </c>
       <c r="I35" t="n">
-        <v>0.6556</v>
+        <v>0.6344</v>
       </c>
       <c r="J35" t="n">
-        <v>12.4564</v>
+        <v>12.0536</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>1.25</v>
       </c>
       <c r="I36" t="n">
-        <v>0.6141</v>
+        <v>0.5904</v>
       </c>
       <c r="J36" t="n">
-        <v>11.6679</v>
+        <v>11.2176</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>0.79</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.2288</v>
+        <v>-0.2141</v>
       </c>
       <c r="J37" t="n">
-        <v>-4.3472</v>
+        <v>-4.0679</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>0.78</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.239</v>
+        <v>-0.2246</v>
       </c>
       <c r="J38" t="n">
-        <v>-4.541</v>
+        <v>-4.2674</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>0.64</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.3677</v>
+        <v>-0.3558</v>
       </c>
       <c r="J39" t="n">
-        <v>-6.9863</v>
+        <v>-6.7602</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>0.62</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.3853</v>
+        <v>-0.3741</v>
       </c>
       <c r="J40" t="n">
-        <v>-7.3207</v>
+        <v>-7.1079</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.4383</v>
+        <v>-0.4304</v>
       </c>
       <c r="J41" t="n">
-        <v>-8.3277</v>
+        <v>-8.1776</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>2.14</v>
       </c>
       <c r="I42" t="n">
-        <v>1.8189</v>
+        <v>1.878</v>
       </c>
       <c r="J42" t="n">
-        <v>36.378</v>
+        <v>37.56</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>1.68</v>
       </c>
       <c r="I43" t="n">
-        <v>1.2816</v>
+        <v>1.3038</v>
       </c>
       <c r="J43" t="n">
-        <v>25.632</v>
+        <v>26.076</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>1.52</v>
       </c>
       <c r="I44" t="n">
-        <v>1.0854</v>
+        <v>1.104</v>
       </c>
       <c r="J44" t="n">
-        <v>21.708</v>
+        <v>22.08</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>1.28</v>
       </c>
       <c r="I45" t="n">
-        <v>0.6667</v>
+        <v>0.6467000000000001</v>
       </c>
       <c r="J45" t="n">
-        <v>13.334</v>
+        <v>12.934</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>1.11</v>
       </c>
       <c r="I46" t="n">
-        <v>0.2833</v>
+        <v>0.2485</v>
       </c>
       <c r="J46" t="n">
-        <v>5.666</v>
+        <v>4.97</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>0.86</v>
       </c>
       <c r="I47" t="n">
-        <v>-0.1215</v>
+        <v>-0.0973</v>
       </c>
       <c r="J47" t="n">
-        <v>-2.43</v>
+        <v>-1.946</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>0.77</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.2241</v>
+        <v>-0.2074</v>
       </c>
       <c r="J48" t="n">
-        <v>-4.482</v>
+        <v>-4.148</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>0.44</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.5286</v>
+        <v>-0.53</v>
       </c>
       <c r="J49" t="n">
-        <v>-10.572</v>
+        <v>-10.6</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>0.4</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.5641</v>
+        <v>-0.5698</v>
       </c>
       <c r="J50" t="n">
-        <v>-11.282</v>
+        <v>-11.396</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.39</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.573</v>
+        <v>-0.5799</v>
       </c>
       <c r="J51" t="n">
-        <v>-11.46</v>
+        <v>-11.598</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.71</v>
       </c>
       <c r="I52" t="n">
-        <v>1.3647</v>
+        <v>1.3879</v>
       </c>
       <c r="J52" t="n">
-        <v>35.4822</v>
+        <v>36.0854</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>1.42</v>
       </c>
       <c r="I53" t="n">
-        <v>0.9686</v>
+        <v>0.9622000000000001</v>
       </c>
       <c r="J53" t="n">
-        <v>25.1836</v>
+        <v>25.0172</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>1.15</v>
       </c>
       <c r="I54" t="n">
-        <v>0.4221</v>
+        <v>0.3898</v>
       </c>
       <c r="J54" t="n">
-        <v>10.9746</v>
+        <v>10.1348</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>1.14</v>
       </c>
       <c r="I55" t="n">
-        <v>0.3982</v>
+        <v>0.3658</v>
       </c>
       <c r="J55" t="n">
-        <v>10.3532</v>
+        <v>9.5108</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>0.96</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.2183</v>
+        <v>-0.1852</v>
       </c>
       <c r="J56" t="n">
-        <v>-5.6758</v>
+        <v>-4.8152</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>0.95</v>
       </c>
       <c r="I57" t="n">
-        <v>-0.0684</v>
+        <v>-0.0566</v>
       </c>
       <c r="J57" t="n">
-        <v>-1.7784</v>
+        <v>-1.4716</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>0.89</v>
       </c>
       <c r="I58" t="n">
-        <v>-0.1427</v>
+        <v>-0.127</v>
       </c>
       <c r="J58" t="n">
-        <v>-3.7102</v>
+        <v>-3.302</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>0.78</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.2542</v>
+        <v>-0.2362</v>
       </c>
       <c r="J59" t="n">
-        <v>-6.6092</v>
+        <v>-6.1412</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>0.74</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.292</v>
+        <v>-0.2744</v>
       </c>
       <c r="J60" t="n">
-        <v>-7.592</v>
+        <v>-7.1344</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>0.71</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.3199</v>
+        <v>-0.3033</v>
       </c>
       <c r="J61" t="n">
-        <v>-8.317399999999999</v>
+        <v>-7.8858</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>1.33</v>
       </c>
       <c r="I62" t="n">
-        <v>0.8475</v>
+        <v>0.8248</v>
       </c>
       <c r="J62" t="n">
-        <v>25.425</v>
+        <v>24.744</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>1.16</v>
       </c>
       <c r="I63" t="n">
-        <v>0.4755</v>
+        <v>0.4344</v>
       </c>
       <c r="J63" t="n">
-        <v>14.265</v>
+        <v>13.032</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>1.1</v>
       </c>
       <c r="I64" t="n">
-        <v>0.3279</v>
+        <v>0.2891</v>
       </c>
       <c r="J64" t="n">
-        <v>9.837</v>
+        <v>8.673</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>1.06</v>
       </c>
       <c r="I65" t="n">
-        <v>0.2202</v>
+        <v>0.1875</v>
       </c>
       <c r="J65" t="n">
-        <v>6.606</v>
+        <v>5.625</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>0.7</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.8228</v>
+        <v>-0.8011</v>
       </c>
       <c r="J66" t="n">
-        <v>-24.684</v>
+        <v>-24.033</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>1.21</v>
       </c>
       <c r="I67" t="n">
-        <v>0.4333</v>
+        <v>0.3764</v>
       </c>
       <c r="J67" t="n">
-        <v>12.999</v>
+        <v>11.292</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>1.15</v>
       </c>
       <c r="I68" t="n">
-        <v>0.3315</v>
+        <v>0.2803</v>
       </c>
       <c r="J68" t="n">
-        <v>9.945</v>
+        <v>8.409000000000001</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>1.07</v>
       </c>
       <c r="I69" t="n">
-        <v>0.1823</v>
+        <v>0.1461</v>
       </c>
       <c r="J69" t="n">
-        <v>5.469</v>
+        <v>4.383</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>1</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.0055</v>
+        <v>-0.0037</v>
       </c>
       <c r="J70" t="n">
-        <v>-0.165</v>
+        <v>-0.111</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>0.99</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.0312</v>
+        <v>-0.0224</v>
       </c>
       <c r="J71" t="n">
-        <v>-0.9360000000000001</v>
+        <v>-0.672</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>1.23</v>
       </c>
       <c r="I72" t="n">
-        <v>0.5007</v>
+        <v>0.4431</v>
       </c>
       <c r="J72" t="n">
-        <v>14.5203</v>
+        <v>12.8499</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>1.04</v>
       </c>
       <c r="I73" t="n">
-        <v>0.1346</v>
+        <v>0.1017</v>
       </c>
       <c r="J73" t="n">
-        <v>3.9034</v>
+        <v>2.9493</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>1.03</v>
       </c>
       <c r="I74" t="n">
-        <v>0.1095</v>
+        <v>0.08069999999999999</v>
       </c>
       <c r="J74" t="n">
-        <v>3.1755</v>
+        <v>2.3403</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>0.71</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.3329</v>
+        <v>-0.3167</v>
       </c>
       <c r="J75" t="n">
-        <v>-9.6541</v>
+        <v>-9.1843</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.3513</v>
+        <v>-0.3364</v>
       </c>
       <c r="J76" t="n">
-        <v>-10.1877</v>
+        <v>-9.755599999999999</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>1.63</v>
       </c>
       <c r="I77" t="n">
-        <v>1.2831</v>
+        <v>1.3028</v>
       </c>
       <c r="J77" t="n">
-        <v>37.2099</v>
+        <v>37.7812</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>1.25</v>
       </c>
       <c r="I78" t="n">
-        <v>0.6526999999999999</v>
+        <v>0.6203</v>
       </c>
       <c r="J78" t="n">
-        <v>18.9283</v>
+        <v>17.9887</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>1.11</v>
       </c>
       <c r="I79" t="n">
-        <v>0.3382</v>
+        <v>0.3044</v>
       </c>
       <c r="J79" t="n">
-        <v>9.8078</v>
+        <v>8.8276</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>1.01</v>
       </c>
       <c r="I80" t="n">
-        <v>0.0287</v>
+        <v>0.0189</v>
       </c>
       <c r="J80" t="n">
-        <v>0.8323</v>
+        <v>0.5481</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>0.93</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.2946</v>
+        <v>-0.255</v>
       </c>
       <c r="J81" t="n">
-        <v>-8.5434</v>
+        <v>-7.395</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>1.29</v>
       </c>
       <c r="I82" t="n">
-        <v>0.4052</v>
+        <v>0.3424</v>
       </c>
       <c r="J82" t="n">
-        <v>11.7508</v>
+        <v>9.929600000000001</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>1.26</v>
       </c>
       <c r="I83" t="n">
-        <v>0.3711</v>
+        <v>0.311</v>
       </c>
       <c r="J83" t="n">
-        <v>10.7619</v>
+        <v>9.019</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>1.22</v>
       </c>
       <c r="I84" t="n">
-        <v>0.3246</v>
+        <v>0.2687</v>
       </c>
       <c r="J84" t="n">
-        <v>9.413399999999999</v>
+        <v>7.7923</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>1.08</v>
       </c>
       <c r="I85" t="n">
-        <v>0.1435</v>
+        <v>0.111</v>
       </c>
       <c r="J85" t="n">
-        <v>4.1615</v>
+        <v>3.219</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>1</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.0121</v>
+        <v>-0.009599999999999999</v>
       </c>
       <c r="J86" t="n">
-        <v>-0.3509</v>
+        <v>-0.2784</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>1.5</v>
       </c>
       <c r="I87" t="n">
-        <v>0.7335</v>
+        <v>0.7944</v>
       </c>
       <c r="J87" t="n">
-        <v>21.2715</v>
+        <v>23.0376</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>0.9</v>
       </c>
       <c r="I88" t="n">
-        <v>-0.1398</v>
+        <v>-0.122</v>
       </c>
       <c r="J88" t="n">
-        <v>-4.0542</v>
+        <v>-3.538</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>0.79</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.2538</v>
+        <v>-0.2342</v>
       </c>
       <c r="J89" t="n">
-        <v>-7.3602</v>
+        <v>-6.7918</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>0.72</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.3206</v>
+        <v>-0.3036</v>
       </c>
       <c r="J90" t="n">
-        <v>-9.2974</v>
+        <v>-8.804399999999999</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>0.64</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.3938</v>
+        <v>-0.3821</v>
       </c>
       <c r="J91" t="n">
-        <v>-11.4202</v>
+        <v>-11.0809</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>1.08</v>
       </c>
       <c r="I92" t="n">
-        <v>0.2574</v>
+        <v>0.2141</v>
       </c>
       <c r="J92" t="n">
-        <v>6.1776</v>
+        <v>5.1384</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>0.87</v>
       </c>
       <c r="I93" t="n">
-        <v>-0.1658</v>
+        <v>-0.1492</v>
       </c>
       <c r="J93" t="n">
-        <v>-3.9792</v>
+        <v>-3.5808</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>0.76</v>
       </c>
       <c r="I94" t="n">
-        <v>-0.2739</v>
+        <v>-0.2559</v>
       </c>
       <c r="J94" t="n">
-        <v>-6.5736</v>
+        <v>-6.1416</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>0.75</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.2834</v>
+        <v>-0.2655</v>
       </c>
       <c r="J95" t="n">
-        <v>-6.8016</v>
+        <v>-6.372</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>0.65</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.3756</v>
+        <v>-0.3622</v>
       </c>
       <c r="J96" t="n">
-        <v>-9.0144</v>
+        <v>-8.6928</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1.58</v>
       </c>
       <c r="I97" t="n">
-        <v>1.2086</v>
+        <v>1.2239</v>
       </c>
       <c r="J97" t="n">
-        <v>29.0064</v>
+        <v>29.3736</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>1.2</v>
       </c>
       <c r="I98" t="n">
-        <v>0.5436</v>
+        <v>0.5104</v>
       </c>
       <c r="J98" t="n">
-        <v>13.0464</v>
+        <v>12.2496</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>1.14</v>
       </c>
       <c r="I99" t="n">
-        <v>0.4072</v>
+        <v>0.3734</v>
       </c>
       <c r="J99" t="n">
-        <v>9.7728</v>
+        <v>8.961600000000001</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>1.14</v>
       </c>
       <c r="I100" t="n">
-        <v>0.4072</v>
+        <v>0.3734</v>
       </c>
       <c r="J100" t="n">
-        <v>9.7728</v>
+        <v>8.961600000000001</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>1.03</v>
       </c>
       <c r="I101" t="n">
-        <v>0.101</v>
+        <v>0.0806</v>
       </c>
       <c r="J101" t="n">
-        <v>2.424</v>
+        <v>1.9344</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.33</v>
       </c>
       <c r="I102" t="n">
-        <v>0.8744</v>
+        <v>0.8563</v>
       </c>
       <c r="J102" t="n">
-        <v>26.232</v>
+        <v>25.689</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>1.19</v>
       </c>
       <c r="I103" t="n">
-        <v>0.5655</v>
+        <v>0.5253</v>
       </c>
       <c r="J103" t="n">
-        <v>16.965</v>
+        <v>15.759</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>0.89</v>
       </c>
       <c r="I104" t="n">
-        <v>-0.3674</v>
+        <v>-0.325</v>
       </c>
       <c r="J104" t="n">
-        <v>-11.022</v>
+        <v>-9.75</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>0.85</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.468</v>
+        <v>-0.4254</v>
       </c>
       <c r="J105" t="n">
-        <v>-14.04</v>
+        <v>-12.762</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.72</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.7652</v>
+        <v>-0.7368</v>
       </c>
       <c r="J106" t="n">
-        <v>-22.956</v>
+        <v>-22.104</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.46</v>
       </c>
       <c r="I107" t="n">
-        <v>0.8022</v>
+        <v>0.7469</v>
       </c>
       <c r="J107" t="n">
-        <v>24.066</v>
+        <v>22.407</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>1.35</v>
       </c>
       <c r="I108" t="n">
-        <v>0.6429</v>
+        <v>0.5834</v>
       </c>
       <c r="J108" t="n">
-        <v>19.287</v>
+        <v>17.502</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>1.21</v>
       </c>
       <c r="I109" t="n">
-        <v>0.4263</v>
+        <v>0.3708</v>
       </c>
       <c r="J109" t="n">
-        <v>12.789</v>
+        <v>11.124</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>0.89</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.1691</v>
+        <v>-0.1489</v>
       </c>
       <c r="J110" t="n">
-        <v>-5.073</v>
+        <v>-4.467</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>0.73</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.3304</v>
+        <v>-0.3155</v>
       </c>
       <c r="J111" t="n">
-        <v>-9.912000000000001</v>
+        <v>-9.465</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>1.18</v>
       </c>
       <c r="I112" t="n">
-        <v>0.3944</v>
+        <v>0.4104</v>
       </c>
       <c r="J112" t="n">
-        <v>8.6768</v>
+        <v>9.0288</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>0.84</v>
       </c>
       <c r="I113" t="n">
-        <v>-0.1845</v>
+        <v>-0.1689</v>
       </c>
       <c r="J113" t="n">
-        <v>-4.059</v>
+        <v>-3.7158</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>0.63</v>
       </c>
       <c r="I114" t="n">
-        <v>-0.3821</v>
+        <v>-0.3698</v>
       </c>
       <c r="J114" t="n">
-        <v>-8.4062</v>
+        <v>-8.1356</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>0.54</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.4619</v>
+        <v>-0.4561</v>
       </c>
       <c r="J115" t="n">
-        <v>-10.1618</v>
+        <v>-10.0342</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>0.43</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.5578</v>
+        <v>-0.5642</v>
       </c>
       <c r="J116" t="n">
-        <v>-12.2716</v>
+        <v>-12.4124</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>1.91</v>
       </c>
       <c r="I117" t="n">
-        <v>0.9762</v>
+        <v>0.9132</v>
       </c>
       <c r="J117" t="n">
-        <v>21.4764</v>
+        <v>20.0904</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>1.58</v>
       </c>
       <c r="I118" t="n">
-        <v>0.6773</v>
+        <v>0.6066</v>
       </c>
       <c r="J118" t="n">
-        <v>14.9006</v>
+        <v>13.3452</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>1.34</v>
       </c>
       <c r="I119" t="n">
-        <v>0.4416</v>
+        <v>0.3816</v>
       </c>
       <c r="J119" t="n">
-        <v>9.715199999999999</v>
+        <v>8.395200000000001</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>1.32</v>
       </c>
       <c r="I120" t="n">
-        <v>0.4204</v>
+        <v>0.3618</v>
       </c>
       <c r="J120" t="n">
-        <v>9.248799999999999</v>
+        <v>7.9596</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>0.87</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.2103</v>
+        <v>-0.1933</v>
       </c>
       <c r="J121" t="n">
-        <v>-4.6266</v>
+        <v>-4.2526</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.67</v>
       </c>
       <c r="I122" t="n">
-        <v>1.3371</v>
+        <v>1.3604</v>
       </c>
       <c r="J122" t="n">
-        <v>34.7646</v>
+        <v>35.3704</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>1.15</v>
       </c>
       <c r="I123" t="n">
-        <v>0.436</v>
+        <v>0.4006</v>
       </c>
       <c r="J123" t="n">
-        <v>11.336</v>
+        <v>10.4156</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>1.14</v>
       </c>
       <c r="I124" t="n">
-        <v>0.4125</v>
+        <v>0.3773</v>
       </c>
       <c r="J124" t="n">
-        <v>10.725</v>
+        <v>9.809799999999999</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>1.07</v>
       </c>
       <c r="I125" t="n">
-        <v>0.2317</v>
+        <v>0.2016</v>
       </c>
       <c r="J125" t="n">
-        <v>6.0242</v>
+        <v>5.2416</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.88</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.4292</v>
+        <v>-0.3879</v>
       </c>
       <c r="J126" t="n">
-        <v>-11.1592</v>
+        <v>-10.0854</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.33</v>
       </c>
       <c r="I127" t="n">
-        <v>0.6653</v>
+        <v>0.6108</v>
       </c>
       <c r="J127" t="n">
-        <v>17.2978</v>
+        <v>15.8808</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>0.96</v>
       </c>
       <c r="I128" t="n">
-        <v>-0.0687</v>
+        <v>-0.0562</v>
       </c>
       <c r="J128" t="n">
-        <v>-1.7862</v>
+        <v>-1.4612</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>0.83</v>
       </c>
       <c r="I129" t="n">
-        <v>-0.2163</v>
+        <v>-0.196</v>
       </c>
       <c r="J129" t="n">
-        <v>-5.6238</v>
+        <v>-5.096</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>0.83</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.2163</v>
+        <v>-0.196</v>
       </c>
       <c r="J130" t="n">
-        <v>-5.6238</v>
+        <v>-5.096</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>0.73</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.3138</v>
+        <v>-0.2965</v>
       </c>
       <c r="J131" t="n">
-        <v>-8.158799999999999</v>
+        <v>-7.709</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>1.1</v>
       </c>
       <c r="I132" t="n">
-        <v>0.3295</v>
+        <v>0.2901</v>
       </c>
       <c r="J132" t="n">
-        <v>9.5555</v>
+        <v>8.4129</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>1.08</v>
       </c>
       <c r="I133" t="n">
-        <v>0.2765</v>
+        <v>0.2396</v>
       </c>
       <c r="J133" t="n">
-        <v>8.0185</v>
+        <v>6.9484</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>1.08</v>
       </c>
       <c r="I134" t="n">
-        <v>0.2765</v>
+        <v>0.2396</v>
       </c>
       <c r="J134" t="n">
-        <v>8.0185</v>
+        <v>6.9484</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>1.03</v>
       </c>
       <c r="I135" t="n">
-        <v>0.1279</v>
+        <v>0.1037</v>
       </c>
       <c r="J135" t="n">
-        <v>3.7091</v>
+        <v>3.0073</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>1.01</v>
       </c>
       <c r="I136" t="n">
-        <v>0.0508</v>
+        <v>0.0382</v>
       </c>
       <c r="J136" t="n">
-        <v>1.4732</v>
+        <v>1.1078</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>1.25</v>
       </c>
       <c r="I137" t="n">
-        <v>0.5192</v>
+        <v>0.4602</v>
       </c>
       <c r="J137" t="n">
-        <v>15.0568</v>
+        <v>13.3458</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>0.95</v>
       </c>
       <c r="I138" t="n">
-        <v>-0.08550000000000001</v>
+        <v>-0.0699</v>
       </c>
       <c r="J138" t="n">
-        <v>-2.4795</v>
+        <v>-2.0271</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I139" t="n">
-        <v>-0.0984</v>
+        <v>-0.08169999999999999</v>
       </c>
       <c r="J139" t="n">
-        <v>-2.8536</v>
+        <v>-2.3693</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>0.93</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.1109</v>
+        <v>-0.09329999999999999</v>
       </c>
       <c r="J140" t="n">
-        <v>-3.2161</v>
+        <v>-2.7057</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>0.89</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.1575</v>
+        <v>-0.1376</v>
       </c>
       <c r="J141" t="n">
-        <v>-4.5675</v>
+        <v>-3.9904</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.35</v>
       </c>
       <c r="I142" t="n">
-        <v>0.8691</v>
+        <v>0.8483000000000001</v>
       </c>
       <c r="J142" t="n">
-        <v>24.3348</v>
+        <v>23.7524</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>1.29</v>
       </c>
       <c r="I143" t="n">
-        <v>0.7467</v>
+        <v>0.717</v>
       </c>
       <c r="J143" t="n">
-        <v>20.9076</v>
+        <v>20.076</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>1.17</v>
       </c>
       <c r="I144" t="n">
-        <v>0.4869</v>
+        <v>0.4487</v>
       </c>
       <c r="J144" t="n">
-        <v>13.6332</v>
+        <v>12.5636</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>0.96</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.1934</v>
+        <v>-0.1587</v>
       </c>
       <c r="J145" t="n">
-        <v>-5.4152</v>
+        <v>-4.4436</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>0.9</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.3682</v>
+        <v>-0.326</v>
       </c>
       <c r="J146" t="n">
-        <v>-10.3096</v>
+        <v>-9.128</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>1.74</v>
       </c>
       <c r="I147" t="n">
-        <v>1.1549</v>
+        <v>1.1457</v>
       </c>
       <c r="J147" t="n">
-        <v>32.3372</v>
+        <v>32.0796</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>1.15</v>
       </c>
       <c r="I148" t="n">
-        <v>0.3351</v>
+        <v>0.2831</v>
       </c>
       <c r="J148" t="n">
-        <v>9.3828</v>
+        <v>7.9268</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>0.89</v>
       </c>
       <c r="I149" t="n">
-        <v>-0.1634</v>
+        <v>-0.1431</v>
       </c>
       <c r="J149" t="n">
-        <v>-4.5752</v>
+        <v>-4.0068</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>0.8</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.2577</v>
+        <v>-0.2382</v>
       </c>
       <c r="J150" t="n">
-        <v>-7.2156</v>
+        <v>-6.6696</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>0.72</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.3343</v>
+        <v>-0.3191</v>
       </c>
       <c r="J151" t="n">
-        <v>-9.3604</v>
+        <v>-8.934799999999999</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>1.05</v>
       </c>
       <c r="I152" t="n">
-        <v>0.311</v>
+        <v>0.3074</v>
       </c>
       <c r="J152" t="n">
-        <v>5.909</v>
+        <v>5.8406</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>0.61</v>
       </c>
       <c r="I153" t="n">
-        <v>-0.3851</v>
+        <v>-0.3771</v>
       </c>
       <c r="J153" t="n">
-        <v>-7.3169</v>
+        <v>-7.1649</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>0.47</v>
       </c>
       <c r="I154" t="n">
-        <v>-0.5056</v>
+        <v>-0.5044</v>
       </c>
       <c r="J154" t="n">
-        <v>-9.606400000000001</v>
+        <v>-9.583600000000001</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>0.46</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.5144</v>
+        <v>-0.5141</v>
       </c>
       <c r="J155" t="n">
-        <v>-9.7736</v>
+        <v>-9.767899999999999</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>0.38</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.5851</v>
+        <v>-0.594</v>
       </c>
       <c r="J156" t="n">
-        <v>-11.1169</v>
+        <v>-11.286</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>1.61</v>
       </c>
       <c r="I157" t="n">
-        <v>1.2068</v>
+        <v>1.2244</v>
       </c>
       <c r="J157" t="n">
-        <v>22.9292</v>
+        <v>23.2636</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>1.58</v>
       </c>
       <c r="I158" t="n">
-        <v>1.1689</v>
+        <v>1.1857</v>
       </c>
       <c r="J158" t="n">
-        <v>22.2091</v>
+        <v>22.5283</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>1.48</v>
       </c>
       <c r="I159" t="n">
-        <v>1.039</v>
+        <v>1.0499</v>
       </c>
       <c r="J159" t="n">
-        <v>19.741</v>
+        <v>19.9481</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>1.45</v>
       </c>
       <c r="I160" t="n">
-        <v>0.9954</v>
+        <v>1.0005</v>
       </c>
       <c r="J160" t="n">
-        <v>18.9126</v>
+        <v>19.0095</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>1.12</v>
       </c>
       <c r="I161" t="n">
-        <v>0.3224</v>
+        <v>0.2896</v>
       </c>
       <c r="J161" t="n">
-        <v>6.1256</v>
+        <v>5.5024</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>1.11</v>
       </c>
       <c r="I162" t="n">
-        <v>0.2783</v>
+        <v>0.2292</v>
       </c>
       <c r="J162" t="n">
-        <v>7.5141</v>
+        <v>6.1884</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>1.07</v>
       </c>
       <c r="I163" t="n">
-        <v>0.1972</v>
+        <v>0.1561</v>
       </c>
       <c r="J163" t="n">
-        <v>5.3244</v>
+        <v>4.2147</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>0.93</v>
       </c>
       <c r="I164" t="n">
-        <v>-0.109</v>
+        <v>-0.0919</v>
       </c>
       <c r="J164" t="n">
-        <v>-2.943</v>
+        <v>-2.4813</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>0.9</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.1442</v>
+        <v>-0.125</v>
       </c>
       <c r="J165" t="n">
-        <v>-3.8934</v>
+        <v>-3.375</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>0.83</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.2193</v>
+        <v>-0.1988</v>
       </c>
       <c r="J166" t="n">
-        <v>-5.9211</v>
+        <v>-5.3676</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>1.44</v>
       </c>
       <c r="I167" t="n">
-        <v>1.0438</v>
+        <v>1.0491</v>
       </c>
       <c r="J167" t="n">
-        <v>28.1826</v>
+        <v>28.3257</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>1.33</v>
       </c>
       <c r="I168" t="n">
-        <v>0.84</v>
+        <v>0.8166</v>
       </c>
       <c r="J168" t="n">
-        <v>22.68</v>
+        <v>22.0482</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>1.16</v>
       </c>
       <c r="I169" t="n">
-        <v>0.4706</v>
+        <v>0.4305</v>
       </c>
       <c r="J169" t="n">
-        <v>12.7062</v>
+        <v>11.6235</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>0.82</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.5598</v>
+        <v>-0.5203</v>
       </c>
       <c r="J170" t="n">
-        <v>-15.1146</v>
+        <v>-14.0481</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>0.72</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.7844</v>
+        <v>-0.7597</v>
       </c>
       <c r="J171" t="n">
-        <v>-21.1788</v>
+        <v>-20.5119</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>1.03</v>
       </c>
       <c r="I172" t="n">
-        <v>0.1365</v>
+        <v>0.1061</v>
       </c>
       <c r="J172" t="n">
-        <v>3.6855</v>
+        <v>2.8647</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>0.88</v>
       </c>
       <c r="I173" t="n">
-        <v>-0.1557</v>
+        <v>-0.1393</v>
       </c>
       <c r="J173" t="n">
-        <v>-4.2039</v>
+        <v>-3.7611</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>0.8</v>
       </c>
       <c r="I174" t="n">
-        <v>-0.2364</v>
+        <v>-0.218</v>
       </c>
       <c r="J174" t="n">
-        <v>-6.3828</v>
+        <v>-5.886</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>0.78</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.2557</v>
+        <v>-0.2373</v>
       </c>
       <c r="J175" t="n">
-        <v>-6.9039</v>
+        <v>-6.4071</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>0.66</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.3674</v>
+        <v>-0.3534</v>
       </c>
       <c r="J176" t="n">
-        <v>-9.9198</v>
+        <v>-9.5418</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>1.35</v>
       </c>
       <c r="I177" t="n">
-        <v>0.8481</v>
+        <v>0.8278</v>
       </c>
       <c r="J177" t="n">
-        <v>22.8987</v>
+        <v>22.3506</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>1.33</v>
       </c>
       <c r="I178" t="n">
-        <v>0.8088</v>
+        <v>0.7858000000000001</v>
       </c>
       <c r="J178" t="n">
-        <v>21.8376</v>
+        <v>21.2166</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>1.16</v>
       </c>
       <c r="I179" t="n">
-        <v>0.4537</v>
+        <v>0.42</v>
       </c>
       <c r="J179" t="n">
-        <v>12.2499</v>
+        <v>11.34</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>1.15</v>
       </c>
       <c r="I180" t="n">
-        <v>0.4304</v>
+        <v>0.3966</v>
       </c>
       <c r="J180" t="n">
-        <v>11.6208</v>
+        <v>10.7082</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>1.12</v>
       </c>
       <c r="I181" t="n">
-        <v>0.3577</v>
+        <v>0.3245</v>
       </c>
       <c r="J181" t="n">
-        <v>9.6579</v>
+        <v>8.7615</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>1.72</v>
       </c>
       <c r="I182" t="n">
-        <v>0.8653</v>
+        <v>0.8007</v>
       </c>
       <c r="J182" t="n">
-        <v>25.0937</v>
+        <v>23.2203</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>1.05</v>
       </c>
       <c r="I183" t="n">
-        <v>0.1019</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="J183" t="n">
-        <v>2.9551</v>
+        <v>2.1982</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I184" t="n">
-        <v>-0.1075</v>
+        <v>-0.0897</v>
       </c>
       <c r="J184" t="n">
-        <v>-3.1175</v>
+        <v>-2.6013</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>0.92</v>
       </c>
       <c r="I185" t="n">
-        <v>-0.1323</v>
+        <v>-0.1131</v>
       </c>
       <c r="J185" t="n">
-        <v>-3.8367</v>
+        <v>-3.2799</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>0.89</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.1671</v>
+        <v>-0.1469</v>
       </c>
       <c r="J186" t="n">
-        <v>-4.8459</v>
+        <v>-4.2601</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>1.39</v>
       </c>
       <c r="I187" t="n">
-        <v>0.5662</v>
+        <v>0.5855</v>
       </c>
       <c r="J187" t="n">
-        <v>16.4198</v>
+        <v>16.9795</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>1.19</v>
       </c>
       <c r="I188" t="n">
-        <v>0.319</v>
+        <v>0.3085</v>
       </c>
       <c r="J188" t="n">
-        <v>9.250999999999999</v>
+        <v>8.9465</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>1.1</v>
       </c>
       <c r="I189" t="n">
-        <v>0.1922</v>
+        <v>0.1763</v>
       </c>
       <c r="J189" t="n">
-        <v>5.5738</v>
+        <v>5.1127</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>0.79</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.2662</v>
+        <v>-0.247</v>
       </c>
       <c r="J190" t="n">
-        <v>-7.7198</v>
+        <v>-7.163</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>0.75</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.3048</v>
+        <v>-0.2875</v>
       </c>
       <c r="J191" t="n">
-        <v>-8.8392</v>
+        <v>-8.3375</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>1.32</v>
       </c>
       <c r="I192" t="n">
-        <v>0.6501</v>
+        <v>0.5951</v>
       </c>
       <c r="J192" t="n">
-        <v>22.1034</v>
+        <v>20.2334</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I193" t="n">
-        <v>-0.0948</v>
+        <v>-0.0796</v>
       </c>
       <c r="J193" t="n">
-        <v>-3.2232</v>
+        <v>-2.7064</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>0.83</v>
       </c>
       <c r="I194" t="n">
-        <v>-0.2161</v>
+        <v>-0.1959</v>
       </c>
       <c r="J194" t="n">
-        <v>-7.3474</v>
+        <v>-6.6606</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>0.79</v>
       </c>
       <c r="I195" t="n">
-        <v>-0.2561</v>
+        <v>-0.2364</v>
       </c>
       <c r="J195" t="n">
-        <v>-8.7074</v>
+        <v>-8.037599999999999</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>0.79</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.2561</v>
+        <v>-0.2364</v>
       </c>
       <c r="J196" t="n">
-        <v>-8.7074</v>
+        <v>-8.037599999999999</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>1.41</v>
       </c>
       <c r="I197" t="n">
-        <v>0.9745</v>
+        <v>0.9668</v>
       </c>
       <c r="J197" t="n">
-        <v>33.133</v>
+        <v>32.8712</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>1.39</v>
       </c>
       <c r="I198" t="n">
-        <v>0.9382</v>
+        <v>0.9248</v>
       </c>
       <c r="J198" t="n">
-        <v>31.8988</v>
+        <v>31.4432</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>1.08</v>
       </c>
       <c r="I199" t="n">
-        <v>0.2619</v>
+        <v>0.2302</v>
       </c>
       <c r="J199" t="n">
-        <v>8.9046</v>
+        <v>7.8268</v>
       </c>
     </row>
     <row r="200">
@@ -10349,10 +10349,10 @@
         <v>1.06</v>
       </c>
       <c r="I200" t="n">
-        <v>0.2051</v>
+        <v>0.1764</v>
       </c>
       <c r="J200" t="n">
-        <v>6.9734</v>
+        <v>5.9976</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>0.9</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.3744</v>
+        <v>-0.3328</v>
       </c>
       <c r="J201" t="n">
-        <v>-12.7296</v>
+        <v>-11.3152</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>1.39</v>
       </c>
       <c r="I202" t="n">
-        <v>0.9445</v>
+        <v>0.9319</v>
       </c>
       <c r="J202" t="n">
-        <v>28.335</v>
+        <v>27.957</v>
       </c>
     </row>
     <row r="203">
@@ -10469,10 +10469,10 @@
         <v>1.25</v>
       </c>
       <c r="I203" t="n">
-        <v>0.6606</v>
+        <v>0.6268</v>
       </c>
       <c r="J203" t="n">
-        <v>19.818</v>
+        <v>18.804</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>1.07</v>
       </c>
       <c r="I204" t="n">
-        <v>0.238</v>
+        <v>0.2069</v>
       </c>
       <c r="J204" t="n">
-        <v>7.14</v>
+        <v>6.207</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>1.01</v>
       </c>
       <c r="I205" t="n">
-        <v>0.0362</v>
+        <v>0.026</v>
       </c>
       <c r="J205" t="n">
-        <v>1.086</v>
+        <v>0.78</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>1</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.0236</v>
+        <v>-0.0183</v>
       </c>
       <c r="J206" t="n">
-        <v>-0.708</v>
+        <v>-0.549</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>1.35</v>
       </c>
       <c r="I207" t="n">
-        <v>0.6816</v>
+        <v>0.6254</v>
       </c>
       <c r="J207" t="n">
-        <v>20.448</v>
+        <v>18.762</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>1.22</v>
       </c>
       <c r="I208" t="n">
-        <v>0.4726</v>
+        <v>0.4143</v>
       </c>
       <c r="J208" t="n">
-        <v>14.178</v>
+        <v>12.429</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>0.87</v>
       </c>
       <c r="I209" t="n">
-        <v>-0.1784</v>
+        <v>-0.1581</v>
       </c>
       <c r="J209" t="n">
-        <v>-5.352</v>
+        <v>-4.743</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>0.73</v>
       </c>
       <c r="I210" t="n">
-        <v>-0.318</v>
+        <v>-0.301</v>
       </c>
       <c r="J210" t="n">
-        <v>-9.539999999999999</v>
+        <v>-9.029999999999999</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>0.73</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.318</v>
+        <v>-0.301</v>
       </c>
       <c r="J211" t="n">
-        <v>-9.539999999999999</v>
+        <v>-9.029999999999999</v>
       </c>
     </row>
     <row r="212">
@@ -10829,10 +10829,10 @@
         <v>1.28</v>
       </c>
       <c r="I212" t="n">
-        <v>0.7274</v>
+        <v>0.6964</v>
       </c>
       <c r="J212" t="n">
-        <v>19.6398</v>
+        <v>18.8028</v>
       </c>
     </row>
     <row r="213">
@@ -10869,10 +10869,10 @@
         <v>1.14</v>
       </c>
       <c r="I213" t="n">
-        <v>0.4184</v>
+        <v>0.3804</v>
       </c>
       <c r="J213" t="n">
-        <v>11.2968</v>
+        <v>10.2708</v>
       </c>
     </row>
     <row r="214">
@@ -10909,10 +10909,10 @@
         <v>1.11</v>
       </c>
       <c r="I214" t="n">
-        <v>0.3465</v>
+        <v>0.3101</v>
       </c>
       <c r="J214" t="n">
-        <v>9.355499999999999</v>
+        <v>8.3727</v>
       </c>
     </row>
     <row r="215">
@@ -10949,10 +10949,10 @@
         <v>1.09</v>
       </c>
       <c r="I215" t="n">
-        <v>0.2952</v>
+        <v>0.2607</v>
       </c>
       <c r="J215" t="n">
-        <v>7.9704</v>
+        <v>7.0389</v>
       </c>
     </row>
     <row r="216">
@@ -10989,10 +10989,10 @@
         <v>1.02</v>
       </c>
       <c r="I216" t="n">
-        <v>0.0803</v>
+        <v>0.0633</v>
       </c>
       <c r="J216" t="n">
-        <v>2.1681</v>
+        <v>1.7091</v>
       </c>
     </row>
     <row r="217">
@@ -11029,10 +11029,10 @@
         <v>1.72</v>
       </c>
       <c r="I217" t="n">
-        <v>1.1529</v>
+        <v>1.1475</v>
       </c>
       <c r="J217" t="n">
-        <v>31.1283</v>
+        <v>30.9825</v>
       </c>
     </row>
     <row r="218">
@@ -11069,10 +11069,10 @@
         <v>1.07</v>
       </c>
       <c r="I218" t="n">
-        <v>0.191</v>
+        <v>0.1512</v>
       </c>
       <c r="J218" t="n">
-        <v>5.157</v>
+        <v>4.0824</v>
       </c>
     </row>
     <row r="219">
@@ -11109,10 +11109,10 @@
         <v>0.91</v>
       </c>
       <c r="I219" t="n">
-        <v>-0.1358</v>
+        <v>-0.1166</v>
       </c>
       <c r="J219" t="n">
-        <v>-3.6666</v>
+        <v>-3.1482</v>
       </c>
     </row>
     <row r="220">
@@ -11149,10 +11149,10 @@
         <v>0.82</v>
       </c>
       <c r="I220" t="n">
-        <v>-0.2327</v>
+        <v>-0.2124</v>
       </c>
       <c r="J220" t="n">
-        <v>-6.2829</v>
+        <v>-5.7348</v>
       </c>
     </row>
     <row r="221">
@@ -11189,10 +11189,10 @@
         <v>0.5</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.5232</v>
+        <v>-0.5283</v>
       </c>
       <c r="J221" t="n">
-        <v>-14.1264</v>
+        <v>-14.2641</v>
       </c>
     </row>
     <row r="222">
@@ -11229,10 +11229,10 @@
         <v>2.05</v>
       </c>
       <c r="I222" t="n">
-        <v>1.7211</v>
+        <v>1.7706</v>
       </c>
       <c r="J222" t="n">
-        <v>30.9798</v>
+        <v>31.8708</v>
       </c>
     </row>
     <row r="223">
@@ -11269,10 +11269,10 @@
         <v>1.82</v>
       </c>
       <c r="I223" t="n">
-        <v>1.4528</v>
+        <v>1.4819</v>
       </c>
       <c r="J223" t="n">
-        <v>26.1504</v>
+        <v>26.6742</v>
       </c>
     </row>
     <row r="224">
@@ -11309,10 +11309,10 @@
         <v>1.4</v>
       </c>
       <c r="I224" t="n">
-        <v>0.903</v>
+        <v>0.9002</v>
       </c>
       <c r="J224" t="n">
-        <v>16.254</v>
+        <v>16.2036</v>
       </c>
     </row>
     <row r="225">
@@ -11349,10 +11349,10 @@
         <v>1.36</v>
       </c>
       <c r="I225" t="n">
-        <v>0.8277</v>
+        <v>0.8189</v>
       </c>
       <c r="J225" t="n">
-        <v>14.8986</v>
+        <v>14.7402</v>
       </c>
     </row>
     <row r="226">
@@ -11389,10 +11389,10 @@
         <v>0.99</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.143</v>
+        <v>-0.1291</v>
       </c>
       <c r="J226" t="n">
-        <v>-2.574</v>
+        <v>-2.3238</v>
       </c>
     </row>
     <row r="227">
@@ -11429,10 +11429,10 @@
         <v>0.8</v>
       </c>
       <c r="I227" t="n">
-        <v>-0.1969</v>
+        <v>-0.1792</v>
       </c>
       <c r="J227" t="n">
-        <v>-3.5442</v>
+        <v>-3.2256</v>
       </c>
     </row>
     <row r="228">
@@ -11469,10 +11469,10 @@
         <v>0.66</v>
       </c>
       <c r="I228" t="n">
-        <v>-0.3393</v>
+        <v>-0.3301</v>
       </c>
       <c r="J228" t="n">
-        <v>-6.1074</v>
+        <v>-5.9418</v>
       </c>
     </row>
     <row r="229">
@@ -11509,10 +11509,10 @@
         <v>0.59</v>
       </c>
       <c r="I229" t="n">
-        <v>-0.4013</v>
+        <v>-0.3939</v>
       </c>
       <c r="J229" t="n">
-        <v>-7.2234</v>
+        <v>-7.0902</v>
       </c>
     </row>
     <row r="230">
@@ -11549,10 +11549,10 @@
         <v>0.52</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.461</v>
+        <v>-0.4562</v>
       </c>
       <c r="J230" t="n">
-        <v>-8.298</v>
+        <v>-8.211600000000001</v>
       </c>
     </row>
     <row r="231">
@@ -11589,10 +11589,10 @@
         <v>0.38</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.5845</v>
+        <v>-0.5933</v>
       </c>
       <c r="J231" t="n">
-        <v>-10.521</v>
+        <v>-10.6794</v>
       </c>
     </row>
     <row r="232">
@@ -11629,10 +11629,10 @@
         <v>1.95</v>
       </c>
       <c r="I232" t="n">
-        <v>1.5969</v>
+        <v>1.636</v>
       </c>
       <c r="J232" t="n">
-        <v>31.938</v>
+        <v>32.72</v>
       </c>
     </row>
     <row r="233">
@@ -11669,10 +11669,10 @@
         <v>1.71</v>
       </c>
       <c r="I233" t="n">
-        <v>1.3146</v>
+        <v>1.3385</v>
       </c>
       <c r="J233" t="n">
-        <v>26.292</v>
+        <v>26.77</v>
       </c>
     </row>
     <row r="234">
@@ -11709,10 +11709,10 @@
         <v>1.5</v>
       </c>
       <c r="I234" t="n">
-        <v>1.0571</v>
+        <v>1.0746</v>
       </c>
       <c r="J234" t="n">
-        <v>21.142</v>
+        <v>21.492</v>
       </c>
     </row>
     <row r="235">
@@ -11749,10 +11749,10 @@
         <v>1.46</v>
       </c>
       <c r="I235" t="n">
-        <v>0.9994</v>
+        <v>1.01</v>
       </c>
       <c r="J235" t="n">
-        <v>19.988</v>
+        <v>20.2</v>
       </c>
     </row>
     <row r="236">
@@ -11789,10 +11789,10 @@
         <v>1.26</v>
       </c>
       <c r="I236" t="n">
-        <v>0.6214</v>
+        <v>0.5986</v>
       </c>
       <c r="J236" t="n">
-        <v>12.428</v>
+        <v>11.972</v>
       </c>
     </row>
     <row r="237">
@@ -11829,10 +11829,10 @@
         <v>0.74</v>
       </c>
       <c r="I237" t="n">
-        <v>-0.2256</v>
+        <v>-0.2033</v>
       </c>
       <c r="J237" t="n">
-        <v>-4.512</v>
+        <v>-4.066</v>
       </c>
     </row>
     <row r="238">
@@ -11869,10 +11869,10 @@
         <v>0.67</v>
       </c>
       <c r="I238" t="n">
-        <v>-0.3014</v>
+        <v>-0.2884</v>
       </c>
       <c r="J238" t="n">
-        <v>-6.028</v>
+        <v>-5.768</v>
       </c>
     </row>
     <row r="239">
@@ -11909,10 +11909,10 @@
         <v>0.51</v>
       </c>
       <c r="I239" t="n">
-        <v>-0.4559</v>
+        <v>-0.4552</v>
       </c>
       <c r="J239" t="n">
-        <v>-9.118</v>
+        <v>-9.103999999999999</v>
       </c>
     </row>
     <row r="240">
@@ -11949,10 +11949,10 @@
         <v>0.3</v>
       </c>
       <c r="I240" t="n">
-        <v>-0.6405</v>
+        <v>-0.6571</v>
       </c>
       <c r="J240" t="n">
-        <v>-12.81</v>
+        <v>-13.142</v>
       </c>
     </row>
     <row r="241">
@@ -11989,10 +11989,10 @@
         <v>0.22</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.7143</v>
+        <v>-0.7455000000000001</v>
       </c>
       <c r="J241" t="n">
-        <v>-14.286</v>
+        <v>-14.91</v>
       </c>
     </row>
     <row r="242">
@@ -12029,10 +12029,10 @@
         <v>1.38</v>
       </c>
       <c r="I242" t="n">
-        <v>0.5252</v>
+        <v>0.4565</v>
       </c>
       <c r="J242" t="n">
-        <v>18.9072</v>
+        <v>16.434</v>
       </c>
     </row>
     <row r="243">
@@ -12069,10 +12069,10 @@
         <v>1.05</v>
       </c>
       <c r="I243" t="n">
-        <v>0.1059</v>
+        <v>0.0779</v>
       </c>
       <c r="J243" t="n">
-        <v>3.8124</v>
+        <v>2.8044</v>
       </c>
     </row>
     <row r="244">
@@ -12109,10 +12109,10 @@
         <v>1</v>
       </c>
       <c r="I244" t="n">
-        <v>-0.0028</v>
+        <v>-0.0017</v>
       </c>
       <c r="J244" t="n">
-        <v>-0.1008</v>
+        <v>-0.0612</v>
       </c>
     </row>
     <row r="245">
@@ -12149,10 +12149,10 @@
         <v>0.98</v>
       </c>
       <c r="I245" t="n">
-        <v>-0.0461</v>
+        <v>-0.0348</v>
       </c>
       <c r="J245" t="n">
-        <v>-1.6596</v>
+        <v>-1.2528</v>
       </c>
     </row>
     <row r="246">
@@ -12189,10 +12189,10 @@
         <v>0.83</v>
       </c>
       <c r="I246" t="n">
-        <v>-0.2265</v>
+        <v>-0.2061</v>
       </c>
       <c r="J246" t="n">
-        <v>-8.154</v>
+        <v>-7.4196</v>
       </c>
     </row>
     <row r="247">
@@ -12229,10 +12229,10 @@
         <v>1.29</v>
       </c>
       <c r="I247" t="n">
-        <v>0.4391</v>
+        <v>0.4403</v>
       </c>
       <c r="J247" t="n">
-        <v>15.8076</v>
+        <v>15.8508</v>
       </c>
     </row>
     <row r="248">
@@ -12269,10 +12269,10 @@
         <v>1.28</v>
       </c>
       <c r="I248" t="n">
-        <v>0.427</v>
+        <v>0.4268</v>
       </c>
       <c r="J248" t="n">
-        <v>15.372</v>
+        <v>15.3648</v>
       </c>
     </row>
     <row r="249">
@@ -12309,10 +12309,10 @@
         <v>1.07</v>
       </c>
       <c r="I249" t="n">
-        <v>0.1426</v>
+        <v>0.1284</v>
       </c>
       <c r="J249" t="n">
-        <v>5.1336</v>
+        <v>4.6224</v>
       </c>
     </row>
     <row r="250">
@@ -12349,10 +12349,10 @@
         <v>0.97</v>
       </c>
       <c r="I250" t="n">
-        <v>-0.0648</v>
+        <v>-0.0508</v>
       </c>
       <c r="J250" t="n">
-        <v>-2.3328</v>
+        <v>-1.8288</v>
       </c>
     </row>
     <row r="251">
@@ -12389,10 +12389,10 @@
         <v>0.82</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.2399</v>
+        <v>-0.22</v>
       </c>
       <c r="J251" t="n">
-        <v>-8.6364</v>
+        <v>-7.92</v>
       </c>
     </row>
     <row r="252">
@@ -12429,10 +12429,10 @@
         <v>1.07</v>
       </c>
       <c r="I252" t="n">
-        <v>0.206</v>
+        <v>0.1638</v>
       </c>
       <c r="J252" t="n">
-        <v>5.974</v>
+        <v>4.7502</v>
       </c>
     </row>
     <row r="253">
@@ -12469,10 +12469,10 @@
         <v>1.01</v>
       </c>
       <c r="I253" t="n">
-        <v>0.0542</v>
+        <v>0.0367</v>
       </c>
       <c r="J253" t="n">
-        <v>1.5718</v>
+        <v>1.0643</v>
       </c>
     </row>
     <row r="254">
@@ -12509,10 +12509,10 @@
         <v>0.99</v>
       </c>
       <c r="I254" t="n">
-        <v>-0.02</v>
+        <v>-0.0149</v>
       </c>
       <c r="J254" t="n">
-        <v>-0.58</v>
+        <v>-0.4321</v>
       </c>
     </row>
     <row r="255">
@@ -12549,10 +12549,10 @@
         <v>0.87</v>
       </c>
       <c r="I255" t="n">
-        <v>-0.1737</v>
+        <v>-0.1541</v>
       </c>
       <c r="J255" t="n">
-        <v>-5.0373</v>
+        <v>-4.4689</v>
       </c>
     </row>
     <row r="256">
@@ -12589,10 +12589,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I256" t="n">
-        <v>-0.35</v>
+        <v>-0.3349</v>
       </c>
       <c r="J256" t="n">
-        <v>-10.15</v>
+        <v>-9.7121</v>
       </c>
     </row>
     <row r="257">
@@ -12629,10 +12629,10 @@
         <v>1.36</v>
       </c>
       <c r="I257" t="n">
-        <v>0.8853</v>
+        <v>0.866</v>
       </c>
       <c r="J257" t="n">
-        <v>25.6737</v>
+        <v>25.114</v>
       </c>
     </row>
     <row r="258">
@@ -12669,10 +12669,10 @@
         <v>1.28</v>
       </c>
       <c r="I258" t="n">
-        <v>0.7227</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="J258" t="n">
-        <v>20.9583</v>
+        <v>20.068</v>
       </c>
     </row>
     <row r="259">
@@ -12709,10 +12709,10 @@
         <v>1.12</v>
       </c>
       <c r="I259" t="n">
-        <v>0.3688</v>
+        <v>0.3327</v>
       </c>
       <c r="J259" t="n">
-        <v>10.6952</v>
+        <v>9.648300000000001</v>
       </c>
     </row>
     <row r="260">
@@ -12749,10 +12749,10 @@
         <v>1.09</v>
       </c>
       <c r="I260" t="n">
-        <v>0.2922</v>
+        <v>0.2586</v>
       </c>
       <c r="J260" t="n">
-        <v>8.473800000000001</v>
+        <v>7.4994</v>
       </c>
     </row>
     <row r="261">
@@ -12789,10 +12789,10 @@
         <v>0.89</v>
       </c>
       <c r="I261" t="n">
-        <v>-0.3971</v>
+        <v>-0.355</v>
       </c>
       <c r="J261" t="n">
-        <v>-11.5159</v>
+        <v>-10.295</v>
       </c>
     </row>
     <row r="262">
@@ -12829,10 +12829,10 @@
         <v>0.85</v>
       </c>
       <c r="I262" t="n">
-        <v>-0.1729</v>
+        <v>-0.1573</v>
       </c>
       <c r="J262" t="n">
-        <v>-3.8038</v>
+        <v>-3.4606</v>
       </c>
     </row>
     <row r="263">
@@ -12869,10 +12869,10 @@
         <v>0.84</v>
       </c>
       <c r="I263" t="n">
-        <v>-0.1838</v>
+        <v>-0.1683</v>
       </c>
       <c r="J263" t="n">
-        <v>-4.0436</v>
+        <v>-3.7026</v>
       </c>
     </row>
     <row r="264">
@@ -12909,10 +12909,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I264" t="n">
-        <v>-0.3279</v>
+        <v>-0.3136</v>
       </c>
       <c r="J264" t="n">
-        <v>-7.2138</v>
+        <v>-6.8992</v>
       </c>
     </row>
     <row r="265">
@@ -12949,10 +12949,10 @@
         <v>0.65</v>
       </c>
       <c r="I265" t="n">
-        <v>-0.3637</v>
+        <v>-0.3506</v>
       </c>
       <c r="J265" t="n">
-        <v>-8.0014</v>
+        <v>-7.7132</v>
       </c>
     </row>
     <row r="266">
@@ -12989,10 +12989,10 @@
         <v>0.57</v>
       </c>
       <c r="I266" t="n">
-        <v>-0.435</v>
+        <v>-0.4265</v>
       </c>
       <c r="J266" t="n">
-        <v>-9.57</v>
+        <v>-9.382999999999999</v>
       </c>
     </row>
     <row r="267">
@@ -13029,10 +13029,10 @@
         <v>1.71</v>
       </c>
       <c r="I267" t="n">
-        <v>1.3359</v>
+        <v>1.3576</v>
       </c>
       <c r="J267" t="n">
-        <v>29.3898</v>
+        <v>29.8672</v>
       </c>
     </row>
     <row r="268">
@@ -13069,10 +13069,10 @@
         <v>1.56</v>
       </c>
       <c r="I268" t="n">
-        <v>1.1468</v>
+        <v>1.1626</v>
       </c>
       <c r="J268" t="n">
-        <v>25.2296</v>
+        <v>25.5772</v>
       </c>
     </row>
     <row r="269">
@@ -13109,10 +13109,10 @@
         <v>1.49</v>
       </c>
       <c r="I269" t="n">
-        <v>1.0555</v>
+        <v>1.0671</v>
       </c>
       <c r="J269" t="n">
-        <v>23.221</v>
+        <v>23.4762</v>
       </c>
     </row>
     <row r="270">
@@ -13149,10 +13149,10 @@
         <v>1.2</v>
       </c>
       <c r="I270" t="n">
-        <v>0.5145999999999999</v>
+        <v>0.4861</v>
       </c>
       <c r="J270" t="n">
-        <v>11.3212</v>
+        <v>10.6942</v>
       </c>
     </row>
     <row r="271">
@@ -13189,10 +13189,10 @@
         <v>1.14</v>
       </c>
       <c r="I271" t="n">
-        <v>0.3759</v>
+        <v>0.3438</v>
       </c>
       <c r="J271" t="n">
-        <v>8.2698</v>
+        <v>7.5636</v>
       </c>
     </row>
     <row r="272">
@@ -13229,10 +13229,10 @@
         <v>1.1</v>
       </c>
       <c r="I272" t="n">
-        <v>0.2163</v>
+        <v>0.2005</v>
       </c>
       <c r="J272" t="n">
-        <v>5.8401</v>
+        <v>5.4135</v>
       </c>
     </row>
     <row r="273">
@@ -13269,10 +13269,10 @@
         <v>0.95</v>
       </c>
       <c r="I273" t="n">
-        <v>-0.0789</v>
+        <v>-0.066</v>
       </c>
       <c r="J273" t="n">
-        <v>-2.1303</v>
+        <v>-1.782</v>
       </c>
     </row>
     <row r="274">
@@ -13309,10 +13309,10 @@
         <v>0.95</v>
       </c>
       <c r="I274" t="n">
-        <v>-0.0789</v>
+        <v>-0.066</v>
       </c>
       <c r="J274" t="n">
-        <v>-2.1303</v>
+        <v>-1.782</v>
       </c>
     </row>
     <row r="275">
@@ -13349,10 +13349,10 @@
         <v>0.77</v>
       </c>
       <c r="I275" t="n">
-        <v>-0.2718</v>
+        <v>-0.2528</v>
       </c>
       <c r="J275" t="n">
-        <v>-7.3386</v>
+        <v>-6.8256</v>
       </c>
     </row>
     <row r="276">
@@ -13389,10 +13389,10 @@
         <v>0.71</v>
       </c>
       <c r="I276" t="n">
-        <v>-0.3285</v>
+        <v>-0.312</v>
       </c>
       <c r="J276" t="n">
-        <v>-8.8695</v>
+        <v>-8.423999999999999</v>
       </c>
     </row>
     <row r="277">
@@ -13429,10 +13429,10 @@
         <v>1.23</v>
       </c>
       <c r="I277" t="n">
-        <v>0.3414</v>
+        <v>0.2829</v>
       </c>
       <c r="J277" t="n">
-        <v>9.2178</v>
+        <v>7.6383</v>
       </c>
     </row>
     <row r="278">
@@ -13469,10 +13469,10 @@
         <v>1.23</v>
       </c>
       <c r="I278" t="n">
-        <v>0.3414</v>
+        <v>0.2829</v>
       </c>
       <c r="J278" t="n">
-        <v>9.2178</v>
+        <v>7.6383</v>
       </c>
     </row>
     <row r="279">
@@ -13509,10 +13509,10 @@
         <v>1.2</v>
       </c>
       <c r="I279" t="n">
-        <v>0.3053</v>
+        <v>0.2502</v>
       </c>
       <c r="J279" t="n">
-        <v>8.2431</v>
+        <v>6.7554</v>
       </c>
     </row>
     <row r="280">
@@ -13549,10 +13549,10 @@
         <v>1</v>
       </c>
       <c r="I280" t="n">
-        <v>-0.008399999999999999</v>
+        <v>-0.0062</v>
       </c>
       <c r="J280" t="n">
-        <v>-0.2268</v>
+        <v>-0.1674</v>
       </c>
     </row>
     <row r="281">
@@ -13589,10 +13589,10 @@
         <v>0.95</v>
       </c>
       <c r="I281" t="n">
-        <v>-0.0959</v>
+        <v>-0.0789</v>
       </c>
       <c r="J281" t="n">
-        <v>-2.5893</v>
+        <v>-2.1303</v>
       </c>
     </row>
     <row r="282">
@@ -13629,10 +13629,10 @@
         <v>1.72</v>
       </c>
       <c r="I282" t="n">
-        <v>1.3296</v>
+        <v>1.3534</v>
       </c>
       <c r="J282" t="n">
-        <v>26.592</v>
+        <v>27.068</v>
       </c>
     </row>
     <row r="283">
@@ -13669,10 +13669,10 @@
         <v>1.61</v>
       </c>
       <c r="I283" t="n">
-        <v>1.1957</v>
+        <v>1.2161</v>
       </c>
       <c r="J283" t="n">
-        <v>23.914</v>
+        <v>24.322</v>
       </c>
     </row>
     <row r="284">
@@ -13709,10 +13709,10 @@
         <v>1.53</v>
       </c>
       <c r="I284" t="n">
-        <v>1.0977</v>
+        <v>1.117</v>
       </c>
       <c r="J284" t="n">
-        <v>21.954</v>
+        <v>22.34</v>
       </c>
     </row>
     <row r="285">
@@ -13749,10 +13749,10 @@
         <v>1.45</v>
       </c>
       <c r="I285" t="n">
-        <v>0.9864000000000001</v>
+        <v>0.9944</v>
       </c>
       <c r="J285" t="n">
-        <v>19.728</v>
+        <v>19.888</v>
       </c>
     </row>
     <row r="286">
@@ -13789,10 +13789,10 @@
         <v>1.44</v>
       </c>
       <c r="I286" t="n">
-        <v>0.9701</v>
+        <v>0.976</v>
       </c>
       <c r="J286" t="n">
-        <v>19.402</v>
+        <v>19.52</v>
       </c>
     </row>
     <row r="287">
@@ -13829,10 +13829,10 @@
         <v>0.84</v>
       </c>
       <c r="I287" t="n">
-        <v>-0.1543</v>
+        <v>-0.1343</v>
       </c>
       <c r="J287" t="n">
-        <v>-3.086</v>
+        <v>-2.686</v>
       </c>
     </row>
     <row r="288">
@@ -13869,10 +13869,10 @@
         <v>0.65</v>
       </c>
       <c r="I288" t="n">
-        <v>-0.35</v>
+        <v>-0.341</v>
       </c>
       <c r="J288" t="n">
-        <v>-7</v>
+        <v>-6.82</v>
       </c>
     </row>
     <row r="289">
@@ -13909,10 +13909,10 @@
         <v>0.58</v>
       </c>
       <c r="I289" t="n">
-        <v>-0.4103</v>
+        <v>-0.4028</v>
       </c>
       <c r="J289" t="n">
-        <v>-8.206</v>
+        <v>-8.055999999999999</v>
       </c>
     </row>
     <row r="290">
@@ -13949,10 +13949,10 @@
         <v>0.5</v>
       </c>
       <c r="I290" t="n">
-        <v>-0.4798</v>
+        <v>-0.4762</v>
       </c>
       <c r="J290" t="n">
-        <v>-9.596</v>
+        <v>-9.523999999999999</v>
       </c>
     </row>
     <row r="291">
@@ -13989,10 +13989,10 @@
         <v>0.42</v>
       </c>
       <c r="I291" t="n">
-        <v>-0.5503</v>
+        <v>-0.5544</v>
       </c>
       <c r="J291" t="n">
-        <v>-11.006</v>
+        <v>-11.088</v>
       </c>
     </row>
     <row r="292">
@@ -14029,10 +14029,10 @@
         <v>1.77</v>
       </c>
       <c r="I292" t="n">
-        <v>1.3945</v>
+        <v>1.4203</v>
       </c>
       <c r="J292" t="n">
-        <v>27.89</v>
+        <v>28.406</v>
       </c>
     </row>
     <row r="293">
@@ -14069,10 +14069,10 @@
         <v>1.63</v>
       </c>
       <c r="I293" t="n">
-        <v>1.2239</v>
+        <v>1.2437</v>
       </c>
       <c r="J293" t="n">
-        <v>24.478</v>
+        <v>24.874</v>
       </c>
     </row>
     <row r="294">
@@ -14109,10 +14109,10 @@
         <v>1.59</v>
       </c>
       <c r="I294" t="n">
-        <v>1.1743</v>
+        <v>1.1932</v>
       </c>
       <c r="J294" t="n">
-        <v>23.486</v>
+        <v>23.864</v>
       </c>
     </row>
     <row r="295">
@@ -14149,10 +14149,10 @@
         <v>1.43</v>
       </c>
       <c r="I295" t="n">
-        <v>0.9574</v>
+        <v>0.9603</v>
       </c>
       <c r="J295" t="n">
-        <v>19.148</v>
+        <v>19.206</v>
       </c>
     </row>
     <row r="296">
@@ -14189,10 +14189,10 @@
         <v>1.15</v>
       </c>
       <c r="I296" t="n">
-        <v>0.3863</v>
+        <v>0.3535</v>
       </c>
       <c r="J296" t="n">
-        <v>7.726</v>
+        <v>7.07</v>
       </c>
     </row>
     <row r="297">
@@ -14229,10 +14229,10 @@
         <v>0.9</v>
       </c>
       <c r="I297" t="n">
-        <v>-0.1015</v>
+        <v>-0.08359999999999999</v>
       </c>
       <c r="J297" t="n">
-        <v>-2.03</v>
+        <v>-1.672</v>
       </c>
     </row>
     <row r="298">
@@ -14269,10 +14269,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I298" t="n">
-        <v>-0.3228</v>
+        <v>-0.3107</v>
       </c>
       <c r="J298" t="n">
-        <v>-6.456</v>
+        <v>-6.214</v>
       </c>
     </row>
     <row r="299">
@@ -14309,10 +14309,10 @@
         <v>0.65</v>
       </c>
       <c r="I299" t="n">
-        <v>-0.3573</v>
+        <v>-0.3458</v>
       </c>
       <c r="J299" t="n">
-        <v>-7.146</v>
+        <v>-6.916</v>
       </c>
     </row>
     <row r="300">
@@ -14349,10 +14349,10 @@
         <v>0.65</v>
       </c>
       <c r="I300" t="n">
-        <v>-0.3573</v>
+        <v>-0.3458</v>
       </c>
       <c r="J300" t="n">
-        <v>-7.146</v>
+        <v>-6.916</v>
       </c>
     </row>
     <row r="301">
@@ -14389,10 +14389,10 @@
         <v>0.42</v>
       </c>
       <c r="I301" t="n">
-        <v>-0.5591</v>
+        <v>-0.5649</v>
       </c>
       <c r="J301" t="n">
-        <v>-11.182</v>
+        <v>-11.298</v>
       </c>
     </row>
     <row r="302">
@@ -14429,10 +14429,10 @@
         <v>1.18</v>
       </c>
       <c r="I302" t="n">
-        <v>0.5165</v>
+        <v>0.4768</v>
       </c>
       <c r="J302" t="n">
-        <v>15.495</v>
+        <v>14.304</v>
       </c>
     </row>
     <row r="303">
@@ -14469,10 +14469,10 @@
         <v>1.18</v>
       </c>
       <c r="I303" t="n">
-        <v>0.5165</v>
+        <v>0.4768</v>
       </c>
       <c r="J303" t="n">
-        <v>15.495</v>
+        <v>14.304</v>
       </c>
     </row>
     <row r="304">
@@ -14509,10 +14509,10 @@
         <v>1.11</v>
       </c>
       <c r="I304" t="n">
-        <v>0.3496</v>
+        <v>0.3115</v>
       </c>
       <c r="J304" t="n">
-        <v>10.488</v>
+        <v>9.345000000000001</v>
       </c>
     </row>
     <row r="305">
@@ -14549,10 +14549,10 @@
         <v>1.04</v>
       </c>
       <c r="I305" t="n">
-        <v>0.1556</v>
+        <v>0.1294</v>
       </c>
       <c r="J305" t="n">
-        <v>4.668</v>
+        <v>3.882</v>
       </c>
     </row>
     <row r="306">
@@ -14589,10 +14589,10 @@
         <v>0.97</v>
       </c>
       <c r="I306" t="n">
-        <v>-0.1526</v>
+        <v>-0.1214</v>
       </c>
       <c r="J306" t="n">
-        <v>-4.578</v>
+        <v>-3.642</v>
       </c>
     </row>
     <row r="307">
@@ -14629,10 +14629,10 @@
         <v>1.31</v>
       </c>
       <c r="I307" t="n">
-        <v>0.6143</v>
+        <v>0.5558</v>
       </c>
       <c r="J307" t="n">
-        <v>18.429</v>
+        <v>16.674</v>
       </c>
     </row>
     <row r="308">
@@ -14669,10 +14669,10 @@
         <v>1.05</v>
       </c>
       <c r="I308" t="n">
-        <v>0.1485</v>
+        <v>0.1142</v>
       </c>
       <c r="J308" t="n">
-        <v>4.455</v>
+        <v>3.426</v>
       </c>
     </row>
     <row r="309">
@@ -14709,10 +14709,10 @@
         <v>0.93</v>
       </c>
       <c r="I309" t="n">
-        <v>-0.1112</v>
+        <v>-0.0935</v>
       </c>
       <c r="J309" t="n">
-        <v>-3.336</v>
+        <v>-2.805</v>
       </c>
     </row>
     <row r="310">
@@ -14749,10 +14749,10 @@
         <v>0.87</v>
       </c>
       <c r="I310" t="n">
-        <v>-0.1798</v>
+        <v>-0.1594</v>
       </c>
       <c r="J310" t="n">
-        <v>-5.394</v>
+        <v>-4.782</v>
       </c>
     </row>
     <row r="311">
@@ -14789,10 +14789,10 @@
         <v>0.82</v>
       </c>
       <c r="I311" t="n">
-        <v>-0.232</v>
+        <v>-0.2117</v>
       </c>
       <c r="J311" t="n">
-        <v>-6.96</v>
+        <v>-6.351</v>
       </c>
     </row>
     <row r="312">
@@ -14829,10 +14829,10 @@
         <v>1.48</v>
       </c>
       <c r="I312" t="n">
-        <v>1.0541</v>
+        <v>1.0622</v>
       </c>
       <c r="J312" t="n">
-        <v>21.082</v>
+        <v>21.244</v>
       </c>
     </row>
     <row r="313">
@@ -14869,10 +14869,10 @@
         <v>1.41</v>
       </c>
       <c r="I313" t="n">
-        <v>0.9429999999999999</v>
+        <v>0.9351</v>
       </c>
       <c r="J313" t="n">
-        <v>18.86</v>
+        <v>18.702</v>
       </c>
     </row>
     <row r="314">
@@ -14909,10 +14909,10 @@
         <v>1.4</v>
       </c>
       <c r="I314" t="n">
-        <v>0.9251</v>
+        <v>0.9151</v>
       </c>
       <c r="J314" t="n">
-        <v>18.502</v>
+        <v>18.302</v>
       </c>
     </row>
     <row r="315">
@@ -14949,10 +14949,10 @@
         <v>1.19</v>
       </c>
       <c r="I315" t="n">
-        <v>0.5067</v>
+        <v>0.4767</v>
       </c>
       <c r="J315" t="n">
-        <v>10.134</v>
+        <v>9.534000000000001</v>
       </c>
     </row>
     <row r="316">
@@ -14989,10 +14989,10 @@
         <v>1.14</v>
       </c>
       <c r="I316" t="n">
-        <v>0.3906</v>
+        <v>0.3587</v>
       </c>
       <c r="J316" t="n">
-        <v>7.812</v>
+        <v>7.174</v>
       </c>
     </row>
     <row r="317">
@@ -15029,10 +15029,10 @@
         <v>1.16</v>
       </c>
       <c r="I317" t="n">
-        <v>0.4303</v>
+        <v>0.3829</v>
       </c>
       <c r="J317" t="n">
-        <v>8.606</v>
+        <v>7.658</v>
       </c>
     </row>
     <row r="318">
@@ -15069,10 +15069,10 @@
         <v>0.8</v>
       </c>
       <c r="I318" t="n">
-        <v>-0.2339</v>
+        <v>-0.2167</v>
       </c>
       <c r="J318" t="n">
-        <v>-4.678</v>
+        <v>-4.334</v>
       </c>
     </row>
     <row r="319">
@@ -15109,10 +15109,10 @@
         <v>0.72</v>
       </c>
       <c r="I319" t="n">
-        <v>-0.3082</v>
+        <v>-0.2916</v>
       </c>
       <c r="J319" t="n">
-        <v>-6.164</v>
+        <v>-5.832</v>
       </c>
     </row>
     <row r="320">
@@ -15149,10 +15149,10 @@
         <v>0.65</v>
       </c>
       <c r="I320" t="n">
-        <v>-0.3722</v>
+        <v>-0.3586</v>
       </c>
       <c r="J320" t="n">
-        <v>-7.444</v>
+        <v>-7.172</v>
       </c>
     </row>
     <row r="321">
@@ -15189,10 +15189,10 @@
         <v>0.63</v>
       </c>
       <c r="I321" t="n">
-        <v>-0.3902</v>
+        <v>-0.3779</v>
       </c>
       <c r="J321" t="n">
-        <v>-7.804</v>
+        <v>-7.558</v>
       </c>
     </row>
     <row r="322">
@@ -15229,10 +15229,10 @@
         <v>1.21</v>
       </c>
       <c r="I322" t="n">
-        <v>0.4833</v>
+        <v>0.4281</v>
       </c>
       <c r="J322" t="n">
-        <v>12.0825</v>
+        <v>10.7025</v>
       </c>
     </row>
     <row r="323">
@@ -15269,10 +15269,10 @@
         <v>1.14</v>
       </c>
       <c r="I323" t="n">
-        <v>0.3565</v>
+        <v>0.304</v>
       </c>
       <c r="J323" t="n">
-        <v>8.9125</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="324">
@@ -15309,10 +15309,10 @@
         <v>0.85</v>
       </c>
       <c r="I324" t="n">
-        <v>-0.1915</v>
+        <v>-0.1722</v>
       </c>
       <c r="J324" t="n">
-        <v>-4.7875</v>
+        <v>-4.305</v>
       </c>
     </row>
     <row r="325">
@@ -15349,10 +15349,10 @@
         <v>0.84</v>
       </c>
       <c r="I325" t="n">
-        <v>-0.2017</v>
+        <v>-0.1823</v>
       </c>
       <c r="J325" t="n">
-        <v>-5.0425</v>
+        <v>-4.5575</v>
       </c>
     </row>
     <row r="326">
@@ -15389,10 +15389,10 @@
         <v>0.4</v>
       </c>
       <c r="I326" t="n">
-        <v>-0.5983000000000001</v>
+        <v>-0.6137</v>
       </c>
       <c r="J326" t="n">
-        <v>-14.9575</v>
+        <v>-15.3425</v>
       </c>
     </row>
     <row r="327">
@@ -15429,10 +15429,10 @@
         <v>1.59</v>
       </c>
       <c r="I327" t="n">
-        <v>1.2118</v>
+        <v>1.227</v>
       </c>
       <c r="J327" t="n">
-        <v>30.295</v>
+        <v>30.675</v>
       </c>
     </row>
     <row r="328">
@@ -15469,10 +15469,10 @@
         <v>1.46</v>
       </c>
       <c r="I328" t="n">
-        <v>1.035</v>
+        <v>1.039</v>
       </c>
       <c r="J328" t="n">
-        <v>25.875</v>
+        <v>25.975</v>
       </c>
     </row>
     <row r="329">
@@ -15509,10 +15509,10 @@
         <v>1.27</v>
       </c>
       <c r="I329" t="n">
-        <v>0.6832</v>
+        <v>0.6561</v>
       </c>
       <c r="J329" t="n">
-        <v>17.08</v>
+        <v>16.4025</v>
       </c>
     </row>
     <row r="330">
@@ -15549,10 +15549,10 @@
         <v>1.03</v>
       </c>
       <c r="I330" t="n">
-        <v>0.09320000000000001</v>
+        <v>0.0727</v>
       </c>
       <c r="J330" t="n">
-        <v>2.33</v>
+        <v>1.8175</v>
       </c>
     </row>
     <row r="331">
@@ -15589,10 +15589,10 @@
         <v>0.97</v>
       </c>
       <c r="I331" t="n">
-        <v>-0.1825</v>
+        <v>-0.152</v>
       </c>
       <c r="J331" t="n">
-        <v>-4.5625</v>
+        <v>-3.8</v>
       </c>
     </row>
     <row r="332">
@@ -15629,10 +15629,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I332" t="n">
-        <v>-0.0623</v>
+        <v>-0.0476</v>
       </c>
       <c r="J332" t="n">
-        <v>-1.3083</v>
+        <v>-0.9996</v>
       </c>
     </row>
     <row r="333">
@@ -15669,10 +15669,10 @@
         <v>0.86</v>
       </c>
       <c r="I333" t="n">
-        <v>-0.1603</v>
+        <v>-0.1446</v>
       </c>
       <c r="J333" t="n">
-        <v>-3.3663</v>
+        <v>-3.0366</v>
       </c>
     </row>
     <row r="334">
@@ -15709,10 +15709,10 @@
         <v>0.71</v>
       </c>
       <c r="I334" t="n">
-        <v>-0.3096</v>
+        <v>-0.2954</v>
       </c>
       <c r="J334" t="n">
-        <v>-6.5016</v>
+        <v>-6.2034</v>
       </c>
     </row>
     <row r="335">
@@ -15749,10 +15749,10 @@
         <v>0.66</v>
       </c>
       <c r="I335" t="n">
-        <v>-0.3539</v>
+        <v>-0.3405</v>
       </c>
       <c r="J335" t="n">
-        <v>-7.4319</v>
+        <v>-7.1505</v>
       </c>
     </row>
     <row r="336">
@@ -15789,10 +15789,10 @@
         <v>0.39</v>
       </c>
       <c r="I336" t="n">
-        <v>-0.591</v>
+        <v>-0.6024</v>
       </c>
       <c r="J336" t="n">
-        <v>-12.411</v>
+        <v>-12.6504</v>
       </c>
     </row>
     <row r="337">
@@ -15829,10 +15829,10 @@
         <v>1.52</v>
       </c>
       <c r="I337" t="n">
-        <v>1.0989</v>
+        <v>1.1129</v>
       </c>
       <c r="J337" t="n">
-        <v>23.0769</v>
+        <v>23.3709</v>
       </c>
     </row>
     <row r="338">
@@ -15869,10 +15869,10 @@
         <v>1.5</v>
       </c>
       <c r="I338" t="n">
-        <v>1.0725</v>
+        <v>1.0847</v>
       </c>
       <c r="J338" t="n">
-        <v>22.5225</v>
+        <v>22.7787</v>
       </c>
     </row>
     <row r="339">
@@ -15909,10 +15909,10 @@
         <v>1.37</v>
       </c>
       <c r="I339" t="n">
-        <v>0.8631</v>
+        <v>0.8518</v>
       </c>
       <c r="J339" t="n">
-        <v>18.1251</v>
+        <v>17.8878</v>
       </c>
     </row>
     <row r="340">
@@ -15949,10 +15949,10 @@
         <v>1.33</v>
       </c>
       <c r="I340" t="n">
-        <v>0.7875</v>
+        <v>0.7715</v>
       </c>
       <c r="J340" t="n">
-        <v>16.5375</v>
+        <v>16.2015</v>
       </c>
     </row>
     <row r="341">
@@ -15989,10 +15989,10 @@
         <v>1.23</v>
       </c>
       <c r="I341" t="n">
-        <v>0.5844</v>
+        <v>0.5582</v>
       </c>
       <c r="J341" t="n">
-        <v>12.2724</v>
+        <v>11.7222</v>
       </c>
     </row>
     <row r="342">
@@ -16029,10 +16029,10 @@
         <v>1.09</v>
       </c>
       <c r="I342" t="n">
-        <v>0.242</v>
+        <v>0.1961</v>
       </c>
       <c r="J342" t="n">
-        <v>7.018</v>
+        <v>5.6869</v>
       </c>
     </row>
     <row r="343">
@@ -16069,10 +16069,10 @@
         <v>1.07</v>
       </c>
       <c r="I343" t="n">
-        <v>0.2003</v>
+        <v>0.1588</v>
       </c>
       <c r="J343" t="n">
-        <v>5.8087</v>
+        <v>4.6052</v>
       </c>
     </row>
     <row r="344">
@@ -16109,10 +16109,10 @@
         <v>1.01</v>
       </c>
       <c r="I344" t="n">
-        <v>0.0496</v>
+        <v>0.0332</v>
       </c>
       <c r="J344" t="n">
-        <v>1.4384</v>
+        <v>0.9628</v>
       </c>
     </row>
     <row r="345">
@@ -16149,10 +16149,10 @@
         <v>0.88</v>
       </c>
       <c r="I345" t="n">
-        <v>-0.1651</v>
+        <v>-0.1454</v>
       </c>
       <c r="J345" t="n">
-        <v>-4.7879</v>
+        <v>-4.2166</v>
       </c>
     </row>
     <row r="346">
@@ -16189,10 +16189,10 @@
         <v>0.71</v>
       </c>
       <c r="I346" t="n">
-        <v>-0.334</v>
+        <v>-0.318</v>
       </c>
       <c r="J346" t="n">
-        <v>-9.686</v>
+        <v>-9.222</v>
       </c>
     </row>
     <row r="347">
@@ -16229,10 +16229,10 @@
         <v>1.15</v>
       </c>
       <c r="I347" t="n">
-        <v>0.4584</v>
+        <v>0.4164</v>
       </c>
       <c r="J347" t="n">
-        <v>13.2936</v>
+        <v>12.0756</v>
       </c>
     </row>
     <row r="348">
@@ -16269,10 +16269,10 @@
         <v>1.12</v>
       </c>
       <c r="I348" t="n">
-        <v>0.3845</v>
+        <v>0.3428</v>
       </c>
       <c r="J348" t="n">
-        <v>11.1505</v>
+        <v>9.9412</v>
       </c>
     </row>
     <row r="349">
@@ -16309,10 +16309,10 @@
         <v>1.04</v>
       </c>
       <c r="I349" t="n">
-        <v>0.1632</v>
+        <v>0.1341</v>
       </c>
       <c r="J349" t="n">
-        <v>4.7328</v>
+        <v>3.8889</v>
       </c>
     </row>
     <row r="350">
@@ -16349,10 +16349,10 @@
         <v>1.01</v>
       </c>
       <c r="I350" t="n">
-        <v>0.054</v>
+        <v>0.0404</v>
       </c>
       <c r="J350" t="n">
-        <v>1.566</v>
+        <v>1.1716</v>
       </c>
     </row>
     <row r="351">
@@ -16389,10 +16389,10 @@
         <v>0.88</v>
       </c>
       <c r="I351" t="n">
-        <v>-0.4021</v>
+        <v>-0.359</v>
       </c>
       <c r="J351" t="n">
-        <v>-11.6609</v>
+        <v>-10.411</v>
       </c>
     </row>
     <row r="352">
@@ -16429,10 +16429,10 @@
         <v>0.98</v>
       </c>
       <c r="I352" t="n">
-        <v>-0.0333</v>
+        <v>-0.0258</v>
       </c>
       <c r="J352" t="n">
-        <v>-0.9324</v>
+        <v>-0.7224</v>
       </c>
     </row>
     <row r="353">
@@ -16469,10 +16469,10 @@
         <v>0.93</v>
       </c>
       <c r="I353" t="n">
-        <v>-0.1033</v>
+        <v>-0.0886</v>
       </c>
       <c r="J353" t="n">
-        <v>-2.8924</v>
+        <v>-2.4808</v>
       </c>
     </row>
     <row r="354">
@@ -16509,10 +16509,10 @@
         <v>0.89</v>
       </c>
       <c r="I354" t="n">
-        <v>-0.1494</v>
+        <v>-0.1318</v>
       </c>
       <c r="J354" t="n">
-        <v>-4.1832</v>
+        <v>-3.6904</v>
       </c>
     </row>
     <row r="355">
@@ -16549,10 +16549,10 @@
         <v>0.88</v>
       </c>
       <c r="I355" t="n">
-        <v>-0.1599</v>
+        <v>-0.1419</v>
       </c>
       <c r="J355" t="n">
-        <v>-4.4772</v>
+        <v>-3.9732</v>
       </c>
     </row>
     <row r="356">
@@ -16589,10 +16589,10 @@
         <v>0.74</v>
       </c>
       <c r="I356" t="n">
-        <v>-0.2992</v>
+        <v>-0.2812</v>
       </c>
       <c r="J356" t="n">
-        <v>-8.377599999999999</v>
+        <v>-7.8736</v>
       </c>
     </row>
     <row r="357">
@@ -16629,10 +16629,10 @@
         <v>1.56</v>
       </c>
       <c r="I357" t="n">
-        <v>1.1943</v>
+        <v>1.2096</v>
       </c>
       <c r="J357" t="n">
-        <v>33.4404</v>
+        <v>33.8688</v>
       </c>
     </row>
     <row r="358">
@@ -16669,10 +16669,10 @@
         <v>1.38</v>
       </c>
       <c r="I358" t="n">
-        <v>0.9197</v>
+        <v>0.904</v>
       </c>
       <c r="J358" t="n">
-        <v>25.7516</v>
+        <v>25.312</v>
       </c>
     </row>
     <row r="359">
@@ -16709,10 +16709,10 @@
         <v>1.09</v>
       </c>
       <c r="I359" t="n">
-        <v>0.2893</v>
+        <v>0.2564</v>
       </c>
       <c r="J359" t="n">
-        <v>8.1004</v>
+        <v>7.1792</v>
       </c>
     </row>
     <row r="360">
@@ -16749,10 +16749,10 @@
         <v>0.97</v>
       </c>
       <c r="I360" t="n">
-        <v>-0.1654</v>
+        <v>-0.1339</v>
       </c>
       <c r="J360" t="n">
-        <v>-4.6312</v>
+        <v>-3.7492</v>
       </c>
     </row>
     <row r="361">
@@ -16789,10 +16789,10 @@
         <v>0.83</v>
       </c>
       <c r="I361" t="n">
-        <v>-0.5494</v>
+        <v>-0.5109</v>
       </c>
       <c r="J361" t="n">
-        <v>-15.3832</v>
+        <v>-14.3052</v>
       </c>
     </row>
     <row r="362">
@@ -16829,10 +16829,10 @@
         <v>1.38</v>
       </c>
       <c r="I362" t="n">
-        <v>0.5033</v>
+        <v>0.435</v>
       </c>
       <c r="J362" t="n">
-        <v>14.0924</v>
+        <v>12.18</v>
       </c>
     </row>
     <row r="363">
@@ -16869,10 +16869,10 @@
         <v>1.25</v>
       </c>
       <c r="I363" t="n">
-        <v>0.359</v>
+        <v>0.3</v>
       </c>
       <c r="J363" t="n">
-        <v>10.052</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="364">
@@ -16909,10 +16909,10 @@
         <v>1.13</v>
       </c>
       <c r="I364" t="n">
-        <v>0.2136</v>
+        <v>0.1709</v>
       </c>
       <c r="J364" t="n">
-        <v>5.9808</v>
+        <v>4.7852</v>
       </c>
     </row>
     <row r="365">
@@ -16949,10 +16949,10 @@
         <v>1.07</v>
       </c>
       <c r="I365" t="n">
-        <v>0.1277</v>
+        <v>0.0977</v>
       </c>
       <c r="J365" t="n">
-        <v>3.5756</v>
+        <v>2.7356</v>
       </c>
     </row>
     <row r="366">
@@ -16989,10 +16989,10 @@
         <v>1.05</v>
       </c>
       <c r="I366" t="n">
-        <v>0.09520000000000001</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="J366" t="n">
-        <v>2.6656</v>
+        <v>1.988</v>
       </c>
     </row>
     <row r="367">
@@ -17029,10 +17029,10 @@
         <v>1.19</v>
       </c>
       <c r="I367" t="n">
-        <v>0.3489</v>
+        <v>0.3429</v>
       </c>
       <c r="J367" t="n">
-        <v>9.7692</v>
+        <v>9.6012</v>
       </c>
     </row>
     <row r="368">
@@ -17069,10 +17069,10 @@
         <v>0.99</v>
       </c>
       <c r="I368" t="n">
-        <v>-0.0167</v>
+        <v>-0.0121</v>
       </c>
       <c r="J368" t="n">
-        <v>-0.4676</v>
+        <v>-0.3388</v>
       </c>
     </row>
     <row r="369">
@@ -17109,10 +17109,10 @@
         <v>0.9</v>
       </c>
       <c r="I369" t="n">
-        <v>-0.1392</v>
+        <v>-0.1218</v>
       </c>
       <c r="J369" t="n">
-        <v>-3.8976</v>
+        <v>-3.4104</v>
       </c>
     </row>
     <row r="370">
@@ -17149,10 +17149,10 @@
         <v>0.73</v>
       </c>
       <c r="I370" t="n">
-        <v>-0.3099</v>
+        <v>-0.2923</v>
       </c>
       <c r="J370" t="n">
-        <v>-8.677199999999999</v>
+        <v>-8.1844</v>
       </c>
     </row>
     <row r="371">
@@ -17189,10 +17189,10 @@
         <v>0.67</v>
       </c>
       <c r="I371" t="n">
-        <v>-0.3653</v>
+        <v>-0.3512</v>
       </c>
       <c r="J371" t="n">
-        <v>-10.2284</v>
+        <v>-9.833600000000001</v>
       </c>
     </row>
     <row r="372">
@@ -17229,10 +17229,10 @@
         <v>1.25</v>
       </c>
       <c r="I372" t="n">
-        <v>0.59</v>
+        <v>0.5448</v>
       </c>
       <c r="J372" t="n">
-        <v>12.98</v>
+        <v>11.9856</v>
       </c>
     </row>
     <row r="373">
@@ -17269,10 +17269,10 @@
         <v>0.82</v>
       </c>
       <c r="I373" t="n">
-        <v>-0.2152</v>
+        <v>-0.198</v>
       </c>
       <c r="J373" t="n">
-        <v>-4.7344</v>
+        <v>-4.356</v>
       </c>
     </row>
     <row r="374">
@@ -17309,10 +17309,10 @@
         <v>0.73</v>
       </c>
       <c r="I374" t="n">
-        <v>-0.2998</v>
+        <v>-0.2828</v>
       </c>
       <c r="J374" t="n">
-        <v>-6.5956</v>
+        <v>-6.2216</v>
       </c>
     </row>
     <row r="375">
@@ -17349,10 +17349,10 @@
         <v>0.64</v>
       </c>
       <c r="I375" t="n">
-        <v>-0.3821</v>
+        <v>-0.3692</v>
       </c>
       <c r="J375" t="n">
-        <v>-8.4062</v>
+        <v>-8.122400000000001</v>
       </c>
     </row>
     <row r="376">
@@ -17389,10 +17389,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I376" t="n">
-        <v>-0.4533</v>
+        <v>-0.4468</v>
       </c>
       <c r="J376" t="n">
-        <v>-9.9726</v>
+        <v>-9.829599999999999</v>
       </c>
     </row>
     <row r="377">
@@ -17429,10 +17429,10 @@
         <v>1.53</v>
       </c>
       <c r="I377" t="n">
-        <v>1.1286</v>
+        <v>1.1414</v>
       </c>
       <c r="J377" t="n">
-        <v>24.8292</v>
+        <v>25.1108</v>
       </c>
     </row>
     <row r="378">
@@ -17469,10 +17469,10 @@
         <v>1.49</v>
       </c>
       <c r="I378" t="n">
-        <v>1.0747</v>
+        <v>1.0844</v>
       </c>
       <c r="J378" t="n">
-        <v>23.6434</v>
+        <v>23.8568</v>
       </c>
     </row>
     <row r="379">
@@ -17509,10 +17509,10 @@
         <v>1.18</v>
       </c>
       <c r="I379" t="n">
-        <v>0.4906</v>
+        <v>0.4592</v>
       </c>
       <c r="J379" t="n">
-        <v>10.7932</v>
+        <v>10.1024</v>
       </c>
     </row>
     <row r="380">
@@ -17549,10 +17549,10 @@
         <v>1.11</v>
       </c>
       <c r="I380" t="n">
-        <v>0.3227</v>
+        <v>0.2908</v>
       </c>
       <c r="J380" t="n">
-        <v>7.0994</v>
+        <v>6.3976</v>
       </c>
     </row>
     <row r="381">
@@ -17589,10 +17589,10 @@
         <v>1.1</v>
       </c>
       <c r="I381" t="n">
-        <v>0.2968</v>
+        <v>0.2653</v>
       </c>
       <c r="J381" t="n">
-        <v>6.5296</v>
+        <v>5.8366</v>
       </c>
     </row>
     <row r="382">
@@ -17629,10 +17629,10 @@
         <v>1.06</v>
       </c>
       <c r="I382" t="n">
-        <v>0.184</v>
+        <v>0.1444</v>
       </c>
       <c r="J382" t="n">
-        <v>5.336</v>
+        <v>4.1876</v>
       </c>
     </row>
     <row r="383">
@@ -17669,10 +17669,10 @@
         <v>0.97</v>
       </c>
       <c r="I383" t="n">
-        <v>-0.0535</v>
+        <v>-0.043</v>
       </c>
       <c r="J383" t="n">
-        <v>-1.5515</v>
+        <v>-1.247</v>
       </c>
     </row>
     <row r="384">
@@ -17709,10 +17709,10 @@
         <v>0.96</v>
       </c>
       <c r="I384" t="n">
-        <v>-0.068</v>
+        <v>-0.0557</v>
       </c>
       <c r="J384" t="n">
-        <v>-1.972</v>
+        <v>-1.6153</v>
       </c>
     </row>
     <row r="385">
@@ -17749,10 +17749,10 @@
         <v>0.86</v>
       </c>
       <c r="I385" t="n">
-        <v>-0.1843</v>
+        <v>-0.1645</v>
       </c>
       <c r="J385" t="n">
-        <v>-5.3447</v>
+        <v>-4.7705</v>
       </c>
     </row>
     <row r="386">
@@ -17789,10 +17789,10 @@
         <v>0.78</v>
       </c>
       <c r="I386" t="n">
-        <v>-0.2651</v>
+        <v>-0.2457</v>
       </c>
       <c r="J386" t="n">
-        <v>-7.6879</v>
+        <v>-7.1253</v>
       </c>
     </row>
     <row r="387">
@@ -17829,10 +17829,10 @@
         <v>1.49</v>
       </c>
       <c r="I387" t="n">
-        <v>1.1048</v>
+        <v>1.1168</v>
       </c>
       <c r="J387" t="n">
-        <v>32.0392</v>
+        <v>32.3872</v>
       </c>
     </row>
     <row r="388">
@@ -17869,10 +17869,10 @@
         <v>1.15</v>
       </c>
       <c r="I388" t="n">
-        <v>0.4405</v>
+        <v>0.4028</v>
       </c>
       <c r="J388" t="n">
-        <v>12.7745</v>
+        <v>11.6812</v>
       </c>
     </row>
     <row r="389">
@@ -17909,10 +17909,10 @@
         <v>1.12</v>
       </c>
       <c r="I389" t="n">
-        <v>0.37</v>
+        <v>0.3334</v>
       </c>
       <c r="J389" t="n">
-        <v>10.73</v>
+        <v>9.6686</v>
       </c>
     </row>
     <row r="390">
@@ -17949,10 +17949,10 @@
         <v>1.08</v>
       </c>
       <c r="I390" t="n">
-        <v>0.2668</v>
+        <v>0.234</v>
       </c>
       <c r="J390" t="n">
-        <v>7.7372</v>
+        <v>6.786</v>
       </c>
     </row>
     <row r="391">
@@ -17989,10 +17989,10 @@
         <v>0.85</v>
       </c>
       <c r="I391" t="n">
-        <v>-0.4962</v>
+        <v>-0.4552</v>
       </c>
       <c r="J391" t="n">
-        <v>-14.3898</v>
+        <v>-13.2008</v>
       </c>
     </row>
   </sheetData>
